--- a/database/SBFG3.xlsx
+++ b/database/SBFG3.xlsx
@@ -472,16 +472,16 @@
         <v>43573</v>
       </c>
       <c r="B3" t="n">
-        <v>10.53836345672607</v>
+        <v>10.53836441040039</v>
       </c>
       <c r="C3" t="n">
-        <v>10.98438567165539</v>
+        <v>10.98438666569271</v>
       </c>
       <c r="D3" t="n">
-        <v>10.33721583989887</v>
+        <v>10.33721677537024</v>
       </c>
       <c r="E3" t="n">
-        <v>10.74825596938503</v>
+        <v>10.74825694205368</v>
       </c>
       <c r="F3" t="n">
         <v>3142100</v>
@@ -512,16 +512,16 @@
         <v>43578</v>
       </c>
       <c r="B5" t="n">
-        <v>10.43341732025146</v>
+        <v>10.43341827392578</v>
       </c>
       <c r="C5" t="n">
-        <v>10.52961784781559</v>
+        <v>10.52961881028319</v>
       </c>
       <c r="D5" t="n">
-        <v>10.36345314856142</v>
+        <v>10.36345409584061</v>
       </c>
       <c r="E5" t="n">
-        <v>10.49463576197057</v>
+        <v>10.4946367212406</v>
       </c>
       <c r="F5" t="n">
         <v>1919200</v>
@@ -532,16 +532,16 @@
         <v>43579</v>
       </c>
       <c r="B6" t="n">
-        <v>10.37219905853271</v>
+        <v>10.3721981048584</v>
       </c>
       <c r="C6" t="n">
-        <v>10.40718114779776</v>
+        <v>10.40718019090701</v>
       </c>
       <c r="D6" t="n">
-        <v>10.19728861220748</v>
+        <v>10.19728767461534</v>
       </c>
       <c r="E6" t="n">
-        <v>10.40718114779776</v>
+        <v>10.40718019090701</v>
       </c>
       <c r="F6" t="n">
         <v>1161400</v>
@@ -552,16 +552,16 @@
         <v>43580</v>
       </c>
       <c r="B7" t="n">
-        <v>10.45090866088867</v>
+        <v>10.45090770721436</v>
       </c>
       <c r="C7" t="n">
-        <v>10.46840012202677</v>
+        <v>10.46839916675631</v>
       </c>
       <c r="D7" t="n">
-        <v>10.21477977379569</v>
+        <v>10.21477884166879</v>
       </c>
       <c r="E7" t="n">
-        <v>10.24101613146407</v>
+        <v>10.24101519694303</v>
       </c>
       <c r="F7" t="n">
         <v>1101400</v>
@@ -572,16 +572,16 @@
         <v>43581</v>
       </c>
       <c r="B8" t="n">
-        <v>10.45090866088867</v>
+        <v>10.45090770721436</v>
       </c>
       <c r="C8" t="n">
-        <v>10.53836429850164</v>
+        <v>10.53836333684676</v>
       </c>
       <c r="D8" t="n">
-        <v>10.38094448441381</v>
+        <v>10.38094353712391</v>
       </c>
       <c r="E8" t="n">
-        <v>10.46840012202677</v>
+        <v>10.46839916675631</v>
       </c>
       <c r="F8" t="n">
         <v>496900</v>
@@ -592,16 +592,16 @@
         <v>43584</v>
       </c>
       <c r="B9" t="n">
-        <v>10.39843654632568</v>
+        <v>10.39843559265137</v>
       </c>
       <c r="C9" t="n">
-        <v>10.56460126654403</v>
+        <v>10.56460029763021</v>
       </c>
       <c r="D9" t="n">
-        <v>10.34596299391847</v>
+        <v>10.34596204505667</v>
       </c>
       <c r="E9" t="n">
-        <v>10.45090926469408</v>
+        <v>10.45090830620732</v>
       </c>
       <c r="F9" t="n">
         <v>423300</v>
@@ -632,16 +632,16 @@
         <v>43587</v>
       </c>
       <c r="B11" t="n">
-        <v>10.17979717254639</v>
+        <v>10.17979621887207</v>
       </c>
       <c r="C11" t="n">
-        <v>10.31972551844442</v>
+        <v>10.31972455166119</v>
       </c>
       <c r="D11" t="n">
-        <v>10.11857789568695</v>
+        <v>10.11857694774784</v>
       </c>
       <c r="E11" t="n">
-        <v>10.15355998216146</v>
+        <v>10.15355903094512</v>
       </c>
       <c r="F11" t="n">
         <v>464300</v>
@@ -652,16 +652,16 @@
         <v>43588</v>
       </c>
       <c r="B12" t="n">
-        <v>10.07485103607178</v>
+        <v>10.07485008239746</v>
       </c>
       <c r="C12" t="n">
-        <v>10.31972564438167</v>
+        <v>10.31972466752779</v>
       </c>
       <c r="D12" t="n">
-        <v>10.0573595756017</v>
+        <v>10.05735862358311</v>
       </c>
       <c r="E12" t="n">
-        <v>10.23227001010876</v>
+        <v>10.23226904153334</v>
       </c>
       <c r="F12" t="n">
         <v>778700</v>
@@ -672,16 +672,16 @@
         <v>43591</v>
       </c>
       <c r="B13" t="n">
-        <v>10.20603370666504</v>
+        <v>10.20603275299072</v>
       </c>
       <c r="C13" t="n">
-        <v>10.27599788083272</v>
+        <v>10.27599692062079</v>
       </c>
       <c r="D13" t="n">
-        <v>9.926177009994333</v>
+        <v>9.926176082470445</v>
       </c>
       <c r="E13" t="n">
-        <v>10.04861389776839</v>
+        <v>10.04861295880373</v>
       </c>
       <c r="F13" t="n">
         <v>180200</v>
@@ -732,16 +732,16 @@
         <v>43594</v>
       </c>
       <c r="B16" t="n">
-        <v>10.43341732025146</v>
+        <v>10.43341827392578</v>
       </c>
       <c r="C16" t="n">
-        <v>10.44216221618368</v>
+        <v>10.44216317065733</v>
       </c>
       <c r="D16" t="n">
-        <v>9.97864937022749</v>
+        <v>9.978650282333401</v>
       </c>
       <c r="E16" t="n">
-        <v>10.31972533274547</v>
+        <v>10.31972627602769</v>
       </c>
       <c r="F16" t="n">
         <v>237700</v>
@@ -752,16 +752,16 @@
         <v>43595</v>
       </c>
       <c r="B17" t="n">
-        <v>10.58209228515625</v>
+        <v>10.58209133148193</v>
       </c>
       <c r="C17" t="n">
-        <v>10.70452917890991</v>
+        <v>10.7045282142014</v>
       </c>
       <c r="D17" t="n">
-        <v>10.40718100715595</v>
+        <v>10.40718006924491</v>
       </c>
       <c r="E17" t="n">
-        <v>10.40718100715595</v>
+        <v>10.40718006924491</v>
       </c>
       <c r="F17" t="n">
         <v>669000</v>
@@ -772,16 +772,16 @@
         <v>43598</v>
       </c>
       <c r="B18" t="n">
-        <v>10.45090866088867</v>
+        <v>10.45090770721436</v>
       </c>
       <c r="C18" t="n">
-        <v>10.49463647969516</v>
+        <v>10.49463552203055</v>
       </c>
       <c r="D18" t="n">
-        <v>10.37219875384475</v>
+        <v>10.37219780735293</v>
       </c>
       <c r="E18" t="n">
-        <v>10.4858907491261</v>
+        <v>10.48588979225958</v>
       </c>
       <c r="F18" t="n">
         <v>433700</v>
@@ -832,16 +832,16 @@
         <v>43601</v>
       </c>
       <c r="B21" t="n">
-        <v>10.10983467102051</v>
+        <v>10.10983371734619</v>
       </c>
       <c r="C21" t="n">
-        <v>10.40718203819384</v>
+        <v>10.40718105647035</v>
       </c>
       <c r="D21" t="n">
-        <v>10.07485257876253</v>
+        <v>10.07485162838813</v>
       </c>
       <c r="E21" t="n">
-        <v>10.20603521622022</v>
+        <v>10.20603425347117</v>
       </c>
       <c r="F21" t="n">
         <v>1038600</v>
@@ -872,16 +872,16 @@
         <v>43605</v>
       </c>
       <c r="B23" t="n">
-        <v>9.707537651062012</v>
+        <v>9.707538604736328</v>
       </c>
       <c r="C23" t="n">
-        <v>9.873702337266524</v>
+        <v>9.873703307264957</v>
       </c>
       <c r="D23" t="n">
-        <v>9.6025905677302</v>
+        <v>9.602591511094451</v>
       </c>
       <c r="E23" t="n">
-        <v>9.873702337266524</v>
+        <v>9.873703307264957</v>
       </c>
       <c r="F23" t="n">
         <v>117200</v>
@@ -892,16 +892,16 @@
         <v>43606</v>
       </c>
       <c r="B24" t="n">
-        <v>9.882449150085449</v>
+        <v>9.882448196411133</v>
       </c>
       <c r="C24" t="n">
-        <v>9.961159054194923</v>
+        <v>9.961158092924956</v>
       </c>
       <c r="D24" t="n">
-        <v>9.725029341866504</v>
+        <v>9.725028403383487</v>
       </c>
       <c r="E24" t="n">
-        <v>9.794993515732981</v>
+        <v>9.794992570498295</v>
       </c>
       <c r="F24" t="n">
         <v>253500</v>
@@ -912,16 +912,16 @@
         <v>43607</v>
       </c>
       <c r="B25" t="n">
-        <v>9.926177978515625</v>
+        <v>9.926177024841309</v>
       </c>
       <c r="C25" t="n">
-        <v>10.13607052149838</v>
+        <v>10.13606954765828</v>
       </c>
       <c r="D25" t="n">
-        <v>9.856213797521374</v>
+        <v>9.856212850568985</v>
       </c>
       <c r="E25" t="n">
-        <v>10.13607052149838</v>
+        <v>10.13606954765828</v>
       </c>
       <c r="F25" t="n">
         <v>223300</v>
@@ -932,16 +932,16 @@
         <v>43608</v>
       </c>
       <c r="B26" t="n">
-        <v>9.882449150085449</v>
+        <v>9.882448196411133</v>
       </c>
       <c r="C26" t="n">
-        <v>10.67829225334568</v>
+        <v>10.67829122287106</v>
       </c>
       <c r="D26" t="n">
-        <v>9.873703419842455</v>
+        <v>9.873702467012118</v>
       </c>
       <c r="E26" t="n">
-        <v>10.35470774070354</v>
+        <v>10.35470674145541</v>
       </c>
       <c r="F26" t="n">
         <v>1121200</v>
@@ -952,16 +952,16 @@
         <v>43609</v>
       </c>
       <c r="B27" t="n">
-        <v>9.882449150085449</v>
+        <v>9.882448196411133</v>
       </c>
       <c r="C27" t="n">
-        <v>10.01363176757541</v>
+        <v>10.01363080124173</v>
       </c>
       <c r="D27" t="n">
-        <v>9.794993515732981</v>
+        <v>9.794992570498295</v>
       </c>
       <c r="E27" t="n">
-        <v>9.882449150085449</v>
+        <v>9.882448196411133</v>
       </c>
       <c r="F27" t="n">
         <v>207200</v>
@@ -992,16 +992,16 @@
         <v>43613</v>
       </c>
       <c r="B29" t="n">
-        <v>10.07485103607178</v>
+        <v>10.07485008239746</v>
       </c>
       <c r="C29" t="n">
-        <v>10.13606947963956</v>
+        <v>10.13606852017038</v>
       </c>
       <c r="D29" t="n">
-        <v>9.882449141094636</v>
+        <v>9.882448205632873</v>
       </c>
       <c r="E29" t="n">
-        <v>9.969903941328798</v>
+        <v>9.969902997588658</v>
       </c>
       <c r="F29" t="n">
         <v>291800</v>
@@ -1072,16 +1072,16 @@
         <v>43619</v>
       </c>
       <c r="B33" t="n">
-        <v>10.36345386505127</v>
+        <v>10.36345291137695</v>
       </c>
       <c r="C33" t="n">
-        <v>10.58209212520814</v>
+        <v>10.58209115141412</v>
       </c>
       <c r="D33" t="n">
-        <v>10.28474395794859</v>
+        <v>10.28474301151738</v>
       </c>
       <c r="E33" t="n">
-        <v>10.46840012984192</v>
+        <v>10.46839916651015</v>
       </c>
       <c r="F33" t="n">
         <v>341500</v>
@@ -1092,16 +1092,16 @@
         <v>43620</v>
       </c>
       <c r="B34" t="n">
-        <v>10.13606834411621</v>
+        <v>10.13606929779053</v>
       </c>
       <c r="C34" t="n">
-        <v>10.35470657126613</v>
+        <v>10.3547075455115</v>
       </c>
       <c r="D34" t="n">
-        <v>10.01363063665835</v>
+        <v>10.01363157881284</v>
       </c>
       <c r="E34" t="n">
-        <v>10.34596084201085</v>
+        <v>10.34596181543337</v>
       </c>
       <c r="F34" t="n">
         <v>433200</v>
@@ -1152,16 +1152,16 @@
         <v>43623</v>
       </c>
       <c r="B37" t="n">
-        <v>10.05735778808594</v>
+        <v>10.05735874176025</v>
       </c>
       <c r="C37" t="n">
-        <v>10.26725027218977</v>
+        <v>10.26725124576684</v>
       </c>
       <c r="D37" t="n">
-        <v>9.908683736669406</v>
+        <v>9.908684676245921</v>
       </c>
       <c r="E37" t="n">
-        <v>10.15355830145721</v>
+        <v>10.1535592642536</v>
       </c>
       <c r="F37" t="n">
         <v>329300</v>
@@ -1192,16 +1192,16 @@
         <v>43627</v>
       </c>
       <c r="B39" t="n">
-        <v>10.02237796783447</v>
+        <v>10.02237701416016</v>
       </c>
       <c r="C39" t="n">
-        <v>10.22352476862402</v>
+        <v>10.22352379580968</v>
       </c>
       <c r="D39" t="n">
-        <v>10.01363223718133</v>
+        <v>10.01363128433921</v>
       </c>
       <c r="E39" t="n">
-        <v>10.09234214498204</v>
+        <v>10.09234118465031</v>
       </c>
       <c r="F39" t="n">
         <v>345200</v>
@@ -1212,16 +1212,16 @@
         <v>43628</v>
       </c>
       <c r="B40" t="n">
-        <v>10.10108757019043</v>
+        <v>10.10108661651611</v>
       </c>
       <c r="C40" t="n">
-        <v>10.22352445947693</v>
+        <v>10.22352349424298</v>
       </c>
       <c r="D40" t="n">
-        <v>10.06610548267446</v>
+        <v>10.06610453230291</v>
       </c>
       <c r="E40" t="n">
-        <v>10.20603383273833</v>
+        <v>10.20603286915571</v>
       </c>
       <c r="F40" t="n">
         <v>109500</v>
@@ -1272,16 +1272,16 @@
         <v>43633</v>
       </c>
       <c r="B43" t="n">
-        <v>10.10983467102051</v>
+        <v>10.10983371734619</v>
       </c>
       <c r="C43" t="n">
-        <v>10.26725366916195</v>
+        <v>10.26725270063809</v>
       </c>
       <c r="D43" t="n">
-        <v>10.06610684718832</v>
+        <v>10.06610589763891</v>
       </c>
       <c r="E43" t="n">
-        <v>10.13607103170427</v>
+        <v>10.13607007555504</v>
       </c>
       <c r="F43" t="n">
         <v>150100</v>
@@ -1292,16 +1292,16 @@
         <v>43634</v>
       </c>
       <c r="B44" t="n">
-        <v>10.4071798324585</v>
+        <v>10.40718078613281</v>
       </c>
       <c r="C44" t="n">
-        <v>10.44216191730224</v>
+        <v>10.44216287418218</v>
       </c>
       <c r="D44" t="n">
-        <v>10.13606888342916</v>
+        <v>10.1360698122599</v>
       </c>
       <c r="E44" t="n">
-        <v>10.22352367851917</v>
+        <v>10.22352461536394</v>
       </c>
       <c r="F44" t="n">
         <v>787900</v>
@@ -1332,16 +1332,16 @@
         <v>43637</v>
       </c>
       <c r="B46" t="n">
-        <v>11.19427871704102</v>
+        <v>11.1942777633667</v>
       </c>
       <c r="C46" t="n">
-        <v>11.28173351779147</v>
+        <v>11.28173255666661</v>
       </c>
       <c r="D46" t="n">
-        <v>10.75700221117253</v>
+        <v>10.75700129475111</v>
       </c>
       <c r="E46" t="n">
-        <v>10.75700221117253</v>
+        <v>10.75700129475111</v>
       </c>
       <c r="F46" t="n">
         <v>990700</v>
@@ -1352,16 +1352,16 @@
         <v>43640</v>
       </c>
       <c r="B47" t="n">
-        <v>11.1592960357666</v>
+        <v>11.15929698944092</v>
       </c>
       <c r="C47" t="n">
-        <v>11.29047864692695</v>
+        <v>11.29047961181215</v>
       </c>
       <c r="D47" t="n">
-        <v>10.97563987971889</v>
+        <v>10.97564081769794</v>
       </c>
       <c r="E47" t="n">
-        <v>11.19427812101194</v>
+        <v>11.19427907767583</v>
       </c>
       <c r="F47" t="n">
         <v>367700</v>
@@ -1392,16 +1392,16 @@
         <v>43642</v>
       </c>
       <c r="B49" t="n">
-        <v>12.02510547637939</v>
+        <v>12.02510452270508</v>
       </c>
       <c r="C49" t="n">
-        <v>12.2000159346826</v>
+        <v>12.20001496713667</v>
       </c>
       <c r="D49" t="n">
-        <v>11.24675289438158</v>
+        <v>11.24675200243602</v>
       </c>
       <c r="E49" t="n">
-        <v>11.28173498604222</v>
+        <v>11.28173409132234</v>
       </c>
       <c r="F49" t="n">
         <v>1344300</v>
@@ -1432,16 +1432,16 @@
         <v>43644</v>
       </c>
       <c r="B51" t="n">
-        <v>12.50610828399658</v>
+        <v>12.50610733032227</v>
       </c>
       <c r="C51" t="n">
-        <v>12.68976445054762</v>
+        <v>12.68976348286829</v>
       </c>
       <c r="D51" t="n">
-        <v>12.24374221263242</v>
+        <v>12.24374127896527</v>
       </c>
       <c r="E51" t="n">
-        <v>12.54983610156373</v>
+        <v>12.54983514455488</v>
       </c>
       <c r="F51" t="n">
         <v>1554600</v>
@@ -1452,16 +1452,16 @@
         <v>43647</v>
       </c>
       <c r="B52" t="n">
-        <v>12.24374103546143</v>
+        <v>12.24374294281006</v>
       </c>
       <c r="C52" t="n">
-        <v>12.68101750101362</v>
+        <v>12.68101947648185</v>
       </c>
       <c r="D52" t="n">
-        <v>12.03384853216565</v>
+        <v>12.03385040681691</v>
       </c>
       <c r="E52" t="n">
-        <v>12.61105333324836</v>
+        <v>12.61105529781747</v>
       </c>
       <c r="F52" t="n">
         <v>990900</v>
@@ -1492,16 +1492,16 @@
         <v>43649</v>
       </c>
       <c r="B54" t="n">
-        <v>12.24374103546143</v>
+        <v>12.24374294281006</v>
       </c>
       <c r="C54" t="n">
-        <v>12.27872311934406</v>
+        <v>12.27872503214225</v>
       </c>
       <c r="D54" t="n">
-        <v>11.91141082155712</v>
+        <v>11.91141267713484</v>
       </c>
       <c r="E54" t="n">
-        <v>12.11255842941124</v>
+        <v>12.11256031632404</v>
       </c>
       <c r="F54" t="n">
         <v>2832200</v>
@@ -1512,16 +1512,16 @@
         <v>43650</v>
       </c>
       <c r="B55" t="n">
-        <v>12.20001411437988</v>
+        <v>12.2000150680542</v>
       </c>
       <c r="C55" t="n">
-        <v>12.59356279535238</v>
+        <v>12.59356377979037</v>
       </c>
       <c r="D55" t="n">
-        <v>12.19126838425992</v>
+        <v>12.19126933725058</v>
       </c>
       <c r="E55" t="n">
-        <v>12.19126838425992</v>
+        <v>12.19126933725058</v>
       </c>
       <c r="F55" t="n">
         <v>336300</v>
@@ -1532,16 +1532,16 @@
         <v>43651</v>
       </c>
       <c r="B56" t="n">
-        <v>12.41865253448486</v>
+        <v>12.41865158081055</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56732661242062</v>
+        <v>12.56732564732907</v>
       </c>
       <c r="D56" t="n">
-        <v>12.24374209986595</v>
+        <v>12.24374115962366</v>
       </c>
       <c r="E56" t="n">
-        <v>12.24374209986595</v>
+        <v>12.24374115962366</v>
       </c>
       <c r="F56" t="n">
         <v>2415300</v>
@@ -1712,16 +1712,16 @@
         <v>43665</v>
       </c>
       <c r="B65" t="n">
-        <v>13.40689659118652</v>
+        <v>13.40689754486084</v>
       </c>
       <c r="C65" t="n">
-        <v>13.76546316548612</v>
+        <v>13.7654641446664</v>
       </c>
       <c r="D65" t="n">
-        <v>13.3281866926254</v>
+        <v>13.32818764070084</v>
       </c>
       <c r="E65" t="n">
-        <v>13.66051691208419</v>
+        <v>13.66051788379931</v>
       </c>
       <c r="F65" t="n">
         <v>227100</v>
@@ -1732,16 +1732,16 @@
         <v>43668</v>
       </c>
       <c r="B66" t="n">
-        <v>13.81793689727783</v>
+        <v>13.81793785095215</v>
       </c>
       <c r="C66" t="n">
-        <v>13.95786523705159</v>
+        <v>13.95786620038336</v>
       </c>
       <c r="D66" t="n">
-        <v>13.50309729874818</v>
+        <v>13.50309823069317</v>
       </c>
       <c r="E66" t="n">
-        <v>13.50309729874818</v>
+        <v>13.50309823069317</v>
       </c>
       <c r="F66" t="n">
         <v>718100</v>
@@ -1772,16 +1772,16 @@
         <v>43670</v>
       </c>
       <c r="B68" t="n">
-        <v>13.94912052154541</v>
+        <v>13.94911956787109</v>
       </c>
       <c r="C68" t="n">
-        <v>14.12403095898033</v>
+        <v>14.12402999334773</v>
       </c>
       <c r="D68" t="n">
-        <v>13.83542852870302</v>
+        <v>13.83542758280161</v>
       </c>
       <c r="E68" t="n">
-        <v>13.83542852870302</v>
+        <v>13.83542758280161</v>
       </c>
       <c r="F68" t="n">
         <v>446900</v>
@@ -1852,16 +1852,16 @@
         <v>43676</v>
       </c>
       <c r="B72" t="n">
-        <v>14.86740112304688</v>
+        <v>14.86740207672119</v>
       </c>
       <c r="C72" t="n">
-        <v>14.86740112304688</v>
+        <v>14.86740207672119</v>
       </c>
       <c r="D72" t="n">
-        <v>14.56130723689806</v>
+        <v>14.56130817093788</v>
       </c>
       <c r="E72" t="n">
-        <v>14.64876287123736</v>
+        <v>14.64876381088706</v>
       </c>
       <c r="F72" t="n">
         <v>235800</v>
@@ -1992,16 +1992,16 @@
         <v>43685</v>
       </c>
       <c r="B79" t="n">
-        <v>15.89937305450439</v>
+        <v>15.89937400817871</v>
       </c>
       <c r="C79" t="n">
-        <v>15.89937305450439</v>
+        <v>15.89937400817871</v>
       </c>
       <c r="D79" t="n">
-        <v>15.4008781349865</v>
+        <v>15.40087905876015</v>
       </c>
       <c r="E79" t="n">
-        <v>15.4533508454417</v>
+        <v>15.45335177236277</v>
       </c>
       <c r="F79" t="n">
         <v>301700</v>
@@ -2032,16 +2032,16 @@
         <v>43689</v>
       </c>
       <c r="B81" t="n">
-        <v>15.99557590484619</v>
+        <v>15.99557781219482</v>
       </c>
       <c r="C81" t="n">
-        <v>16.14424832031563</v>
+        <v>16.14425024539229</v>
       </c>
       <c r="D81" t="n">
-        <v>15.69822773775223</v>
+        <v>15.6982296096444</v>
       </c>
       <c r="E81" t="n">
-        <v>16.13550425782246</v>
+        <v>16.13550618185647</v>
       </c>
       <c r="F81" t="n">
         <v>611500</v>
@@ -2072,16 +2072,16 @@
         <v>43691</v>
       </c>
       <c r="B83" t="n">
-        <v>15.08604049682617</v>
+        <v>15.08603954315186</v>
       </c>
       <c r="C83" t="n">
-        <v>16.29292300261812</v>
+        <v>16.2929219726499</v>
       </c>
       <c r="D83" t="n">
-        <v>15.05105757325773</v>
+        <v>15.05105662179488</v>
       </c>
       <c r="E83" t="n">
-        <v>15.74195530103601</v>
+        <v>15.74195430589759</v>
       </c>
       <c r="F83" t="n">
         <v>474000</v>
@@ -2152,16 +2152,16 @@
         <v>43697</v>
       </c>
       <c r="B87" t="n">
-        <v>15.23471355438232</v>
+        <v>15.23471260070801</v>
       </c>
       <c r="C87" t="n">
-        <v>15.4795889985495</v>
+        <v>15.47958802954628</v>
       </c>
       <c r="D87" t="n">
-        <v>14.97234831769267</v>
+        <v>14.97234738044209</v>
       </c>
       <c r="E87" t="n">
-        <v>15.4795889985495</v>
+        <v>15.47958802954628</v>
       </c>
       <c r="F87" t="n">
         <v>1185200</v>
@@ -2192,16 +2192,16 @@
         <v>43699</v>
       </c>
       <c r="B89" t="n">
-        <v>16.04804801940918</v>
+        <v>16.04804992675781</v>
       </c>
       <c r="C89" t="n">
-        <v>16.24919481077263</v>
+        <v>16.24919674202804</v>
       </c>
       <c r="D89" t="n">
-        <v>15.61077151570908</v>
+        <v>15.61077337108636</v>
       </c>
       <c r="E89" t="n">
-        <v>15.82940976755913</v>
+        <v>15.82941164892209</v>
       </c>
       <c r="F89" t="n">
         <v>1339200</v>
@@ -2292,16 +2292,16 @@
         <v>43706</v>
       </c>
       <c r="B94" t="n">
-        <v>17.85837364196777</v>
+        <v>17.85837173461914</v>
       </c>
       <c r="C94" t="n">
-        <v>17.85837364196777</v>
+        <v>17.85837173461914</v>
       </c>
       <c r="D94" t="n">
-        <v>16.99256630837155</v>
+        <v>16.99256449349474</v>
       </c>
       <c r="E94" t="n">
-        <v>17.03629329436099</v>
+        <v>17.03629147481396</v>
       </c>
       <c r="F94" t="n">
         <v>557500</v>
@@ -2312,16 +2312,16 @@
         <v>43707</v>
       </c>
       <c r="B95" t="n">
-        <v>18.14697647094727</v>
+        <v>18.14697456359863</v>
       </c>
       <c r="C95" t="n">
-        <v>18.44432465259213</v>
+        <v>18.44432271399054</v>
       </c>
       <c r="D95" t="n">
-        <v>17.9021010072169</v>
+        <v>17.90209912560605</v>
       </c>
       <c r="E95" t="n">
-        <v>17.91959246921428</v>
+        <v>17.91959058576497</v>
       </c>
       <c r="F95" t="n">
         <v>944900</v>
@@ -2372,16 +2372,16 @@
         <v>43712</v>
       </c>
       <c r="B98" t="n">
-        <v>18.97780418395996</v>
+        <v>18.97780227661133</v>
       </c>
       <c r="C98" t="n">
-        <v>19.45880775332797</v>
+        <v>19.45880579763647</v>
       </c>
       <c r="D98" t="n">
-        <v>18.81163861698213</v>
+        <v>18.81163672633383</v>
       </c>
       <c r="E98" t="n">
-        <v>19.0215311746015</v>
+        <v>19.02152926285812</v>
       </c>
       <c r="F98" t="n">
         <v>1207700</v>
@@ -2392,16 +2392,16 @@
         <v>43713</v>
       </c>
       <c r="B99" t="n">
-        <v>18.53177833557129</v>
+        <v>18.53177642822266</v>
       </c>
       <c r="C99" t="n">
-        <v>19.43256684820771</v>
+        <v>19.4325648481471</v>
       </c>
       <c r="D99" t="n">
-        <v>18.53177833557129</v>
+        <v>18.53177642822266</v>
       </c>
       <c r="E99" t="n">
-        <v>18.98654462288788</v>
+        <v>18.98654266873328</v>
       </c>
       <c r="F99" t="n">
         <v>461900</v>
@@ -2412,16 +2412,16 @@
         <v>43714</v>
       </c>
       <c r="B100" t="n">
-        <v>18.23443031311035</v>
+        <v>18.23442840576172</v>
       </c>
       <c r="C100" t="n">
-        <v>18.62797816074218</v>
+        <v>18.62797621222785</v>
       </c>
       <c r="D100" t="n">
-        <v>18.02453779409122</v>
+        <v>18.02453590869765</v>
       </c>
       <c r="E100" t="n">
-        <v>18.53177846540682</v>
+        <v>18.53177652695513</v>
       </c>
       <c r="F100" t="n">
         <v>948300</v>
@@ -2432,16 +2432,16 @@
         <v>43717</v>
       </c>
       <c r="B101" t="n">
-        <v>17.69220542907715</v>
+        <v>17.69220733642578</v>
       </c>
       <c r="C101" t="n">
-        <v>18.76790513601398</v>
+        <v>18.76790715933088</v>
       </c>
       <c r="D101" t="n">
-        <v>17.44733167547826</v>
+        <v>17.44733355642772</v>
       </c>
       <c r="E101" t="n">
-        <v>18.36561158762876</v>
+        <v>18.36561356757549</v>
       </c>
       <c r="F101" t="n">
         <v>611800</v>
@@ -2532,16 +2532,16 @@
         <v>43724</v>
       </c>
       <c r="B106" t="n">
-        <v>16.61650848388672</v>
+        <v>16.61650657653809</v>
       </c>
       <c r="C106" t="n">
-        <v>17.25493183056058</v>
+        <v>17.25492984992965</v>
       </c>
       <c r="D106" t="n">
-        <v>16.45908866293642</v>
+        <v>16.45908677365744</v>
       </c>
       <c r="E106" t="n">
-        <v>17.05378502293637</v>
+        <v>17.05378306539435</v>
       </c>
       <c r="F106" t="n">
         <v>1080000</v>
@@ -2572,16 +2572,16 @@
         <v>43726</v>
       </c>
       <c r="B108" t="n">
-        <v>18.45306777954102</v>
+        <v>18.45306968688965</v>
       </c>
       <c r="C108" t="n">
-        <v>18.52303194957972</v>
+        <v>18.52303386416</v>
       </c>
       <c r="D108" t="n">
-        <v>17.66597044958621</v>
+        <v>17.66597227557878</v>
       </c>
       <c r="E108" t="n">
-        <v>17.71844316009589</v>
+        <v>17.71844499151215</v>
       </c>
       <c r="F108" t="n">
         <v>1567400</v>
@@ -2592,16 +2592,16 @@
         <v>43727</v>
       </c>
       <c r="B109" t="n">
-        <v>19.06525421142578</v>
+        <v>19.06525611877441</v>
       </c>
       <c r="C109" t="n">
-        <v>19.29263818537722</v>
+        <v>19.29264011547406</v>
       </c>
       <c r="D109" t="n">
-        <v>18.56675928194962</v>
+        <v>18.56676113942724</v>
       </c>
       <c r="E109" t="n">
-        <v>18.56675928194962</v>
+        <v>18.56676113942724</v>
       </c>
       <c r="F109" t="n">
         <v>586300</v>
@@ -2652,16 +2652,16 @@
         <v>43732</v>
       </c>
       <c r="B112" t="n">
-        <v>19.67744255065918</v>
+        <v>19.67744064331055</v>
       </c>
       <c r="C112" t="n">
-        <v>20.73565088270633</v>
+        <v>20.7356488727848</v>
       </c>
       <c r="D112" t="n">
-        <v>19.67744255065918</v>
+        <v>19.67744064331055</v>
       </c>
       <c r="E112" t="n">
-        <v>20.38583001542122</v>
+        <v>20.38582803940808</v>
       </c>
       <c r="F112" t="n">
         <v>1691800</v>
@@ -2672,16 +2672,16 @@
         <v>43733</v>
       </c>
       <c r="B113" t="n">
-        <v>19.9835376739502</v>
+        <v>19.98353576660156</v>
       </c>
       <c r="C113" t="n">
-        <v>20.63945246630254</v>
+        <v>20.63945049634946</v>
       </c>
       <c r="D113" t="n">
-        <v>19.52876968424729</v>
+        <v>19.52876782030444</v>
       </c>
       <c r="E113" t="n">
-        <v>20.44704972630954</v>
+        <v>20.44704777472053</v>
       </c>
       <c r="F113" t="n">
         <v>1513200</v>
@@ -2752,16 +2752,16 @@
         <v>43739</v>
       </c>
       <c r="B117" t="n">
-        <v>19.33636665344238</v>
+        <v>19.33636856079102</v>
       </c>
       <c r="C117" t="n">
-        <v>19.89608001909592</v>
+        <v>19.89608198165495</v>
       </c>
       <c r="D117" t="n">
-        <v>19.32762092359437</v>
+        <v>19.32762283008032</v>
       </c>
       <c r="E117" t="n">
-        <v>19.89608001909592</v>
+        <v>19.89608198165495</v>
       </c>
       <c r="F117" t="n">
         <v>517200</v>
@@ -2772,16 +2772,16 @@
         <v>43740</v>
       </c>
       <c r="B118" t="n">
-        <v>18.71543502807617</v>
+        <v>18.71543312072754</v>
       </c>
       <c r="C118" t="n">
-        <v>19.43256826569718</v>
+        <v>19.43256628526325</v>
       </c>
       <c r="D118" t="n">
-        <v>18.67170804259297</v>
+        <v>18.67170613970069</v>
       </c>
       <c r="E118" t="n">
-        <v>19.32762283330646</v>
+        <v>19.32762086356785</v>
       </c>
       <c r="F118" t="n">
         <v>478800</v>
@@ -2812,16 +2812,16 @@
         <v>43742</v>
       </c>
       <c r="B120" t="n">
-        <v>19.41507530212402</v>
+        <v>19.41507720947266</v>
       </c>
       <c r="C120" t="n">
-        <v>19.98353436097165</v>
+        <v>19.98353632416604</v>
       </c>
       <c r="D120" t="n">
-        <v>18.82037905542412</v>
+        <v>18.82038090434943</v>
       </c>
       <c r="E120" t="n">
-        <v>18.89034322161956</v>
+        <v>18.8903450774182</v>
       </c>
       <c r="F120" t="n">
         <v>953700</v>
@@ -2892,16 +2892,16 @@
         <v>43748</v>
       </c>
       <c r="B124" t="n">
-        <v>18.33937835693359</v>
+        <v>18.33937454223633</v>
       </c>
       <c r="C124" t="n">
-        <v>18.69794500329429</v>
+        <v>18.69794111401308</v>
       </c>
       <c r="D124" t="n">
-        <v>18.33937835693359</v>
+        <v>18.33937454223633</v>
       </c>
       <c r="E124" t="n">
-        <v>18.40934253992891</v>
+        <v>18.40933871067869</v>
       </c>
       <c r="F124" t="n">
         <v>1209500</v>
@@ -2932,16 +2932,16 @@
         <v>43752</v>
       </c>
       <c r="B126" t="n">
-        <v>20.00102615356445</v>
+        <v>20.00102806091309</v>
       </c>
       <c r="C126" t="n">
-        <v>20.09722584114144</v>
+        <v>20.09722775766392</v>
       </c>
       <c r="D126" t="n">
-        <v>19.00403468353265</v>
+        <v>19.00403649580565</v>
       </c>
       <c r="E126" t="n">
-        <v>19.27514729163531</v>
+        <v>19.27514912976229</v>
       </c>
       <c r="F126" t="n">
         <v>922100</v>
@@ -2952,16 +2952,16 @@
         <v>43753</v>
       </c>
       <c r="B127" t="n">
-        <v>20.43830490112305</v>
+        <v>20.43830680847168</v>
       </c>
       <c r="C127" t="n">
-        <v>21.19041936733377</v>
+        <v>21.19042134487142</v>
       </c>
       <c r="D127" t="n">
-        <v>20.01851818194036</v>
+        <v>20.01852005011355</v>
       </c>
       <c r="E127" t="n">
-        <v>20.07099256438664</v>
+        <v>20.07099443745686</v>
       </c>
       <c r="F127" t="n">
         <v>1169600</v>
@@ -2972,16 +2972,16 @@
         <v>43754</v>
       </c>
       <c r="B128" t="n">
-        <v>20.72690773010254</v>
+        <v>20.72690582275391</v>
       </c>
       <c r="C128" t="n">
-        <v>20.91056306795709</v>
+        <v>20.91056114370798</v>
       </c>
       <c r="D128" t="n">
-        <v>20.18468411095937</v>
+        <v>20.18468225350769</v>
       </c>
       <c r="E128" t="n">
-        <v>20.46454081706776</v>
+        <v>20.46453893386288</v>
       </c>
       <c r="F128" t="n">
         <v>774000</v>
@@ -3032,16 +3032,16 @@
         <v>43759</v>
       </c>
       <c r="B131" t="n">
-        <v>21.6014575958252</v>
+        <v>21.60145950317383</v>
       </c>
       <c r="C131" t="n">
-        <v>21.6014575958252</v>
+        <v>21.60145950317383</v>
       </c>
       <c r="D131" t="n">
-        <v>20.30711801819497</v>
+        <v>20.30711981125701</v>
       </c>
       <c r="E131" t="n">
-        <v>20.72690468373636</v>
+        <v>20.7269065138644</v>
       </c>
       <c r="F131" t="n">
         <v>689100</v>
@@ -3072,16 +3072,16 @@
         <v>43761</v>
       </c>
       <c r="B133" t="n">
-        <v>22.03873634338379</v>
+        <v>22.03873443603516</v>
       </c>
       <c r="C133" t="n">
-        <v>22.80834225208901</v>
+        <v>22.80834027813461</v>
       </c>
       <c r="D133" t="n">
-        <v>21.99500769238621</v>
+        <v>21.99500578882208</v>
       </c>
       <c r="E133" t="n">
-        <v>22.37106575057804</v>
+        <v>22.37106381446786</v>
       </c>
       <c r="F133" t="n">
         <v>2305600</v>
@@ -3172,16 +3172,16 @@
         <v>43768</v>
       </c>
       <c r="B138" t="n">
-        <v>23.6391658782959</v>
+        <v>23.63916778564453</v>
       </c>
       <c r="C138" t="n">
-        <v>24.30382629345293</v>
+        <v>24.30382825443032</v>
       </c>
       <c r="D138" t="n">
-        <v>23.6216744196682</v>
+        <v>23.62167632560551</v>
       </c>
       <c r="E138" t="n">
-        <v>23.78783994047678</v>
+        <v>23.78784185982132</v>
       </c>
       <c r="F138" t="n">
         <v>986800</v>
@@ -3192,16 +3192,16 @@
         <v>43769</v>
       </c>
       <c r="B139" t="n">
-        <v>23.60418510437012</v>
+        <v>23.60418319702148</v>
       </c>
       <c r="C139" t="n">
-        <v>23.93651617616393</v>
+        <v>23.93651424196111</v>
       </c>
       <c r="D139" t="n">
-        <v>23.35056560354822</v>
+        <v>23.35056371669345</v>
       </c>
       <c r="E139" t="n">
-        <v>23.66540354704859</v>
+        <v>23.66540163475317</v>
       </c>
       <c r="F139" t="n">
         <v>983900</v>
@@ -3232,16 +3232,16 @@
         <v>43773</v>
       </c>
       <c r="B141" t="n">
-        <v>24.48748207092285</v>
+        <v>24.48748588562012</v>
       </c>
       <c r="C141" t="n">
-        <v>24.64490186541402</v>
+        <v>24.64490570463438</v>
       </c>
       <c r="D141" t="n">
-        <v>24.03271414641001</v>
+        <v>24.03271789026283</v>
       </c>
       <c r="E141" t="n">
-        <v>24.03271414641001</v>
+        <v>24.03271789026283</v>
       </c>
       <c r="F141" t="n">
         <v>674600</v>
@@ -3272,16 +3272,16 @@
         <v>43775</v>
       </c>
       <c r="B143" t="n">
-        <v>24.40002822875977</v>
+        <v>24.4000301361084</v>
       </c>
       <c r="C143" t="n">
-        <v>24.83730472629337</v>
+        <v>24.83730666782388</v>
       </c>
       <c r="D143" t="n">
-        <v>24.40002822875977</v>
+        <v>24.4000301361084</v>
       </c>
       <c r="E143" t="n">
-        <v>24.65364939800644</v>
+        <v>24.65365132518062</v>
       </c>
       <c r="F143" t="n">
         <v>511100</v>
@@ -3292,16 +3292,16 @@
         <v>43776</v>
       </c>
       <c r="B144" t="n">
-        <v>24.48748207092285</v>
+        <v>24.48748588562012</v>
       </c>
       <c r="C144" t="n">
-        <v>24.79357593042485</v>
+        <v>24.79357979280589</v>
       </c>
       <c r="D144" t="n">
-        <v>24.21637112934215</v>
+        <v>24.21637490180534</v>
       </c>
       <c r="E144" t="n">
-        <v>24.4699906119622</v>
+        <v>24.46999442393462</v>
       </c>
       <c r="F144" t="n">
         <v>513300</v>
@@ -3312,16 +3312,16 @@
         <v>43777</v>
       </c>
       <c r="B145" t="n">
-        <v>24.05021095275879</v>
+        <v>24.05020904541016</v>
       </c>
       <c r="C145" t="n">
-        <v>24.74110872262443</v>
+        <v>24.74110676048281</v>
       </c>
       <c r="D145" t="n">
-        <v>24.04146522133392</v>
+        <v>24.04146331467888</v>
       </c>
       <c r="E145" t="n">
-        <v>24.37379634316828</v>
+        <v>24.37379441015708</v>
       </c>
       <c r="F145" t="n">
         <v>636200</v>
@@ -3332,16 +3332,16 @@
         <v>43780</v>
       </c>
       <c r="B146" t="n">
-        <v>24.70612144470215</v>
+        <v>24.70612335205078</v>
       </c>
       <c r="C146" t="n">
-        <v>25.178380849986</v>
+        <v>25.17838279379375</v>
       </c>
       <c r="D146" t="n">
-        <v>24.25135349918675</v>
+        <v>24.25135537142663</v>
       </c>
       <c r="E146" t="n">
-        <v>24.31257194029893</v>
+        <v>24.31257381726497</v>
       </c>
       <c r="F146" t="n">
         <v>1360200</v>
@@ -3352,16 +3352,16 @@
         <v>43781</v>
       </c>
       <c r="B147" t="n">
-        <v>24.47873878479004</v>
+        <v>24.47873687744141</v>
       </c>
       <c r="C147" t="n">
-        <v>25.46698462970316</v>
+        <v>25.46698264535181</v>
       </c>
       <c r="D147" t="n">
-        <v>24.17264489473525</v>
+        <v>24.17264301123702</v>
       </c>
       <c r="E147" t="n">
-        <v>24.90726956363575</v>
+        <v>24.9072676228966</v>
       </c>
       <c r="F147" t="n">
         <v>1405000</v>
@@ -3392,16 +3392,16 @@
         <v>43783</v>
       </c>
       <c r="B149" t="n">
-        <v>24.05021095275879</v>
+        <v>24.05020904541016</v>
       </c>
       <c r="C149" t="n">
-        <v>25.04720098210647</v>
+        <v>25.04719899568961</v>
       </c>
       <c r="D149" t="n">
-        <v>23.48175175476367</v>
+        <v>23.4817498924978</v>
       </c>
       <c r="E149" t="n">
-        <v>24.63616161360366</v>
+        <v>24.63615965978507</v>
       </c>
       <c r="F149" t="n">
         <v>1658400</v>
@@ -3412,16 +3412,16 @@
         <v>43787</v>
       </c>
       <c r="B150" t="n">
-        <v>24.05021095275879</v>
+        <v>24.05020904541016</v>
       </c>
       <c r="C150" t="n">
-        <v>24.60992441932904</v>
+        <v>24.60992246759124</v>
       </c>
       <c r="D150" t="n">
-        <v>23.91028258611623</v>
+        <v>23.91028068986488</v>
       </c>
       <c r="E150" t="n">
-        <v>24.43501479506469</v>
+        <v>24.43501285719844</v>
       </c>
       <c r="F150" t="n">
         <v>1045200</v>
@@ -3432,16 +3432,16 @@
         <v>43788</v>
       </c>
       <c r="B151" t="n">
-        <v>23.7178783416748</v>
+        <v>23.71788024902344</v>
       </c>
       <c r="C151" t="n">
-        <v>24.312572986701</v>
+        <v>24.3125749418739</v>
       </c>
       <c r="D151" t="n">
-        <v>23.7178783416748</v>
+        <v>23.71788024902344</v>
       </c>
       <c r="E151" t="n">
-        <v>24.24260881269336</v>
+        <v>24.24261076223987</v>
       </c>
       <c r="F151" t="n">
         <v>778500</v>
@@ -3452,16 +3452,16 @@
         <v>43790</v>
       </c>
       <c r="B152" t="n">
-        <v>23.52547454833984</v>
+        <v>23.52547645568848</v>
       </c>
       <c r="C152" t="n">
-        <v>23.97149676299973</v>
+        <v>23.97149870651001</v>
       </c>
       <c r="D152" t="n">
-        <v>23.45551037749579</v>
+        <v>23.45551227917201</v>
       </c>
       <c r="E152" t="n">
-        <v>23.87529540256013</v>
+        <v>23.87529733827079</v>
       </c>
       <c r="F152" t="n">
         <v>699200</v>
@@ -3472,16 +3472,16 @@
         <v>43791</v>
       </c>
       <c r="B153" t="n">
-        <v>23.30683708190918</v>
+        <v>23.30683517456055</v>
       </c>
       <c r="C153" t="n">
-        <v>23.66540367793259</v>
+        <v>23.66540174124015</v>
       </c>
       <c r="D153" t="n">
-        <v>23.07070737191987</v>
+        <v>23.07070548389525</v>
       </c>
       <c r="E153" t="n">
-        <v>23.53422106174213</v>
+        <v>23.5342191357852</v>
       </c>
       <c r="F153" t="n">
         <v>919200</v>
@@ -3492,16 +3492,16 @@
         <v>43794</v>
       </c>
       <c r="B154" t="n">
-        <v>23.9102783203125</v>
+        <v>23.91028022766113</v>
       </c>
       <c r="C154" t="n">
-        <v>24.22511792312697</v>
+        <v>24.22511985559069</v>
       </c>
       <c r="D154" t="n">
-        <v>23.44676464595536</v>
+        <v>23.44676651632901</v>
       </c>
       <c r="E154" t="n">
-        <v>23.44676464595536</v>
+        <v>23.44676651632901</v>
       </c>
       <c r="F154" t="n">
         <v>1617500</v>
@@ -3512,16 +3512,16 @@
         <v>43795</v>
       </c>
       <c r="B155" t="n">
-        <v>23.42053031921387</v>
+        <v>23.4205322265625</v>
       </c>
       <c r="C155" t="n">
-        <v>24.13766352391739</v>
+        <v>24.13766548966876</v>
       </c>
       <c r="D155" t="n">
-        <v>23.3155832235628</v>
+        <v>23.31558512236463</v>
       </c>
       <c r="E155" t="n">
-        <v>24.06769934950918</v>
+        <v>24.06770130956273</v>
       </c>
       <c r="F155" t="n">
         <v>1676700</v>
@@ -3532,16 +3532,16 @@
         <v>43796</v>
       </c>
       <c r="B156" t="n">
-        <v>22.91329002380371</v>
+        <v>22.91328811645508</v>
       </c>
       <c r="C156" t="n">
-        <v>23.62167751013223</v>
+        <v>23.62167554381599</v>
       </c>
       <c r="D156" t="n">
-        <v>22.70339582896505</v>
+        <v>22.70339393908844</v>
       </c>
       <c r="E156" t="n">
-        <v>23.42927644428724</v>
+        <v>23.42927449398685</v>
       </c>
       <c r="F156" t="n">
         <v>1534800</v>
@@ -3552,16 +3552,16 @@
         <v>43797</v>
       </c>
       <c r="B157" t="n">
-        <v>23.42927742004395</v>
+        <v>23.42927551269531</v>
       </c>
       <c r="C157" t="n">
-        <v>23.58669557061263</v>
+        <v>23.58669365044878</v>
       </c>
       <c r="D157" t="n">
-        <v>22.5459786239224</v>
+        <v>22.54597678848203</v>
       </c>
       <c r="E157" t="n">
-        <v>22.91329097807118</v>
+        <v>22.91328911272837</v>
       </c>
       <c r="F157" t="n">
         <v>1150500</v>
@@ -3612,16 +3612,16 @@
         <v>43802</v>
       </c>
       <c r="B160" t="n">
-        <v>26.34153747558594</v>
+        <v>26.3415355682373</v>
       </c>
       <c r="C160" t="n">
-        <v>26.39401018928447</v>
+        <v>26.39400827813636</v>
       </c>
       <c r="D160" t="n">
-        <v>25.20461755826795</v>
+        <v>25.20461573324187</v>
       </c>
       <c r="E160" t="n">
-        <v>25.44949300232355</v>
+        <v>25.44949115956643</v>
       </c>
       <c r="F160" t="n">
         <v>1627600</v>
@@ -3732,16 +3732,16 @@
         <v>43810</v>
       </c>
       <c r="B166" t="n">
-        <v>26.90124893188477</v>
+        <v>26.9012508392334</v>
       </c>
       <c r="C166" t="n">
-        <v>27.02368581105319</v>
+        <v>27.02368772708283</v>
       </c>
       <c r="D166" t="n">
-        <v>26.15787859105349</v>
+        <v>26.15788044569578</v>
       </c>
       <c r="E166" t="n">
-        <v>26.15787859105349</v>
+        <v>26.15788044569578</v>
       </c>
       <c r="F166" t="n">
         <v>1303000</v>
@@ -3772,16 +3772,16 @@
         <v>43812</v>
       </c>
       <c r="B168" t="n">
-        <v>28.86025047302246</v>
+        <v>28.86024856567383</v>
       </c>
       <c r="C168" t="n">
-        <v>29.55989224150107</v>
+        <v>29.55989028791373</v>
       </c>
       <c r="D168" t="n">
-        <v>28.51917531939883</v>
+        <v>28.51917343459155</v>
       </c>
       <c r="E168" t="n">
-        <v>28.81652348802163</v>
+        <v>28.81652158356287</v>
       </c>
       <c r="F168" t="n">
         <v>1941500</v>
@@ -3792,16 +3792,16 @@
         <v>43815</v>
       </c>
       <c r="B169" t="n">
-        <v>29.48118019104004</v>
+        <v>29.48118209838867</v>
       </c>
       <c r="C169" t="n">
-        <v>30.15458638679904</v>
+        <v>30.15458833771514</v>
       </c>
       <c r="D169" t="n">
-        <v>29.21881496395137</v>
+        <v>29.21881685432572</v>
       </c>
       <c r="E169" t="n">
-        <v>29.29752486569346</v>
+        <v>29.29752676116011</v>
       </c>
       <c r="F169" t="n">
         <v>1422400</v>
@@ -3812,16 +3812,16 @@
         <v>43816</v>
       </c>
       <c r="B170" t="n">
-        <v>28.53666496276855</v>
+        <v>28.53666305541992</v>
       </c>
       <c r="C170" t="n">
-        <v>30.0059142510561</v>
+        <v>30.00591224550501</v>
       </c>
       <c r="D170" t="n">
-        <v>28.33551817565424</v>
+        <v>28.33551628174996</v>
       </c>
       <c r="E170" t="n">
-        <v>29.86598590627419</v>
+        <v>29.8659839100757</v>
       </c>
       <c r="F170" t="n">
         <v>1262300</v>
@@ -3852,16 +3852,16 @@
         <v>43818</v>
       </c>
       <c r="B172" t="n">
-        <v>29.16634178161621</v>
+        <v>29.16633987426758</v>
       </c>
       <c r="C172" t="n">
-        <v>29.47243733925006</v>
+        <v>29.47243541188415</v>
       </c>
       <c r="D172" t="n">
-        <v>28.77279559290198</v>
+        <v>28.77279371128951</v>
       </c>
       <c r="E172" t="n">
-        <v>29.03516083076314</v>
+        <v>29.03515893199315</v>
       </c>
       <c r="F172" t="n">
         <v>679700</v>
@@ -3872,16 +3872,16 @@
         <v>43819</v>
       </c>
       <c r="B173" t="n">
-        <v>29.08763122558594</v>
+        <v>29.08763313293457</v>
       </c>
       <c r="C173" t="n">
-        <v>29.31501687315646</v>
+        <v>29.31501879541534</v>
       </c>
       <c r="D173" t="n">
-        <v>28.89523183474349</v>
+        <v>28.89523372947601</v>
       </c>
       <c r="E173" t="n">
-        <v>29.28003395258332</v>
+        <v>29.28003587254828</v>
       </c>
       <c r="F173" t="n">
         <v>2528100</v>
@@ -3912,16 +3912,16 @@
         <v>43825</v>
       </c>
       <c r="B175" t="n">
-        <v>30.65308380126953</v>
+        <v>30.65308570861816</v>
       </c>
       <c r="C175" t="n">
-        <v>31.28276306619496</v>
+        <v>31.28276501272458</v>
       </c>
       <c r="D175" t="n">
-        <v>30.32950010619625</v>
+        <v>30.3295019934103</v>
       </c>
       <c r="E175" t="n">
-        <v>30.3644830289488</v>
+        <v>30.36448491833962</v>
       </c>
       <c r="F175" t="n">
         <v>940400</v>
@@ -3952,16 +3952,16 @@
         <v>43829</v>
       </c>
       <c r="B177" t="n">
-        <v>30.76677894592285</v>
+        <v>30.76677703857422</v>
       </c>
       <c r="C177" t="n">
-        <v>30.99416128860425</v>
+        <v>30.99415936715932</v>
       </c>
       <c r="D177" t="n">
-        <v>30.62685058054459</v>
+        <v>30.62684868187065</v>
       </c>
       <c r="E177" t="n">
-        <v>30.62685058054459</v>
+        <v>30.62684868187065</v>
       </c>
       <c r="F177" t="n">
         <v>643600</v>
@@ -4012,16 +4012,16 @@
         <v>43836</v>
       </c>
       <c r="B180" t="n">
-        <v>33.23301696777344</v>
+        <v>33.23301315307617</v>
       </c>
       <c r="C180" t="n">
-        <v>33.67029350682309</v>
+        <v>33.67028964193243</v>
       </c>
       <c r="D180" t="n">
-        <v>32.49839224872381</v>
+        <v>32.49838851835145</v>
       </c>
       <c r="E180" t="n">
-        <v>33.20678144300013</v>
+        <v>33.20677763131435</v>
       </c>
       <c r="F180" t="n">
         <v>1231600</v>
@@ -4072,16 +4072,16 @@
         <v>43839</v>
       </c>
       <c r="B183" t="n">
-        <v>34.02011108398438</v>
+        <v>34.02011489868164</v>
       </c>
       <c r="C183" t="n">
-        <v>34.17753088185141</v>
+        <v>34.17753471420026</v>
       </c>
       <c r="D183" t="n">
-        <v>33.53036023104752</v>
+        <v>33.5303639908287</v>
       </c>
       <c r="E183" t="n">
-        <v>33.86269128611734</v>
+        <v>33.86269508316303</v>
       </c>
       <c r="F183" t="n">
         <v>1002900</v>
@@ -4112,16 +4112,16 @@
         <v>43843</v>
       </c>
       <c r="B185" t="n">
-        <v>35.20950317382812</v>
+        <v>35.20950698852539</v>
       </c>
       <c r="C185" t="n">
-        <v>35.46312435071257</v>
+        <v>35.46312819288787</v>
       </c>
       <c r="D185" t="n">
-        <v>34.27373170781794</v>
+        <v>34.27373542113109</v>
       </c>
       <c r="E185" t="n">
-        <v>34.41366005779643</v>
+        <v>34.4136637862698</v>
       </c>
       <c r="F185" t="n">
         <v>1839000</v>
@@ -4132,16 +4132,16 @@
         <v>43844</v>
       </c>
       <c r="B186" t="n">
-        <v>36.53007888793945</v>
+        <v>36.53008270263672</v>
       </c>
       <c r="C186" t="n">
-        <v>36.74871713600984</v>
+        <v>36.74872097353867</v>
       </c>
       <c r="D186" t="n">
-        <v>35.20950200134754</v>
+        <v>35.20950567814199</v>
       </c>
       <c r="E186" t="n">
-        <v>35.37566920502018</v>
+        <v>35.37567289916683</v>
       </c>
       <c r="F186" t="n">
         <v>1956900</v>
@@ -4152,16 +4152,16 @@
         <v>43845</v>
       </c>
       <c r="B187" t="n">
-        <v>36.99359130859375</v>
+        <v>36.99358749389648</v>
       </c>
       <c r="C187" t="n">
-        <v>37.62327053745397</v>
+        <v>37.62326665782557</v>
       </c>
       <c r="D187" t="n">
-        <v>35.76921910777715</v>
+        <v>35.76921541933444</v>
       </c>
       <c r="E187" t="n">
-        <v>36.2939495743907</v>
+        <v>36.29394583183894</v>
       </c>
       <c r="F187" t="n">
         <v>2561700</v>
@@ -4212,16 +4212,16 @@
         <v>43850</v>
       </c>
       <c r="B190" t="n">
-        <v>35.62929153442383</v>
+        <v>35.62929534912109</v>
       </c>
       <c r="C190" t="n">
-        <v>36.09280356786682</v>
+        <v>36.09280743219062</v>
       </c>
       <c r="D190" t="n">
-        <v>34.54484432075029</v>
+        <v>34.54484801933979</v>
       </c>
       <c r="E190" t="n">
-        <v>34.58857130455822</v>
+        <v>34.58857500782939</v>
       </c>
       <c r="F190" t="n">
         <v>1893400</v>
@@ -4232,16 +4232,16 @@
         <v>43851</v>
       </c>
       <c r="B191" t="n">
-        <v>35.68176651000977</v>
+        <v>35.6817626953125</v>
       </c>
       <c r="C191" t="n">
-        <v>36.2939543592033</v>
+        <v>36.29395047905773</v>
       </c>
       <c r="D191" t="n">
-        <v>35.28821694008853</v>
+        <v>35.28821316746521</v>
       </c>
       <c r="E191" t="n">
-        <v>35.62929545812386</v>
+        <v>35.62929164903621</v>
       </c>
       <c r="F191" t="n">
         <v>1445700</v>
@@ -4292,16 +4292,16 @@
         <v>43854</v>
       </c>
       <c r="B194" t="n">
-        <v>35.29695892333984</v>
+        <v>35.29695510864258</v>
       </c>
       <c r="C194" t="n">
-        <v>36.04032762433681</v>
+        <v>36.04032372930043</v>
       </c>
       <c r="D194" t="n">
-        <v>34.8072080519041</v>
+        <v>34.80720429013636</v>
       </c>
       <c r="E194" t="n">
-        <v>35.63803405288327</v>
+        <v>35.63803020132452</v>
       </c>
       <c r="F194" t="n">
         <v>1110500</v>
@@ -4332,16 +4332,16 @@
         <v>43858</v>
       </c>
       <c r="B196" t="n">
-        <v>36.15402221679688</v>
+        <v>36.15402603149414</v>
       </c>
       <c r="C196" t="n">
-        <v>36.15402221679688</v>
+        <v>36.15402603149414</v>
       </c>
       <c r="D196" t="n">
-        <v>34.02885809739983</v>
+        <v>34.02886168786595</v>
       </c>
       <c r="E196" t="n">
-        <v>34.50111753196695</v>
+        <v>34.50112117226229</v>
       </c>
       <c r="F196" t="n">
         <v>1763600</v>
@@ -4392,16 +4392,16 @@
         <v>43861</v>
       </c>
       <c r="B199" t="n">
-        <v>34.50111389160156</v>
+        <v>34.50111770629883</v>
       </c>
       <c r="C199" t="n">
-        <v>35.2094996325523</v>
+        <v>35.20950352557391</v>
       </c>
       <c r="D199" t="n">
-        <v>34.19501836320331</v>
+        <v>34.1950221440564</v>
       </c>
       <c r="E199" t="n">
-        <v>34.46613097358667</v>
+        <v>34.46613478441597</v>
       </c>
       <c r="F199" t="n">
         <v>1600100</v>
@@ -4412,16 +4412,16 @@
         <v>43864</v>
       </c>
       <c r="B200" t="n">
-        <v>36.90613555908203</v>
+        <v>36.9061393737793</v>
       </c>
       <c r="C200" t="n">
-        <v>36.99358952057237</v>
+        <v>36.99359334430907</v>
       </c>
       <c r="D200" t="n">
-        <v>34.50111492039505</v>
+        <v>34.50111848650423</v>
       </c>
       <c r="E200" t="n">
-        <v>34.50111492039505</v>
+        <v>34.50111848650423</v>
       </c>
       <c r="F200" t="n">
         <v>1703600</v>
@@ -4452,16 +4452,16 @@
         <v>43866</v>
       </c>
       <c r="B202" t="n">
-        <v>37.90312576293945</v>
+        <v>37.90312957763672</v>
       </c>
       <c r="C202" t="n">
-        <v>38.42785620922731</v>
+        <v>38.42786007673521</v>
       </c>
       <c r="D202" t="n">
-        <v>37.18599259614046</v>
+        <v>37.18599633866305</v>
       </c>
       <c r="E202" t="n">
-        <v>38.04305410435987</v>
+        <v>38.04305793313999</v>
       </c>
       <c r="F202" t="n">
         <v>2731900</v>
@@ -4492,16 +4492,16 @@
         <v>43868</v>
       </c>
       <c r="B204" t="n">
-        <v>40.86785888671875</v>
+        <v>40.86786270141602</v>
       </c>
       <c r="C204" t="n">
-        <v>47.30456912203875</v>
+        <v>47.30457353755293</v>
       </c>
       <c r="D204" t="n">
-        <v>40.84162336583092</v>
+        <v>40.84162717807931</v>
       </c>
       <c r="E204" t="n">
-        <v>44.61094443906375</v>
+        <v>44.61094860314898</v>
       </c>
       <c r="F204" t="n">
         <v>8429100</v>
@@ -4512,16 +4512,16 @@
         <v>43871</v>
       </c>
       <c r="B205" t="n">
-        <v>41.96980285644531</v>
+        <v>41.96979904174805</v>
       </c>
       <c r="C205" t="n">
-        <v>43.01926386049981</v>
+        <v>43.01925995041548</v>
       </c>
       <c r="D205" t="n">
-        <v>40.67546139062178</v>
+        <v>40.67545769356912</v>
       </c>
       <c r="E205" t="n">
-        <v>40.85912006887098</v>
+        <v>40.8591163551253</v>
       </c>
       <c r="F205" t="n">
         <v>2911200</v>
@@ -4552,16 +4552,16 @@
         <v>43873</v>
       </c>
       <c r="B207" t="n">
-        <v>41.96980285644531</v>
+        <v>41.96979904174805</v>
       </c>
       <c r="C207" t="n">
-        <v>42.97553687469006</v>
+        <v>42.97553296858015</v>
       </c>
       <c r="D207" t="n">
-        <v>41.14772084413941</v>
+        <v>41.14771710416239</v>
       </c>
       <c r="E207" t="n">
-        <v>42.61697025320191</v>
+        <v>42.61696637968264</v>
       </c>
       <c r="F207" t="n">
         <v>1198300</v>
@@ -4592,16 +4592,16 @@
         <v>43875</v>
       </c>
       <c r="B209" t="n">
-        <v>41.45381546020508</v>
+        <v>41.45381164550781</v>
       </c>
       <c r="C209" t="n">
-        <v>41.81238207341615</v>
+        <v>41.81237822572257</v>
       </c>
       <c r="D209" t="n">
-        <v>40.45682219151946</v>
+        <v>40.45681846856834</v>
       </c>
       <c r="E209" t="n">
-        <v>41.69868924401114</v>
+        <v>41.6986854067799</v>
       </c>
       <c r="F209" t="n">
         <v>954600</v>
@@ -4632,16 +4632,16 @@
         <v>43879</v>
       </c>
       <c r="B211" t="n">
-        <v>42.86184310913086</v>
+        <v>42.86183929443359</v>
       </c>
       <c r="C211" t="n">
-        <v>43.37782953722005</v>
+        <v>43.37782567660008</v>
       </c>
       <c r="D211" t="n">
-        <v>42.06599997456838</v>
+        <v>42.06599623070103</v>
       </c>
       <c r="E211" t="n">
-        <v>42.59073380132211</v>
+        <v>42.59073001075353</v>
       </c>
       <c r="F211" t="n">
         <v>1138300</v>
@@ -4652,16 +4652,16 @@
         <v>43880</v>
       </c>
       <c r="B212" t="n">
-        <v>44.54098129272461</v>
+        <v>44.54098510742188</v>
       </c>
       <c r="C212" t="n">
-        <v>44.54972535417563</v>
+        <v>44.54972916962178</v>
       </c>
       <c r="D212" t="n">
-        <v>42.97553073677084</v>
+        <v>42.97553441739561</v>
       </c>
       <c r="E212" t="n">
-        <v>43.24664334791823</v>
+        <v>43.24664705176236</v>
       </c>
       <c r="F212" t="n">
         <v>2000400</v>
@@ -4692,16 +4692,16 @@
         <v>43882</v>
       </c>
       <c r="B214" t="n">
-        <v>44.17367553710938</v>
+        <v>44.17367172241211</v>
       </c>
       <c r="C214" t="n">
-        <v>44.8820647479068</v>
+        <v>44.88206087203531</v>
       </c>
       <c r="D214" t="n">
-        <v>42.46829966396702</v>
+        <v>42.46829599654055</v>
       </c>
       <c r="E214" t="n">
-        <v>43.43030673785016</v>
+        <v>43.43030298734784</v>
       </c>
       <c r="F214" t="n">
         <v>811000</v>
@@ -4712,16 +4712,16 @@
         <v>43887</v>
       </c>
       <c r="B215" t="n">
-        <v>41.89109039306641</v>
+        <v>41.89108657836914</v>
       </c>
       <c r="C215" t="n">
-        <v>42.372093879953</v>
+        <v>42.37209002145447</v>
       </c>
       <c r="D215" t="n">
-        <v>40.23818240654671</v>
+        <v>40.23817874236698</v>
       </c>
       <c r="E215" t="n">
-        <v>41.23517563745151</v>
+        <v>41.23517188248333</v>
       </c>
       <c r="F215" t="n">
         <v>987000</v>
@@ -4832,16 +4832,16 @@
         <v>43895</v>
       </c>
       <c r="B221" t="n">
-        <v>38.99631881713867</v>
+        <v>38.99632263183594</v>
       </c>
       <c r="C221" t="n">
-        <v>41.96980038314483</v>
+        <v>41.96980448871395</v>
       </c>
       <c r="D221" t="n">
-        <v>37.78069066802747</v>
+        <v>37.78069436380958</v>
       </c>
       <c r="E221" t="n">
-        <v>41.96980038314483</v>
+        <v>41.96980448871395</v>
       </c>
       <c r="F221" t="n">
         <v>1378200</v>
@@ -4872,16 +4872,16 @@
         <v>43899</v>
       </c>
       <c r="B223" t="n">
-        <v>30.7492847442627</v>
+        <v>30.74928283691406</v>
       </c>
       <c r="C223" t="n">
-        <v>34.72850040790698</v>
+        <v>34.72849825373142</v>
       </c>
       <c r="D223" t="n">
-        <v>30.7492847442627</v>
+        <v>30.74928283691406</v>
       </c>
       <c r="E223" t="n">
-        <v>33.23301551060689</v>
+        <v>33.23301344919482</v>
       </c>
       <c r="F223" t="n">
         <v>2155800</v>
@@ -4912,16 +4912,16 @@
         <v>43901</v>
       </c>
       <c r="B225" t="n">
-        <v>30.88921356201172</v>
+        <v>30.88921165466309</v>
       </c>
       <c r="C225" t="n">
-        <v>34.19502303445503</v>
+        <v>34.19502092297912</v>
       </c>
       <c r="D225" t="n">
-        <v>28.51917558929342</v>
+        <v>28.51917382829</v>
       </c>
       <c r="E225" t="n">
-        <v>33.06685213167455</v>
+        <v>33.06685008986098</v>
       </c>
       <c r="F225" t="n">
         <v>2211100</v>
@@ -4952,16 +4952,16 @@
         <v>43903</v>
       </c>
       <c r="B227" t="n">
-        <v>29.34999847412109</v>
+        <v>29.35000038146973</v>
       </c>
       <c r="C227" t="n">
-        <v>32.29724100872139</v>
+        <v>32.29724310760049</v>
       </c>
       <c r="D227" t="n">
-        <v>26.673865221386</v>
+        <v>26.67386695482255</v>
       </c>
       <c r="E227" t="n">
-        <v>31.48390649081626</v>
+        <v>31.48390853683973</v>
       </c>
       <c r="F227" t="n">
         <v>2426800</v>
@@ -5032,16 +5032,16 @@
         <v>43909</v>
       </c>
       <c r="B231" t="n">
-        <v>17.8758659362793</v>
+        <v>17.87586402893066</v>
       </c>
       <c r="C231" t="n">
-        <v>19.41507960150845</v>
+        <v>19.41507752992625</v>
       </c>
       <c r="D231" t="n">
-        <v>12.88216683848594</v>
+        <v>12.88216546396326</v>
       </c>
       <c r="E231" t="n">
-        <v>13.96661332273852</v>
+        <v>13.96661183250577</v>
       </c>
       <c r="F231" t="n">
         <v>3933800</v>
@@ -5072,16 +5072,16 @@
         <v>43913</v>
       </c>
       <c r="B233" t="n">
-        <v>18.95156288146973</v>
+        <v>18.95156478881836</v>
       </c>
       <c r="C233" t="n">
-        <v>20.86683434826814</v>
+        <v>20.86683644837609</v>
       </c>
       <c r="D233" t="n">
-        <v>17.49105935832638</v>
+        <v>17.49106111868505</v>
       </c>
       <c r="E233" t="n">
-        <v>19.24016529415902</v>
+        <v>19.24016723055356</v>
       </c>
       <c r="F233" t="n">
         <v>2404900</v>
@@ -5092,16 +5092,16 @@
         <v>43914</v>
       </c>
       <c r="B234" t="n">
-        <v>20.8231086730957</v>
+        <v>20.82310676574707</v>
       </c>
       <c r="C234" t="n">
-        <v>21.68891603482289</v>
+        <v>21.68891404816831</v>
       </c>
       <c r="D234" t="n">
-        <v>18.97780278152826</v>
+        <v>18.97780104320539</v>
       </c>
       <c r="E234" t="n">
-        <v>20.7356530301977</v>
+        <v>20.7356511308598</v>
       </c>
       <c r="F234" t="n">
         <v>2869200</v>
@@ -5132,16 +5132,16 @@
         <v>43916</v>
       </c>
       <c r="B236" t="n">
-        <v>25.69436836242676</v>
+        <v>25.69436645507812</v>
       </c>
       <c r="C236" t="n">
-        <v>26.2803189837644</v>
+        <v>26.28031703291938</v>
       </c>
       <c r="D236" t="n">
-        <v>22.3360861213569</v>
+        <v>22.33608446330083</v>
       </c>
       <c r="E236" t="n">
-        <v>22.73837973131053</v>
+        <v>22.73837804339134</v>
       </c>
       <c r="F236" t="n">
         <v>1725800</v>
@@ -5252,16 +5252,16 @@
         <v>43924</v>
       </c>
       <c r="B242" t="n">
-        <v>17.05378341674805</v>
+        <v>17.05378150939941</v>
       </c>
       <c r="C242" t="n">
-        <v>18.55801396889691</v>
+        <v>18.55801189331041</v>
       </c>
       <c r="D242" t="n">
-        <v>16.61650691888271</v>
+        <v>16.61650506044046</v>
       </c>
       <c r="E242" t="n">
-        <v>18.55801396889691</v>
+        <v>18.55801189331041</v>
       </c>
       <c r="F242" t="n">
         <v>2202300</v>
@@ -5272,16 +5272,16 @@
         <v>43927</v>
       </c>
       <c r="B243" t="n">
-        <v>20.12346649169922</v>
+        <v>20.12346458435059</v>
       </c>
       <c r="C243" t="n">
-        <v>21.40031318279222</v>
+        <v>21.40031115442111</v>
       </c>
       <c r="D243" t="n">
-        <v>18.24317771072155</v>
+        <v>18.24317598159103</v>
       </c>
       <c r="E243" t="n">
-        <v>18.88160105626805</v>
+        <v>18.8815992666263</v>
       </c>
       <c r="F243" t="n">
         <v>4954700</v>
@@ -5292,16 +5292,16 @@
         <v>43928</v>
       </c>
       <c r="B244" t="n">
-        <v>22.03873634338379</v>
+        <v>22.03873443603516</v>
       </c>
       <c r="C244" t="n">
-        <v>23.07945321596411</v>
+        <v>23.07945121854635</v>
       </c>
       <c r="D244" t="n">
-        <v>21.86382507554841</v>
+        <v>21.86382318333752</v>
       </c>
       <c r="E244" t="n">
-        <v>22.30110157705938</v>
+        <v>22.30109964700427</v>
       </c>
       <c r="F244" t="n">
         <v>4003700</v>
@@ -5372,16 +5372,16 @@
         <v>43935</v>
       </c>
       <c r="B248" t="n">
-        <v>21.86382675170898</v>
+        <v>21.86382484436035</v>
       </c>
       <c r="C248" t="n">
-        <v>22.69465283550497</v>
+        <v>22.69465085567703</v>
       </c>
       <c r="D248" t="n">
-        <v>21.58397003617953</v>
+        <v>21.58396815324493</v>
       </c>
       <c r="E248" t="n">
-        <v>21.95128239233134</v>
+        <v>21.95128047735329</v>
       </c>
       <c r="F248" t="n">
         <v>1384100</v>
@@ -5392,16 +5392,16 @@
         <v>43936</v>
       </c>
       <c r="B249" t="n">
-        <v>21.3390941619873</v>
+        <v>21.33909606933594</v>
       </c>
       <c r="C249" t="n">
-        <v>22.37106703153592</v>
+        <v>22.37106903112521</v>
       </c>
       <c r="D249" t="n">
-        <v>20.55199674781419</v>
+        <v>20.55199858480983</v>
       </c>
       <c r="E249" t="n">
-        <v>20.99801900506372</v>
+        <v>20.99802088192609</v>
       </c>
       <c r="F249" t="n">
         <v>1195900</v>
@@ -5452,16 +5452,16 @@
         <v>43941</v>
       </c>
       <c r="B252" t="n">
-        <v>23.58669471740723</v>
+        <v>23.58669281005859</v>
       </c>
       <c r="C252" t="n">
-        <v>23.79658724531726</v>
+        <v>23.79658532099557</v>
       </c>
       <c r="D252" t="n">
-        <v>21.03299979238556</v>
+        <v>21.03299809154262</v>
       </c>
       <c r="E252" t="n">
-        <v>21.07672844491528</v>
+        <v>21.07672674053619</v>
       </c>
       <c r="F252" t="n">
         <v>2563500</v>
@@ -5472,16 +5472,16 @@
         <v>43943</v>
       </c>
       <c r="B253" t="n">
-        <v>26.7788143157959</v>
+        <v>26.77881240844727</v>
       </c>
       <c r="C253" t="n">
-        <v>27.23358062031557</v>
+        <v>27.23357868057574</v>
       </c>
       <c r="D253" t="n">
-        <v>24.04146241788527</v>
+        <v>24.04146070550734</v>
       </c>
       <c r="E253" t="n">
-        <v>24.05020814829031</v>
+        <v>24.05020643528946</v>
       </c>
       <c r="F253" t="n">
         <v>4273300</v>
@@ -5492,16 +5492,16 @@
         <v>43944</v>
       </c>
       <c r="B254" t="n">
-        <v>25.66813087463379</v>
+        <v>25.66813278198242</v>
       </c>
       <c r="C254" t="n">
-        <v>29.38497945525573</v>
+        <v>29.38498163879612</v>
       </c>
       <c r="D254" t="n">
-        <v>25.39701991179034</v>
+        <v>25.39702179899325</v>
       </c>
       <c r="E254" t="n">
-        <v>27.98569599020734</v>
+        <v>27.98569806976971</v>
       </c>
       <c r="F254" t="n">
         <v>2837200</v>
@@ -5532,16 +5532,16 @@
         <v>43948</v>
       </c>
       <c r="B256" t="n">
-        <v>24.95974540710449</v>
+        <v>24.95974349975586</v>
       </c>
       <c r="C256" t="n">
-        <v>25.92175244920407</v>
+        <v>25.92175046834176</v>
       </c>
       <c r="D256" t="n">
-        <v>24.00648242779263</v>
+        <v>24.00648059328949</v>
       </c>
       <c r="E256" t="n">
-        <v>25.27458337786827</v>
+        <v>25.27458144646067</v>
       </c>
       <c r="F256" t="n">
         <v>2033000</v>
@@ -5552,16 +5552,16 @@
         <v>43949</v>
       </c>
       <c r="B257" t="n">
-        <v>28.33551597595215</v>
+        <v>28.33551788330078</v>
       </c>
       <c r="C257" t="n">
-        <v>28.9389562904497</v>
+        <v>28.93895823841771</v>
       </c>
       <c r="D257" t="n">
-        <v>25.58941866961391</v>
+        <v>25.58942039211449</v>
       </c>
       <c r="E257" t="n">
-        <v>25.81680262925194</v>
+        <v>25.81680436705841</v>
       </c>
       <c r="F257" t="n">
         <v>3349000</v>
@@ -5572,16 +5572,16 @@
         <v>43950</v>
       </c>
       <c r="B258" t="n">
-        <v>28.86025047302246</v>
+        <v>28.86024856567383</v>
       </c>
       <c r="C258" t="n">
-        <v>30.34699131613646</v>
+        <v>30.34698931053043</v>
       </c>
       <c r="D258" t="n">
-        <v>27.70584072099397</v>
+        <v>27.70583888993927</v>
       </c>
       <c r="E258" t="n">
-        <v>29.12261571918255</v>
+        <v>29.12261379449443</v>
       </c>
       <c r="F258" t="n">
         <v>3060300</v>
@@ -5592,16 +5592,16 @@
         <v>43951</v>
       </c>
       <c r="B259" t="n">
-        <v>27.63587379455566</v>
+        <v>27.6358757019043</v>
       </c>
       <c r="C259" t="n">
-        <v>29.00017594138851</v>
+        <v>29.00017794289736</v>
       </c>
       <c r="D259" t="n">
-        <v>27.09365022687431</v>
+        <v>27.09365209680023</v>
       </c>
       <c r="E259" t="n">
-        <v>27.98569464399006</v>
+        <v>27.98569657548233</v>
       </c>
       <c r="F259" t="n">
         <v>2013400</v>
@@ -5612,16 +5612,16 @@
         <v>43955</v>
       </c>
       <c r="B260" t="n">
-        <v>27.63587379455566</v>
+        <v>27.6358757019043</v>
       </c>
       <c r="C260" t="n">
-        <v>27.76705640458389</v>
+        <v>27.76705832098637</v>
       </c>
       <c r="D260" t="n">
-        <v>25.53694702987189</v>
+        <v>25.53694879235862</v>
       </c>
       <c r="E260" t="n">
-        <v>26.22784299899515</v>
+        <v>26.22784480916554</v>
       </c>
       <c r="F260" t="n">
         <v>1608500</v>
@@ -5632,16 +5632,16 @@
         <v>43956</v>
       </c>
       <c r="B261" t="n">
-        <v>26.46397399902344</v>
+        <v>26.46397590637207</v>
       </c>
       <c r="C261" t="n">
-        <v>28.89523194126346</v>
+        <v>28.89523402384113</v>
       </c>
       <c r="D261" t="n">
-        <v>26.2540814790432</v>
+        <v>26.25408337126416</v>
       </c>
       <c r="E261" t="n">
-        <v>28.42297252024982</v>
+        <v>28.42297456879014</v>
       </c>
       <c r="F261" t="n">
         <v>1862000</v>
@@ -5672,16 +5672,16 @@
         <v>43958</v>
       </c>
       <c r="B263" t="n">
-        <v>24.2513542175293</v>
+        <v>24.25135231018066</v>
       </c>
       <c r="C263" t="n">
-        <v>27.18110709243067</v>
+        <v>27.18110495465943</v>
       </c>
       <c r="D263" t="n">
-        <v>24.2513542175293</v>
+        <v>24.25135231018066</v>
       </c>
       <c r="E263" t="n">
-        <v>27.12863437964844</v>
+        <v>27.12863224600413</v>
       </c>
       <c r="F263" t="n">
         <v>2878900</v>
@@ -5712,16 +5712,16 @@
         <v>43962</v>
       </c>
       <c r="B265" t="n">
-        <v>21.88131523132324</v>
+        <v>21.88131713867188</v>
       </c>
       <c r="C265" t="n">
-        <v>22.42353712674469</v>
+        <v>22.42353908135768</v>
       </c>
       <c r="D265" t="n">
-        <v>21.32160020846827</v>
+        <v>21.32160206702771</v>
       </c>
       <c r="E265" t="n">
-        <v>22.10869919872098</v>
+        <v>22.1087011258902</v>
       </c>
       <c r="F265" t="n">
         <v>2649400</v>
@@ -5772,16 +5772,16 @@
         <v>43965</v>
       </c>
       <c r="B268" t="n">
-        <v>20.11471557617188</v>
+        <v>20.11471748352051</v>
       </c>
       <c r="C268" t="n">
-        <v>20.35959097499828</v>
+        <v>20.35959290556686</v>
       </c>
       <c r="D268" t="n">
-        <v>19.12647158834</v>
+        <v>19.12647340197984</v>
       </c>
       <c r="E268" t="n">
-        <v>19.58123780319305</v>
+        <v>19.58123965995543</v>
       </c>
       <c r="F268" t="n">
         <v>1812500</v>
@@ -5792,16 +5792,16 @@
         <v>43966</v>
       </c>
       <c r="B269" t="n">
-        <v>21.57522201538086</v>
+        <v>21.57522010803223</v>
       </c>
       <c r="C269" t="n">
-        <v>21.7676230698671</v>
+        <v>21.76762114550933</v>
       </c>
       <c r="D269" t="n">
-        <v>19.91357169222903</v>
+        <v>19.91356993177791</v>
       </c>
       <c r="E269" t="n">
-        <v>20.10597274671526</v>
+        <v>20.10597096925501</v>
       </c>
       <c r="F269" t="n">
         <v>3697100</v>
@@ -5872,16 +5872,16 @@
         <v>43972</v>
       </c>
       <c r="B273" t="n">
-        <v>23.44676399230957</v>
+        <v>23.4467658996582</v>
       </c>
       <c r="C273" t="n">
-        <v>24.24260703894648</v>
+        <v>24.24260901103539</v>
       </c>
       <c r="D273" t="n">
-        <v>23.03572470859868</v>
+        <v>23.03572658251007</v>
       </c>
       <c r="E273" t="n">
-        <v>23.35056430263609</v>
+        <v>23.35056620215907</v>
       </c>
       <c r="F273" t="n">
         <v>1207900</v>
@@ -5892,16 +5892,16 @@
         <v>43973</v>
       </c>
       <c r="B274" t="n">
-        <v>22.33608436584473</v>
+        <v>22.33608245849609</v>
       </c>
       <c r="C274" t="n">
-        <v>23.33307424961244</v>
+        <v>23.3330722571277</v>
       </c>
       <c r="D274" t="n">
-        <v>22.12619017845182</v>
+        <v>22.12618828902671</v>
       </c>
       <c r="E274" t="n">
-        <v>22.78210492684163</v>
+        <v>22.78210298140589</v>
       </c>
       <c r="F274" t="n">
         <v>1380900</v>
@@ -5972,16 +5972,16 @@
         <v>43979</v>
       </c>
       <c r="B278" t="n">
-        <v>25.36203575134277</v>
+        <v>25.36203765869141</v>
       </c>
       <c r="C278" t="n">
-        <v>26.29780714837925</v>
+        <v>26.29780912610245</v>
       </c>
       <c r="D278" t="n">
-        <v>24.60991967458716</v>
+        <v>24.609921525373</v>
       </c>
       <c r="E278" t="n">
-        <v>25.18712449272325</v>
+        <v>25.1871263869177</v>
       </c>
       <c r="F278" t="n">
         <v>2478400</v>
@@ -6012,16 +6012,16 @@
         <v>43983</v>
       </c>
       <c r="B280" t="n">
-        <v>25.14339828491211</v>
+        <v>25.14340019226074</v>
       </c>
       <c r="C280" t="n">
-        <v>25.99171407871257</v>
+        <v>25.99171605041344</v>
       </c>
       <c r="D280" t="n">
-        <v>24.96848702091653</v>
+        <v>24.9684889149966</v>
       </c>
       <c r="E280" t="n">
-        <v>25.08217984293689</v>
+        <v>25.08218174564156</v>
       </c>
       <c r="F280" t="n">
         <v>1604400</v>
@@ -6052,16 +6052,16 @@
         <v>43985</v>
       </c>
       <c r="B282" t="n">
-        <v>28.53666496276855</v>
+        <v>28.53666305541992</v>
       </c>
       <c r="C282" t="n">
-        <v>29.07888688177911</v>
+        <v>29.07888493818917</v>
       </c>
       <c r="D282" t="n">
-        <v>27.17236109902872</v>
+        <v>27.17235928286815</v>
       </c>
       <c r="E282" t="n">
-        <v>27.17236109902872</v>
+        <v>27.17235928286815</v>
       </c>
       <c r="F282" t="n">
         <v>3286900</v>
@@ -6112,16 +6112,16 @@
         <v>43990</v>
       </c>
       <c r="B285" t="n">
-        <v>30.56562805175781</v>
+        <v>30.56562995910645</v>
       </c>
       <c r="C285" t="n">
-        <v>31.23903426285709</v>
+        <v>31.23903621222744</v>
       </c>
       <c r="D285" t="n">
-        <v>29.14885312428081</v>
+        <v>29.14885494322021</v>
       </c>
       <c r="E285" t="n">
-        <v>30.8717202676416</v>
+        <v>30.87172219409092</v>
       </c>
       <c r="F285" t="n">
         <v>7141600</v>
@@ -6152,16 +6152,16 @@
         <v>43992</v>
       </c>
       <c r="B287" t="n">
-        <v>27.99443817138672</v>
+        <v>27.99444007873535</v>
       </c>
       <c r="C287" t="n">
-        <v>30.2507863603505</v>
+        <v>30.25078842143119</v>
       </c>
       <c r="D287" t="n">
-        <v>27.43472649105112</v>
+        <v>27.43472836026485</v>
       </c>
       <c r="E287" t="n">
-        <v>29.99716520680253</v>
+        <v>29.99716725060322</v>
       </c>
       <c r="F287" t="n">
         <v>3410700</v>
@@ -6232,16 +6232,16 @@
         <v>43999</v>
       </c>
       <c r="B291" t="n">
-        <v>29.47243499755859</v>
+        <v>29.47243690490723</v>
       </c>
       <c r="C291" t="n">
-        <v>29.77852719471731</v>
+        <v>29.77852912187512</v>
       </c>
       <c r="D291" t="n">
-        <v>28.11687859618397</v>
+        <v>28.11688041580593</v>
       </c>
       <c r="E291" t="n">
-        <v>28.51042475362954</v>
+        <v>28.51042659872037</v>
       </c>
       <c r="F291" t="n">
         <v>1934300</v>
@@ -6272,16 +6272,16 @@
         <v>44001</v>
       </c>
       <c r="B293" t="n">
-        <v>30.71430206298828</v>
+        <v>30.71430397033691</v>
       </c>
       <c r="C293" t="n">
-        <v>30.71430206298828</v>
+        <v>30.71430397033691</v>
       </c>
       <c r="D293" t="n">
-        <v>29.26254413905392</v>
+        <v>29.26254595624884</v>
       </c>
       <c r="E293" t="n">
-        <v>29.76978650744496</v>
+        <v>29.76978835613947</v>
       </c>
       <c r="F293" t="n">
         <v>2489900</v>
@@ -6332,16 +6332,16 @@
         <v>44006</v>
       </c>
       <c r="B296" t="n">
-        <v>29.17508697509766</v>
+        <v>29.17508888244629</v>
       </c>
       <c r="C296" t="n">
-        <v>29.4724351118426</v>
+        <v>29.47243703863064</v>
       </c>
       <c r="D296" t="n">
-        <v>28.01192994907473</v>
+        <v>28.01193178038088</v>
       </c>
       <c r="E296" t="n">
-        <v>29.4724351118426</v>
+        <v>29.47243703863064</v>
       </c>
       <c r="F296" t="n">
         <v>2563900</v>
@@ -6392,16 +6392,16 @@
         <v>44011</v>
       </c>
       <c r="B299" t="n">
-        <v>29.47243499755859</v>
+        <v>29.47243690490723</v>
       </c>
       <c r="C299" t="n">
-        <v>29.47243499755859</v>
+        <v>29.47243690490723</v>
       </c>
       <c r="D299" t="n">
-        <v>27.63587347421944</v>
+        <v>27.6358752627125</v>
       </c>
       <c r="E299" t="n">
-        <v>27.84576598144715</v>
+        <v>27.84576778352368</v>
       </c>
       <c r="F299" t="n">
         <v>1781900</v>
@@ -6492,16 +6492,16 @@
         <v>44018</v>
       </c>
       <c r="B304" t="n">
-        <v>28.16060829162598</v>
+        <v>28.16060638427734</v>
       </c>
       <c r="C304" t="n">
-        <v>29.29752656575252</v>
+        <v>29.29752458139918</v>
       </c>
       <c r="D304" t="n">
-        <v>28.02067993998202</v>
+        <v>28.02067804211088</v>
       </c>
       <c r="E304" t="n">
-        <v>28.86899411225568</v>
+        <v>28.86899215692731</v>
       </c>
       <c r="F304" t="n">
         <v>1899100</v>
@@ -6512,16 +6512,16 @@
         <v>44019</v>
       </c>
       <c r="B305" t="n">
-        <v>28.3967342376709</v>
+        <v>28.39673614501953</v>
       </c>
       <c r="C305" t="n">
-        <v>29.46368652613916</v>
+        <v>29.46368850515272</v>
       </c>
       <c r="D305" t="n">
-        <v>27.96820184111028</v>
+        <v>27.96820371967529</v>
       </c>
       <c r="E305" t="n">
-        <v>27.98569329976118</v>
+        <v>27.98569517950106</v>
       </c>
       <c r="F305" t="n">
         <v>2271100</v>
@@ -6552,16 +6552,16 @@
         <v>44021</v>
       </c>
       <c r="B307" t="n">
-        <v>29.66483688354492</v>
+        <v>29.66483879089355</v>
       </c>
       <c r="C307" t="n">
-        <v>30.27702466573552</v>
+        <v>30.27702661244576</v>
       </c>
       <c r="D307" t="n">
-        <v>28.95645107137374</v>
+        <v>28.95645293317557</v>
       </c>
       <c r="E307" t="n">
-        <v>29.21007224824849</v>
+        <v>29.2100741263573</v>
       </c>
       <c r="F307" t="n">
         <v>1551300</v>
@@ -6612,16 +6612,16 @@
         <v>44026</v>
       </c>
       <c r="B310" t="n">
-        <v>28.41422653198242</v>
+        <v>28.41422843933105</v>
       </c>
       <c r="C310" t="n">
-        <v>28.83401154348613</v>
+        <v>28.83401347901348</v>
       </c>
       <c r="D310" t="n">
-        <v>27.36476233514578</v>
+        <v>27.36476417204751</v>
       </c>
       <c r="E310" t="n">
-        <v>28.51042455315965</v>
+        <v>28.51042646696572</v>
       </c>
       <c r="F310" t="n">
         <v>1676500</v>
@@ -6692,16 +6692,16 @@
         <v>44032</v>
       </c>
       <c r="B314" t="n">
-        <v>29.03515815734863</v>
+        <v>29.03516006469727</v>
       </c>
       <c r="C314" t="n">
-        <v>29.06139367787261</v>
+        <v>29.06139558694468</v>
       </c>
       <c r="D314" t="n">
-        <v>27.82827417092524</v>
+        <v>27.82827599899246</v>
       </c>
       <c r="E314" t="n">
-        <v>28.1606052208993</v>
+        <v>28.16060707079768</v>
       </c>
       <c r="F314" t="n">
         <v>1808200</v>
@@ -6712,16 +6712,16 @@
         <v>44033</v>
       </c>
       <c r="B315" t="n">
-        <v>28.75530242919922</v>
+        <v>28.75530052185059</v>
       </c>
       <c r="C315" t="n">
-        <v>29.41996121482692</v>
+        <v>29.41995926339126</v>
       </c>
       <c r="D315" t="n">
-        <v>28.24806010804126</v>
+        <v>28.24805823433818</v>
       </c>
       <c r="E315" t="n">
-        <v>29.20132297353225</v>
+        <v>29.20132103659892</v>
       </c>
       <c r="F315" t="n">
         <v>1290100</v>
@@ -6732,16 +6732,16 @@
         <v>44034</v>
       </c>
       <c r="B316" t="n">
-        <v>28.11687850952148</v>
+        <v>28.11688041687012</v>
       </c>
       <c r="C316" t="n">
-        <v>28.69408331963795</v>
+        <v>28.6940852661421</v>
       </c>
       <c r="D316" t="n">
-        <v>27.92447579409775</v>
+        <v>27.92447768839448</v>
       </c>
       <c r="E316" t="n">
-        <v>28.58913456423152</v>
+        <v>28.58913650361632</v>
       </c>
       <c r="F316" t="n">
         <v>1990600</v>
@@ -6772,16 +6772,16 @@
         <v>44036</v>
       </c>
       <c r="B318" t="n">
-        <v>26.15788269042969</v>
+        <v>26.15788078308105</v>
       </c>
       <c r="C318" t="n">
-        <v>26.66512341400575</v>
+        <v>26.66512146967075</v>
       </c>
       <c r="D318" t="n">
-        <v>25.44949515724604</v>
+        <v>25.44949330155075</v>
       </c>
       <c r="E318" t="n">
-        <v>26.66512341400575</v>
+        <v>26.66512146967075</v>
       </c>
       <c r="F318" t="n">
         <v>3685600</v>
@@ -6792,16 +6792,16 @@
         <v>44039</v>
       </c>
       <c r="B319" t="n">
-        <v>25.14339828491211</v>
+        <v>25.14340019226074</v>
       </c>
       <c r="C319" t="n">
-        <v>26.54268339264445</v>
+        <v>26.5426854061412</v>
       </c>
       <c r="D319" t="n">
-        <v>24.75859450496829</v>
+        <v>24.75859638312616</v>
       </c>
       <c r="E319" t="n">
-        <v>26.22784378468338</v>
+        <v>26.22784577429677</v>
       </c>
       <c r="F319" t="n">
         <v>2575800</v>
@@ -6812,16 +6812,16 @@
         <v>44040</v>
       </c>
       <c r="B320" t="n">
-        <v>24.63615989685059</v>
+        <v>24.63615798950195</v>
       </c>
       <c r="C320" t="n">
-        <v>25.18712759360217</v>
+        <v>25.18712564359724</v>
       </c>
       <c r="D320" t="n">
-        <v>24.35630318306708</v>
+        <v>24.35630129738515</v>
       </c>
       <c r="E320" t="n">
-        <v>24.92476234144953</v>
+        <v>24.9247604117571</v>
       </c>
       <c r="F320" t="n">
         <v>2550000</v>
@@ -6872,16 +6872,16 @@
         <v>44043</v>
       </c>
       <c r="B323" t="n">
-        <v>25.45823669433594</v>
+        <v>25.45823860168457</v>
       </c>
       <c r="C323" t="n">
-        <v>25.79931180818481</v>
+        <v>25.79931374108703</v>
       </c>
       <c r="D323" t="n">
-        <v>24.95099605432184</v>
+        <v>24.95099792366765</v>
       </c>
       <c r="E323" t="n">
-        <v>25.79931180818481</v>
+        <v>25.79931374108703</v>
       </c>
       <c r="F323" t="n">
         <v>1806700</v>
@@ -6892,16 +6892,16 @@
         <v>44046</v>
       </c>
       <c r="B324" t="n">
-        <v>25.67687797546387</v>
+        <v>25.67687606811523</v>
       </c>
       <c r="C324" t="n">
-        <v>26.24533712199452</v>
+        <v>26.24533517241919</v>
       </c>
       <c r="D324" t="n">
-        <v>25.29207416799552</v>
+        <v>25.29207228923116</v>
       </c>
       <c r="E324" t="n">
-        <v>25.53694962148948</v>
+        <v>25.53694772453511</v>
       </c>
       <c r="F324" t="n">
         <v>1504200</v>
@@ -6912,16 +6912,16 @@
         <v>44047</v>
       </c>
       <c r="B325" t="n">
-        <v>25.59816932678223</v>
+        <v>25.59816741943359</v>
       </c>
       <c r="C325" t="n">
-        <v>25.95673595998589</v>
+        <v>25.95673402592005</v>
       </c>
       <c r="D325" t="n">
-        <v>25.2046197693257</v>
+        <v>25.20461789130089</v>
       </c>
       <c r="E325" t="n">
-        <v>25.2046197693257</v>
+        <v>25.20461789130089</v>
       </c>
       <c r="F325" t="n">
         <v>2035900</v>
@@ -6932,16 +6932,16 @@
         <v>44048</v>
       </c>
       <c r="B326" t="n">
-        <v>25.96548080444336</v>
+        <v>25.96547889709473</v>
       </c>
       <c r="C326" t="n">
-        <v>26.21910032430609</v>
+        <v>26.21909839832731</v>
       </c>
       <c r="D326" t="n">
-        <v>25.60691418348315</v>
+        <v>25.60691230247378</v>
       </c>
       <c r="E326" t="n">
-        <v>25.71185961650304</v>
+        <v>25.71185772778469</v>
       </c>
       <c r="F326" t="n">
         <v>1719300</v>
@@ -6992,16 +6992,16 @@
         <v>44053</v>
       </c>
       <c r="B329" t="n">
-        <v>25.26583480834961</v>
+        <v>25.26583671569824</v>
       </c>
       <c r="C329" t="n">
-        <v>26.34153623084183</v>
+        <v>26.34153821939647</v>
       </c>
       <c r="D329" t="n">
-        <v>25.04719656551356</v>
+        <v>25.04719845635692</v>
       </c>
       <c r="E329" t="n">
-        <v>26.219097680561</v>
+        <v>26.2190996598726</v>
       </c>
       <c r="F329" t="n">
         <v>1821300</v>
@@ -7012,16 +7012,16 @@
         <v>44054</v>
       </c>
       <c r="B330" t="n">
-        <v>26.04418754577637</v>
+        <v>26.044189453125</v>
       </c>
       <c r="C330" t="n">
-        <v>26.98870466847201</v>
+        <v>26.98870664499245</v>
       </c>
       <c r="D330" t="n">
-        <v>25.20461584333725</v>
+        <v>25.20461768919977</v>
       </c>
       <c r="E330" t="n">
-        <v>25.44949127073145</v>
+        <v>25.44949313452744</v>
       </c>
       <c r="F330" t="n">
         <v>2049400</v>
@@ -7092,16 +7092,16 @@
         <v>44060</v>
       </c>
       <c r="B334" t="n">
-        <v>23.9627513885498</v>
+        <v>23.96275329589844</v>
       </c>
       <c r="C334" t="n">
-        <v>26.4552277224635</v>
+        <v>26.45522982820427</v>
       </c>
       <c r="D334" t="n">
-        <v>23.39429228350079</v>
+        <v>23.39429414560212</v>
       </c>
       <c r="E334" t="n">
-        <v>25.79931298554292</v>
+        <v>25.79931503907524</v>
       </c>
       <c r="F334" t="n">
         <v>3495400</v>
@@ -7112,16 +7112,16 @@
         <v>44061</v>
       </c>
       <c r="B335" t="n">
-        <v>24.90727043151855</v>
+        <v>24.90726852416992</v>
       </c>
       <c r="C335" t="n">
-        <v>25.03845305523375</v>
+        <v>25.03845113783942</v>
       </c>
       <c r="D335" t="n">
-        <v>23.93651768156406</v>
+        <v>23.93651584855371</v>
       </c>
       <c r="E335" t="n">
-        <v>23.96275320546056</v>
+        <v>23.96275137044115</v>
       </c>
       <c r="F335" t="n">
         <v>2792800</v>
@@ -7152,16 +7152,16 @@
         <v>44063</v>
       </c>
       <c r="B337" t="n">
-        <v>23.87529754638672</v>
+        <v>23.87529563903809</v>
       </c>
       <c r="C337" t="n">
-        <v>23.9714989154645</v>
+        <v>23.97149700043054</v>
       </c>
       <c r="D337" t="n">
-        <v>23.26311141355075</v>
+        <v>23.26310955510841</v>
       </c>
       <c r="E337" t="n">
-        <v>23.64791522178433</v>
+        <v>23.6479133326008</v>
       </c>
       <c r="F337" t="n">
         <v>2411800</v>
@@ -7252,16 +7252,16 @@
         <v>44070</v>
       </c>
       <c r="B342" t="n">
-        <v>26.66512107849121</v>
+        <v>26.66511917114258</v>
       </c>
       <c r="C342" t="n">
-        <v>26.90125079156311</v>
+        <v>26.90124886732418</v>
       </c>
       <c r="D342" t="n">
-        <v>25.44074719793404</v>
+        <v>25.44074537816453</v>
       </c>
       <c r="E342" t="n">
-        <v>25.60691273691917</v>
+        <v>25.60691090526388</v>
       </c>
       <c r="F342" t="n">
         <v>2287100</v>
@@ -7272,16 +7272,16 @@
         <v>44071</v>
       </c>
       <c r="B343" t="n">
-        <v>26.62139129638672</v>
+        <v>26.62139511108398</v>
       </c>
       <c r="C343" t="n">
-        <v>26.99744931809544</v>
+        <v>26.99745318667973</v>
       </c>
       <c r="D343" t="n">
-        <v>25.88676671167138</v>
+        <v>25.88677042110103</v>
       </c>
       <c r="E343" t="n">
-        <v>26.66511827506467</v>
+        <v>26.66512209602777</v>
       </c>
       <c r="F343" t="n">
         <v>1984400</v>
@@ -7292,16 +7292,16 @@
         <v>44074</v>
       </c>
       <c r="B344" t="n">
-        <v>26.56891822814941</v>
+        <v>26.56892013549805</v>
       </c>
       <c r="C344" t="n">
-        <v>26.84003084714579</v>
+        <v>26.84003277395725</v>
       </c>
       <c r="D344" t="n">
-        <v>26.00045913696676</v>
+        <v>26.00046100350644</v>
       </c>
       <c r="E344" t="n">
-        <v>26.38526290696871</v>
+        <v>26.38526480113296</v>
       </c>
       <c r="F344" t="n">
         <v>2254500</v>
@@ -7332,16 +7332,16 @@
         <v>44076</v>
       </c>
       <c r="B346" t="n">
-        <v>27.85451126098633</v>
+        <v>27.85451507568359</v>
       </c>
       <c r="C346" t="n">
-        <v>28.37924335461506</v>
+        <v>28.3792472411748</v>
       </c>
       <c r="D346" t="n">
-        <v>27.50469042125962</v>
+        <v>27.50469418804865</v>
       </c>
       <c r="E346" t="n">
-        <v>28.08189522382802</v>
+        <v>28.0818990696657</v>
       </c>
       <c r="F346" t="n">
         <v>1806800</v>
@@ -7352,16 +7352,16 @@
         <v>44077</v>
       </c>
       <c r="B347" t="n">
-        <v>27.37350654602051</v>
+        <v>27.37350845336914</v>
       </c>
       <c r="C347" t="n">
-        <v>28.26555095139155</v>
+        <v>28.26555292089662</v>
       </c>
       <c r="D347" t="n">
-        <v>26.84877611281624</v>
+        <v>26.84877798360237</v>
       </c>
       <c r="E347" t="n">
-        <v>28.07314823567778</v>
+        <v>28.07315019177649</v>
       </c>
       <c r="F347" t="n">
         <v>2237800</v>
@@ -7372,16 +7372,16 @@
         <v>44078</v>
       </c>
       <c r="B348" t="n">
-        <v>27.08490371704102</v>
+        <v>27.08490562438965</v>
       </c>
       <c r="C348" t="n">
-        <v>27.65336445758641</v>
+        <v>27.65336640496668</v>
       </c>
       <c r="D348" t="n">
-        <v>25.93049411311761</v>
+        <v>25.93049593917146</v>
       </c>
       <c r="E348" t="n">
-        <v>27.5396716422464</v>
+        <v>27.53967358162028</v>
       </c>
       <c r="F348" t="n">
         <v>2510700</v>
@@ -7452,16 +7452,16 @@
         <v>44085</v>
       </c>
       <c r="B352" t="n">
-        <v>24.74985122680664</v>
+        <v>24.74984741210938</v>
       </c>
       <c r="C352" t="n">
-        <v>26.08791802511944</v>
+        <v>26.08791400418579</v>
       </c>
       <c r="D352" t="n">
-        <v>24.5924330753089</v>
+        <v>24.59242928487451</v>
       </c>
       <c r="E352" t="n">
-        <v>26.04419103882745</v>
+        <v>26.04418702463344</v>
       </c>
       <c r="F352" t="n">
         <v>1642200</v>
@@ -7472,16 +7472,16 @@
         <v>44088</v>
       </c>
       <c r="B353" t="n">
-        <v>25.5544376373291</v>
+        <v>25.55443954467773</v>
       </c>
       <c r="C353" t="n">
-        <v>25.84304005583825</v>
+        <v>25.84304198472778</v>
       </c>
       <c r="D353" t="n">
-        <v>24.88103310619272</v>
+        <v>24.88103496327935</v>
       </c>
       <c r="E353" t="n">
-        <v>25.09967135258078</v>
+        <v>25.09967322598628</v>
       </c>
       <c r="F353" t="n">
         <v>899700</v>
@@ -7492,16 +7492,16 @@
         <v>44089</v>
       </c>
       <c r="B354" t="n">
-        <v>25.52820205688477</v>
+        <v>25.5282039642334</v>
       </c>
       <c r="C354" t="n">
-        <v>25.96547854865974</v>
+        <v>25.96548048867964</v>
       </c>
       <c r="D354" t="n">
-        <v>24.9422514911832</v>
+        <v>24.94225335475233</v>
       </c>
       <c r="E354" t="n">
-        <v>25.6244017507826</v>
+        <v>25.62440366531883</v>
       </c>
       <c r="F354" t="n">
         <v>1187000</v>
@@ -7552,16 +7552,16 @@
         <v>44092</v>
       </c>
       <c r="B357" t="n">
-        <v>24.02396965026855</v>
+        <v>24.02397155761719</v>
       </c>
       <c r="C357" t="n">
-        <v>24.96848679762768</v>
+        <v>24.96848877996489</v>
       </c>
       <c r="D357" t="n">
-        <v>23.78784161448684</v>
+        <v>23.78784350308843</v>
       </c>
       <c r="E357" t="n">
-        <v>24.80232293320303</v>
+        <v>24.80232490234791</v>
       </c>
       <c r="F357" t="n">
         <v>1344400</v>
@@ -7572,16 +7572,16 @@
         <v>44095</v>
       </c>
       <c r="B358" t="n">
-        <v>23.42927742004395</v>
+        <v>23.42927551269531</v>
       </c>
       <c r="C358" t="n">
-        <v>23.75286112008121</v>
+        <v>23.75285918639003</v>
       </c>
       <c r="D358" t="n">
-        <v>22.87830805478197</v>
+        <v>22.87830619228708</v>
       </c>
       <c r="E358" t="n">
-        <v>23.49049586772248</v>
+        <v>23.49049395539013</v>
       </c>
       <c r="F358" t="n">
         <v>1701600</v>
@@ -7592,16 +7592,16 @@
         <v>44096</v>
       </c>
       <c r="B359" t="n">
-        <v>23.06196212768555</v>
+        <v>23.06196403503418</v>
       </c>
       <c r="C359" t="n">
-        <v>23.79658507431088</v>
+        <v>23.79658704241679</v>
       </c>
       <c r="D359" t="n">
-        <v>22.9132880588034</v>
+        <v>22.91328995385588</v>
       </c>
       <c r="E359" t="n">
-        <v>23.53421985537879</v>
+        <v>23.53422180178568</v>
       </c>
       <c r="F359" t="n">
         <v>1853300</v>
@@ -7612,16 +7612,16 @@
         <v>44097</v>
       </c>
       <c r="B360" t="n">
-        <v>22.91329002380371</v>
+        <v>22.91328811645508</v>
       </c>
       <c r="C360" t="n">
-        <v>23.32432934686791</v>
+        <v>23.32432740530353</v>
       </c>
       <c r="D360" t="n">
-        <v>22.51974049357813</v>
+        <v>22.51973861898936</v>
       </c>
       <c r="E360" t="n">
-        <v>23.06196410543587</v>
+        <v>23.06196218571131</v>
       </c>
       <c r="F360" t="n">
         <v>3121100</v>
@@ -7652,16 +7652,16 @@
         <v>44099</v>
       </c>
       <c r="B362" t="n">
-        <v>22.38855743408203</v>
+        <v>22.3885555267334</v>
       </c>
       <c r="C362" t="n">
-        <v>22.96576228838224</v>
+        <v>22.96576033185978</v>
       </c>
       <c r="D362" t="n">
-        <v>22.18741064172113</v>
+        <v>22.18740875150879</v>
       </c>
       <c r="E362" t="n">
-        <v>22.84332540052386</v>
+        <v>22.84332345443217</v>
       </c>
       <c r="F362" t="n">
         <v>3181400</v>
@@ -7692,16 +7692,16 @@
         <v>44103</v>
       </c>
       <c r="B364" t="n">
-        <v>21.82009506225586</v>
+        <v>21.82009696960449</v>
       </c>
       <c r="C364" t="n">
-        <v>22.29235275090032</v>
+        <v>22.29235469953017</v>
       </c>
       <c r="D364" t="n">
-        <v>21.55772819694027</v>
+        <v>21.55773008135477</v>
       </c>
       <c r="E364" t="n">
-        <v>22.29235275090032</v>
+        <v>22.29235469953017</v>
       </c>
       <c r="F364" t="n">
         <v>1168900</v>
@@ -7732,16 +7732,16 @@
         <v>44105</v>
       </c>
       <c r="B366" t="n">
-        <v>22.92203330993652</v>
+        <v>22.92203521728516</v>
       </c>
       <c r="C366" t="n">
-        <v>23.02698040380185</v>
+        <v>23.02698231988316</v>
       </c>
       <c r="D366" t="n">
-        <v>21.82009799877666</v>
+        <v>21.82009981443295</v>
       </c>
       <c r="E366" t="n">
-        <v>22.30110148113886</v>
+        <v>22.30110333681959</v>
       </c>
       <c r="F366" t="n">
         <v>1386900</v>
@@ -7812,16 +7812,16 @@
         <v>44111</v>
       </c>
       <c r="B370" t="n">
-        <v>21.3828239440918</v>
+        <v>21.38282012939453</v>
       </c>
       <c r="C370" t="n">
-        <v>21.77637183791135</v>
+        <v>21.77636795300511</v>
       </c>
       <c r="D370" t="n">
-        <v>21.07673002573593</v>
+        <v>21.07672626564584</v>
       </c>
       <c r="E370" t="n">
-        <v>21.60146221890632</v>
+        <v>21.60145836520397</v>
       </c>
       <c r="F370" t="n">
         <v>1798600</v>
@@ -7832,16 +7832,16 @@
         <v>44112</v>
       </c>
       <c r="B371" t="n">
-        <v>21.531494140625</v>
+        <v>21.53149604797363</v>
       </c>
       <c r="C371" t="n">
-        <v>21.67142247773394</v>
+        <v>21.67142439747801</v>
       </c>
       <c r="D371" t="n">
-        <v>21.09421767014021</v>
+        <v>21.09421953875309</v>
       </c>
       <c r="E371" t="n">
-        <v>21.48776549273011</v>
+        <v>21.48776739620508</v>
       </c>
       <c r="F371" t="n">
         <v>1373200</v>
@@ -7952,16 +7952,16 @@
         <v>44123</v>
       </c>
       <c r="B377" t="n">
-        <v>22.78210258483887</v>
+        <v>22.7821044921875</v>
       </c>
       <c r="C377" t="n">
-        <v>22.9745052921571</v>
+        <v>22.97450721561395</v>
       </c>
       <c r="D377" t="n">
-        <v>21.75013155464405</v>
+        <v>21.75013337559466</v>
       </c>
       <c r="E377" t="n">
-        <v>21.85507696947464</v>
+        <v>21.85507879921143</v>
       </c>
       <c r="F377" t="n">
         <v>2183200</v>
@@ -7992,16 +7992,16 @@
         <v>44125</v>
       </c>
       <c r="B379" t="n">
-        <v>21.86382675170898</v>
+        <v>21.86382484436035</v>
       </c>
       <c r="C379" t="n">
-        <v>22.4235401827679</v>
+        <v>22.42353822659119</v>
       </c>
       <c r="D379" t="n">
-        <v>21.86382675170898</v>
+        <v>21.86382484436035</v>
       </c>
       <c r="E379" t="n">
-        <v>22.37981319649553</v>
+        <v>22.37981124413345</v>
       </c>
       <c r="F379" t="n">
         <v>1597600</v>
@@ -8012,16 +8012,16 @@
         <v>44126</v>
       </c>
       <c r="B380" t="n">
-        <v>22.0737190246582</v>
+        <v>22.07371711730957</v>
       </c>
       <c r="C380" t="n">
-        <v>22.17866612576683</v>
+        <v>22.17866420934991</v>
       </c>
       <c r="D380" t="n">
-        <v>21.47027694645817</v>
+        <v>21.47027509125183</v>
       </c>
       <c r="E380" t="n">
-        <v>21.91629920703405</v>
+        <v>21.91629731328777</v>
       </c>
       <c r="F380" t="n">
         <v>2196600</v>
@@ -8052,16 +8052,16 @@
         <v>44130</v>
       </c>
       <c r="B382" t="n">
-        <v>22.08246231079102</v>
+        <v>22.08246421813965</v>
       </c>
       <c r="C382" t="n">
-        <v>22.58095723269669</v>
+        <v>22.58095918310227</v>
       </c>
       <c r="D382" t="n">
-        <v>21.64518582938921</v>
+        <v>21.64518769896857</v>
       </c>
       <c r="E382" t="n">
-        <v>22.20489919179875</v>
+        <v>22.20490110972274</v>
       </c>
       <c r="F382" t="n">
         <v>1812600</v>
@@ -8152,16 +8152,16 @@
         <v>44138</v>
       </c>
       <c r="B387" t="n">
-        <v>20.49077796936035</v>
+        <v>20.49077987670898</v>
       </c>
       <c r="C387" t="n">
-        <v>20.67443330686146</v>
+        <v>20.67443523130533</v>
       </c>
       <c r="D387" t="n">
-        <v>19.99228300405444</v>
+        <v>19.99228486500153</v>
       </c>
       <c r="E387" t="n">
-        <v>20.4033223318504</v>
+        <v>20.40332423105838</v>
       </c>
       <c r="F387" t="n">
         <v>1832100</v>
@@ -8172,16 +8172,16 @@
         <v>44139</v>
       </c>
       <c r="B388" t="n">
-        <v>21.72389602661133</v>
+        <v>21.72389793395996</v>
       </c>
       <c r="C388" t="n">
-        <v>21.77636873803556</v>
+        <v>21.77637064999127</v>
       </c>
       <c r="D388" t="n">
-        <v>20.53450344714602</v>
+        <v>20.53450525006649</v>
       </c>
       <c r="E388" t="n">
-        <v>20.87558024159705</v>
+        <v>20.87558207446392</v>
       </c>
       <c r="F388" t="n">
         <v>1697200</v>
@@ -8192,16 +8192,16 @@
         <v>44140</v>
       </c>
       <c r="B389" t="n">
-        <v>22.30109977722168</v>
+        <v>22.30110168457031</v>
       </c>
       <c r="C389" t="n">
-        <v>22.32733696570272</v>
+        <v>22.32733887529535</v>
       </c>
       <c r="D389" t="n">
-        <v>21.45278403326266</v>
+        <v>21.4527858680573</v>
       </c>
       <c r="E389" t="n">
-        <v>22.05622435563062</v>
+        <v>22.05622624203577</v>
       </c>
       <c r="F389" t="n">
         <v>1467100</v>
@@ -8212,16 +8212,16 @@
         <v>44141</v>
       </c>
       <c r="B390" t="n">
-        <v>22.06497192382812</v>
+        <v>22.06497001647949</v>
       </c>
       <c r="C390" t="n">
-        <v>22.44102998300715</v>
+        <v>22.44102804315117</v>
       </c>
       <c r="D390" t="n">
-        <v>21.5664769776894</v>
+        <v>21.56647511343186</v>
       </c>
       <c r="E390" t="n">
-        <v>21.92504357642348</v>
+        <v>21.92504168117059</v>
       </c>
       <c r="F390" t="n">
         <v>935600</v>
@@ -8232,16 +8232,16 @@
         <v>44144</v>
       </c>
       <c r="B391" t="n">
-        <v>24.47873878479004</v>
+        <v>24.47873687744141</v>
       </c>
       <c r="C391" t="n">
-        <v>24.55744868989206</v>
+        <v>24.55744677641046</v>
       </c>
       <c r="D391" t="n">
-        <v>22.72963274799409</v>
+        <v>22.72963097693332</v>
       </c>
       <c r="E391" t="n">
-        <v>23.00948944698904</v>
+        <v>23.00948765412223</v>
       </c>
       <c r="F391" t="n">
         <v>4038900</v>
@@ -8252,16 +8252,16 @@
         <v>44145</v>
       </c>
       <c r="B392" t="n">
-        <v>24.27758979797363</v>
+        <v>24.27759170532227</v>
       </c>
       <c r="C392" t="n">
-        <v>24.89852158427205</v>
+        <v>24.89852354040367</v>
       </c>
       <c r="D392" t="n">
-        <v>23.78784061897008</v>
+        <v>23.78784248784197</v>
       </c>
       <c r="E392" t="n">
-        <v>24.17264271129134</v>
+        <v>24.17264461039489</v>
       </c>
       <c r="F392" t="n">
         <v>3009700</v>
@@ -8292,16 +8292,16 @@
         <v>44147</v>
       </c>
       <c r="B394" t="n">
-        <v>23.74411392211914</v>
+        <v>23.74411582946777</v>
       </c>
       <c r="C394" t="n">
-        <v>24.57493995004803</v>
+        <v>24.57494192413636</v>
       </c>
       <c r="D394" t="n">
-        <v>23.15816333785121</v>
+        <v>23.15816519813083</v>
       </c>
       <c r="E394" t="n">
-        <v>23.65665828737755</v>
+        <v>23.65666018770093</v>
       </c>
       <c r="F394" t="n">
         <v>3176300</v>
@@ -8312,16 +8312,16 @@
         <v>44148</v>
       </c>
       <c r="B395" t="n">
-        <v>25.1871223449707</v>
+        <v>25.18712425231934</v>
       </c>
       <c r="C395" t="n">
-        <v>25.34454213068932</v>
+        <v>25.3445440499589</v>
       </c>
       <c r="D395" t="n">
-        <v>23.17565138275495</v>
+        <v>23.17565313778064</v>
       </c>
       <c r="E395" t="n">
-        <v>23.612927823939</v>
+        <v>23.61292961207839</v>
       </c>
       <c r="F395" t="n">
         <v>2680000</v>
@@ -8432,16 +8432,16 @@
         <v>44159</v>
       </c>
       <c r="B401" t="n">
-        <v>24.47873878479004</v>
+        <v>24.47873687744141</v>
       </c>
       <c r="C401" t="n">
-        <v>24.97723373838448</v>
+        <v>24.97723179219383</v>
       </c>
       <c r="D401" t="n">
-        <v>23.95400664013575</v>
+        <v>23.95400477367351</v>
       </c>
       <c r="E401" t="n">
-        <v>24.85479684959357</v>
+        <v>24.85479491294302</v>
       </c>
       <c r="F401" t="n">
         <v>2384200</v>
@@ -8452,16 +8452,16 @@
         <v>44160</v>
       </c>
       <c r="B402" t="n">
-        <v>24.89852333068848</v>
+        <v>24.89852523803711</v>
       </c>
       <c r="C402" t="n">
-        <v>25.07343459806837</v>
+        <v>25.07343651881606</v>
       </c>
       <c r="D402" t="n">
-        <v>24.05020752047418</v>
+        <v>24.05020936283768</v>
       </c>
       <c r="E402" t="n">
-        <v>24.46999256049296</v>
+        <v>24.46999443501404</v>
       </c>
       <c r="F402" t="n">
         <v>1261400</v>
@@ -8472,16 +8472,16 @@
         <v>44161</v>
       </c>
       <c r="B403" t="n">
-        <v>24.85479545593262</v>
+        <v>24.85479354858398</v>
       </c>
       <c r="C403" t="n">
-        <v>25.09092515799838</v>
+        <v>25.09092323252923</v>
       </c>
       <c r="D403" t="n">
-        <v>24.43501043097842</v>
+        <v>24.43500855584395</v>
       </c>
       <c r="E403" t="n">
-        <v>24.85479545593262</v>
+        <v>24.85479354858398</v>
       </c>
       <c r="F403" t="n">
         <v>546200</v>
@@ -8492,16 +8492,16 @@
         <v>44162</v>
       </c>
       <c r="B404" t="n">
-        <v>24.18138885498047</v>
+        <v>24.1813907623291</v>
       </c>
       <c r="C404" t="n">
-        <v>25.27458004795497</v>
+        <v>25.27458204153094</v>
       </c>
       <c r="D404" t="n">
-        <v>24.13766187449244</v>
+        <v>24.13766377839204</v>
       </c>
       <c r="E404" t="n">
-        <v>24.96848618030663</v>
+        <v>24.96848814973892</v>
       </c>
       <c r="F404" t="n">
         <v>1199600</v>
@@ -8532,16 +8532,16 @@
         <v>44166</v>
       </c>
       <c r="B406" t="n">
-        <v>24.96848678588867</v>
+        <v>24.9684886932373</v>
       </c>
       <c r="C406" t="n">
-        <v>25.08217960683885</v>
+        <v>25.0821815228725</v>
       </c>
       <c r="D406" t="n">
-        <v>23.42927501675685</v>
+        <v>23.42927680652473</v>
       </c>
       <c r="E406" t="n">
-        <v>23.74411295367693</v>
+        <v>23.74411476749535</v>
       </c>
       <c r="F406" t="n">
         <v>1601900</v>
@@ -8572,16 +8572,16 @@
         <v>44168</v>
       </c>
       <c r="B408" t="n">
-        <v>24.09393501281738</v>
+        <v>24.09393310546875</v>
       </c>
       <c r="C408" t="n">
-        <v>25.08218085868143</v>
+        <v>25.08217887310027</v>
       </c>
       <c r="D408" t="n">
-        <v>23.73536840837539</v>
+        <v>23.73536652941197</v>
       </c>
       <c r="E408" t="n">
-        <v>24.59243163496901</v>
+        <v>24.59242968815787</v>
       </c>
       <c r="F408" t="n">
         <v>3140600</v>
@@ -8592,16 +8592,16 @@
         <v>44169</v>
       </c>
       <c r="B409" t="n">
-        <v>23.60418510437012</v>
+        <v>23.60418319702148</v>
       </c>
       <c r="C409" t="n">
-        <v>24.6274121739206</v>
+        <v>24.62741018388957</v>
       </c>
       <c r="D409" t="n">
-        <v>23.36805539568675</v>
+        <v>23.3680535074187</v>
       </c>
       <c r="E409" t="n">
-        <v>24.22511859741778</v>
+        <v>24.22511663989429</v>
       </c>
       <c r="F409" t="n">
         <v>2314400</v>
@@ -8672,16 +8672,16 @@
         <v>44175</v>
       </c>
       <c r="B413" t="n">
-        <v>24.63615989685059</v>
+        <v>24.63615798950195</v>
       </c>
       <c r="C413" t="n">
-        <v>24.83730670137279</v>
+        <v>24.83730477845123</v>
       </c>
       <c r="D413" t="n">
-        <v>23.39429447837807</v>
+        <v>23.39429266717552</v>
       </c>
       <c r="E413" t="n">
-        <v>24.18139190291359</v>
+        <v>24.18139003077341</v>
       </c>
       <c r="F413" t="n">
         <v>1331100</v>
@@ -8752,16 +8752,16 @@
         <v>44181</v>
       </c>
       <c r="B417" t="n">
-        <v>26.31529998779297</v>
+        <v>26.31529808044434</v>
       </c>
       <c r="C417" t="n">
-        <v>26.60390241199491</v>
+        <v>26.6039004837282</v>
       </c>
       <c r="D417" t="n">
-        <v>24.7673407724928</v>
+        <v>24.76733897734118</v>
       </c>
       <c r="E417" t="n">
-        <v>25.39702000208065</v>
+        <v>25.3970181612895</v>
       </c>
       <c r="F417" t="n">
         <v>2062300</v>
@@ -8812,16 +8812,16 @@
         <v>44186</v>
       </c>
       <c r="B420" t="n">
-        <v>25.27458190917969</v>
+        <v>25.27458000183105</v>
       </c>
       <c r="C420" t="n">
-        <v>25.79056832370717</v>
+        <v>25.79056637741958</v>
       </c>
       <c r="D420" t="n">
-        <v>24.79357841608068</v>
+        <v>24.79357654503102</v>
       </c>
       <c r="E420" t="n">
-        <v>25.36203754467337</v>
+        <v>25.36203563072489</v>
       </c>
       <c r="F420" t="n">
         <v>1168100</v>
@@ -8832,16 +8832,16 @@
         <v>44187</v>
       </c>
       <c r="B421" t="n">
-        <v>25.14339828491211</v>
+        <v>25.14340019226074</v>
       </c>
       <c r="C421" t="n">
-        <v>25.6244017587838</v>
+        <v>25.62440370262079</v>
       </c>
       <c r="D421" t="n">
-        <v>25.05594265291432</v>
+        <v>25.05594455362867</v>
       </c>
       <c r="E421" t="n">
-        <v>25.40576351282805</v>
+        <v>25.40576544007939</v>
       </c>
       <c r="F421" t="n">
         <v>837000</v>
@@ -8872,16 +8872,16 @@
         <v>44193</v>
       </c>
       <c r="B423" t="n">
-        <v>25.27458190917969</v>
+        <v>25.27458000183105</v>
       </c>
       <c r="C423" t="n">
-        <v>25.49322016387515</v>
+        <v>25.49321824002696</v>
       </c>
       <c r="D423" t="n">
-        <v>24.67113985915852</v>
+        <v>24.67113799734869</v>
       </c>
       <c r="E423" t="n">
-        <v>25.16963648104927</v>
+        <v>25.16963458162035</v>
       </c>
       <c r="F423" t="n">
         <v>745000</v>
@@ -8912,16 +8912,16 @@
         <v>44195</v>
       </c>
       <c r="B425" t="n">
-        <v>25.99171257019043</v>
+        <v>25.99171447753906</v>
       </c>
       <c r="C425" t="n">
-        <v>26.10540538561222</v>
+        <v>26.10540730130397</v>
       </c>
       <c r="D425" t="n">
-        <v>25.15214255512494</v>
+        <v>25.15214440086345</v>
       </c>
       <c r="E425" t="n">
-        <v>25.36203505889132</v>
+        <v>25.36203692003235</v>
       </c>
       <c r="F425" t="n">
         <v>1298700</v>
@@ -8952,16 +8952,16 @@
         <v>44201</v>
       </c>
       <c r="B427" t="n">
-        <v>23.95400619506836</v>
+        <v>23.95400428771973</v>
       </c>
       <c r="C427" t="n">
-        <v>24.95974348200135</v>
+        <v>24.95974149457043</v>
       </c>
       <c r="D427" t="n">
-        <v>23.90153348200113</v>
+        <v>23.90153157883066</v>
       </c>
       <c r="E427" t="n">
-        <v>24.88977764047509</v>
+        <v>24.88977565861522</v>
       </c>
       <c r="F427" t="n">
         <v>1214100</v>
@@ -9012,16 +9012,16 @@
         <v>44204</v>
       </c>
       <c r="B430" t="n">
-        <v>23.1756534576416</v>
+        <v>23.17565536499023</v>
       </c>
       <c r="C430" t="n">
-        <v>23.75285827823479</v>
+        <v>23.75286023308718</v>
       </c>
       <c r="D430" t="n">
-        <v>21.54898441701859</v>
+        <v>21.5489861904929</v>
       </c>
       <c r="E430" t="n">
-        <v>21.68016869558037</v>
+        <v>21.6801704798511</v>
       </c>
       <c r="F430" t="n">
         <v>2774700</v>
@@ -9032,16 +9032,16 @@
         <v>44207</v>
       </c>
       <c r="B431" t="n">
-        <v>22.82583427429199</v>
+        <v>22.82583236694336</v>
       </c>
       <c r="C431" t="n">
-        <v>23.38554767621726</v>
+        <v>23.38554572209844</v>
       </c>
       <c r="D431" t="n">
-        <v>22.58095882691093</v>
+        <v>22.58095694002433</v>
       </c>
       <c r="E431" t="n">
-        <v>22.81708854387722</v>
+        <v>22.81708663725939</v>
       </c>
       <c r="F431" t="n">
         <v>1353300</v>
@@ -9092,16 +9092,16 @@
         <v>44210</v>
       </c>
       <c r="B434" t="n">
-        <v>23.52547454833984</v>
+        <v>23.52547645568848</v>
       </c>
       <c r="C434" t="n">
-        <v>23.52547454833984</v>
+        <v>23.52547645568848</v>
       </c>
       <c r="D434" t="n">
-        <v>22.58095740790637</v>
+        <v>22.58095923867744</v>
       </c>
       <c r="E434" t="n">
-        <v>22.92203253226147</v>
+        <v>22.92203439068551</v>
       </c>
       <c r="F434" t="n">
         <v>1124400</v>
@@ -9112,16 +9112,16 @@
         <v>44211</v>
       </c>
       <c r="B435" t="n">
-        <v>23.11443710327148</v>
+        <v>23.11443901062012</v>
       </c>
       <c r="C435" t="n">
-        <v>23.52547643137114</v>
+        <v>23.52547837263777</v>
       </c>
       <c r="D435" t="n">
-        <v>22.73837902935513</v>
+        <v>22.73838090567234</v>
       </c>
       <c r="E435" t="n">
-        <v>23.52547643137114</v>
+        <v>23.52547837263777</v>
       </c>
       <c r="F435" t="n">
         <v>950400</v>
@@ -9172,16 +9172,16 @@
         <v>44216</v>
       </c>
       <c r="B438" t="n">
-        <v>22.7296314239502</v>
+        <v>22.72963333129883</v>
       </c>
       <c r="C438" t="n">
-        <v>23.33307343855487</v>
+        <v>23.33307539654111</v>
       </c>
       <c r="D438" t="n">
-        <v>22.38855630042806</v>
+        <v>22.3885581791555</v>
       </c>
       <c r="E438" t="n">
-        <v>22.61594027213529</v>
+        <v>22.61594216994357</v>
       </c>
       <c r="F438" t="n">
         <v>1221100</v>
@@ -9232,16 +9232,16 @@
         <v>44222</v>
       </c>
       <c r="B441" t="n">
-        <v>21.93378829956055</v>
+        <v>21.93379020690918</v>
       </c>
       <c r="C441" t="n">
-        <v>22.30110061165203</v>
+        <v>22.30110255094191</v>
       </c>
       <c r="D441" t="n">
-        <v>21.3128564949721</v>
+        <v>21.31285834832488</v>
       </c>
       <c r="E441" t="n">
-        <v>21.5314947362628</v>
+        <v>21.53149660862823</v>
       </c>
       <c r="F441" t="n">
         <v>1600800</v>
@@ -9252,16 +9252,16 @@
         <v>44223</v>
       </c>
       <c r="B442" t="n">
-        <v>21.48776626586914</v>
+        <v>21.48776435852051</v>
       </c>
       <c r="C442" t="n">
-        <v>22.17866391477103</v>
+        <v>22.17866194609529</v>
       </c>
       <c r="D442" t="n">
-        <v>21.33909219383186</v>
+        <v>21.33909029968019</v>
       </c>
       <c r="E442" t="n">
-        <v>21.94253421187463</v>
+        <v>21.9425322641588</v>
       </c>
       <c r="F442" t="n">
         <v>1472500</v>
@@ -9292,16 +9292,16 @@
         <v>44225</v>
       </c>
       <c r="B444" t="n">
-        <v>22.30109977722168</v>
+        <v>22.30110168457031</v>
       </c>
       <c r="C444" t="n">
-        <v>23.00074145594279</v>
+        <v>23.00074342312976</v>
       </c>
       <c r="D444" t="n">
-        <v>21.75013216373847</v>
+        <v>21.75013402396443</v>
       </c>
       <c r="E444" t="n">
-        <v>22.30984550671536</v>
+        <v>22.30984741481199</v>
       </c>
       <c r="F444" t="n">
         <v>1668700</v>
@@ -9472,16 +9472,16 @@
         <v>44238</v>
       </c>
       <c r="B453" t="n">
-        <v>20.21091842651367</v>
+        <v>20.2109203338623</v>
       </c>
       <c r="C453" t="n">
-        <v>20.58697644735989</v>
+        <v>20.58697839019794</v>
       </c>
       <c r="D453" t="n">
-        <v>20.12346280128104</v>
+        <v>20.12346470037629</v>
       </c>
       <c r="E453" t="n">
-        <v>20.33335530099298</v>
+        <v>20.33335721989625</v>
       </c>
       <c r="F453" t="n">
         <v>1364100</v>
@@ -9492,16 +9492,16 @@
         <v>44239</v>
       </c>
       <c r="B454" t="n">
-        <v>20.3508472442627</v>
+        <v>20.35084915161133</v>
       </c>
       <c r="C454" t="n">
-        <v>20.47328412165755</v>
+        <v>20.47328604048137</v>
       </c>
       <c r="D454" t="n">
-        <v>20.0010264030793</v>
+        <v>20.00102827764157</v>
       </c>
       <c r="E454" t="n">
-        <v>20.17593598963232</v>
+        <v>20.17593788058769</v>
       </c>
       <c r="F454" t="n">
         <v>1081700</v>
@@ -9552,16 +9552,16 @@
         <v>44246</v>
       </c>
       <c r="B457" t="n">
-        <v>21.19916343688965</v>
+        <v>21.19916534423828</v>
       </c>
       <c r="C457" t="n">
-        <v>21.21665489633471</v>
+        <v>21.21665680525709</v>
       </c>
       <c r="D457" t="n">
-        <v>19.99228109249628</v>
+        <v>19.9922828912583</v>
       </c>
       <c r="E457" t="n">
-        <v>20.34210194101049</v>
+        <v>20.34210377124688</v>
       </c>
       <c r="F457" t="n">
         <v>1586300</v>
@@ -9592,16 +9592,16 @@
         <v>44250</v>
       </c>
       <c r="B459" t="n">
-        <v>20.81435966491699</v>
+        <v>20.81436157226562</v>
       </c>
       <c r="C459" t="n">
-        <v>21.12045353282876</v>
+        <v>21.12045546822667</v>
       </c>
       <c r="D459" t="n">
-        <v>20.2459005776965</v>
+        <v>20.2459024329537</v>
       </c>
       <c r="E459" t="n">
-        <v>20.46453881647956</v>
+        <v>20.46454069177194</v>
       </c>
       <c r="F459" t="n">
         <v>988000</v>
@@ -9692,16 +9692,16 @@
         <v>44257</v>
       </c>
       <c r="B464" t="n">
-        <v>19.46755027770996</v>
+        <v>19.46754837036133</v>
       </c>
       <c r="C464" t="n">
-        <v>19.72116978418598</v>
+        <v>19.72116785198877</v>
       </c>
       <c r="D464" t="n">
-        <v>18.49679589908823</v>
+        <v>18.49679408685002</v>
       </c>
       <c r="E464" t="n">
-        <v>19.3800946427578</v>
+        <v>19.3800927439777</v>
       </c>
       <c r="F464" t="n">
         <v>1214000</v>
@@ -9752,16 +9752,16 @@
         <v>44260</v>
       </c>
       <c r="B467" t="n">
-        <v>20.8930721282959</v>
+        <v>20.89307022094727</v>
       </c>
       <c r="C467" t="n">
-        <v>20.90181785908977</v>
+        <v>20.90181595094273</v>
       </c>
       <c r="D467" t="n">
-        <v>19.31887728310561</v>
+        <v>19.31887551946674</v>
       </c>
       <c r="E467" t="n">
-        <v>19.49378856282791</v>
+        <v>19.49378678322121</v>
       </c>
       <c r="F467" t="n">
         <v>2934300</v>
@@ -9832,16 +9832,16 @@
         <v>44266</v>
       </c>
       <c r="B471" t="n">
-        <v>20.37708282470703</v>
+        <v>20.37708473205566</v>
       </c>
       <c r="C471" t="n">
-        <v>20.78812377387357</v>
+        <v>20.78812571969672</v>
       </c>
       <c r="D471" t="n">
-        <v>18.36561173093122</v>
+        <v>18.36561345000086</v>
       </c>
       <c r="E471" t="n">
-        <v>18.36561173093122</v>
+        <v>18.36561345000086</v>
       </c>
       <c r="F471" t="n">
         <v>3874700</v>
@@ -9852,16 +9852,16 @@
         <v>44267</v>
       </c>
       <c r="B472" t="n">
-        <v>20.65694046020508</v>
+        <v>20.65694236755371</v>
       </c>
       <c r="C472" t="n">
-        <v>21.37407357923675</v>
+        <v>21.37407555280153</v>
       </c>
       <c r="D472" t="n">
-        <v>19.82611452879387</v>
+        <v>19.82611635942859</v>
       </c>
       <c r="E472" t="n">
-        <v>20.24589952509378</v>
+        <v>20.24590139448915</v>
       </c>
       <c r="F472" t="n">
         <v>2643100</v>
@@ -9892,16 +9892,16 @@
         <v>44271</v>
       </c>
       <c r="B474" t="n">
-        <v>20.81435966491699</v>
+        <v>20.81436157226562</v>
       </c>
       <c r="C474" t="n">
-        <v>21.17292624307503</v>
+        <v>21.17292818328134</v>
       </c>
       <c r="D474" t="n">
-        <v>20.53450298616705</v>
+        <v>20.53450486787068</v>
       </c>
       <c r="E474" t="n">
-        <v>20.90181529404569</v>
+        <v>20.90181720940843</v>
       </c>
       <c r="F474" t="n">
         <v>1100300</v>
@@ -9972,16 +9972,16 @@
         <v>44277</v>
       </c>
       <c r="B478" t="n">
-        <v>22.30109977722168</v>
+        <v>22.30110168457031</v>
       </c>
       <c r="C478" t="n">
-        <v>22.58095644871013</v>
+        <v>22.58095837999409</v>
       </c>
       <c r="D478" t="n">
-        <v>21.31285569751843</v>
+        <v>21.31285752034541</v>
       </c>
       <c r="E478" t="n">
-        <v>21.42654684478161</v>
+        <v>21.42654867733226</v>
       </c>
       <c r="F478" t="n">
         <v>3225800</v>
@@ -10012,16 +10012,16 @@
         <v>44279</v>
       </c>
       <c r="B480" t="n">
-        <v>23.3942928314209</v>
+        <v>23.39429092407227</v>
       </c>
       <c r="C480" t="n">
-        <v>23.98898914038306</v>
+        <v>23.98898718454853</v>
       </c>
       <c r="D480" t="n">
-        <v>23.01823477321968</v>
+        <v>23.01823289653125</v>
       </c>
       <c r="E480" t="n">
-        <v>23.60418535198211</v>
+        <v>23.60418342752083</v>
       </c>
       <c r="F480" t="n">
         <v>3020300</v>
@@ -10112,16 +10112,16 @@
         <v>44286</v>
       </c>
       <c r="B485" t="n">
-        <v>23.09694290161133</v>
+        <v>23.09694480895996</v>
       </c>
       <c r="C485" t="n">
-        <v>25.02970575717804</v>
+        <v>25.02970782413449</v>
       </c>
       <c r="D485" t="n">
-        <v>23.09694290161133</v>
+        <v>23.09694480895996</v>
       </c>
       <c r="E485" t="n">
-        <v>24.19013407138876</v>
+        <v>24.19013606901326</v>
       </c>
       <c r="F485" t="n">
         <v>7601000</v>
@@ -10132,16 +10132,16 @@
         <v>44287</v>
       </c>
       <c r="B486" t="n">
-        <v>23.5167293548584</v>
+        <v>23.51672744750977</v>
       </c>
       <c r="C486" t="n">
-        <v>23.52547508492306</v>
+        <v>23.52547317686509</v>
       </c>
       <c r="D486" t="n">
-        <v>22.2223913306826</v>
+        <v>22.22238952831259</v>
       </c>
       <c r="E486" t="n">
-        <v>23.5167293548584</v>
+        <v>23.51672744750977</v>
       </c>
       <c r="F486" t="n">
         <v>1244600</v>
@@ -10152,16 +10152,16 @@
         <v>44291</v>
       </c>
       <c r="B487" t="n">
-        <v>23.9627513885498</v>
+        <v>23.96275329589844</v>
       </c>
       <c r="C487" t="n">
-        <v>24.13766265229293</v>
+        <v>24.13766457356387</v>
       </c>
       <c r="D487" t="n">
-        <v>23.39429228350079</v>
+        <v>23.39429414560212</v>
       </c>
       <c r="E487" t="n">
-        <v>23.49923937536215</v>
+        <v>23.4992412458169</v>
       </c>
       <c r="F487" t="n">
         <v>1183400</v>
@@ -10192,16 +10192,16 @@
         <v>44293</v>
       </c>
       <c r="B489" t="n">
-        <v>24.09393501281738</v>
+        <v>24.09393310546875</v>
       </c>
       <c r="C489" t="n">
-        <v>24.82855968242477</v>
+        <v>24.82855771692103</v>
       </c>
       <c r="D489" t="n">
-        <v>23.84031550463823</v>
+        <v>23.84031361736688</v>
       </c>
       <c r="E489" t="n">
-        <v>24.55744871352222</v>
+        <v>24.55744676948045</v>
       </c>
       <c r="F489" t="n">
         <v>331100</v>
@@ -10212,16 +10212,16 @@
         <v>44294</v>
       </c>
       <c r="B490" t="n">
-        <v>23.54296493530273</v>
+        <v>23.54296684265137</v>
       </c>
       <c r="C490" t="n">
-        <v>24.60991890907674</v>
+        <v>24.60992090286534</v>
       </c>
       <c r="D490" t="n">
-        <v>23.30683524393459</v>
+        <v>23.30683713215302</v>
       </c>
       <c r="E490" t="n">
-        <v>23.962749941239</v>
+        <v>23.96275188259679</v>
       </c>
       <c r="F490" t="n">
         <v>2327300</v>
@@ -10312,16 +10312,16 @@
         <v>44301</v>
       </c>
       <c r="B495" t="n">
-        <v>24.05021095275879</v>
+        <v>24.05020904541016</v>
       </c>
       <c r="C495" t="n">
-        <v>24.40003186936519</v>
+        <v>24.40002993427333</v>
       </c>
       <c r="D495" t="n">
-        <v>23.70039003615238</v>
+        <v>23.70038815654698</v>
       </c>
       <c r="E495" t="n">
-        <v>23.70039003615238</v>
+        <v>23.70038815654698</v>
       </c>
       <c r="F495" t="n">
         <v>383100</v>
@@ -10432,16 +10432,16 @@
         <v>44312</v>
       </c>
       <c r="B501" t="n">
-        <v>23.9627513885498</v>
+        <v>23.96275329589844</v>
       </c>
       <c r="C501" t="n">
-        <v>24.66239477544489</v>
+        <v>24.66239673848261</v>
       </c>
       <c r="D501" t="n">
-        <v>23.66540324103294</v>
+        <v>23.66540512471374</v>
       </c>
       <c r="E501" t="n">
-        <v>23.98898857853451</v>
+        <v>23.98899048797152</v>
       </c>
       <c r="F501" t="n">
         <v>650400</v>
@@ -10472,16 +10472,16 @@
         <v>44314</v>
       </c>
       <c r="B503" t="n">
-        <v>23.4904956817627</v>
+        <v>23.49049377441406</v>
       </c>
       <c r="C503" t="n">
-        <v>23.4904956817627</v>
+        <v>23.49049377441406</v>
       </c>
       <c r="D503" t="n">
-        <v>22.72963378702149</v>
+        <v>22.72963194145226</v>
       </c>
       <c r="E503" t="n">
-        <v>23.39429431155652</v>
+        <v>23.39429241201911</v>
       </c>
       <c r="F503" t="n">
         <v>522700</v>
@@ -10512,16 +10512,16 @@
         <v>44316</v>
       </c>
       <c r="B505" t="n">
-        <v>22.76461219787598</v>
+        <v>22.76461410522461</v>
       </c>
       <c r="C505" t="n">
-        <v>23.52547227373006</v>
+        <v>23.52547424482788</v>
       </c>
       <c r="D505" t="n">
-        <v>22.56346376658004</v>
+        <v>22.56346565707531</v>
       </c>
       <c r="E505" t="n">
-        <v>23.23686988839278</v>
+        <v>23.23687183530985</v>
       </c>
       <c r="F505" t="n">
         <v>743400</v>
@@ -10532,16 +10532,16 @@
         <v>44319</v>
       </c>
       <c r="B506" t="n">
-        <v>23.08819961547852</v>
+        <v>23.08819770812988</v>
       </c>
       <c r="C506" t="n">
-        <v>23.75286011721265</v>
+        <v>23.75285815495547</v>
       </c>
       <c r="D506" t="n">
-        <v>22.76461592910326</v>
+        <v>22.76461404848633</v>
       </c>
       <c r="E506" t="n">
-        <v>22.76461592910326</v>
+        <v>22.76461404848633</v>
       </c>
       <c r="F506" t="n">
         <v>492900</v>
@@ -10552,16 +10552,16 @@
         <v>44320</v>
       </c>
       <c r="B507" t="n">
-        <v>23.5167293548584</v>
+        <v>23.51672744750977</v>
       </c>
       <c r="C507" t="n">
-        <v>23.90153313731625</v>
+        <v>23.90153119875771</v>
       </c>
       <c r="D507" t="n">
-        <v>22.790850440266</v>
+        <v>22.79084859179052</v>
       </c>
       <c r="E507" t="n">
-        <v>23.08819859015469</v>
+        <v>23.08819671756248</v>
       </c>
       <c r="F507" t="n">
         <v>826900</v>
@@ -10612,16 +10612,16 @@
         <v>44323</v>
       </c>
       <c r="B510" t="n">
-        <v>24.70612144470215</v>
+        <v>24.70612335205078</v>
       </c>
       <c r="C510" t="n">
-        <v>24.88103270623189</v>
+        <v>24.88103462708393</v>
       </c>
       <c r="D510" t="n">
-        <v>24.22511797761148</v>
+        <v>24.22511984782594</v>
       </c>
       <c r="E510" t="n">
-        <v>24.22511797761148</v>
+        <v>24.22511984782594</v>
       </c>
       <c r="F510" t="n">
         <v>827500</v>
@@ -10632,16 +10632,16 @@
         <v>44326</v>
       </c>
       <c r="B511" t="n">
-        <v>25.09967231750488</v>
+        <v>25.09967041015625</v>
       </c>
       <c r="C511" t="n">
-        <v>25.18712628496021</v>
+        <v>25.18712437096586</v>
       </c>
       <c r="D511" t="n">
-        <v>24.51372172793567</v>
+        <v>24.51371986511399</v>
       </c>
       <c r="E511" t="n">
-        <v>24.55744871166333</v>
+        <v>24.5574468455188</v>
       </c>
       <c r="F511" t="n">
         <v>963200</v>
@@ -10672,16 +10672,16 @@
         <v>44328</v>
       </c>
       <c r="B513" t="n">
-        <v>23.42053031921387</v>
+        <v>23.4205322265625</v>
       </c>
       <c r="C513" t="n">
-        <v>25.3532916797891</v>
+        <v>25.35329374454022</v>
       </c>
       <c r="D513" t="n">
-        <v>22.87830671649212</v>
+        <v>22.87830857968251</v>
       </c>
       <c r="E513" t="n">
-        <v>25.28332750538089</v>
+        <v>25.28332956443419</v>
       </c>
       <c r="F513" t="n">
         <v>1663700</v>
@@ -10732,16 +10732,16 @@
         <v>44333</v>
       </c>
       <c r="B516" t="n">
-        <v>24.81107139587402</v>
+        <v>24.81106948852539</v>
       </c>
       <c r="C516" t="n">
-        <v>25.01221820217063</v>
+        <v>25.01221627935886</v>
       </c>
       <c r="D516" t="n">
-        <v>23.4817503255982</v>
+        <v>23.48174852044099</v>
       </c>
       <c r="E516" t="n">
-        <v>23.83157122091352</v>
+        <v>23.83156938886387</v>
       </c>
       <c r="F516" t="n">
         <v>854000</v>
@@ -10812,16 +10812,16 @@
         <v>44337</v>
       </c>
       <c r="B520" t="n">
-        <v>25.14339828491211</v>
+        <v>25.14340019226074</v>
       </c>
       <c r="C520" t="n">
-        <v>25.95673282675992</v>
+        <v>25.95673479580715</v>
       </c>
       <c r="D520" t="n">
-        <v>24.88977711892626</v>
+        <v>24.88977900703549</v>
       </c>
       <c r="E520" t="n">
-        <v>25.30956381890017</v>
+        <v>25.30956573885392</v>
       </c>
       <c r="F520" t="n">
         <v>1456100</v>
@@ -10852,16 +10852,16 @@
         <v>44341</v>
       </c>
       <c r="B522" t="n">
-        <v>26.06167984008789</v>
+        <v>26.06167793273926</v>
       </c>
       <c r="C522" t="n">
-        <v>26.54268501137151</v>
+        <v>26.54268306882006</v>
       </c>
       <c r="D522" t="n">
-        <v>25.76433167400785</v>
+        <v>25.76432978842092</v>
       </c>
       <c r="E522" t="n">
-        <v>25.88677023350274</v>
+        <v>25.88676833895504</v>
       </c>
       <c r="F522" t="n">
         <v>802500</v>
@@ -10912,16 +10912,16 @@
         <v>44344</v>
       </c>
       <c r="B525" t="n">
-        <v>28.5978832244873</v>
+        <v>28.59788513183594</v>
       </c>
       <c r="C525" t="n">
-        <v>28.80777407225714</v>
+        <v>28.80777599360453</v>
       </c>
       <c r="D525" t="n">
-        <v>27.37350771326209</v>
+        <v>27.37350953895044</v>
       </c>
       <c r="E525" t="n">
-        <v>27.67960159106839</v>
+        <v>27.67960343717182</v>
       </c>
       <c r="F525" t="n">
         <v>1543700</v>
@@ -10932,16 +10932,16 @@
         <v>44347</v>
       </c>
       <c r="B526" t="n">
-        <v>29.21881675720215</v>
+        <v>29.21881484985352</v>
       </c>
       <c r="C526" t="n">
-        <v>29.35000104687511</v>
+        <v>29.34999913096302</v>
       </c>
       <c r="D526" t="n">
-        <v>28.42297362903536</v>
+        <v>28.42297177363785</v>
       </c>
       <c r="E526" t="n">
-        <v>28.59788490321429</v>
+        <v>28.5978830363989</v>
       </c>
       <c r="F526" t="n">
         <v>1368000</v>
@@ -10952,16 +10952,16 @@
         <v>44348</v>
       </c>
       <c r="B527" t="n">
-        <v>30.37322235107422</v>
+        <v>30.37322425842285</v>
       </c>
       <c r="C527" t="n">
-        <v>31.21279234916924</v>
+        <v>31.21279430924039</v>
       </c>
       <c r="D527" t="n">
-        <v>29.13135881257798</v>
+        <v>29.13136064194126</v>
       </c>
       <c r="E527" t="n">
-        <v>29.29752266548597</v>
+        <v>29.29752450528385</v>
       </c>
       <c r="F527" t="n">
         <v>3409000</v>
@@ -10972,16 +10972,16 @@
         <v>44349</v>
       </c>
       <c r="B528" t="n">
-        <v>30.69680786132812</v>
+        <v>30.69680595397949</v>
       </c>
       <c r="C528" t="n">
-        <v>31.42268842657149</v>
+        <v>31.42268647412021</v>
       </c>
       <c r="D528" t="n">
-        <v>29.90971219133409</v>
+        <v>29.90971033289171</v>
       </c>
       <c r="E528" t="n">
-        <v>30.3732241970913</v>
+        <v>30.37322230984856</v>
       </c>
       <c r="F528" t="n">
         <v>1420200</v>
@@ -10992,16 +10992,16 @@
         <v>44351</v>
       </c>
       <c r="B529" t="n">
-        <v>30.52190017700195</v>
+        <v>30.52190208435059</v>
       </c>
       <c r="C529" t="n">
-        <v>30.85422790563423</v>
+        <v>30.8542298337504</v>
       </c>
       <c r="D529" t="n">
-        <v>30.18082171421382</v>
+        <v>30.18082360024806</v>
       </c>
       <c r="E529" t="n">
-        <v>30.60935414008311</v>
+        <v>30.60935605289684</v>
       </c>
       <c r="F529" t="n">
         <v>1113000</v>
@@ -11012,16 +11012,16 @@
         <v>44354</v>
       </c>
       <c r="B530" t="n">
-        <v>30.60061073303223</v>
+        <v>30.60061264038086</v>
       </c>
       <c r="C530" t="n">
-        <v>31.96491126875886</v>
+        <v>31.9649132611449</v>
       </c>
       <c r="D530" t="n">
-        <v>30.03214995237619</v>
+        <v>30.03215182429243</v>
       </c>
       <c r="E530" t="n">
-        <v>30.521900830113</v>
+        <v>30.52190273255562</v>
       </c>
       <c r="F530" t="n">
         <v>1187500</v>
@@ -11032,16 +11032,16 @@
         <v>44355</v>
       </c>
       <c r="B531" t="n">
-        <v>31.42268943786621</v>
+        <v>31.42268753051758</v>
       </c>
       <c r="C531" t="n">
-        <v>31.60634476649336</v>
+        <v>31.6063428479969</v>
       </c>
       <c r="D531" t="n">
-        <v>30.30326266967607</v>
+        <v>30.30326083027634</v>
       </c>
       <c r="E531" t="n">
-        <v>30.30326266967607</v>
+        <v>30.30326083027634</v>
       </c>
       <c r="F531" t="n">
         <v>1062900</v>
@@ -11052,16 +11052,16 @@
         <v>44356</v>
       </c>
       <c r="B532" t="n">
-        <v>31.91244125366211</v>
+        <v>31.91243934631348</v>
       </c>
       <c r="C532" t="n">
-        <v>32.10484064999491</v>
+        <v>32.10483873114692</v>
       </c>
       <c r="D532" t="n">
-        <v>30.91544800580656</v>
+        <v>30.91544615804641</v>
       </c>
       <c r="E532" t="n">
-        <v>31.42269036012719</v>
+        <v>31.42268848205008</v>
       </c>
       <c r="F532" t="n">
         <v>930900</v>
@@ -11192,16 +11192,16 @@
         <v>44365</v>
       </c>
       <c r="B539" t="n">
-        <v>33.9676399230957</v>
+        <v>33.96763610839844</v>
       </c>
       <c r="C539" t="n">
-        <v>34.53610072880572</v>
+        <v>34.53609685026812</v>
       </c>
       <c r="D539" t="n">
-        <v>33.10183095282514</v>
+        <v>33.10182723536157</v>
       </c>
       <c r="E539" t="n">
-        <v>33.93265700111092</v>
+        <v>33.93265319034237</v>
       </c>
       <c r="F539" t="n">
         <v>1658000</v>
@@ -11212,16 +11212,16 @@
         <v>44368</v>
       </c>
       <c r="B540" t="n">
-        <v>33.9676399230957</v>
+        <v>33.96763610839844</v>
       </c>
       <c r="C540" t="n">
-        <v>34.29997100964103</v>
+        <v>34.29996715762169</v>
       </c>
       <c r="D540" t="n">
-        <v>33.29423368758639</v>
+        <v>33.29422994851525</v>
       </c>
       <c r="E540" t="n">
-        <v>33.85394709472268</v>
+        <v>33.85394329279357</v>
       </c>
       <c r="F540" t="n">
         <v>1020900</v>
@@ -11232,16 +11232,16 @@
         <v>44369</v>
       </c>
       <c r="B541" t="n">
-        <v>33.6702880859375</v>
+        <v>33.67028427124023</v>
       </c>
       <c r="C541" t="n">
-        <v>34.22125737055798</v>
+        <v>34.22125349343828</v>
       </c>
       <c r="D541" t="n">
-        <v>33.28548599454248</v>
+        <v>33.28548222344162</v>
       </c>
       <c r="E541" t="n">
-        <v>33.42541433106382</v>
+        <v>33.42541054410969</v>
       </c>
       <c r="F541" t="n">
         <v>903100</v>
@@ -11252,16 +11252,16 @@
         <v>44370</v>
       </c>
       <c r="B542" t="n">
-        <v>32.9619026184082</v>
+        <v>32.96189880371094</v>
       </c>
       <c r="C542" t="n">
-        <v>34.09882423042728</v>
+        <v>34.0988202841535</v>
       </c>
       <c r="D542" t="n">
-        <v>32.48089911740671</v>
+        <v>32.48089535837622</v>
       </c>
       <c r="E542" t="n">
-        <v>33.53910748684101</v>
+        <v>33.53910360534354</v>
       </c>
       <c r="F542" t="n">
         <v>952800</v>
@@ -11272,16 +11272,16 @@
         <v>44371</v>
       </c>
       <c r="B543" t="n">
-        <v>32.3234748840332</v>
+        <v>32.32347869873047</v>
       </c>
       <c r="C543" t="n">
-        <v>33.58283321468035</v>
+        <v>33.58283717800244</v>
       </c>
       <c r="D543" t="n">
-        <v>32.04361821859042</v>
+        <v>32.04362200026004</v>
       </c>
       <c r="E543" t="n">
-        <v>32.96189811058422</v>
+        <v>32.96190200062584</v>
       </c>
       <c r="F543" t="n">
         <v>1167600</v>
@@ -11372,16 +11372,16 @@
         <v>44378</v>
       </c>
       <c r="B548" t="n">
-        <v>33.53910446166992</v>
+        <v>33.53910827636719</v>
       </c>
       <c r="C548" t="n">
-        <v>33.78398155744986</v>
+        <v>33.78398539999915</v>
       </c>
       <c r="D548" t="n">
-        <v>32.76075286615723</v>
+        <v>32.76075659232573</v>
       </c>
       <c r="E548" t="n">
-        <v>33.23301226213844</v>
+        <v>33.23301604202116</v>
       </c>
       <c r="F548" t="n">
         <v>860200</v>
@@ -11412,16 +11412,16 @@
         <v>44382</v>
       </c>
       <c r="B550" t="n">
-        <v>34.14255142211914</v>
+        <v>34.14254760742188</v>
       </c>
       <c r="C550" t="n">
-        <v>34.76348327874786</v>
+        <v>34.76347939467478</v>
       </c>
       <c r="D550" t="n">
-        <v>33.84520325559686</v>
+        <v>33.84519947412186</v>
       </c>
       <c r="E550" t="n">
-        <v>34.02885859299604</v>
+        <v>34.02885479100151</v>
       </c>
       <c r="F550" t="n">
         <v>928400</v>
@@ -11432,16 +11432,16 @@
         <v>44383</v>
       </c>
       <c r="B551" t="n">
-        <v>33.39043807983398</v>
+        <v>33.39043426513672</v>
       </c>
       <c r="C551" t="n">
-        <v>34.24749972917273</v>
+        <v>34.24749581656028</v>
       </c>
       <c r="D551" t="n">
-        <v>32.94441412450997</v>
+        <v>32.9444103607688</v>
       </c>
       <c r="E551" t="n">
-        <v>34.09007990213547</v>
+        <v>34.09007600750749</v>
       </c>
       <c r="F551" t="n">
         <v>1010200</v>
@@ -11452,16 +11452,16 @@
         <v>44384</v>
       </c>
       <c r="B552" t="n">
-        <v>33.6702880859375</v>
+        <v>33.67028427124023</v>
       </c>
       <c r="C552" t="n">
-        <v>34.02885465678312</v>
+        <v>34.02885080146181</v>
       </c>
       <c r="D552" t="n">
-        <v>33.32921297417639</v>
+        <v>33.32920919812145</v>
       </c>
       <c r="E552" t="n">
-        <v>33.71401506557142</v>
+        <v>33.71401124592007</v>
       </c>
       <c r="F552" t="n">
         <v>852100</v>
@@ -11472,16 +11472,16 @@
         <v>44385</v>
       </c>
       <c r="B553" t="n">
-        <v>34.21250915527344</v>
+        <v>34.21250534057617</v>
       </c>
       <c r="C553" t="n">
-        <v>34.21250915527344</v>
+        <v>34.21250534057617</v>
       </c>
       <c r="D553" t="n">
-        <v>32.20978551220497</v>
+        <v>32.20978192081154</v>
       </c>
       <c r="E553" t="n">
-        <v>32.93566269801294</v>
+        <v>32.93565902568415</v>
       </c>
       <c r="F553" t="n">
         <v>781400</v>
@@ -11512,16 +11512,16 @@
         <v>44390</v>
       </c>
       <c r="B555" t="n">
-        <v>34.04635238647461</v>
+        <v>34.04634857177734</v>
       </c>
       <c r="C555" t="n">
-        <v>34.57108291103507</v>
+        <v>34.57107903754478</v>
       </c>
       <c r="D555" t="n">
-        <v>33.39043756269638</v>
+        <v>33.39043382149058</v>
       </c>
       <c r="E555" t="n">
-        <v>34.57108291103507</v>
+        <v>34.57107903754478</v>
       </c>
       <c r="F555" t="n">
         <v>920800</v>
@@ -11532,16 +11532,16 @@
         <v>44391</v>
       </c>
       <c r="B556" t="n">
-        <v>34.54484558105469</v>
+        <v>34.54484176635742</v>
       </c>
       <c r="C556" t="n">
-        <v>35.75172972788333</v>
+        <v>35.75172577991299</v>
       </c>
       <c r="D556" t="n">
-        <v>33.86269526753009</v>
+        <v>33.8626915281609</v>
       </c>
       <c r="E556" t="n">
-        <v>34.10756905471222</v>
+        <v>34.10756528830226</v>
       </c>
       <c r="F556" t="n">
         <v>1491000</v>
@@ -11552,16 +11552,16 @@
         <v>44392</v>
       </c>
       <c r="B557" t="n">
-        <v>34.14255142211914</v>
+        <v>34.14254760742188</v>
       </c>
       <c r="C557" t="n">
-        <v>34.80721026343979</v>
+        <v>34.80720637448117</v>
       </c>
       <c r="D557" t="n">
-        <v>33.93265722498073</v>
+        <v>33.93265343373464</v>
       </c>
       <c r="E557" t="n">
-        <v>34.29122383730274</v>
+        <v>34.29122000599452</v>
       </c>
       <c r="F557" t="n">
         <v>384200</v>
@@ -11572,16 +11572,16 @@
         <v>44393</v>
       </c>
       <c r="B558" t="n">
-        <v>33.42541885375977</v>
+        <v>33.4254150390625</v>
       </c>
       <c r="C558" t="n">
-        <v>34.50986277449446</v>
+        <v>34.50985883603434</v>
       </c>
       <c r="D558" t="n">
-        <v>32.72577374033141</v>
+        <v>32.72577000548159</v>
       </c>
       <c r="E558" t="n">
-        <v>34.28248044793884</v>
+        <v>34.28247653542888</v>
       </c>
       <c r="F558" t="n">
         <v>877400</v>
@@ -11632,16 +11632,16 @@
         <v>44398</v>
       </c>
       <c r="B561" t="n">
-        <v>32.3497200012207</v>
+        <v>32.34971618652344</v>
       </c>
       <c r="C561" t="n">
-        <v>33.0755973251561</v>
+        <v>33.07559342486297</v>
       </c>
       <c r="D561" t="n">
-        <v>32.19230017942165</v>
+        <v>32.19229638328742</v>
       </c>
       <c r="E561" t="n">
-        <v>33.0755973251561</v>
+        <v>33.07559342486297</v>
       </c>
       <c r="F561" t="n">
         <v>460900</v>
@@ -11672,16 +11672,16 @@
         <v>44400</v>
       </c>
       <c r="B563" t="n">
-        <v>32.76074981689453</v>
+        <v>32.7607536315918</v>
       </c>
       <c r="C563" t="n">
-        <v>33.33795457954011</v>
+        <v>33.33795846144773</v>
       </c>
       <c r="D563" t="n">
-        <v>32.3672003568738</v>
+        <v>32.36720412574574</v>
       </c>
       <c r="E563" t="n">
-        <v>33.11931636132353</v>
+        <v>33.11932021777268</v>
       </c>
       <c r="F563" t="n">
         <v>561000</v>
@@ -11692,16 +11692,16 @@
         <v>44403</v>
       </c>
       <c r="B564" t="n">
-        <v>32.97064590454102</v>
+        <v>32.97064971923828</v>
       </c>
       <c r="C564" t="n">
-        <v>33.41666642790693</v>
+        <v>33.41667029420868</v>
       </c>
       <c r="D564" t="n">
-        <v>32.37594964928337</v>
+        <v>32.3759533951744</v>
       </c>
       <c r="E564" t="n">
-        <v>33.08433871879298</v>
+        <v>33.08434254664448</v>
       </c>
       <c r="F564" t="n">
         <v>436800</v>
@@ -11712,16 +11712,16 @@
         <v>44404</v>
       </c>
       <c r="B565" t="n">
-        <v>32.09609603881836</v>
+        <v>32.09609985351562</v>
       </c>
       <c r="C565" t="n">
-        <v>32.97939310838438</v>
+        <v>32.9793970280636</v>
       </c>
       <c r="D565" t="n">
-        <v>31.17781604827914</v>
+        <v>31.17781975383665</v>
       </c>
       <c r="E565" t="n">
-        <v>32.49838962154526</v>
+        <v>32.49839348405607</v>
       </c>
       <c r="F565" t="n">
         <v>900400</v>
@@ -11732,16 +11732,16 @@
         <v>44405</v>
       </c>
       <c r="B566" t="n">
-        <v>32.62083053588867</v>
+        <v>32.62082290649414</v>
       </c>
       <c r="C566" t="n">
-        <v>32.69079638647246</v>
+        <v>32.69078874071425</v>
       </c>
       <c r="D566" t="n">
-        <v>31.60634905551132</v>
+        <v>31.6063416633848</v>
       </c>
       <c r="E566" t="n">
-        <v>32.09610000113174</v>
+        <v>32.09609249446174</v>
       </c>
       <c r="F566" t="n">
         <v>535400</v>
@@ -11772,16 +11772,16 @@
         <v>44407</v>
       </c>
       <c r="B568" t="n">
-        <v>30.69680786132812</v>
+        <v>30.69680595397949</v>
       </c>
       <c r="C568" t="n">
-        <v>31.65007073048404</v>
+        <v>31.65006876390434</v>
       </c>
       <c r="D568" t="n">
-        <v>30.48691701712498</v>
+        <v>30.48691512281793</v>
       </c>
       <c r="E568" t="n">
-        <v>31.52763384867307</v>
+        <v>31.52763188970099</v>
       </c>
       <c r="F568" t="n">
         <v>1140100</v>
@@ -11812,16 +11812,16 @@
         <v>44411</v>
       </c>
       <c r="B570" t="n">
-        <v>31.45767211914062</v>
+        <v>31.45767021179199</v>
       </c>
       <c r="C570" t="n">
-        <v>31.80749131346182</v>
+        <v>31.80748938490287</v>
       </c>
       <c r="D570" t="n">
-        <v>30.52190068669521</v>
+        <v>30.52189883608448</v>
       </c>
       <c r="E570" t="n">
-        <v>30.83673696073781</v>
+        <v>30.83673509103786</v>
       </c>
       <c r="F570" t="n">
         <v>798700</v>
@@ -11832,16 +11832,16 @@
         <v>44412</v>
       </c>
       <c r="B571" t="n">
-        <v>31.17781448364258</v>
+        <v>31.17781257629395</v>
       </c>
       <c r="C571" t="n">
-        <v>31.73752784650509</v>
+        <v>31.73752590491517</v>
       </c>
       <c r="D571" t="n">
-        <v>30.53938788446305</v>
+        <v>30.5393860161711</v>
       </c>
       <c r="E571" t="n">
-        <v>31.45767116507383</v>
+        <v>31.45766924060456</v>
       </c>
       <c r="F571" t="n">
         <v>454700</v>
@@ -11852,16 +11852,16 @@
         <v>44413</v>
       </c>
       <c r="B572" t="n">
-        <v>30.79300880432129</v>
+        <v>30.79301071166992</v>
       </c>
       <c r="C572" t="n">
-        <v>31.4139406028929</v>
+        <v>31.41394254870265</v>
       </c>
       <c r="D572" t="n">
-        <v>30.32949680484596</v>
+        <v>30.32949868348422</v>
       </c>
       <c r="E572" t="n">
-        <v>31.18655830206202</v>
+        <v>31.18656023378749</v>
       </c>
       <c r="F572" t="n">
         <v>680400</v>
@@ -11892,16 +11892,16 @@
         <v>44417</v>
       </c>
       <c r="B574" t="n">
-        <v>30.5568790435791</v>
+        <v>30.55687713623047</v>
       </c>
       <c r="C574" t="n">
-        <v>31.12533979873324</v>
+        <v>31.12533785590151</v>
       </c>
       <c r="D574" t="n">
-        <v>30.16333288279291</v>
+        <v>30.16333100000927</v>
       </c>
       <c r="E574" t="n">
-        <v>30.16333288279291</v>
+        <v>30.16333100000927</v>
       </c>
       <c r="F574" t="n">
         <v>444900</v>
@@ -11912,16 +11912,16 @@
         <v>44418</v>
       </c>
       <c r="B575" t="n">
-        <v>30.79300880432129</v>
+        <v>30.79301071166992</v>
       </c>
       <c r="C575" t="n">
-        <v>31.1953023637208</v>
+        <v>31.19530429598789</v>
       </c>
       <c r="D575" t="n">
-        <v>30.32949680484596</v>
+        <v>30.32949868348422</v>
       </c>
       <c r="E575" t="n">
-        <v>30.5656265034904</v>
+        <v>30.56562839675476</v>
       </c>
       <c r="F575" t="n">
         <v>335500</v>
@@ -11932,16 +11932,16 @@
         <v>44419</v>
       </c>
       <c r="B576" t="n">
-        <v>30.5568790435791</v>
+        <v>30.55687713623047</v>
       </c>
       <c r="C576" t="n">
-        <v>30.90670156000546</v>
+        <v>30.90669963082104</v>
       </c>
       <c r="D576" t="n">
-        <v>29.72605640533734</v>
+        <v>29.72605454984834</v>
       </c>
       <c r="E576" t="n">
-        <v>30.90670156000546</v>
+        <v>30.90669963082104</v>
       </c>
       <c r="F576" t="n">
         <v>544900</v>
@@ -11972,16 +11972,16 @@
         <v>44421</v>
       </c>
       <c r="B578" t="n">
-        <v>29.66483688354492</v>
+        <v>29.66483879089355</v>
       </c>
       <c r="C578" t="n">
-        <v>30.72304857488147</v>
+        <v>30.72305055026953</v>
       </c>
       <c r="D578" t="n">
-        <v>29.22756037285949</v>
+        <v>29.22756225209273</v>
       </c>
       <c r="E578" t="n">
-        <v>30.39071749263714</v>
+        <v>30.39071944665744</v>
       </c>
       <c r="F578" t="n">
         <v>1030500</v>
@@ -11992,16 +11992,16 @@
         <v>44424</v>
       </c>
       <c r="B579" t="n">
-        <v>29.34999847412109</v>
+        <v>29.35000038146973</v>
       </c>
       <c r="C579" t="n">
-        <v>29.76978349366007</v>
+        <v>29.76978542828899</v>
       </c>
       <c r="D579" t="n">
-        <v>27.74081922973357</v>
+        <v>27.74082103250755</v>
       </c>
       <c r="E579" t="n">
-        <v>29.56863671364065</v>
+        <v>29.56863863519778</v>
       </c>
       <c r="F579" t="n">
         <v>1220000</v>
@@ -12012,16 +12012,16 @@
         <v>44425</v>
       </c>
       <c r="B580" t="n">
-        <v>28.75530242919922</v>
+        <v>28.75530052185059</v>
       </c>
       <c r="C580" t="n">
-        <v>28.86024785089732</v>
+        <v>28.86024593658762</v>
       </c>
       <c r="D580" t="n">
-        <v>26.63888251866625</v>
+        <v>26.63888075170044</v>
       </c>
       <c r="E580" t="n">
-        <v>28.85150378915365</v>
+        <v>28.85150187542395</v>
       </c>
       <c r="F580" t="n">
         <v>2491100</v>
@@ -12112,16 +12112,16 @@
         <v>44432</v>
       </c>
       <c r="B585" t="n">
-        <v>32.09609603881836</v>
+        <v>32.09609985351562</v>
       </c>
       <c r="C585" t="n">
-        <v>32.38469679645984</v>
+        <v>32.384700645458</v>
       </c>
       <c r="D585" t="n">
-        <v>30.27702418207156</v>
+        <v>30.27702778056781</v>
       </c>
       <c r="E585" t="n">
-        <v>30.62684671949362</v>
+        <v>30.62685035956712</v>
       </c>
       <c r="F585" t="n">
         <v>1338400</v>
@@ -12172,16 +12172,16 @@
         <v>44435</v>
       </c>
       <c r="B588" t="n">
-        <v>30.46942710876465</v>
+        <v>30.46942520141602</v>
       </c>
       <c r="C588" t="n">
-        <v>30.7317923454543</v>
+        <v>30.73179042168193</v>
       </c>
       <c r="D588" t="n">
-        <v>29.77852942776306</v>
+        <v>29.77852756366378</v>
       </c>
       <c r="E588" t="n">
-        <v>30.7317923454543</v>
+        <v>30.73179042168193</v>
       </c>
       <c r="F588" t="n">
         <v>654900</v>
@@ -12192,16 +12192,16 @@
         <v>44438</v>
       </c>
       <c r="B589" t="n">
-        <v>30.65308380126953</v>
+        <v>30.65308570861816</v>
       </c>
       <c r="C589" t="n">
-        <v>31.0641248032242</v>
+        <v>31.06412673614933</v>
       </c>
       <c r="D589" t="n">
-        <v>29.89222358025473</v>
+        <v>29.89222544025981</v>
       </c>
       <c r="E589" t="n">
-        <v>30.12835330460176</v>
+        <v>30.12835517929972</v>
       </c>
       <c r="F589" t="n">
         <v>678700</v>
@@ -12232,16 +12232,16 @@
         <v>44440</v>
       </c>
       <c r="B591" t="n">
-        <v>29.4287109375</v>
+        <v>29.42870903015137</v>
       </c>
       <c r="C591" t="n">
-        <v>30.52190223033202</v>
+        <v>30.52190025213092</v>
       </c>
       <c r="D591" t="n">
-        <v>29.4287109375</v>
+        <v>29.42870903015137</v>
       </c>
       <c r="E591" t="n">
-        <v>30.37322647970623</v>
+        <v>30.37322451114117</v>
       </c>
       <c r="F591" t="n">
         <v>539500</v>
@@ -12252,16 +12252,16 @@
         <v>44441</v>
       </c>
       <c r="B592" t="n">
-        <v>29.23630714416504</v>
+        <v>29.23630523681641</v>
       </c>
       <c r="C592" t="n">
-        <v>29.6298566625708</v>
+        <v>29.62985472954738</v>
       </c>
       <c r="D592" t="n">
-        <v>28.74655626168732</v>
+        <v>28.74655438628956</v>
       </c>
       <c r="E592" t="n">
-        <v>29.4724368552085</v>
+        <v>29.47243493245499</v>
       </c>
       <c r="F592" t="n">
         <v>669700</v>
@@ -12272,16 +12272,16 @@
         <v>44442</v>
       </c>
       <c r="B593" t="n">
-        <v>28.41422653198242</v>
+        <v>28.41422843933105</v>
       </c>
       <c r="C593" t="n">
-        <v>29.50741770865503</v>
+        <v>29.5074196893858</v>
       </c>
       <c r="D593" t="n">
-        <v>27.65336473906425</v>
+        <v>27.65336659533887</v>
       </c>
       <c r="E593" t="n">
-        <v>29.28877947332051</v>
+        <v>29.28878143937485</v>
       </c>
       <c r="F593" t="n">
         <v>1806900</v>
@@ -12292,16 +12292,16 @@
         <v>44445</v>
       </c>
       <c r="B594" t="n">
-        <v>27.98569679260254</v>
+        <v>27.98569488525391</v>
       </c>
       <c r="C594" t="n">
-        <v>28.59788457717173</v>
+        <v>28.5978826280998</v>
       </c>
       <c r="D594" t="n">
-        <v>27.8720056333367</v>
+        <v>27.87200373373662</v>
       </c>
       <c r="E594" t="n">
-        <v>28.27430089213067</v>
+        <v>28.27429896511239</v>
       </c>
       <c r="F594" t="n">
         <v>607700</v>
@@ -12312,16 +12312,16 @@
         <v>44447</v>
       </c>
       <c r="B595" t="n">
-        <v>26.70884895324707</v>
+        <v>26.7088508605957</v>
       </c>
       <c r="C595" t="n">
-        <v>27.96820405019139</v>
+        <v>27.96820604747386</v>
       </c>
       <c r="D595" t="n">
-        <v>26.70884895324707</v>
+        <v>26.7088508605957</v>
       </c>
       <c r="E595" t="n">
-        <v>27.89823987813893</v>
+        <v>27.89824187042507</v>
       </c>
       <c r="F595" t="n">
         <v>518300</v>
@@ -12332,16 +12332,16 @@
         <v>44448</v>
       </c>
       <c r="B596" t="n">
-        <v>27.41723823547363</v>
+        <v>27.417236328125</v>
       </c>
       <c r="C596" t="n">
-        <v>28.02942436481213</v>
+        <v>28.02942241487524</v>
       </c>
       <c r="D596" t="n">
-        <v>26.33279266217231</v>
+        <v>26.33279083026585</v>
       </c>
       <c r="E596" t="n">
-        <v>26.72634053073045</v>
+        <v>26.72633867144584</v>
       </c>
       <c r="F596" t="n">
         <v>1711000</v>
@@ -12352,16 +12352,16 @@
         <v>44449</v>
       </c>
       <c r="B597" t="n">
-        <v>28.16060829162598</v>
+        <v>28.16060638427734</v>
       </c>
       <c r="C597" t="n">
-        <v>28.72906576061172</v>
+        <v>28.72906381476085</v>
       </c>
       <c r="D597" t="n">
-        <v>27.81078574443855</v>
+        <v>27.81078386078378</v>
       </c>
       <c r="E597" t="n">
-        <v>28.03817140095689</v>
+        <v>28.03816950190105</v>
       </c>
       <c r="F597" t="n">
         <v>695400</v>
@@ -12372,16 +12372,16 @@
         <v>44452</v>
       </c>
       <c r="B598" t="n">
-        <v>28.86025047302246</v>
+        <v>28.86024856567383</v>
       </c>
       <c r="C598" t="n">
-        <v>29.41996388780535</v>
+        <v>29.41996194346575</v>
       </c>
       <c r="D598" t="n">
-        <v>28.06440733584895</v>
+        <v>28.06440548109689</v>
       </c>
       <c r="E598" t="n">
-        <v>28.2130797520828</v>
+        <v>28.21307788750511</v>
       </c>
       <c r="F598" t="n">
         <v>676500</v>
@@ -12392,16 +12392,16 @@
         <v>44453</v>
       </c>
       <c r="B599" t="n">
-        <v>29.4549446105957</v>
+        <v>29.45494651794434</v>
       </c>
       <c r="C599" t="n">
-        <v>29.90971256018386</v>
+        <v>29.9097144969809</v>
       </c>
       <c r="D599" t="n">
-        <v>28.83401279595133</v>
+        <v>28.83401466309166</v>
       </c>
       <c r="E599" t="n">
-        <v>29.1138694824433</v>
+        <v>29.11387136770569</v>
       </c>
       <c r="F599" t="n">
         <v>353200</v>
@@ -12472,16 +12472,16 @@
         <v>44459</v>
       </c>
       <c r="B603" t="n">
-        <v>26.66512107849121</v>
+        <v>26.66511917114258</v>
       </c>
       <c r="C603" t="n">
-        <v>27.34727302689531</v>
+        <v>27.34727107075254</v>
       </c>
       <c r="D603" t="n">
-        <v>26.28031728697525</v>
+        <v>26.28031540715152</v>
       </c>
       <c r="E603" t="n">
-        <v>27.08490612301182</v>
+        <v>27.08490418563607</v>
       </c>
       <c r="F603" t="n">
         <v>409200</v>
@@ -12492,16 +12492,16 @@
         <v>44460</v>
       </c>
       <c r="B604" t="n">
-        <v>27.69709396362305</v>
+        <v>27.69709587097168</v>
       </c>
       <c r="C604" t="n">
-        <v>28.16935172281972</v>
+        <v>28.16935366269018</v>
       </c>
       <c r="D604" t="n">
-        <v>26.90125085595213</v>
+        <v>26.90125270849537</v>
       </c>
       <c r="E604" t="n">
-        <v>27.25107172722328</v>
+        <v>27.25107360385678</v>
       </c>
       <c r="F604" t="n">
         <v>267700</v>
@@ -12512,16 +12512,16 @@
         <v>44461</v>
       </c>
       <c r="B605" t="n">
-        <v>28.85150527954102</v>
+        <v>28.85150337219238</v>
       </c>
       <c r="C605" t="n">
-        <v>29.03516061103851</v>
+        <v>29.03515869154857</v>
       </c>
       <c r="D605" t="n">
-        <v>27.81953079235146</v>
+        <v>27.81952895322579</v>
       </c>
       <c r="E605" t="n">
-        <v>27.81953079235146</v>
+        <v>27.81952895322579</v>
       </c>
       <c r="F605" t="n">
         <v>672500</v>
@@ -12552,16 +12552,16 @@
         <v>44463</v>
       </c>
       <c r="B607" t="n">
-        <v>27.79329490661621</v>
+        <v>27.79329299926758</v>
       </c>
       <c r="C607" t="n">
-        <v>29.03516023182496</v>
+        <v>29.03515823925181</v>
       </c>
       <c r="D607" t="n">
-        <v>27.45221810273945</v>
+        <v>27.45221621879763</v>
       </c>
       <c r="E607" t="n">
-        <v>28.88648448720569</v>
+        <v>28.88648250483559</v>
       </c>
       <c r="F607" t="n">
         <v>1265100</v>
@@ -12612,16 +12612,16 @@
         <v>44468</v>
       </c>
       <c r="B610" t="n">
-        <v>25.05594444274902</v>
+        <v>25.05594253540039</v>
       </c>
       <c r="C610" t="n">
-        <v>26.09666303490232</v>
+        <v>26.09666104833045</v>
       </c>
       <c r="D610" t="n">
-        <v>24.79357919609141</v>
+        <v>24.79357730871497</v>
       </c>
       <c r="E610" t="n">
-        <v>24.97723453513623</v>
+        <v>24.97723263377928</v>
       </c>
       <c r="F610" t="n">
         <v>1006800</v>
@@ -12672,16 +12672,16 @@
         <v>44473</v>
       </c>
       <c r="B613" t="n">
-        <v>24.40002822875977</v>
+        <v>24.4000301361084</v>
       </c>
       <c r="C613" t="n">
-        <v>25.08218016542008</v>
+        <v>25.08218212609248</v>
       </c>
       <c r="D613" t="n">
-        <v>24.06769882458831</v>
+        <v>24.06770070595877</v>
       </c>
       <c r="E613" t="n">
-        <v>25.08218016542008</v>
+        <v>25.08218212609248</v>
       </c>
       <c r="F613" t="n">
         <v>966400</v>
@@ -12752,16 +12752,16 @@
         <v>44477</v>
       </c>
       <c r="B617" t="n">
-        <v>25.84304046630859</v>
+        <v>25.84304237365723</v>
       </c>
       <c r="C617" t="n">
-        <v>26.37651832975359</v>
+        <v>26.37652027647562</v>
       </c>
       <c r="D617" t="n">
-        <v>25.27458135028616</v>
+        <v>25.2745832156796</v>
       </c>
       <c r="E617" t="n">
-        <v>25.44074688724201</v>
+        <v>25.44074876489932</v>
       </c>
       <c r="F617" t="n">
         <v>712200</v>
@@ -12812,16 +12812,16 @@
         <v>44483</v>
       </c>
       <c r="B620" t="n">
-        <v>24.80232238769531</v>
+        <v>24.80232048034668</v>
       </c>
       <c r="C620" t="n">
-        <v>25.65063815525139</v>
+        <v>25.65063618266556</v>
       </c>
       <c r="D620" t="n">
-        <v>24.48748278947445</v>
+        <v>24.48748090633762</v>
       </c>
       <c r="E620" t="n">
-        <v>24.99472343767618</v>
+        <v>24.99472151553152</v>
       </c>
       <c r="F620" t="n">
         <v>655700</v>
@@ -12852,16 +12852,16 @@
         <v>44487</v>
       </c>
       <c r="B622" t="n">
-        <v>24.80232238769531</v>
+        <v>24.80232048034668</v>
       </c>
       <c r="C622" t="n">
-        <v>24.98597770793922</v>
+        <v>24.98597578646713</v>
       </c>
       <c r="D622" t="n">
-        <v>24.02396912188011</v>
+        <v>24.02396727438841</v>
       </c>
       <c r="E622" t="n">
-        <v>24.40002716018228</v>
+        <v>24.40002528377096</v>
       </c>
       <c r="F622" t="n">
         <v>1188100</v>
@@ -12892,16 +12892,16 @@
         <v>44489</v>
       </c>
       <c r="B624" t="n">
-        <v>22.92203330993652</v>
+        <v>22.92203521728516</v>
       </c>
       <c r="C624" t="n">
-        <v>23.23687292345504</v>
+        <v>23.23687485700156</v>
       </c>
       <c r="D624" t="n">
-        <v>22.22239157775923</v>
+        <v>22.22239342689049</v>
       </c>
       <c r="E624" t="n">
-        <v>23.23687292345504</v>
+        <v>23.23687485700156</v>
       </c>
       <c r="F624" t="n">
         <v>1977700</v>
@@ -12952,16 +12952,16 @@
         <v>44494</v>
       </c>
       <c r="B627" t="n">
-        <v>21.74138641357422</v>
+        <v>21.74138832092285</v>
       </c>
       <c r="C627" t="n">
-        <v>22.17866287937851</v>
+        <v>22.17866482508894</v>
       </c>
       <c r="D627" t="n">
-        <v>20.98927035860608</v>
+        <v>20.98927219997238</v>
       </c>
       <c r="E627" t="n">
-        <v>21.01550754706219</v>
+        <v>21.01550939073024</v>
       </c>
       <c r="F627" t="n">
         <v>1250000</v>
@@ -12972,16 +12972,16 @@
         <v>44495</v>
       </c>
       <c r="B628" t="n">
-        <v>20.12346649169922</v>
+        <v>20.12346458435059</v>
       </c>
       <c r="C628" t="n">
-        <v>21.57522446533426</v>
+        <v>21.57522242038466</v>
       </c>
       <c r="D628" t="n">
-        <v>19.9223196844302</v>
+        <v>19.92231779614673</v>
       </c>
       <c r="E628" t="n">
-        <v>21.55773300346453</v>
+        <v>21.55773096017281</v>
       </c>
       <c r="F628" t="n">
         <v>1203400</v>
@@ -13052,16 +13052,16 @@
         <v>44501</v>
       </c>
       <c r="B632" t="n">
-        <v>19.67744255065918</v>
+        <v>19.67744064331055</v>
       </c>
       <c r="C632" t="n">
-        <v>19.97479070487089</v>
+        <v>19.97478876870009</v>
       </c>
       <c r="D632" t="n">
-        <v>18.37435877747371</v>
+        <v>18.37435699643392</v>
       </c>
       <c r="E632" t="n">
-        <v>18.46181441131436</v>
+        <v>18.46181262179743</v>
       </c>
       <c r="F632" t="n">
         <v>2083000</v>
@@ -13092,16 +13092,16 @@
         <v>44504</v>
       </c>
       <c r="B634" t="n">
-        <v>20.17593574523926</v>
+        <v>20.17593765258789</v>
       </c>
       <c r="C634" t="n">
-        <v>21.11170710959876</v>
+        <v>21.11170910541131</v>
       </c>
       <c r="D634" t="n">
-        <v>19.6424579263483</v>
+        <v>19.64245978326417</v>
       </c>
       <c r="E634" t="n">
-        <v>20.64819512617433</v>
+        <v>20.64819707816839</v>
       </c>
       <c r="F634" t="n">
         <v>1063000</v>
@@ -13112,16 +13112,16 @@
         <v>44505</v>
       </c>
       <c r="B635" t="n">
-        <v>20.90181732177734</v>
+        <v>20.90181541442871</v>
       </c>
       <c r="C635" t="n">
-        <v>21.17292829710776</v>
+        <v>21.1729263650195</v>
       </c>
       <c r="D635" t="n">
-        <v>20.33335817940937</v>
+        <v>20.3333563239342</v>
       </c>
       <c r="E635" t="n">
-        <v>20.43830527816043</v>
+        <v>20.43830341310856</v>
       </c>
       <c r="F635" t="n">
         <v>709700</v>
@@ -13132,16 +13132,16 @@
         <v>44508</v>
       </c>
       <c r="B636" t="n">
-        <v>20.21091842651367</v>
+        <v>20.2109203338623</v>
       </c>
       <c r="C636" t="n">
-        <v>20.77937748840984</v>
+        <v>20.7793794494052</v>
       </c>
       <c r="D636" t="n">
-        <v>19.72116759244183</v>
+        <v>19.72116945357161</v>
       </c>
       <c r="E636" t="n">
-        <v>20.77937748840984</v>
+        <v>20.7793794494052</v>
       </c>
       <c r="F636" t="n">
         <v>938800</v>
@@ -13152,16 +13152,16 @@
         <v>44509</v>
       </c>
       <c r="B637" t="n">
-        <v>21.48776626586914</v>
+        <v>21.48776435852051</v>
       </c>
       <c r="C637" t="n">
-        <v>21.87257004080282</v>
+        <v>21.87256809929731</v>
       </c>
       <c r="D637" t="n">
-        <v>20.1934282670019</v>
+        <v>20.1934264745444</v>
       </c>
       <c r="E637" t="n">
-        <v>20.29837368957091</v>
+        <v>20.29837188779799</v>
       </c>
       <c r="F637" t="n">
         <v>1107100</v>
@@ -13192,16 +13192,16 @@
         <v>44511</v>
       </c>
       <c r="B639" t="n">
-        <v>22.7296314239502</v>
+        <v>22.72963333129883</v>
       </c>
       <c r="C639" t="n">
-        <v>23.09694373700381</v>
+        <v>23.09694567517532</v>
       </c>
       <c r="D639" t="n">
-        <v>22.4760119307889</v>
+        <v>22.47601381685515</v>
       </c>
       <c r="E639" t="n">
-        <v>22.49350172239914</v>
+        <v>22.49350360993304</v>
       </c>
       <c r="F639" t="n">
         <v>1201600</v>
@@ -13312,16 +13312,16 @@
         <v>44522</v>
       </c>
       <c r="B645" t="n">
-        <v>23.60418510437012</v>
+        <v>23.60418319702148</v>
       </c>
       <c r="C645" t="n">
-        <v>24.76734051949353</v>
+        <v>24.76733851815552</v>
       </c>
       <c r="D645" t="n">
-        <v>23.01823453175441</v>
+        <v>23.01823267175383</v>
       </c>
       <c r="E645" t="n">
-        <v>24.57493946135012</v>
+        <v>24.57493747555916</v>
       </c>
       <c r="F645" t="n">
         <v>1417300</v>
@@ -13332,16 +13332,16 @@
         <v>44523</v>
       </c>
       <c r="B646" t="n">
-        <v>22.82583427429199</v>
+        <v>22.82583236694336</v>
       </c>
       <c r="C646" t="n">
-        <v>23.90153409414619</v>
+        <v>23.90153209691105</v>
       </c>
       <c r="D646" t="n">
-        <v>22.46726766767393</v>
+        <v>22.46726579028746</v>
       </c>
       <c r="E646" t="n">
-        <v>23.61293166276878</v>
+        <v>23.61292968964954</v>
       </c>
       <c r="F646" t="n">
         <v>1018600</v>
@@ -13352,16 +13352,16 @@
         <v>44524</v>
       </c>
       <c r="B647" t="n">
-        <v>23.0794506072998</v>
+        <v>23.07945251464844</v>
       </c>
       <c r="C647" t="n">
-        <v>23.5429642470185</v>
+        <v>23.54296619267316</v>
       </c>
       <c r="D647" t="n">
-        <v>22.23113489076132</v>
+        <v>22.23113672800283</v>
       </c>
       <c r="E647" t="n">
-        <v>22.82583113249028</v>
+        <v>22.8258330188791</v>
       </c>
       <c r="F647" t="n">
         <v>983600</v>
@@ -13452,16 +13452,16 @@
         <v>44531</v>
       </c>
       <c r="B652" t="n">
-        <v>21.12045288085938</v>
+        <v>21.12045478820801</v>
       </c>
       <c r="C652" t="n">
-        <v>22.61593925537147</v>
+        <v>22.61594129777468</v>
       </c>
       <c r="D652" t="n">
-        <v>20.89306891937484</v>
+        <v>20.89307080618885</v>
       </c>
       <c r="E652" t="n">
-        <v>21.5402378860259</v>
+        <v>21.54023983128454</v>
       </c>
       <c r="F652" t="n">
         <v>1232500</v>
@@ -13492,16 +13492,16 @@
         <v>44533</v>
       </c>
       <c r="B654" t="n">
-        <v>22.09995460510254</v>
+        <v>22.09995651245117</v>
       </c>
       <c r="C654" t="n">
-        <v>22.79085060441233</v>
+        <v>22.79085257138912</v>
       </c>
       <c r="D654" t="n">
-        <v>21.03299888261361</v>
+        <v>21.03300069787805</v>
       </c>
       <c r="E654" t="n">
-        <v>21.03299888261361</v>
+        <v>21.03300069787805</v>
       </c>
       <c r="F654" t="n">
         <v>1059100</v>
@@ -13512,16 +13512,16 @@
         <v>44536</v>
       </c>
       <c r="B655" t="n">
-        <v>22.54597854614258</v>
+        <v>22.54597663879395</v>
       </c>
       <c r="C655" t="n">
-        <v>22.93078069253087</v>
+        <v>22.93077875262868</v>
       </c>
       <c r="D655" t="n">
-        <v>21.99500918278135</v>
+        <v>21.99500732204372</v>
       </c>
       <c r="E655" t="n">
-        <v>22.30110308819564</v>
+        <v>22.30110120156302</v>
       </c>
       <c r="F655" t="n">
         <v>546700</v>
@@ -13532,16 +13532,16 @@
         <v>44537</v>
       </c>
       <c r="B656" t="n">
-        <v>22.51099395751953</v>
+        <v>22.51099586486816</v>
       </c>
       <c r="C656" t="n">
-        <v>23.21063735642938</v>
+        <v>23.21063932305855</v>
       </c>
       <c r="D656" t="n">
-        <v>22.48475676708427</v>
+        <v>22.48475867220984</v>
       </c>
       <c r="E656" t="n">
-        <v>22.91328920380625</v>
+        <v>22.91329114524122</v>
       </c>
       <c r="F656" t="n">
         <v>687200</v>
@@ -13552,16 +13552,16 @@
         <v>44538</v>
       </c>
       <c r="B657" t="n">
-        <v>22.3448314666748</v>
+        <v>22.34482955932617</v>
       </c>
       <c r="C657" t="n">
-        <v>22.69465404785173</v>
+        <v>22.69465211064233</v>
       </c>
       <c r="D657" t="n">
-        <v>21.76762654304165</v>
+        <v>21.76762468496307</v>
       </c>
       <c r="E657" t="n">
-        <v>22.43228711196904</v>
+        <v>22.43228519715521</v>
       </c>
       <c r="F657" t="n">
         <v>918600</v>
@@ -13592,16 +13592,16 @@
         <v>44540</v>
       </c>
       <c r="B659" t="n">
-        <v>22.3185920715332</v>
+        <v>22.31859397888184</v>
       </c>
       <c r="C659" t="n">
-        <v>22.65092146434458</v>
+        <v>22.65092340009411</v>
       </c>
       <c r="D659" t="n">
-        <v>21.39156472743494</v>
+        <v>21.39156655555974</v>
       </c>
       <c r="E659" t="n">
-        <v>21.84633266966306</v>
+        <v>21.84633453665237</v>
       </c>
       <c r="F659" t="n">
         <v>1318200</v>
@@ -13612,16 +13612,16 @@
         <v>44543</v>
       </c>
       <c r="B660" t="n">
-        <v>21.6014575958252</v>
+        <v>21.60145950317383</v>
       </c>
       <c r="C660" t="n">
-        <v>22.98325113020246</v>
+        <v>22.98325315955962</v>
       </c>
       <c r="D660" t="n">
-        <v>21.6014575958252</v>
+        <v>21.60145950317383</v>
       </c>
       <c r="E660" t="n">
-        <v>22.32733644613584</v>
+        <v>22.32733841757755</v>
       </c>
       <c r="F660" t="n">
         <v>718000</v>
@@ -13632,16 +13632,16 @@
         <v>44544</v>
       </c>
       <c r="B661" t="n">
-        <v>20.06224822998047</v>
+        <v>20.06224632263184</v>
       </c>
       <c r="C661" t="n">
-        <v>22.05622819551692</v>
+        <v>22.05622609859756</v>
       </c>
       <c r="D661" t="n">
-        <v>19.87859121479401</v>
+        <v>19.87858932490593</v>
       </c>
       <c r="E661" t="n">
-        <v>22.038738401562</v>
+        <v>22.03873630630543</v>
       </c>
       <c r="F661" t="n">
         <v>1317100</v>
@@ -13652,16 +13652,16 @@
         <v>44545</v>
       </c>
       <c r="B662" t="n">
-        <v>20.20217514038086</v>
+        <v>20.20217323303223</v>
       </c>
       <c r="C662" t="n">
-        <v>20.29837483850132</v>
+        <v>20.29837292207018</v>
       </c>
       <c r="D662" t="n">
-        <v>19.28389346649956</v>
+        <v>19.28389164584869</v>
       </c>
       <c r="E662" t="n">
-        <v>20.23715639385807</v>
+        <v>20.23715448320675</v>
       </c>
       <c r="F662" t="n">
         <v>804500</v>
@@ -13712,16 +13712,16 @@
         <v>44550</v>
       </c>
       <c r="B665" t="n">
-        <v>19.06525421142578</v>
+        <v>19.06525611877441</v>
       </c>
       <c r="C665" t="n">
-        <v>19.38883954653136</v>
+        <v>19.3888414862525</v>
       </c>
       <c r="D665" t="n">
-        <v>18.64546918324348</v>
+        <v>18.64547104859549</v>
       </c>
       <c r="E665" t="n">
-        <v>19.25765693373407</v>
+        <v>19.25765886033128</v>
       </c>
       <c r="F665" t="n">
         <v>742400</v>
@@ -13752,16 +13752,16 @@
         <v>44552</v>
       </c>
       <c r="B667" t="n">
-        <v>19.1527099609375</v>
+        <v>19.15271186828613</v>
       </c>
       <c r="C667" t="n">
-        <v>19.38009393629327</v>
+        <v>19.38009586628624</v>
       </c>
       <c r="D667" t="n">
-        <v>18.59299658657096</v>
+        <v>18.59299843817978</v>
       </c>
       <c r="E667" t="n">
-        <v>19.10023724910999</v>
+        <v>19.10023915123306</v>
       </c>
       <c r="F667" t="n">
         <v>388700</v>
@@ -13772,16 +13772,16 @@
         <v>44553</v>
       </c>
       <c r="B668" t="n">
-        <v>18.68045234680176</v>
+        <v>18.68045425415039</v>
       </c>
       <c r="C668" t="n">
-        <v>19.34511281747166</v>
+        <v>19.34511479268477</v>
       </c>
       <c r="D668" t="n">
-        <v>18.56675952430328</v>
+        <v>18.56676142004343</v>
       </c>
       <c r="E668" t="n">
-        <v>19.34511281747166</v>
+        <v>19.34511479268477</v>
       </c>
       <c r="F668" t="n">
         <v>595700</v>
@@ -13832,16 +13832,16 @@
         <v>44559</v>
       </c>
       <c r="B671" t="n">
-        <v>18.97780418395996</v>
+        <v>18.97780227661133</v>
       </c>
       <c r="C671" t="n">
-        <v>19.55500913443268</v>
+        <v>19.55500716907254</v>
       </c>
       <c r="D671" t="n">
-        <v>18.6892017087236</v>
+        <v>18.68919983038072</v>
       </c>
       <c r="E671" t="n">
-        <v>19.55500913443268</v>
+        <v>19.55500716907254</v>
       </c>
       <c r="F671" t="n">
         <v>517900</v>
@@ -13872,16 +13872,16 @@
         <v>44564</v>
       </c>
       <c r="B673" t="n">
-        <v>18.41808700561523</v>
+        <v>18.4180850982666</v>
       </c>
       <c r="C673" t="n">
-        <v>19.69493534263136</v>
+        <v>19.69493330305429</v>
       </c>
       <c r="D673" t="n">
-        <v>18.41808700561523</v>
+        <v>18.4180850982666</v>
       </c>
       <c r="E673" t="n">
-        <v>19.43256842337061</v>
+        <v>19.43256641096385</v>
       </c>
       <c r="F673" t="n">
         <v>684800</v>
@@ -13892,16 +13892,16 @@
         <v>44565</v>
       </c>
       <c r="B674" t="n">
-        <v>17.84088325500488</v>
+        <v>17.84088134765625</v>
       </c>
       <c r="C674" t="n">
-        <v>18.62798072676966</v>
+        <v>18.62797873527332</v>
       </c>
       <c r="D674" t="n">
-        <v>17.70970062105703</v>
+        <v>17.70969872773299</v>
       </c>
       <c r="E674" t="n">
-        <v>18.50554382416203</v>
+        <v>18.50554184575528</v>
       </c>
       <c r="F674" t="n">
         <v>701900</v>
@@ -13912,16 +13912,16 @@
         <v>44566</v>
       </c>
       <c r="B675" t="n">
-        <v>17.25493240356445</v>
+        <v>17.25493049621582</v>
       </c>
       <c r="C675" t="n">
-        <v>18.1907039613135</v>
+        <v>18.19070195052531</v>
       </c>
       <c r="D675" t="n">
-        <v>17.10625830862728</v>
+        <v>17.10625641771298</v>
       </c>
       <c r="E675" t="n">
-        <v>17.6834632258945</v>
+        <v>17.68346127117636</v>
       </c>
       <c r="F675" t="n">
         <v>1257700</v>
@@ -13932,16 +13932,16 @@
         <v>44567</v>
       </c>
       <c r="B676" t="n">
-        <v>17.2636775970459</v>
+        <v>17.26367568969727</v>
       </c>
       <c r="C676" t="n">
-        <v>17.6747169440907</v>
+        <v>17.67471499132907</v>
       </c>
       <c r="D676" t="n">
-        <v>16.83514678806448</v>
+        <v>16.83514492806136</v>
       </c>
       <c r="E676" t="n">
-        <v>17.25493186607759</v>
+        <v>17.25492995969521</v>
       </c>
       <c r="F676" t="n">
         <v>1271200</v>
@@ -13972,16 +13972,16 @@
         <v>44571</v>
       </c>
       <c r="B678" t="n">
-        <v>17.31614875793457</v>
+        <v>17.31614685058594</v>
       </c>
       <c r="C678" t="n">
-        <v>17.79715390948009</v>
+        <v>17.79715194914944</v>
       </c>
       <c r="D678" t="n">
-        <v>16.94883643067766</v>
+        <v>16.94883456378794</v>
       </c>
       <c r="E678" t="n">
-        <v>17.79715390948009</v>
+        <v>17.79715194914944</v>
       </c>
       <c r="F678" t="n">
         <v>513900</v>
@@ -14032,16 +14032,16 @@
         <v>44574</v>
       </c>
       <c r="B681" t="n">
-        <v>18.26066589355469</v>
+        <v>18.26066398620605</v>
       </c>
       <c r="C681" t="n">
-        <v>18.5667597769608</v>
+        <v>18.56675783764029</v>
       </c>
       <c r="D681" t="n">
-        <v>17.89335356708285</v>
+        <v>17.89335169810044</v>
       </c>
       <c r="E681" t="n">
-        <v>18.47056008131928</v>
+        <v>18.47055815204695</v>
       </c>
       <c r="F681" t="n">
         <v>578400</v>
@@ -14052,16 +14052,16 @@
         <v>44575</v>
       </c>
       <c r="B682" t="n">
-        <v>18.34812164306641</v>
+        <v>18.34812355041504</v>
       </c>
       <c r="C682" t="n">
-        <v>18.42683154695619</v>
+        <v>18.42683346248698</v>
       </c>
       <c r="D682" t="n">
-        <v>17.51729728923059</v>
+        <v>17.51729911021225</v>
       </c>
       <c r="E682" t="n">
-        <v>18.2781574693952</v>
+        <v>18.27815936947083</v>
       </c>
       <c r="F682" t="n">
         <v>846900</v>
@@ -14072,16 +14072,16 @@
         <v>44578</v>
       </c>
       <c r="B683" t="n">
-        <v>18.10324668884277</v>
+        <v>18.10324859619141</v>
       </c>
       <c r="C683" t="n">
-        <v>18.66296004171654</v>
+        <v>18.66296200803628</v>
       </c>
       <c r="D683" t="n">
-        <v>17.84087980362516</v>
+        <v>17.84088168333096</v>
       </c>
       <c r="E683" t="n">
-        <v>18.47055899368553</v>
+        <v>18.47056093973399</v>
       </c>
       <c r="F683" t="n">
         <v>353900</v>
@@ -14372,16 +14372,16 @@
         <v>44599</v>
       </c>
       <c r="B698" t="n">
-        <v>19.82611465454102</v>
+        <v>19.82611656188965</v>
       </c>
       <c r="C698" t="n">
-        <v>20.61321194461484</v>
+        <v>20.61321392768527</v>
       </c>
       <c r="D698" t="n">
-        <v>19.52002080060194</v>
+        <v>19.52002267850317</v>
       </c>
       <c r="E698" t="n">
-        <v>20.001025904814</v>
+        <v>20.00102782898977</v>
       </c>
       <c r="F698" t="n">
         <v>648500</v>
@@ -14452,16 +14452,16 @@
         <v>44603</v>
       </c>
       <c r="B702" t="n">
-        <v>19.06525421142578</v>
+        <v>19.06525611877441</v>
       </c>
       <c r="C702" t="n">
-        <v>20.08848126016853</v>
+        <v>20.08848326988405</v>
       </c>
       <c r="D702" t="n">
-        <v>18.75916200425791</v>
+        <v>18.7591638809841</v>
       </c>
       <c r="E702" t="n">
-        <v>20.00977135887467</v>
+        <v>20.0097733607158</v>
       </c>
       <c r="F702" t="n">
         <v>2202700</v>
@@ -14532,16 +14532,16 @@
         <v>44609</v>
       </c>
       <c r="B706" t="n">
-        <v>19.78238868713379</v>
+        <v>19.78238677978516</v>
       </c>
       <c r="C706" t="n">
-        <v>20.91930686778672</v>
+        <v>20.91930485082042</v>
       </c>
       <c r="D706" t="n">
-        <v>19.78238868713379</v>
+        <v>19.78238677978516</v>
       </c>
       <c r="E706" t="n">
-        <v>20.38582902845644</v>
+        <v>20.3858270629262</v>
       </c>
       <c r="F706" t="n">
         <v>844900</v>
@@ -14592,16 +14592,16 @@
         <v>44614</v>
       </c>
       <c r="B709" t="n">
-        <v>19.47629356384277</v>
+        <v>19.47629547119141</v>
       </c>
       <c r="C709" t="n">
-        <v>19.83486012087871</v>
+        <v>19.83486206334241</v>
       </c>
       <c r="D709" t="n">
-        <v>19.04776284124074</v>
+        <v>19.04776470662258</v>
       </c>
       <c r="E709" t="n">
-        <v>19.15270825555125</v>
+        <v>19.15271013121059</v>
       </c>
       <c r="F709" t="n">
         <v>681200</v>
@@ -14612,16 +14612,16 @@
         <v>44615</v>
       </c>
       <c r="B710" t="n">
-        <v>20.35959434509277</v>
+        <v>20.35959243774414</v>
       </c>
       <c r="C710" t="n">
-        <v>20.94554491906982</v>
+        <v>20.94554295682756</v>
       </c>
       <c r="D710" t="n">
-        <v>19.48504134919136</v>
+        <v>19.48503952377351</v>
       </c>
       <c r="E710" t="n">
-        <v>19.53751406188375</v>
+        <v>19.5375122315501</v>
       </c>
       <c r="F710" t="n">
         <v>2509600</v>
@@ -14632,16 +14632,16 @@
         <v>44616</v>
       </c>
       <c r="B711" t="n">
-        <v>20.42081260681152</v>
+        <v>20.42081069946289</v>
       </c>
       <c r="C711" t="n">
-        <v>20.61321366369564</v>
+        <v>20.61321173837633</v>
       </c>
       <c r="D711" t="n">
-        <v>19.02152749216333</v>
+        <v>19.02152571551099</v>
       </c>
       <c r="E711" t="n">
-        <v>19.85235349813248</v>
+        <v>19.85235164387917</v>
       </c>
       <c r="F711" t="n">
         <v>1354200</v>
@@ -14692,16 +14692,16 @@
         <v>44623</v>
       </c>
       <c r="B714" t="n">
-        <v>19.1527099609375</v>
+        <v>19.15271186828613</v>
       </c>
       <c r="C714" t="n">
-        <v>20.95428863573788</v>
+        <v>20.95429072249917</v>
       </c>
       <c r="D714" t="n">
-        <v>19.14396423095334</v>
+        <v>19.14396613743102</v>
       </c>
       <c r="E714" t="n">
-        <v>20.05350013237641</v>
+        <v>20.05350212943145</v>
       </c>
       <c r="F714" t="n">
         <v>833100</v>
@@ -14712,16 +14712,16 @@
         <v>44624</v>
       </c>
       <c r="B715" t="n">
-        <v>18.29564666748047</v>
+        <v>18.2956485748291</v>
       </c>
       <c r="C715" t="n">
-        <v>19.10898112838356</v>
+        <v>19.10898312052353</v>
       </c>
       <c r="D715" t="n">
-        <v>17.93708011324451</v>
+        <v>17.93708198321204</v>
       </c>
       <c r="E715" t="n">
-        <v>19.10898112838356</v>
+        <v>19.10898312052353</v>
       </c>
       <c r="F715" t="n">
         <v>1368000</v>
@@ -14792,16 +14792,16 @@
         <v>44630</v>
       </c>
       <c r="B719" t="n">
-        <v>17.70095252990723</v>
+        <v>17.70095062255859</v>
       </c>
       <c r="C719" t="n">
-        <v>18.61048845110218</v>
+        <v>18.6104864457474</v>
       </c>
       <c r="D719" t="n">
-        <v>17.51729720047986</v>
+        <v>17.51729531292083</v>
       </c>
       <c r="E719" t="n">
-        <v>18.61048845110218</v>
+        <v>18.6104864457474</v>
       </c>
       <c r="F719" t="n">
         <v>1059400</v>
@@ -14832,16 +14832,16 @@
         <v>44634</v>
       </c>
       <c r="B721" t="n">
-        <v>16.52030563354492</v>
+        <v>16.52030372619629</v>
       </c>
       <c r="C721" t="n">
-        <v>16.66897971024399</v>
+        <v>16.66897778573022</v>
       </c>
       <c r="D721" t="n">
-        <v>15.98682943792383</v>
+        <v>15.98682759216759</v>
       </c>
       <c r="E721" t="n">
-        <v>16.60776126714628</v>
+        <v>16.60775934970047</v>
       </c>
       <c r="F721" t="n">
         <v>1266200</v>
@@ -14852,16 +14852,16 @@
         <v>44635</v>
       </c>
       <c r="B722" t="n">
-        <v>16.47657775878906</v>
+        <v>16.4765796661377</v>
       </c>
       <c r="C722" t="n">
-        <v>16.66897880783404</v>
+        <v>16.66898073745525</v>
       </c>
       <c r="D722" t="n">
-        <v>15.8731357544935</v>
+        <v>15.87313759198696</v>
       </c>
       <c r="E722" t="n">
-        <v>16.45034056970582</v>
+        <v>16.4503424740172</v>
       </c>
       <c r="F722" t="n">
         <v>1881800</v>
@@ -14872,16 +14872,16 @@
         <v>44636</v>
       </c>
       <c r="B723" t="n">
-        <v>16.80890655517578</v>
+        <v>16.80890846252441</v>
       </c>
       <c r="C723" t="n">
-        <v>17.1762188490262</v>
+        <v>17.17622079805467</v>
       </c>
       <c r="D723" t="n">
-        <v>16.25793894843882</v>
+        <v>16.25794079326778</v>
       </c>
       <c r="E723" t="n">
-        <v>16.68646967991808</v>
+        <v>16.6864715733735</v>
       </c>
       <c r="F723" t="n">
         <v>1316100</v>
@@ -14912,16 +14912,16 @@
         <v>44638</v>
       </c>
       <c r="B725" t="n">
-        <v>18.00704383850098</v>
+        <v>18.00704574584961</v>
       </c>
       <c r="C725" t="n">
-        <v>18.21693632843434</v>
+        <v>18.21693825801528</v>
       </c>
       <c r="D725" t="n">
-        <v>17.14123669199689</v>
+        <v>17.14123850763719</v>
       </c>
       <c r="E725" t="n">
-        <v>17.46482032178187</v>
+        <v>17.46482217169691</v>
       </c>
       <c r="F725" t="n">
         <v>1389200</v>
@@ -14932,16 +14932,16 @@
         <v>44641</v>
       </c>
       <c r="B726" t="n">
-        <v>17.95457458496094</v>
+        <v>17.9545726776123</v>
       </c>
       <c r="C726" t="n">
-        <v>18.26066681574773</v>
+        <v>18.26066487588234</v>
       </c>
       <c r="D726" t="n">
-        <v>17.46482367954697</v>
+        <v>17.4648218242255</v>
       </c>
       <c r="E726" t="n">
-        <v>17.91959166254099</v>
+        <v>17.91958975890866</v>
       </c>
       <c r="F726" t="n">
         <v>801400</v>
@@ -14972,16 +14972,16 @@
         <v>44643</v>
       </c>
       <c r="B728" t="n">
-        <v>19.1527099609375</v>
+        <v>19.15271186828613</v>
       </c>
       <c r="C728" t="n">
-        <v>19.1527099609375</v>
+        <v>19.15271186828613</v>
       </c>
       <c r="D728" t="n">
-        <v>17.89335320053535</v>
+        <v>17.89335498246923</v>
       </c>
       <c r="E728" t="n">
-        <v>18.80288910195841</v>
+        <v>18.80289097446966</v>
       </c>
       <c r="F728" t="n">
         <v>1156800</v>
@@ -15032,16 +15032,16 @@
         <v>44648</v>
       </c>
       <c r="B731" t="n">
-        <v>20.52576065063477</v>
+        <v>20.52575874328613</v>
       </c>
       <c r="C731" t="n">
-        <v>21.27787685020499</v>
+        <v>21.27787487296624</v>
       </c>
       <c r="D731" t="n">
-        <v>19.98353866291298</v>
+        <v>19.98353680595013</v>
       </c>
       <c r="E731" t="n">
-        <v>21.27787685020499</v>
+        <v>21.27787487296624</v>
       </c>
       <c r="F731" t="n">
         <v>1564100</v>
@@ -15112,16 +15112,16 @@
         <v>44652</v>
       </c>
       <c r="B735" t="n">
-        <v>23.50798606872559</v>
+        <v>23.50798416137695</v>
       </c>
       <c r="C735" t="n">
-        <v>23.62167890330844</v>
+        <v>23.62167698673521</v>
       </c>
       <c r="D735" t="n">
-        <v>22.02124683279554</v>
+        <v>22.02124504607528</v>
       </c>
       <c r="E735" t="n">
-        <v>22.35357626941498</v>
+        <v>22.35357445573077</v>
       </c>
       <c r="F735" t="n">
         <v>2217800</v>
@@ -15192,16 +15192,16 @@
         <v>44658</v>
       </c>
       <c r="B739" t="n">
-        <v>23.26310920715332</v>
+        <v>23.26311111450195</v>
       </c>
       <c r="C739" t="n">
-        <v>23.62167578942707</v>
+        <v>23.62167772617468</v>
       </c>
       <c r="D739" t="n">
-        <v>22.23988217118062</v>
+        <v>22.2398839946346</v>
       </c>
       <c r="E739" t="n">
-        <v>22.45852041247328</v>
+        <v>22.45852225385346</v>
       </c>
       <c r="F739" t="n">
         <v>1772800</v>
@@ -15252,16 +15252,16 @@
         <v>44663</v>
       </c>
       <c r="B742" t="n">
-        <v>22.91329002380371</v>
+        <v>22.91328811645508</v>
       </c>
       <c r="C742" t="n">
-        <v>23.14941807386153</v>
+        <v>23.14941614685713</v>
       </c>
       <c r="D742" t="n">
-        <v>22.44103058753301</v>
+        <v>22.44102871949622</v>
       </c>
       <c r="E742" t="n">
-        <v>22.79085146546824</v>
+        <v>22.79084956831164</v>
       </c>
       <c r="F742" t="n">
         <v>1246700</v>
@@ -15272,16 +15272,16 @@
         <v>44664</v>
       </c>
       <c r="B743" t="n">
-        <v>22.91329002380371</v>
+        <v>22.91328811645508</v>
       </c>
       <c r="C743" t="n">
-        <v>23.31558361640984</v>
+        <v>23.31558167557347</v>
       </c>
       <c r="D743" t="n">
-        <v>22.79959719592631</v>
+        <v>22.7995952980417</v>
       </c>
       <c r="E743" t="n">
-        <v>23.08819962873256</v>
+        <v>23.0881977068241</v>
       </c>
       <c r="F743" t="n">
         <v>777300</v>
@@ -15432,16 +15432,16 @@
         <v>44678</v>
       </c>
       <c r="B751" t="n">
-        <v>21.3828239440918</v>
+        <v>21.38282012939453</v>
       </c>
       <c r="C751" t="n">
-        <v>22.09121148742912</v>
+        <v>22.09120754635547</v>
       </c>
       <c r="D751" t="n">
-        <v>21.19916692584721</v>
+        <v>21.19916314391437</v>
       </c>
       <c r="E751" t="n">
-        <v>21.19916692584721</v>
+        <v>21.19916314391437</v>
       </c>
       <c r="F751" t="n">
         <v>820200</v>
@@ -15472,16 +15472,16 @@
         <v>44680</v>
       </c>
       <c r="B753" t="n">
-        <v>21.10296440124512</v>
+        <v>21.10296249389648</v>
       </c>
       <c r="C753" t="n">
-        <v>21.9075532754437</v>
+        <v>21.90755129537393</v>
       </c>
       <c r="D753" t="n">
-        <v>20.79687216764585</v>
+        <v>20.79687028796274</v>
       </c>
       <c r="E753" t="n">
-        <v>21.7676249206333</v>
+        <v>21.76762295321067</v>
       </c>
       <c r="F753" t="n">
         <v>1100200</v>
@@ -15492,16 +15492,16 @@
         <v>44683</v>
       </c>
       <c r="B754" t="n">
-        <v>20.47709083557129</v>
+        <v>20.47709274291992</v>
       </c>
       <c r="C754" t="n">
-        <v>21.06591713906269</v>
+        <v>21.06591910125784</v>
       </c>
       <c r="D754" t="n">
-        <v>20.14313042410133</v>
+        <v>20.14313230034305</v>
       </c>
       <c r="E754" t="n">
-        <v>20.78468696597976</v>
+        <v>20.78468890197959</v>
       </c>
       <c r="F754" t="n">
         <v>1185300</v>
@@ -15532,16 +15532,16 @@
         <v>44685</v>
       </c>
       <c r="B756" t="n">
-        <v>21.71626091003418</v>
+        <v>21.71626281738281</v>
       </c>
       <c r="C756" t="n">
-        <v>21.71626091003418</v>
+        <v>21.71626281738281</v>
       </c>
       <c r="D756" t="n">
-        <v>19.7388594993526</v>
+        <v>19.7388612330252</v>
       </c>
       <c r="E756" t="n">
-        <v>20.20464799065705</v>
+        <v>20.20464976524007</v>
       </c>
       <c r="F756" t="n">
         <v>1110100</v>
@@ -15592,16 +15592,16 @@
         <v>44690</v>
       </c>
       <c r="B759" t="n">
-        <v>19.17640113830566</v>
+        <v>19.17639923095703</v>
       </c>
       <c r="C759" t="n">
-        <v>19.7915934213024</v>
+        <v>19.7915914527647</v>
       </c>
       <c r="D759" t="n">
-        <v>18.94790119537156</v>
+        <v>18.9478993107503</v>
       </c>
       <c r="E759" t="n">
-        <v>19.4576313215279</v>
+        <v>19.45762938620718</v>
       </c>
       <c r="F759" t="n">
         <v>887700</v>
@@ -15612,16 +15612,16 @@
         <v>44691</v>
       </c>
       <c r="B760" t="n">
-        <v>20.08161354064941</v>
+        <v>20.08161163330078</v>
       </c>
       <c r="C760" t="n">
-        <v>20.38920970180549</v>
+        <v>20.38920776524142</v>
       </c>
       <c r="D760" t="n">
-        <v>19.20276832378304</v>
+        <v>19.202766499907</v>
       </c>
       <c r="E760" t="n">
-        <v>19.29944015777867</v>
+        <v>19.29943832472075</v>
       </c>
       <c r="F760" t="n">
         <v>949400</v>
@@ -15632,16 +15632,16 @@
         <v>44692</v>
       </c>
       <c r="B761" t="n">
-        <v>19.23791885375977</v>
+        <v>19.2379207611084</v>
       </c>
       <c r="C761" t="n">
-        <v>20.52982223372001</v>
+        <v>20.52982426915475</v>
       </c>
       <c r="D761" t="n">
-        <v>19.11488107519746</v>
+        <v>19.11488297034748</v>
       </c>
       <c r="E761" t="n">
-        <v>20.07282237582572</v>
+        <v>20.07282436595109</v>
       </c>
       <c r="F761" t="n">
         <v>1307500</v>
@@ -15652,16 +15652,16 @@
         <v>44693</v>
       </c>
       <c r="B762" t="n">
-        <v>19.23791885375977</v>
+        <v>19.2379207611084</v>
       </c>
       <c r="C762" t="n">
-        <v>20.13434126510687</v>
+        <v>20.13434326133154</v>
       </c>
       <c r="D762" t="n">
-        <v>18.91274710291253</v>
+        <v>18.91274897802192</v>
       </c>
       <c r="E762" t="n">
-        <v>19.03578488147484</v>
+        <v>19.03578676878284</v>
       </c>
       <c r="F762" t="n">
         <v>1657900</v>
@@ -15672,16 +15672,16 @@
         <v>44694</v>
       </c>
       <c r="B763" t="n">
-        <v>19.65097808837891</v>
+        <v>19.65097999572754</v>
       </c>
       <c r="C763" t="n">
-        <v>20.30132329816018</v>
+        <v>20.30132526863213</v>
       </c>
       <c r="D763" t="n">
-        <v>19.4664197352406</v>
+        <v>19.46642162467577</v>
       </c>
       <c r="E763" t="n">
-        <v>19.55430458548436</v>
+        <v>19.55430648344974</v>
       </c>
       <c r="F763" t="n">
         <v>1216300</v>
@@ -15712,16 +15712,16 @@
         <v>44698</v>
       </c>
       <c r="B765" t="n">
-        <v>20.75832176208496</v>
+        <v>20.75832366943359</v>
       </c>
       <c r="C765" t="n">
-        <v>21.71626136796344</v>
+        <v>21.71626336333097</v>
       </c>
       <c r="D765" t="n">
-        <v>20.70558984977813</v>
+        <v>20.70559175228156</v>
       </c>
       <c r="E765" t="n">
-        <v>20.70558984977813</v>
+        <v>20.70559175228156</v>
       </c>
       <c r="F765" t="n">
         <v>809000</v>
@@ -15732,16 +15732,16 @@
         <v>44699</v>
       </c>
       <c r="B766" t="n">
-        <v>20.62649726867676</v>
+        <v>20.62649536132812</v>
       </c>
       <c r="C766" t="n">
-        <v>20.75832539625911</v>
+        <v>20.75832347672022</v>
       </c>
       <c r="D766" t="n">
-        <v>20.01130660377097</v>
+        <v>20.01130475330951</v>
       </c>
       <c r="E766" t="n">
-        <v>20.74074808907956</v>
+        <v>20.74074617116606</v>
       </c>
       <c r="F766" t="n">
         <v>1276700</v>
@@ -15812,16 +15812,16 @@
         <v>44705</v>
       </c>
       <c r="B770" t="n">
-        <v>20.47709083557129</v>
+        <v>20.47709274291992</v>
       </c>
       <c r="C770" t="n">
-        <v>20.94287935740492</v>
+        <v>20.94288130813965</v>
       </c>
       <c r="D770" t="n">
-        <v>20.14313042410133</v>
+        <v>20.14313230034305</v>
       </c>
       <c r="E770" t="n">
-        <v>20.78468696597976</v>
+        <v>20.78468890197959</v>
       </c>
       <c r="F770" t="n">
         <v>904900</v>
@@ -15872,16 +15872,16 @@
         <v>44708</v>
       </c>
       <c r="B773" t="n">
-        <v>21.37351417541504</v>
+        <v>21.37351226806641</v>
       </c>
       <c r="C773" t="n">
-        <v>21.37351417541504</v>
+        <v>21.37351226806641</v>
       </c>
       <c r="D773" t="n">
-        <v>20.45072742134017</v>
+        <v>20.45072559634</v>
       </c>
       <c r="E773" t="n">
-        <v>20.64407275446386</v>
+        <v>20.64407091220977</v>
       </c>
       <c r="F773" t="n">
         <v>733300</v>
@@ -15912,16 +15912,16 @@
         <v>44712</v>
       </c>
       <c r="B775" t="n">
-        <v>21.1362247467041</v>
+        <v>21.13622665405273</v>
       </c>
       <c r="C775" t="n">
-        <v>21.68110946590977</v>
+        <v>21.6811114224292</v>
       </c>
       <c r="D775" t="n">
-        <v>20.90772648757637</v>
+        <v>20.90772837430515</v>
       </c>
       <c r="E775" t="n">
-        <v>21.2328982475948</v>
+        <v>21.23290016366732</v>
       </c>
       <c r="F775" t="n">
         <v>717400</v>
@@ -15972,16 +15972,16 @@
         <v>44715</v>
       </c>
       <c r="B778" t="n">
-        <v>21.97113037109375</v>
+        <v>21.97112846374512</v>
       </c>
       <c r="C778" t="n">
-        <v>22.26114922494162</v>
+        <v>22.26114729241599</v>
       </c>
       <c r="D778" t="n">
-        <v>21.76020772068296</v>
+        <v>21.76020583164485</v>
       </c>
       <c r="E778" t="n">
-        <v>22.26114922494162</v>
+        <v>22.26114729241599</v>
       </c>
       <c r="F778" t="n">
         <v>447800</v>
@@ -16052,16 +16052,16 @@
         <v>44721</v>
       </c>
       <c r="B782" t="n">
-        <v>20.55618667602539</v>
+        <v>20.55618858337402</v>
       </c>
       <c r="C782" t="n">
-        <v>20.68801478411077</v>
+        <v>20.68801670369135</v>
       </c>
       <c r="D782" t="n">
-        <v>20.04645657705588</v>
+        <v>20.04645843710815</v>
       </c>
       <c r="E782" t="n">
-        <v>20.35405270214838</v>
+        <v>20.3540545907416</v>
       </c>
       <c r="F782" t="n">
         <v>748400</v>
@@ -16112,16 +16112,16 @@
         <v>44726</v>
       </c>
       <c r="B785" t="n">
-        <v>18.07784271240234</v>
+        <v>18.07784461975098</v>
       </c>
       <c r="C785" t="n">
-        <v>18.83365000443733</v>
+        <v>18.83365199152933</v>
       </c>
       <c r="D785" t="n">
-        <v>17.831767167099</v>
+        <v>17.83176904848481</v>
       </c>
       <c r="E785" t="n">
-        <v>18.55241985193983</v>
+        <v>18.55242180935992</v>
       </c>
       <c r="F785" t="n">
         <v>1231100</v>
@@ -16152,16 +16152,16 @@
         <v>44729</v>
       </c>
       <c r="B787" t="n">
-        <v>18.20967292785645</v>
+        <v>18.20967102050781</v>
       </c>
       <c r="C787" t="n">
-        <v>18.21846158148466</v>
+        <v>18.21845967321547</v>
       </c>
       <c r="D787" t="n">
-        <v>17.41871254022415</v>
+        <v>17.41871071572364</v>
       </c>
       <c r="E787" t="n">
-        <v>18.06026916870535</v>
+        <v>18.06026727700582</v>
       </c>
       <c r="F787" t="n">
         <v>1568800</v>
@@ -16172,16 +16172,16 @@
         <v>44732</v>
       </c>
       <c r="B788" t="n">
-        <v>17.8405590057373</v>
+        <v>17.84055709838867</v>
       </c>
       <c r="C788" t="n">
-        <v>18.47332869760538</v>
+        <v>18.47332672260683</v>
       </c>
       <c r="D788" t="n">
-        <v>17.47144391090239</v>
+        <v>17.47144204301615</v>
       </c>
       <c r="E788" t="n">
-        <v>18.10421360277047</v>
+        <v>18.10421166723431</v>
       </c>
       <c r="F788" t="n">
         <v>715300</v>
@@ -16212,16 +16212,16 @@
         <v>44734</v>
       </c>
       <c r="B790" t="n">
-        <v>17.62084579467773</v>
+        <v>17.6208438873291</v>
       </c>
       <c r="C790" t="n">
-        <v>17.98117219677237</v>
+        <v>17.98117025042061</v>
       </c>
       <c r="D790" t="n">
-        <v>17.30446265885331</v>
+        <v>17.30446078575121</v>
       </c>
       <c r="E790" t="n">
-        <v>17.46265506489762</v>
+        <v>17.46265317467217</v>
       </c>
       <c r="F790" t="n">
         <v>1115800</v>
@@ -16232,16 +16232,16 @@
         <v>44735</v>
       </c>
       <c r="B791" t="n">
-        <v>17.8405590057373</v>
+        <v>17.84055709838867</v>
       </c>
       <c r="C791" t="n">
-        <v>18.20088544637801</v>
+        <v>18.20088350050658</v>
       </c>
       <c r="D791" t="n">
-        <v>17.43629097038994</v>
+        <v>17.43628910626192</v>
       </c>
       <c r="E791" t="n">
-        <v>17.8405590057373</v>
+        <v>17.84055709838867</v>
       </c>
       <c r="F791" t="n">
         <v>3238200</v>
@@ -16252,16 +16252,16 @@
         <v>44736</v>
       </c>
       <c r="B792" t="n">
-        <v>17.4099235534668</v>
+        <v>17.40992164611816</v>
       </c>
       <c r="C792" t="n">
-        <v>18.17451964184861</v>
+        <v>18.17451765073446</v>
       </c>
       <c r="D792" t="n">
-        <v>17.21657820613845</v>
+        <v>17.21657631997182</v>
       </c>
       <c r="E792" t="n">
-        <v>17.98996127171607</v>
+        <v>17.98995930082126</v>
       </c>
       <c r="F792" t="n">
         <v>1906300</v>
@@ -16292,16 +16292,16 @@
         <v>44740</v>
       </c>
       <c r="B794" t="n">
-        <v>16.82988357543945</v>
+        <v>16.82988548278809</v>
       </c>
       <c r="C794" t="n">
-        <v>17.92843996647681</v>
+        <v>17.92844199832601</v>
       </c>
       <c r="D794" t="n">
-        <v>16.3992496713045</v>
+        <v>16.39925152984893</v>
       </c>
       <c r="E794" t="n">
-        <v>17.77903623024517</v>
+        <v>17.77903824516228</v>
       </c>
       <c r="F794" t="n">
         <v>1885300</v>
@@ -16352,16 +16352,16 @@
         <v>44743</v>
       </c>
       <c r="B797" t="n">
-        <v>16.67169380187988</v>
+        <v>16.67169189453125</v>
       </c>
       <c r="C797" t="n">
-        <v>16.86504082983788</v>
+        <v>16.8650389003691</v>
       </c>
       <c r="D797" t="n">
-        <v>16.28500309849247</v>
+        <v>16.28500123538373</v>
       </c>
       <c r="E797" t="n">
-        <v>16.72442572383077</v>
+        <v>16.72442381044926</v>
       </c>
       <c r="F797" t="n">
         <v>780700</v>
@@ -16372,16 +16372,16 @@
         <v>44746</v>
       </c>
       <c r="B798" t="n">
-        <v>16.20590400695801</v>
+        <v>16.20590591430664</v>
       </c>
       <c r="C798" t="n">
-        <v>16.78594163504879</v>
+        <v>16.78594361066477</v>
       </c>
       <c r="D798" t="n">
-        <v>16.1180191622822</v>
+        <v>16.11802105928725</v>
       </c>
       <c r="E798" t="n">
-        <v>16.4519795605335</v>
+        <v>16.45198149684391</v>
       </c>
       <c r="F798" t="n">
         <v>455600</v>
@@ -16452,16 +16452,16 @@
         <v>44750</v>
       </c>
       <c r="B802" t="n">
-        <v>17.96359825134277</v>
+        <v>17.96359634399414</v>
       </c>
       <c r="C802" t="n">
-        <v>18.09542470998903</v>
+        <v>18.09542278864326</v>
       </c>
       <c r="D802" t="n">
-        <v>17.53296425909066</v>
+        <v>17.53296239746611</v>
       </c>
       <c r="E802" t="n">
-        <v>17.67357937181525</v>
+        <v>17.6735774952604</v>
       </c>
       <c r="F802" t="n">
         <v>1053700</v>
@@ -16572,16 +16572,16 @@
         <v>44760</v>
       </c>
       <c r="B808" t="n">
-        <v>15.86315441131592</v>
+        <v>15.86315536499023</v>
       </c>
       <c r="C808" t="n">
-        <v>17.08475031924931</v>
+        <v>17.08475134636454</v>
       </c>
       <c r="D808" t="n">
-        <v>15.86315441131592</v>
+        <v>15.86315536499023</v>
       </c>
       <c r="E808" t="n">
-        <v>16.68926932814423</v>
+        <v>16.68927033148361</v>
       </c>
       <c r="F808" t="n">
         <v>925600</v>
@@ -16612,16 +16612,16 @@
         <v>44762</v>
       </c>
       <c r="B810" t="n">
-        <v>16.98807716369629</v>
+        <v>16.98807907104492</v>
       </c>
       <c r="C810" t="n">
-        <v>17.1814224987184</v>
+        <v>17.18142442777502</v>
       </c>
       <c r="D810" t="n">
-        <v>15.95103958911631</v>
+        <v>15.9510413800308</v>
       </c>
       <c r="E810" t="n">
-        <v>15.95103958911631</v>
+        <v>15.9510413800308</v>
       </c>
       <c r="F810" t="n">
         <v>1160100</v>
@@ -16672,16 +16672,16 @@
         <v>44767</v>
       </c>
       <c r="B813" t="n">
-        <v>17.77024841308594</v>
+        <v>17.7702465057373</v>
       </c>
       <c r="C813" t="n">
-        <v>18.00753700700486</v>
+        <v>18.00753507418713</v>
       </c>
       <c r="D813" t="n">
-        <v>17.21657670353923</v>
+        <v>17.2165748556183</v>
       </c>
       <c r="E813" t="n">
-        <v>17.49780688465909</v>
+        <v>17.49780500655265</v>
       </c>
       <c r="F813" t="n">
         <v>924300</v>
@@ -16772,16 +16772,16 @@
         <v>44774</v>
       </c>
       <c r="B818" t="n">
-        <v>19.26428413391113</v>
+        <v>19.26428604125977</v>
       </c>
       <c r="C818" t="n">
-        <v>19.46641809909765</v>
+        <v>19.46642002645948</v>
       </c>
       <c r="D818" t="n">
-        <v>18.1745164407696</v>
+        <v>18.1745182402208</v>
       </c>
       <c r="E818" t="n">
-        <v>18.29755421501114</v>
+        <v>18.29755602664425</v>
       </c>
       <c r="F818" t="n">
         <v>1521200</v>
@@ -16792,16 +16792,16 @@
         <v>44775</v>
       </c>
       <c r="B819" t="n">
-        <v>18.06026649475098</v>
+        <v>18.06026840209961</v>
       </c>
       <c r="C819" t="n">
-        <v>19.11488130629347</v>
+        <v>19.1148833250202</v>
       </c>
       <c r="D819" t="n">
-        <v>17.7702476730164</v>
+        <v>17.77024954973608</v>
       </c>
       <c r="E819" t="n">
-        <v>19.06215106859556</v>
+        <v>19.06215308175343</v>
       </c>
       <c r="F819" t="n">
         <v>3204200</v>
@@ -16812,16 +16812,16 @@
         <v>44776</v>
       </c>
       <c r="B820" t="n">
-        <v>18.73698043823242</v>
+        <v>18.73697853088379</v>
       </c>
       <c r="C820" t="n">
-        <v>18.73698043823242</v>
+        <v>18.73697853088379</v>
       </c>
       <c r="D820" t="n">
-        <v>17.06717480058537</v>
+        <v>17.06717306321618</v>
       </c>
       <c r="E820" t="n">
-        <v>18.13936540078175</v>
+        <v>18.1393635542679</v>
       </c>
       <c r="F820" t="n">
         <v>3348000</v>
@@ -16872,16 +16872,16 @@
         <v>44781</v>
       </c>
       <c r="B823" t="n">
-        <v>19.73007392883301</v>
+        <v>19.73007583618164</v>
       </c>
       <c r="C823" t="n">
-        <v>20.16949649583362</v>
+        <v>20.16949844566217</v>
       </c>
       <c r="D823" t="n">
-        <v>19.39611183920467</v>
+        <v>19.39611371426847</v>
       </c>
       <c r="E823" t="n">
-        <v>19.73007392883301</v>
+        <v>19.73007583618164</v>
       </c>
       <c r="F823" t="n">
         <v>1006200</v>
@@ -16952,16 +16952,16 @@
         <v>44785</v>
       </c>
       <c r="B827" t="n">
-        <v>19.87947845458984</v>
+        <v>19.87947654724121</v>
       </c>
       <c r="C827" t="n">
-        <v>19.98493893613145</v>
+        <v>19.98493701866434</v>
       </c>
       <c r="D827" t="n">
-        <v>19.39611260602109</v>
+        <v>19.39611074504928</v>
       </c>
       <c r="E827" t="n">
-        <v>19.39611260602109</v>
+        <v>19.39611074504928</v>
       </c>
       <c r="F827" t="n">
         <v>1366700</v>
@@ -17092,16 +17092,16 @@
         <v>44796</v>
       </c>
       <c r="B834" t="n">
-        <v>18.06026649475098</v>
+        <v>18.06026840209961</v>
       </c>
       <c r="C834" t="n">
-        <v>18.23603618876274</v>
+        <v>18.23603811467444</v>
       </c>
       <c r="D834" t="n">
-        <v>17.52417211291677</v>
+        <v>17.52417396364836</v>
       </c>
       <c r="E834" t="n">
-        <v>17.65599854529357</v>
+        <v>17.65600040994738</v>
       </c>
       <c r="F834" t="n">
         <v>3245100</v>
@@ -17132,16 +17132,16 @@
         <v>44798</v>
       </c>
       <c r="B836" t="n">
-        <v>18.80728721618652</v>
+        <v>18.80728530883789</v>
       </c>
       <c r="C836" t="n">
-        <v>19.20276823240005</v>
+        <v>19.20276628494355</v>
       </c>
       <c r="D836" t="n">
-        <v>18.42938350653009</v>
+        <v>18.42938163750672</v>
       </c>
       <c r="E836" t="n">
-        <v>18.6842494228153</v>
+        <v>18.6842475279446</v>
       </c>
       <c r="F836" t="n">
         <v>1238700</v>
@@ -17152,16 +17152,16 @@
         <v>44799</v>
       </c>
       <c r="B837" t="n">
-        <v>19.11488342285156</v>
+        <v>19.11488151550293</v>
       </c>
       <c r="C837" t="n">
-        <v>19.23792121652514</v>
+        <v>19.23791929689937</v>
       </c>
       <c r="D837" t="n">
-        <v>18.54363436845597</v>
+        <v>18.54363251810853</v>
       </c>
       <c r="E837" t="n">
-        <v>18.80728726240341</v>
+        <v>18.80728538574777</v>
       </c>
       <c r="F837" t="n">
         <v>1224800</v>
@@ -17252,16 +17252,16 @@
         <v>44806</v>
       </c>
       <c r="B842" t="n">
-        <v>19.86190223693848</v>
+        <v>19.86190032958984</v>
       </c>
       <c r="C842" t="n">
-        <v>20.21343998844113</v>
+        <v>20.21343804733415</v>
       </c>
       <c r="D842" t="n">
-        <v>19.54551742245398</v>
+        <v>19.54551554548794</v>
       </c>
       <c r="E842" t="n">
-        <v>19.94978709388019</v>
+        <v>19.94978517809193</v>
       </c>
       <c r="F842" t="n">
         <v>920700</v>
@@ -17472,16 +17472,16 @@
         <v>44824</v>
       </c>
       <c r="B853" t="n">
-        <v>19.65097808837891</v>
+        <v>19.65097999572754</v>
       </c>
       <c r="C853" t="n">
-        <v>19.99372716043906</v>
+        <v>19.99372910105535</v>
       </c>
       <c r="D853" t="n">
-        <v>19.53672728018279</v>
+        <v>19.5367291764421</v>
       </c>
       <c r="E853" t="n">
-        <v>19.77401587296171</v>
+        <v>19.77401779225255</v>
       </c>
       <c r="F853" t="n">
         <v>968100</v>
@@ -17512,16 +17512,16 @@
         <v>44826</v>
       </c>
       <c r="B855" t="n">
-        <v>20.91651344299316</v>
+        <v>20.9165153503418</v>
       </c>
       <c r="C855" t="n">
-        <v>21.07470583474289</v>
+        <v>21.07470775651687</v>
       </c>
       <c r="D855" t="n">
-        <v>19.79159274835349</v>
+        <v>19.79159455312212</v>
       </c>
       <c r="E855" t="n">
-        <v>20.31890016209787</v>
+        <v>20.31890201495095</v>
       </c>
       <c r="F855" t="n">
         <v>1592700</v>
@@ -17532,16 +17532,16 @@
         <v>44827</v>
       </c>
       <c r="B856" t="n">
-        <v>20.15191841125488</v>
+        <v>20.15192031860352</v>
       </c>
       <c r="C856" t="n">
-        <v>20.61770524144714</v>
+        <v>20.61770719288179</v>
       </c>
       <c r="D856" t="n">
-        <v>19.95857141644542</v>
+        <v>19.95857330549405</v>
       </c>
       <c r="E856" t="n">
-        <v>20.4858788116996</v>
+        <v>20.48588075065707</v>
       </c>
       <c r="F856" t="n">
         <v>1009700</v>
@@ -17572,16 +17572,16 @@
         <v>44831</v>
       </c>
       <c r="B858" t="n">
-        <v>18.37665176391602</v>
+        <v>18.37664985656738</v>
       </c>
       <c r="C858" t="n">
-        <v>19.28186286258666</v>
+        <v>19.28186086128439</v>
       </c>
       <c r="D858" t="n">
-        <v>18.35028580623137</v>
+        <v>18.35028390161931</v>
       </c>
       <c r="E858" t="n">
-        <v>19.21155531835834</v>
+        <v>19.21155332435344</v>
       </c>
       <c r="F858" t="n">
         <v>1438200</v>
@@ -17612,16 +17612,16 @@
         <v>44833</v>
       </c>
       <c r="B860" t="n">
-        <v>17.13748168945312</v>
+        <v>17.13747978210449</v>
       </c>
       <c r="C860" t="n">
-        <v>17.92844204755966</v>
+        <v>17.92844005217959</v>
       </c>
       <c r="D860" t="n">
-        <v>16.87382879550569</v>
+        <v>16.8738269175008</v>
       </c>
       <c r="E860" t="n">
-        <v>17.8932891106233</v>
+        <v>17.89328711915564</v>
       </c>
       <c r="F860" t="n">
         <v>2571700</v>
@@ -17652,16 +17652,16 @@
         <v>44837</v>
       </c>
       <c r="B862" t="n">
-        <v>18.80728721618652</v>
+        <v>18.80728530883789</v>
       </c>
       <c r="C862" t="n">
-        <v>18.92153803254341</v>
+        <v>18.92153611360799</v>
       </c>
       <c r="D862" t="n">
-        <v>18.10421171654494</v>
+        <v>18.104209880499</v>
       </c>
       <c r="E862" t="n">
-        <v>18.10421171654494</v>
+        <v>18.104209880499</v>
       </c>
       <c r="F862" t="n">
         <v>1460600</v>
@@ -17692,16 +17692,16 @@
         <v>44839</v>
       </c>
       <c r="B864" t="n">
-        <v>18.42938423156738</v>
+        <v>18.42938232421875</v>
       </c>
       <c r="C864" t="n">
-        <v>18.81607660971537</v>
+        <v>18.81607466234602</v>
       </c>
       <c r="D864" t="n">
-        <v>18.14815402064677</v>
+        <v>18.14815214240405</v>
       </c>
       <c r="E864" t="n">
-        <v>18.76334636423382</v>
+        <v>18.76334442232179</v>
       </c>
       <c r="F864" t="n">
         <v>1100000</v>
@@ -17732,16 +17732,16 @@
         <v>44841</v>
       </c>
       <c r="B866" t="n">
-        <v>17.4714412689209</v>
+        <v>17.47144317626953</v>
       </c>
       <c r="C866" t="n">
-        <v>18.50847883931848</v>
+        <v>18.50848085988</v>
       </c>
       <c r="D866" t="n">
-        <v>17.41871102799374</v>
+        <v>17.41871292958584</v>
       </c>
       <c r="E866" t="n">
-        <v>18.44695994552611</v>
+        <v>18.44696195937163</v>
       </c>
       <c r="F866" t="n">
         <v>1871900</v>
@@ -17752,16 +17752,16 @@
         <v>44844</v>
       </c>
       <c r="B867" t="n">
-        <v>17.6384220123291</v>
+        <v>17.63842391967773</v>
       </c>
       <c r="C867" t="n">
-        <v>17.86692195403576</v>
+        <v>17.86692388609347</v>
       </c>
       <c r="D867" t="n">
-        <v>16.99686545076662</v>
+        <v>16.99686728873989</v>
       </c>
       <c r="E867" t="n">
-        <v>17.50659557418483</v>
+        <v>17.50659746727828</v>
       </c>
       <c r="F867" t="n">
         <v>1289600</v>
@@ -17792,16 +17792,16 @@
         <v>44847</v>
       </c>
       <c r="B869" t="n">
-        <v>17.35719299316406</v>
+        <v>17.35719108581543</v>
       </c>
       <c r="C869" t="n">
-        <v>18.08663445443381</v>
+        <v>18.08663246692825</v>
       </c>
       <c r="D869" t="n">
-        <v>17.05838548601605</v>
+        <v>17.0583836115028</v>
       </c>
       <c r="E869" t="n">
-        <v>17.31325140292756</v>
+        <v>17.31324950040759</v>
       </c>
       <c r="F869" t="n">
         <v>1490400</v>
@@ -17832,16 +17832,16 @@
         <v>44851</v>
       </c>
       <c r="B871" t="n">
-        <v>16.71563720703125</v>
+        <v>16.71563529968262</v>
       </c>
       <c r="C871" t="n">
-        <v>17.18142412089432</v>
+        <v>17.18142216039677</v>
       </c>
       <c r="D871" t="n">
-        <v>16.53107883122067</v>
+        <v>16.53107694493119</v>
       </c>
       <c r="E871" t="n">
-        <v>16.69805989957037</v>
+        <v>16.69805799422741</v>
       </c>
       <c r="F871" t="n">
         <v>1186700</v>
@@ -17852,16 +17852,16 @@
         <v>44852</v>
       </c>
       <c r="B872" t="n">
-        <v>16.49592590332031</v>
+        <v>16.49592399597168</v>
       </c>
       <c r="C872" t="n">
-        <v>17.09354094726535</v>
+        <v>17.09353897081722</v>
       </c>
       <c r="D872" t="n">
-        <v>16.39046373475059</v>
+        <v>16.39046183959607</v>
       </c>
       <c r="E872" t="n">
-        <v>16.90019391759825</v>
+        <v>16.90019196350595</v>
       </c>
       <c r="F872" t="n">
         <v>864000</v>
@@ -17872,16 +17872,16 @@
         <v>44853</v>
       </c>
       <c r="B873" t="n">
-        <v>16.10923385620117</v>
+        <v>16.10923194885254</v>
       </c>
       <c r="C873" t="n">
-        <v>16.53107918674884</v>
+        <v>16.53107722945332</v>
       </c>
       <c r="D873" t="n">
-        <v>15.90709984484679</v>
+        <v>15.90709796143102</v>
       </c>
       <c r="E873" t="n">
-        <v>16.43440734616354</v>
+        <v>16.43440540031406</v>
       </c>
       <c r="F873" t="n">
         <v>1513900</v>
@@ -17912,16 +17912,16 @@
         <v>44855</v>
       </c>
       <c r="B875" t="n">
-        <v>15.79284858703613</v>
+        <v>15.79284763336182</v>
       </c>
       <c r="C875" t="n">
-        <v>15.98619561543282</v>
+        <v>15.98619465008296</v>
       </c>
       <c r="D875" t="n">
-        <v>15.37979192173608</v>
+        <v>15.3797909930048</v>
       </c>
       <c r="E875" t="n">
-        <v>15.67859944174524</v>
+        <v>15.67859849497003</v>
       </c>
       <c r="F875" t="n">
         <v>2557500</v>
@@ -17952,16 +17952,16 @@
         <v>44859</v>
       </c>
       <c r="B877" t="n">
-        <v>16.10923385620117</v>
+        <v>16.10923194885254</v>
       </c>
       <c r="C877" t="n">
-        <v>16.45198297773811</v>
+        <v>16.45198102980765</v>
       </c>
       <c r="D877" t="n">
-        <v>15.42373393686296</v>
+        <v>15.42373211067817</v>
       </c>
       <c r="E877" t="n">
-        <v>15.50283014587369</v>
+        <v>15.50282831032383</v>
       </c>
       <c r="F877" t="n">
         <v>2142700</v>
@@ -18052,16 +18052,16 @@
         <v>44866</v>
       </c>
       <c r="B882" t="n">
-        <v>16.61896133422852</v>
+        <v>16.61896324157715</v>
       </c>
       <c r="C882" t="n">
-        <v>16.9529234235427</v>
+        <v>16.95292536921997</v>
       </c>
       <c r="D882" t="n">
-        <v>16.3289425073315</v>
+        <v>16.32894438139483</v>
       </c>
       <c r="E882" t="n">
-        <v>16.64532729167881</v>
+        <v>16.64532920205345</v>
       </c>
       <c r="F882" t="n">
         <v>868200</v>
@@ -18092,16 +18092,16 @@
         <v>44869</v>
       </c>
       <c r="B884" t="n">
-        <v>17.57690238952637</v>
+        <v>17.576904296875</v>
       </c>
       <c r="C884" t="n">
-        <v>18.57878528932488</v>
+        <v>18.57878730539232</v>
       </c>
       <c r="D884" t="n">
-        <v>17.45386460920417</v>
+        <v>17.45386650320143</v>
       </c>
       <c r="E884" t="n">
-        <v>18.18330599131896</v>
+        <v>18.18330796447117</v>
       </c>
       <c r="F884" t="n">
         <v>3920800</v>
@@ -18112,16 +18112,16 @@
         <v>44872</v>
       </c>
       <c r="B885" t="n">
-        <v>16.56623077392578</v>
+        <v>16.56623268127441</v>
       </c>
       <c r="C885" t="n">
-        <v>17.60326827913779</v>
+        <v>17.60327030588547</v>
       </c>
       <c r="D885" t="n">
-        <v>16.35530814721107</v>
+        <v>16.35531003027518</v>
       </c>
       <c r="E885" t="n">
-        <v>17.44507589003575</v>
+        <v>17.44507789856999</v>
       </c>
       <c r="F885" t="n">
         <v>2016600</v>
@@ -18132,16 +18132,16 @@
         <v>44873</v>
       </c>
       <c r="B886" t="n">
-        <v>16.62774848937988</v>
+        <v>16.62775039672852</v>
       </c>
       <c r="C886" t="n">
-        <v>16.85624840458048</v>
+        <v>16.85625033814005</v>
       </c>
       <c r="D886" t="n">
-        <v>16.09165247001449</v>
+        <v>16.09165431586821</v>
       </c>
       <c r="E886" t="n">
-        <v>16.34651834029113</v>
+        <v>16.3465202153802</v>
       </c>
       <c r="F886" t="n">
         <v>1504900</v>
@@ -18172,16 +18172,16 @@
         <v>44875</v>
       </c>
       <c r="B888" t="n">
-        <v>14.7997522354126</v>
+        <v>14.79975318908691</v>
       </c>
       <c r="C888" t="n">
-        <v>16.2146934418356</v>
+        <v>16.21469448668665</v>
       </c>
       <c r="D888" t="n">
-        <v>14.59761825628476</v>
+        <v>14.59761919693386</v>
       </c>
       <c r="E888" t="n">
-        <v>16.2146934418356</v>
+        <v>16.21469448668665</v>
       </c>
       <c r="F888" t="n">
         <v>2325200</v>
@@ -18252,16 +18252,16 @@
         <v>44882</v>
       </c>
       <c r="B892" t="n">
-        <v>13.12115955352783</v>
+        <v>13.12115859985352</v>
       </c>
       <c r="C892" t="n">
-        <v>13.42875488118198</v>
+        <v>13.42875390515097</v>
       </c>
       <c r="D892" t="n">
-        <v>12.40929454837236</v>
+        <v>12.40929364643793</v>
       </c>
       <c r="E892" t="n">
-        <v>13.34965867637224</v>
+        <v>13.34965770609012</v>
       </c>
       <c r="F892" t="n">
         <v>4205200</v>
@@ -18292,16 +18292,16 @@
         <v>44886</v>
       </c>
       <c r="B894" t="n">
-        <v>13.67483043670654</v>
+        <v>13.67483139038086</v>
       </c>
       <c r="C894" t="n">
-        <v>13.8505992930895</v>
+        <v>13.85060025902183</v>
       </c>
       <c r="D894" t="n">
-        <v>13.12994572472134</v>
+        <v>13.12994664039573</v>
       </c>
       <c r="E894" t="n">
-        <v>13.25298434325542</v>
+        <v>13.25298526751045</v>
       </c>
       <c r="F894" t="n">
         <v>1078200</v>
@@ -18452,16 +18452,16 @@
         <v>44896</v>
       </c>
       <c r="B902" t="n">
-        <v>12.48838996887207</v>
+        <v>12.48838901519775</v>
       </c>
       <c r="C902" t="n">
-        <v>12.77840880953892</v>
+        <v>12.77840783371735</v>
       </c>
       <c r="D902" t="n">
-        <v>12.15442870183375</v>
+        <v>12.15442777366234</v>
       </c>
       <c r="E902" t="n">
-        <v>12.77840880953892</v>
+        <v>12.77840783371735</v>
       </c>
       <c r="F902" t="n">
         <v>3444900</v>
@@ -18572,16 +18572,16 @@
         <v>44904</v>
       </c>
       <c r="B908" t="n">
-        <v>10.65160274505615</v>
+        <v>10.65160369873047</v>
       </c>
       <c r="C908" t="n">
-        <v>11.18769796608733</v>
+        <v>11.18769896776008</v>
       </c>
       <c r="D908" t="n">
-        <v>10.55493008366326</v>
+        <v>10.55493102868214</v>
       </c>
       <c r="E908" t="n">
-        <v>11.0470828811042</v>
+        <v>11.0470838701872</v>
       </c>
       <c r="F908" t="n">
         <v>1248000</v>
@@ -18672,16 +18672,16 @@
         <v>44911</v>
       </c>
       <c r="B913" t="n">
-        <v>9.368490219116211</v>
+        <v>9.368489265441895</v>
       </c>
       <c r="C913" t="n">
-        <v>10.03641280942789</v>
+        <v>10.03641178776176</v>
       </c>
       <c r="D913" t="n">
-        <v>9.368490219116211</v>
+        <v>9.368489265441895</v>
       </c>
       <c r="E913" t="n">
-        <v>9.948527949285561</v>
+        <v>9.948526936565756</v>
       </c>
       <c r="F913" t="n">
         <v>2559600</v>
@@ -18692,16 +18692,16 @@
         <v>44914</v>
       </c>
       <c r="B914" t="n">
-        <v>10.22975826263428</v>
+        <v>10.22975730895996</v>
       </c>
       <c r="C914" t="n">
-        <v>10.33521958433582</v>
+        <v>10.33521862082982</v>
       </c>
       <c r="D914" t="n">
-        <v>9.421220624790395</v>
+        <v>9.421219746492405</v>
       </c>
       <c r="E914" t="n">
-        <v>9.421220624790395</v>
+        <v>9.421219746492405</v>
       </c>
       <c r="F914" t="n">
         <v>2225500</v>
@@ -18772,16 +18772,16 @@
         <v>44918</v>
       </c>
       <c r="B918" t="n">
-        <v>11.80289173126221</v>
+        <v>11.80289077758789</v>
       </c>
       <c r="C918" t="n">
-        <v>12.08412193723559</v>
+        <v>12.08412096083786</v>
       </c>
       <c r="D918" t="n">
-        <v>11.32831533961606</v>
+        <v>11.32831442428754</v>
       </c>
       <c r="E918" t="n">
-        <v>11.38104558417001</v>
+        <v>11.38104466458088</v>
       </c>
       <c r="F918" t="n">
         <v>2056800</v>
@@ -18812,16 +18812,16 @@
         <v>44922</v>
       </c>
       <c r="B920" t="n">
-        <v>11.05587291717529</v>
+        <v>11.05587196350098</v>
       </c>
       <c r="C920" t="n">
-        <v>11.70621818568393</v>
+        <v>11.70621717591114</v>
       </c>
       <c r="D920" t="n">
-        <v>10.95920024368308</v>
+        <v>10.9591992983477</v>
       </c>
       <c r="E920" t="n">
-        <v>11.51287283869949</v>
+        <v>11.51287184560458</v>
       </c>
       <c r="F920" t="n">
         <v>1934200</v>
@@ -18852,16 +18852,16 @@
         <v>44924</v>
       </c>
       <c r="B922" t="n">
-        <v>11.23164081573486</v>
+        <v>11.23164176940918</v>
       </c>
       <c r="C922" t="n">
-        <v>11.61833315223914</v>
+        <v>11.61833413874736</v>
       </c>
       <c r="D922" t="n">
-        <v>10.8361606646848</v>
+        <v>10.83616158477905</v>
       </c>
       <c r="E922" t="n">
-        <v>11.25800677376837</v>
+        <v>11.25800772968141</v>
       </c>
       <c r="F922" t="n">
         <v>1066700</v>
@@ -18892,16 +18892,16 @@
         <v>44929</v>
       </c>
       <c r="B924" t="n">
-        <v>9.957315444946289</v>
+        <v>9.957314491271973</v>
       </c>
       <c r="C924" t="n">
-        <v>10.59008418524001</v>
+        <v>10.59008317096148</v>
       </c>
       <c r="D924" t="n">
-        <v>9.922161672603973</v>
+        <v>9.922160722296553</v>
       </c>
       <c r="E924" t="n">
-        <v>10.44946909587075</v>
+        <v>10.4494680950598</v>
       </c>
       <c r="F924" t="n">
         <v>920100</v>
@@ -18912,16 +18912,16 @@
         <v>44930</v>
       </c>
       <c r="B925" t="n">
-        <v>10.18581485748291</v>
+        <v>10.18581581115723</v>
       </c>
       <c r="C925" t="n">
-        <v>10.3527950579406</v>
+        <v>10.35279602724888</v>
       </c>
       <c r="D925" t="n">
-        <v>9.89579604112398</v>
+        <v>9.895796967644506</v>
       </c>
       <c r="E925" t="n">
-        <v>10.00125735269705</v>
+        <v>10.00125828909167</v>
       </c>
       <c r="F925" t="n">
         <v>928500</v>
@@ -19032,16 +19032,16 @@
         <v>44938</v>
       </c>
       <c r="B931" t="n">
-        <v>9.66729736328125</v>
+        <v>9.667296409606934</v>
       </c>
       <c r="C931" t="n">
-        <v>10.12429727730341</v>
+        <v>10.12429627854627</v>
       </c>
       <c r="D931" t="n">
-        <v>9.412432284501847</v>
+        <v>9.412431355969849</v>
       </c>
       <c r="E931" t="n">
-        <v>10.06277754233452</v>
+        <v>10.06277654964627</v>
       </c>
       <c r="F931" t="n">
         <v>3972100</v>
@@ -19072,16 +19072,16 @@
         <v>44942</v>
       </c>
       <c r="B933" t="n">
-        <v>9.403643608093262</v>
+        <v>9.403642654418945</v>
       </c>
       <c r="C933" t="n">
-        <v>9.56183601457867</v>
+        <v>9.561835044861208</v>
       </c>
       <c r="D933" t="n">
-        <v>9.157567183218708</v>
+        <v>9.157566254500333</v>
       </c>
       <c r="E933" t="n">
-        <v>9.544258708021578</v>
+        <v>9.544257740086724</v>
       </c>
       <c r="F933" t="n">
         <v>2501700</v>
@@ -19112,16 +19112,16 @@
         <v>44944</v>
       </c>
       <c r="B935" t="n">
-        <v>9.456375122070312</v>
+        <v>9.456374168395996</v>
       </c>
       <c r="C935" t="n">
-        <v>9.939740178777154</v>
+        <v>9.939739176355527</v>
       </c>
       <c r="D935" t="n">
-        <v>9.377278915210557</v>
+        <v>9.377277969513083</v>
       </c>
       <c r="E935" t="n">
-        <v>9.623355351338128</v>
+        <v>9.623354380823875</v>
       </c>
       <c r="F935" t="n">
         <v>1595600</v>
@@ -19152,16 +19152,16 @@
         <v>44946</v>
       </c>
       <c r="B937" t="n">
-        <v>9.403643608093262</v>
+        <v>9.403642654418945</v>
       </c>
       <c r="C937" t="n">
-        <v>9.588201136282203</v>
+        <v>9.58820016389091</v>
       </c>
       <c r="D937" t="n">
-        <v>9.166355836497255</v>
+        <v>9.166354906887573</v>
       </c>
       <c r="E937" t="n">
-        <v>9.359701179832637</v>
+        <v>9.359700230614759</v>
       </c>
       <c r="F937" t="n">
         <v>1347600</v>
@@ -19292,16 +19292,16 @@
         <v>44957</v>
       </c>
       <c r="B944" t="n">
-        <v>9.737605094909668</v>
+        <v>9.737604141235352</v>
       </c>
       <c r="C944" t="n">
-        <v>9.799123992893056</v>
+        <v>9.799123033193748</v>
       </c>
       <c r="D944" t="n">
-        <v>9.509105133639757</v>
+        <v>9.509104202344099</v>
       </c>
       <c r="E944" t="n">
-        <v>9.526682440567654</v>
+        <v>9.526681507550524</v>
       </c>
       <c r="F944" t="n">
         <v>1073600</v>
@@ -19352,16 +19352,16 @@
         <v>44960</v>
       </c>
       <c r="B947" t="n">
-        <v>8.876336097717285</v>
+        <v>8.876337051391602</v>
       </c>
       <c r="C947" t="n">
-        <v>9.66729637496131</v>
+        <v>9.667297413616467</v>
       </c>
       <c r="D947" t="n">
-        <v>8.876336097717285</v>
+        <v>8.876337051391602</v>
       </c>
       <c r="E947" t="n">
-        <v>9.66729637496131</v>
+        <v>9.667297413616467</v>
       </c>
       <c r="F947" t="n">
         <v>3569600</v>
@@ -19452,16 +19452,16 @@
         <v>44967</v>
       </c>
       <c r="B952" t="n">
-        <v>7.55806827545166</v>
+        <v>7.558067798614502</v>
       </c>
       <c r="C952" t="n">
-        <v>7.681106054352737</v>
+        <v>7.681105569753147</v>
       </c>
       <c r="D952" t="n">
-        <v>7.452606124776438</v>
+        <v>7.452605654592868</v>
       </c>
       <c r="E952" t="n">
-        <v>7.55806827545166</v>
+        <v>7.558067798614502</v>
       </c>
       <c r="F952" t="n">
         <v>1100200</v>
@@ -19512,16 +19512,16 @@
         <v>44972</v>
       </c>
       <c r="B955" t="n">
-        <v>7.76020336151123</v>
+        <v>7.760202884674072</v>
       </c>
       <c r="C955" t="n">
-        <v>8.120529773923153</v>
+        <v>8.120529274945206</v>
       </c>
       <c r="D955" t="n">
-        <v>7.030761883181699</v>
+        <v>7.030761451166151</v>
       </c>
       <c r="E955" t="n">
-        <v>7.030761883181699</v>
+        <v>7.030761451166151</v>
       </c>
       <c r="F955" t="n">
         <v>5528900</v>
@@ -19532,16 +19532,16 @@
         <v>44973</v>
       </c>
       <c r="B956" t="n">
-        <v>7.979913711547852</v>
+        <v>7.979913234710693</v>
       </c>
       <c r="C956" t="n">
-        <v>8.111740145765278</v>
+        <v>8.111739661050875</v>
       </c>
       <c r="D956" t="n">
-        <v>7.566856265864138</v>
+        <v>7.566855813709092</v>
       </c>
       <c r="E956" t="n">
-        <v>7.663529766546811</v>
+        <v>7.663529308615072</v>
       </c>
       <c r="F956" t="n">
         <v>2076600</v>
@@ -19592,16 +19592,16 @@
         <v>44980</v>
       </c>
       <c r="B959" t="n">
-        <v>7.55806827545166</v>
+        <v>7.558067798614502</v>
       </c>
       <c r="C959" t="n">
-        <v>7.628375817147136</v>
+        <v>7.628375335874287</v>
       </c>
       <c r="D959" t="n">
-        <v>7.311991041385489</v>
+        <v>7.311990580073298</v>
       </c>
       <c r="E959" t="n">
-        <v>7.443818310663511</v>
+        <v>7.443817841034362</v>
       </c>
       <c r="F959" t="n">
         <v>2884000</v>
@@ -19672,16 +19672,16 @@
         <v>44986</v>
       </c>
       <c r="B963" t="n">
-        <v>6.969242095947266</v>
+        <v>6.969241619110107</v>
       </c>
       <c r="C963" t="n">
-        <v>7.303203782523349</v>
+        <v>7.303203282836455</v>
       </c>
       <c r="D963" t="n">
-        <v>6.872569428299123</v>
+        <v>6.872568958076331</v>
       </c>
       <c r="E963" t="n">
-        <v>7.25047270317668</v>
+        <v>7.250472207097658</v>
       </c>
       <c r="F963" t="n">
         <v>3168200</v>
@@ -19692,16 +19692,16 @@
         <v>44987</v>
       </c>
       <c r="B964" t="n">
-        <v>7.162587642669678</v>
+        <v>7.162588119506836</v>
       </c>
       <c r="C964" t="n">
-        <v>7.426241355495689</v>
+        <v>7.426241849885147</v>
       </c>
       <c r="D964" t="n">
-        <v>6.978030546570699</v>
+        <v>6.978031011121281</v>
       </c>
       <c r="E964" t="n">
-        <v>6.978030546570699</v>
+        <v>6.978031011121281</v>
       </c>
       <c r="F964" t="n">
         <v>1592200</v>
@@ -19712,16 +19712,16 @@
         <v>44988</v>
       </c>
       <c r="B965" t="n">
-        <v>6.767107963562012</v>
+        <v>6.767107486724854</v>
       </c>
       <c r="C965" t="n">
-        <v>7.215319222753471</v>
+        <v>7.215318714333577</v>
       </c>
       <c r="D965" t="n">
-        <v>6.591339088819902</v>
+        <v>6.591338624368113</v>
       </c>
       <c r="E965" t="n">
-        <v>7.215319222753471</v>
+        <v>7.215318714333577</v>
       </c>
       <c r="F965" t="n">
         <v>7336400</v>
@@ -19732,16 +19732,16 @@
         <v>44991</v>
       </c>
       <c r="B966" t="n">
-        <v>7.382299423217773</v>
+        <v>7.382298946380615</v>
       </c>
       <c r="C966" t="n">
-        <v>7.575645603949946</v>
+        <v>7.575645114624179</v>
       </c>
       <c r="D966" t="n">
-        <v>6.767107944304977</v>
+        <v>6.767107507204239</v>
       </c>
       <c r="E966" t="n">
-        <v>6.819839025643607</v>
+        <v>6.819838585136866</v>
       </c>
       <c r="F966" t="n">
         <v>3674900</v>
@@ -19812,16 +19812,16 @@
         <v>44995</v>
       </c>
       <c r="B970" t="n">
-        <v>7.76020336151123</v>
+        <v>7.760202884674072</v>
       </c>
       <c r="C970" t="n">
-        <v>8.085375998032529</v>
+        <v>8.085375501214658</v>
       </c>
       <c r="D970" t="n">
-        <v>7.602010950937361</v>
+        <v>7.602010483820569</v>
       </c>
       <c r="E970" t="n">
-        <v>8.02385709975697</v>
+        <v>8.023856606719219</v>
       </c>
       <c r="F970" t="n">
         <v>1865700</v>
@@ -19832,16 +19832,16 @@
         <v>44998</v>
       </c>
       <c r="B971" t="n">
-        <v>7.71626091003418</v>
+        <v>7.716261386871338</v>
       </c>
       <c r="C971" t="n">
-        <v>7.839299544365341</v>
+        <v>7.839300028805843</v>
       </c>
       <c r="D971" t="n">
-        <v>7.478973132984524</v>
+        <v>7.478973595158151</v>
       </c>
       <c r="E971" t="n">
-        <v>7.71626091003418</v>
+        <v>7.716261386871338</v>
       </c>
       <c r="F971" t="n">
         <v>789800</v>
@@ -19912,16 +19912,16 @@
         <v>45002</v>
       </c>
       <c r="B975" t="n">
-        <v>7.71626091003418</v>
+        <v>7.716261386871338</v>
       </c>
       <c r="C975" t="n">
-        <v>8.050222199105507</v>
+        <v>8.050222696580271</v>
       </c>
       <c r="D975" t="n">
-        <v>7.575645806874069</v>
+        <v>7.575646275021719</v>
       </c>
       <c r="E975" t="n">
-        <v>8.050222199105507</v>
+        <v>8.050222696580271</v>
       </c>
       <c r="F975" t="n">
         <v>1382600</v>
@@ -19972,16 +19972,16 @@
         <v>45007</v>
       </c>
       <c r="B978" t="n">
-        <v>7.285626411437988</v>
+        <v>7.28562593460083</v>
       </c>
       <c r="C978" t="n">
-        <v>7.54049147671118</v>
+        <v>7.540490983193351</v>
       </c>
       <c r="D978" t="n">
-        <v>7.171376438986963</v>
+        <v>7.171375969627354</v>
       </c>
       <c r="E978" t="n">
-        <v>7.34714530501467</v>
+        <v>7.34714482415116</v>
       </c>
       <c r="F978" t="n">
         <v>921100</v>
@@ -20012,16 +20012,16 @@
         <v>45009</v>
       </c>
       <c r="B980" t="n">
-        <v>7.013184547424316</v>
+        <v>7.013185024261475</v>
       </c>
       <c r="C980" t="n">
-        <v>7.109857634483707</v>
+        <v>7.109858117893817</v>
       </c>
       <c r="D980" t="n">
-        <v>6.767107712836605</v>
+        <v>6.767108172942622</v>
       </c>
       <c r="E980" t="n">
-        <v>6.890146339663479</v>
+        <v>6.890146808135082</v>
       </c>
       <c r="F980" t="n">
         <v>2102500</v>
@@ -20112,16 +20112,16 @@
         <v>45016</v>
       </c>
       <c r="B985" t="n">
-        <v>7.294414520263672</v>
+        <v>7.29441499710083</v>
       </c>
       <c r="C985" t="n">
-        <v>7.768990842211179</v>
+        <v>7.768991350071474</v>
       </c>
       <c r="D985" t="n">
-        <v>7.118645667344596</v>
+        <v>7.118646132691714</v>
       </c>
       <c r="E985" t="n">
-        <v>7.628375759875918</v>
+        <v>7.62837625854418</v>
       </c>
       <c r="F985" t="n">
         <v>3070300</v>
@@ -20132,16 +20132,16 @@
         <v>45019</v>
       </c>
       <c r="B986" t="n">
-        <v>7.03076171875</v>
+        <v>7.030761241912842</v>
       </c>
       <c r="C986" t="n">
-        <v>7.285626797529403</v>
+        <v>7.2856263034069</v>
       </c>
       <c r="D986" t="n">
-        <v>6.608915998862358</v>
+        <v>6.60891555063543</v>
       </c>
       <c r="E986" t="n">
-        <v>7.285626797529403</v>
+        <v>7.2856263034069</v>
       </c>
       <c r="F986" t="n">
         <v>4689200</v>
@@ -20152,16 +20152,16 @@
         <v>45020</v>
       </c>
       <c r="B987" t="n">
-        <v>6.503454208374023</v>
+        <v>6.503454685211182</v>
       </c>
       <c r="C987" t="n">
-        <v>7.162587653283757</v>
+        <v>7.162588178448974</v>
       </c>
       <c r="D987" t="n">
-        <v>6.397992890713748</v>
+        <v>6.397993359818419</v>
       </c>
       <c r="E987" t="n">
-        <v>6.995607443188001</v>
+        <v>6.995607956110129</v>
       </c>
       <c r="F987" t="n">
         <v>3212200</v>
@@ -20232,16 +20232,16 @@
         <v>45027</v>
       </c>
       <c r="B991" t="n">
-        <v>7.224107265472412</v>
+        <v>7.224106788635254</v>
       </c>
       <c r="C991" t="n">
-        <v>7.347145048327199</v>
+        <v>7.347144563368762</v>
       </c>
       <c r="D991" t="n">
-        <v>6.485877215815548</v>
+        <v>6.485876787706282</v>
       </c>
       <c r="E991" t="n">
-        <v>6.494665449276882</v>
+        <v>6.494665020587536</v>
       </c>
       <c r="F991" t="n">
         <v>3985600</v>
@@ -20372,16 +20372,16 @@
         <v>45036</v>
       </c>
       <c r="B998" t="n">
-        <v>6.485877990722656</v>
+        <v>6.485877513885498</v>
       </c>
       <c r="C998" t="n">
-        <v>6.600127972832264</v>
+        <v>6.600127487595527</v>
       </c>
       <c r="D998" t="n">
-        <v>6.292531802680848</v>
+        <v>6.292531340058365</v>
       </c>
       <c r="E998" t="n">
-        <v>6.42435867287916</v>
+        <v>6.424358200564858</v>
       </c>
       <c r="F998" t="n">
         <v>2265600</v>
@@ -20392,16 +20392,16 @@
         <v>45040</v>
       </c>
       <c r="B999" t="n">
-        <v>6.433146953582764</v>
+        <v>6.433147430419922</v>
       </c>
       <c r="C999" t="n">
-        <v>6.538608276002306</v>
+        <v>6.53860876065646</v>
       </c>
       <c r="D999" t="n">
-        <v>6.318896978095237</v>
+        <v>6.318897446463969</v>
       </c>
       <c r="E999" t="n">
-        <v>6.485877614792535</v>
+        <v>6.485878095538191</v>
       </c>
       <c r="F999" t="n">
         <v>1057400</v>
@@ -20412,16 +20412,16 @@
         <v>45041</v>
       </c>
       <c r="B1000" t="n">
-        <v>6.239800930023193</v>
+        <v>6.239800453186035</v>
       </c>
       <c r="C1000" t="n">
-        <v>6.415570224106105</v>
+        <v>6.415569733836894</v>
       </c>
       <c r="D1000" t="n">
-        <v>6.195858920802007</v>
+        <v>6.195858447322837</v>
       </c>
       <c r="E1000" t="n">
-        <v>6.406781570822235</v>
+        <v>6.406781081224642</v>
       </c>
       <c r="F1000" t="n">
         <v>2491800</v>
@@ -20452,16 +20452,16 @@
         <v>45043</v>
       </c>
       <c r="B1002" t="n">
-        <v>6.389204502105713</v>
+        <v>6.389204025268555</v>
       </c>
       <c r="C1002" t="n">
-        <v>6.450723816149789</v>
+        <v>6.45072333472134</v>
       </c>
       <c r="D1002" t="n">
-        <v>6.187070092036369</v>
+        <v>6.187069630284845</v>
       </c>
       <c r="E1002" t="n">
-        <v>6.29253141405532</v>
+        <v>6.292530944433039</v>
       </c>
       <c r="F1002" t="n">
         <v>1042500</v>
@@ -36729,42 +36729,42 @@
     </row>
     <row r="1816">
       <c r="A1816" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1816" t="n">
-        <v>9.449999809265137</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="C1816" t="n">
-        <v>9.539999961853027</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="D1816" t="n">
-        <v>9.359999656677246</v>
+        <v>9.409999847412109</v>
       </c>
       <c r="E1816" t="n">
         <v>9.5</v>
       </c>
       <c r="F1816" t="n">
-        <v>1011900</v>
+        <v>1819000</v>
       </c>
     </row>
     <row r="1817">
       <c r="A1817" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1817" t="n">
-        <v>9.65</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="C1817" t="n">
-        <v>9.65</v>
+        <v>9.83</v>
       </c>
       <c r="D1817" t="n">
-        <v>9.41</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="E1817" t="n">
-        <v>9.5</v>
+        <v>9.77</v>
       </c>
       <c r="F1817" t="n">
-        <v>1819000</v>
+        <v>1167200</v>
       </c>
     </row>
   </sheetData>

--- a/database/SBFG3.xlsx
+++ b/database/SBFG3.xlsx
@@ -452,16 +452,16 @@
         <v>43572</v>
       </c>
       <c r="B2" t="n">
-        <v>10.75700092315674</v>
+        <v>10.75700187683105</v>
       </c>
       <c r="C2" t="n">
-        <v>11.14180383526864</v>
+        <v>11.1418048230581</v>
       </c>
       <c r="D2" t="n">
-        <v>10.55585332084199</v>
+        <v>10.55585425668333</v>
       </c>
       <c r="E2" t="n">
-        <v>10.66954529883926</v>
+        <v>10.66954624476009</v>
       </c>
       <c r="F2" t="n">
         <v>10338900</v>
@@ -472,16 +472,16 @@
         <v>43573</v>
       </c>
       <c r="B3" t="n">
-        <v>10.53836345672607</v>
+        <v>10.53836441040039</v>
       </c>
       <c r="C3" t="n">
-        <v>10.98438567165539</v>
+        <v>10.98438666569271</v>
       </c>
       <c r="D3" t="n">
-        <v>10.33721583989887</v>
+        <v>10.33721677537024</v>
       </c>
       <c r="E3" t="n">
-        <v>10.74825596938503</v>
+        <v>10.74825694205368</v>
       </c>
       <c r="F3" t="n">
         <v>3142100</v>
@@ -532,16 +532,16 @@
         <v>43579</v>
       </c>
       <c r="B6" t="n">
-        <v>10.3721981048584</v>
+        <v>10.37219905853271</v>
       </c>
       <c r="C6" t="n">
-        <v>10.40718019090701</v>
+        <v>10.40718114779776</v>
       </c>
       <c r="D6" t="n">
-        <v>10.19728767461534</v>
+        <v>10.19728861220748</v>
       </c>
       <c r="E6" t="n">
-        <v>10.40718019090701</v>
+        <v>10.40718114779776</v>
       </c>
       <c r="F6" t="n">
         <v>1161400</v>
@@ -592,16 +592,16 @@
         <v>43584</v>
       </c>
       <c r="B9" t="n">
-        <v>10.39843559265137</v>
+        <v>10.39843654632568</v>
       </c>
       <c r="C9" t="n">
-        <v>10.56460029763021</v>
+        <v>10.56460126654403</v>
       </c>
       <c r="D9" t="n">
-        <v>10.34596204505667</v>
+        <v>10.34596299391847</v>
       </c>
       <c r="E9" t="n">
-        <v>10.45090830620732</v>
+        <v>10.45090926469408</v>
       </c>
       <c r="F9" t="n">
         <v>423300</v>
@@ -612,16 +612,16 @@
         <v>43585</v>
       </c>
       <c r="B10" t="n">
-        <v>10.23227024078369</v>
+        <v>10.23226928710938</v>
       </c>
       <c r="C10" t="n">
-        <v>10.58209195172289</v>
+        <v>10.58209096544428</v>
       </c>
       <c r="D10" t="n">
-        <v>9.760011639948713</v>
+        <v>9.760010730290132</v>
       </c>
       <c r="E10" t="n">
-        <v>10.40718067923391</v>
+        <v>10.40717970925749</v>
       </c>
       <c r="F10" t="n">
         <v>3631900</v>
@@ -632,16 +632,16 @@
         <v>43587</v>
       </c>
       <c r="B11" t="n">
-        <v>10.17979717254639</v>
+        <v>10.1797981262207</v>
       </c>
       <c r="C11" t="n">
-        <v>10.31972551844442</v>
+        <v>10.31972648522765</v>
       </c>
       <c r="D11" t="n">
-        <v>10.11857789568695</v>
+        <v>10.11857884362606</v>
       </c>
       <c r="E11" t="n">
-        <v>10.15355998216146</v>
+        <v>10.1535609333778</v>
       </c>
       <c r="F11" t="n">
         <v>464300</v>
@@ -672,16 +672,16 @@
         <v>43591</v>
       </c>
       <c r="B13" t="n">
-        <v>10.20603370666504</v>
+        <v>10.20603275299072</v>
       </c>
       <c r="C13" t="n">
-        <v>10.27599788083272</v>
+        <v>10.27599692062079</v>
       </c>
       <c r="D13" t="n">
-        <v>9.926177009994333</v>
+        <v>9.926176082470445</v>
       </c>
       <c r="E13" t="n">
-        <v>10.04861389776839</v>
+        <v>10.04861295880373</v>
       </c>
       <c r="F13" t="n">
         <v>180200</v>
@@ -692,16 +692,16 @@
         <v>43592</v>
       </c>
       <c r="B14" t="n">
-        <v>10.27599906921387</v>
+        <v>10.27599811553955</v>
       </c>
       <c r="C14" t="n">
-        <v>10.31098116034326</v>
+        <v>10.31098020342239</v>
       </c>
       <c r="D14" t="n">
-        <v>10.05736079114549</v>
+        <v>10.05735985776211</v>
       </c>
       <c r="E14" t="n">
-        <v>10.14481643598838</v>
+        <v>10.14481549448859</v>
       </c>
       <c r="F14" t="n">
         <v>232800</v>
@@ -752,16 +752,16 @@
         <v>43595</v>
       </c>
       <c r="B17" t="n">
-        <v>10.58209228515625</v>
+        <v>10.58209133148193</v>
       </c>
       <c r="C17" t="n">
-        <v>10.70452917890991</v>
+        <v>10.7045282142014</v>
       </c>
       <c r="D17" t="n">
-        <v>10.40718100715595</v>
+        <v>10.40718006924491</v>
       </c>
       <c r="E17" t="n">
-        <v>10.40718100715595</v>
+        <v>10.40718006924491</v>
       </c>
       <c r="F17" t="n">
         <v>669000</v>
@@ -812,16 +812,16 @@
         <v>43600</v>
       </c>
       <c r="B20" t="n">
-        <v>10.31972503662109</v>
+        <v>10.31972599029541</v>
       </c>
       <c r="C20" t="n">
-        <v>10.625818070472</v>
+        <v>10.62581905243322</v>
       </c>
       <c r="D20" t="n">
-        <v>10.31972503662109</v>
+        <v>10.31972599029541</v>
       </c>
       <c r="E20" t="n">
-        <v>10.57334536022953</v>
+        <v>10.57334633734161</v>
       </c>
       <c r="F20" t="n">
         <v>1335000</v>
@@ -872,16 +872,16 @@
         <v>43605</v>
       </c>
       <c r="B23" t="n">
-        <v>9.707537651062012</v>
+        <v>9.707538604736328</v>
       </c>
       <c r="C23" t="n">
-        <v>9.873702337266524</v>
+        <v>9.873703307264957</v>
       </c>
       <c r="D23" t="n">
-        <v>9.6025905677302</v>
+        <v>9.602591511094451</v>
       </c>
       <c r="E23" t="n">
-        <v>9.873702337266524</v>
+        <v>9.873703307264957</v>
       </c>
       <c r="F23" t="n">
         <v>117200</v>
@@ -892,16 +892,16 @@
         <v>43606</v>
       </c>
       <c r="B24" t="n">
-        <v>9.882448196411133</v>
+        <v>9.882449150085449</v>
       </c>
       <c r="C24" t="n">
-        <v>9.961158092924956</v>
+        <v>9.961159054194923</v>
       </c>
       <c r="D24" t="n">
-        <v>9.725028403383487</v>
+        <v>9.725029341866504</v>
       </c>
       <c r="E24" t="n">
-        <v>9.794992570498295</v>
+        <v>9.794993515732981</v>
       </c>
       <c r="F24" t="n">
         <v>253500</v>
@@ -932,16 +932,16 @@
         <v>43608</v>
       </c>
       <c r="B26" t="n">
-        <v>9.882448196411133</v>
+        <v>9.882449150085449</v>
       </c>
       <c r="C26" t="n">
-        <v>10.67829122287106</v>
+        <v>10.67829225334568</v>
       </c>
       <c r="D26" t="n">
-        <v>9.873702467012118</v>
+        <v>9.873703419842455</v>
       </c>
       <c r="E26" t="n">
-        <v>10.35470674145541</v>
+        <v>10.35470774070354</v>
       </c>
       <c r="F26" t="n">
         <v>1121200</v>
@@ -952,16 +952,16 @@
         <v>43609</v>
       </c>
       <c r="B27" t="n">
-        <v>9.882448196411133</v>
+        <v>9.882449150085449</v>
       </c>
       <c r="C27" t="n">
-        <v>10.01363080124173</v>
+        <v>10.01363176757541</v>
       </c>
       <c r="D27" t="n">
-        <v>9.794992570498295</v>
+        <v>9.794993515732981</v>
       </c>
       <c r="E27" t="n">
-        <v>9.882448196411133</v>
+        <v>9.882449150085449</v>
       </c>
       <c r="F27" t="n">
         <v>207200</v>
@@ -1012,16 +1012,16 @@
         <v>43614</v>
       </c>
       <c r="B30" t="n">
-        <v>10.23227024078369</v>
+        <v>10.23226928710938</v>
       </c>
       <c r="C30" t="n">
-        <v>10.30223441616378</v>
+        <v>10.30223345596862</v>
       </c>
       <c r="D30" t="n">
-        <v>9.97864989652118</v>
+        <v>9.978648966484943</v>
       </c>
       <c r="E30" t="n">
-        <v>10.22352451035149</v>
+        <v>10.2235235574923</v>
       </c>
       <c r="F30" t="n">
         <v>497500</v>
@@ -1032,16 +1032,16 @@
         <v>43615</v>
       </c>
       <c r="B31" t="n">
-        <v>10.25850486755371</v>
+        <v>10.25850677490234</v>
       </c>
       <c r="C31" t="n">
-        <v>10.36345194695928</v>
+        <v>10.36345387382057</v>
       </c>
       <c r="D31" t="n">
-        <v>10.14481372726848</v>
+        <v>10.14481561347869</v>
       </c>
       <c r="E31" t="n">
-        <v>10.25850486755371</v>
+        <v>10.25850677490234</v>
       </c>
       <c r="F31" t="n">
         <v>445800</v>
@@ -1092,16 +1092,16 @@
         <v>43620</v>
       </c>
       <c r="B34" t="n">
-        <v>10.13606834411621</v>
+        <v>10.13606929779053</v>
       </c>
       <c r="C34" t="n">
-        <v>10.35470657126613</v>
+        <v>10.3547075455115</v>
       </c>
       <c r="D34" t="n">
-        <v>10.01363063665835</v>
+        <v>10.01363157881284</v>
       </c>
       <c r="E34" t="n">
-        <v>10.34596084201085</v>
+        <v>10.34596181543337</v>
       </c>
       <c r="F34" t="n">
         <v>433200</v>
@@ -1112,16 +1112,16 @@
         <v>43621</v>
       </c>
       <c r="B35" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="C35" t="n">
-        <v>10.19728815949492</v>
+        <v>10.19728720088784</v>
       </c>
       <c r="D35" t="n">
-        <v>10.0223777209349</v>
+        <v>10.02237677877047</v>
       </c>
       <c r="E35" t="n">
-        <v>10.03986834777152</v>
+        <v>10.03986740396287</v>
       </c>
       <c r="F35" t="n">
         <v>186800</v>
@@ -1132,16 +1132,16 @@
         <v>43622</v>
       </c>
       <c r="B36" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="C36" t="n">
-        <v>10.31098015306862</v>
+        <v>10.31097918377381</v>
       </c>
       <c r="D36" t="n">
-        <v>10.0573598086469</v>
+        <v>10.05735886319394</v>
       </c>
       <c r="E36" t="n">
-        <v>10.17979753265829</v>
+        <v>10.17979657569545</v>
       </c>
       <c r="F36" t="n">
         <v>146300</v>
@@ -1172,16 +1172,16 @@
         <v>43626</v>
       </c>
       <c r="B38" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="C38" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="D38" t="n">
-        <v>9.89119510052457</v>
+        <v>9.891194170692108</v>
       </c>
       <c r="E38" t="n">
-        <v>10.07485126952228</v>
+        <v>10.07485032242502</v>
       </c>
       <c r="F38" t="n">
         <v>348000</v>
@@ -1232,16 +1232,16 @@
         <v>43629</v>
       </c>
       <c r="B41" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="C41" t="n">
-        <v>10.35470797121831</v>
+        <v>10.35470699781282</v>
       </c>
       <c r="D41" t="n">
-        <v>9.996141363660582</v>
+        <v>9.996140423962533</v>
       </c>
       <c r="E41" t="n">
-        <v>10.08359616592121</v>
+        <v>10.08359521800188</v>
       </c>
       <c r="F41" t="n">
         <v>344300</v>
@@ -1252,16 +1252,16 @@
         <v>43630</v>
       </c>
       <c r="B42" t="n">
-        <v>10.14481544494629</v>
+        <v>10.14481449127197</v>
       </c>
       <c r="C42" t="n">
-        <v>10.2497617080823</v>
+        <v>10.2497607445424</v>
       </c>
       <c r="D42" t="n">
-        <v>9.899939996923502</v>
+        <v>9.899939066268965</v>
       </c>
       <c r="E42" t="n">
-        <v>10.22352451676923</v>
+        <v>10.22352355569578</v>
       </c>
       <c r="F42" t="n">
         <v>475700</v>
@@ -1292,16 +1292,16 @@
         <v>43634</v>
       </c>
       <c r="B44" t="n">
-        <v>10.4071798324585</v>
+        <v>10.40718078613281</v>
       </c>
       <c r="C44" t="n">
-        <v>10.44216191730224</v>
+        <v>10.44216287418218</v>
       </c>
       <c r="D44" t="n">
-        <v>10.13606888342916</v>
+        <v>10.1360698122599</v>
       </c>
       <c r="E44" t="n">
-        <v>10.22352367851917</v>
+        <v>10.22352461536394</v>
       </c>
       <c r="F44" t="n">
         <v>787900</v>
@@ -1312,16 +1312,16 @@
         <v>43635</v>
       </c>
       <c r="B45" t="n">
-        <v>10.75700092315674</v>
+        <v>10.75700187683105</v>
       </c>
       <c r="C45" t="n">
-        <v>10.78323727683652</v>
+        <v>10.78323823283686</v>
       </c>
       <c r="D45" t="n">
-        <v>10.31972446964662</v>
+        <v>10.31972538455368</v>
       </c>
       <c r="E45" t="n">
-        <v>10.39843436472462</v>
+        <v>10.39843528660981</v>
       </c>
       <c r="F45" t="n">
         <v>221700</v>
@@ -1332,16 +1332,16 @@
         <v>43637</v>
       </c>
       <c r="B46" t="n">
-        <v>11.1942777633667</v>
+        <v>11.19427871704102</v>
       </c>
       <c r="C46" t="n">
-        <v>11.28173255666661</v>
+        <v>11.28173351779147</v>
       </c>
       <c r="D46" t="n">
-        <v>10.75700129475111</v>
+        <v>10.75700221117253</v>
       </c>
       <c r="E46" t="n">
-        <v>10.75700129475111</v>
+        <v>10.75700221117253</v>
       </c>
       <c r="F46" t="n">
         <v>990700</v>
@@ -1372,16 +1372,16 @@
         <v>43641</v>
       </c>
       <c r="B48" t="n">
-        <v>11.35169696807861</v>
+        <v>11.35169792175293</v>
       </c>
       <c r="C48" t="n">
-        <v>11.36044269780754</v>
+        <v>11.3604436522166</v>
       </c>
       <c r="D48" t="n">
-        <v>11.0718402890624</v>
+        <v>11.07184121922551</v>
       </c>
       <c r="E48" t="n">
-        <v>11.14180445881646</v>
+        <v>11.14180539485737</v>
       </c>
       <c r="F48" t="n">
         <v>1743100</v>
@@ -1392,16 +1392,16 @@
         <v>43642</v>
       </c>
       <c r="B49" t="n">
-        <v>12.02510452270508</v>
+        <v>12.02510356903076</v>
       </c>
       <c r="C49" t="n">
-        <v>12.20001496713667</v>
+        <v>12.20001399959074</v>
       </c>
       <c r="D49" t="n">
-        <v>11.24675200243602</v>
+        <v>11.24675111049047</v>
       </c>
       <c r="E49" t="n">
-        <v>11.28173409132234</v>
+        <v>11.28173319660246</v>
       </c>
       <c r="F49" t="n">
         <v>1344300</v>
@@ -1432,16 +1432,16 @@
         <v>43644</v>
       </c>
       <c r="B51" t="n">
-        <v>12.50610828399658</v>
+        <v>12.50610733032227</v>
       </c>
       <c r="C51" t="n">
-        <v>12.68976445054762</v>
+        <v>12.68976348286829</v>
       </c>
       <c r="D51" t="n">
-        <v>12.24374221263242</v>
+        <v>12.24374127896527</v>
       </c>
       <c r="E51" t="n">
-        <v>12.54983610156373</v>
+        <v>12.54983514455488</v>
       </c>
       <c r="F51" t="n">
         <v>1554600</v>
@@ -1472,16 +1472,16 @@
         <v>43648</v>
       </c>
       <c r="B53" t="n">
-        <v>12.0688304901123</v>
+        <v>12.06883144378662</v>
       </c>
       <c r="C53" t="n">
-        <v>12.33119653351361</v>
+        <v>12.33119750792</v>
       </c>
       <c r="D53" t="n">
-        <v>11.99012059368805</v>
+        <v>11.99012154114274</v>
       </c>
       <c r="E53" t="n">
-        <v>12.24374090770029</v>
+        <v>12.24374187519596</v>
       </c>
       <c r="F53" t="n">
         <v>273500</v>
@@ -1512,16 +1512,16 @@
         <v>43650</v>
       </c>
       <c r="B55" t="n">
-        <v>12.20001316070557</v>
+        <v>12.20001411437988</v>
       </c>
       <c r="C55" t="n">
-        <v>12.59356181091439</v>
+        <v>12.59356279535238</v>
       </c>
       <c r="D55" t="n">
-        <v>12.19126743126925</v>
+        <v>12.19126838425992</v>
       </c>
       <c r="E55" t="n">
-        <v>12.19126743126925</v>
+        <v>12.19126838425992</v>
       </c>
       <c r="F55" t="n">
         <v>336300</v>
@@ -1532,16 +1532,16 @@
         <v>43651</v>
       </c>
       <c r="B56" t="n">
-        <v>12.41865253448486</v>
+        <v>12.41865348815918</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56732661242062</v>
+        <v>12.56732757751217</v>
       </c>
       <c r="D56" t="n">
-        <v>12.24374209986595</v>
+        <v>12.24374304010825</v>
       </c>
       <c r="E56" t="n">
-        <v>12.24374209986595</v>
+        <v>12.24374304010825</v>
       </c>
       <c r="F56" t="n">
         <v>2415300</v>
@@ -1612,16 +1612,16 @@
         <v>43658</v>
       </c>
       <c r="B60" t="n">
-        <v>13.12704086303711</v>
+        <v>13.12703990936279</v>
       </c>
       <c r="C60" t="n">
-        <v>13.5030980896971</v>
+        <v>13.50309710870238</v>
       </c>
       <c r="D60" t="n">
-        <v>12.91714834108194</v>
+        <v>12.91714740265623</v>
       </c>
       <c r="E60" t="n">
-        <v>13.35442484550792</v>
+        <v>13.35442387531424</v>
       </c>
       <c r="F60" t="n">
         <v>162300</v>
@@ -1652,16 +1652,16 @@
         <v>43662</v>
       </c>
       <c r="B62" t="n">
-        <v>13.11829376220703</v>
+        <v>13.11829471588135</v>
       </c>
       <c r="C62" t="n">
-        <v>13.24073147090821</v>
+        <v>13.24073243348351</v>
       </c>
       <c r="D62" t="n">
-        <v>13.01334751219401</v>
+        <v>13.01334845823894</v>
       </c>
       <c r="E62" t="n">
-        <v>13.19700365822646</v>
+        <v>13.19700461762283</v>
       </c>
       <c r="F62" t="n">
         <v>133000</v>
@@ -1712,16 +1712,16 @@
         <v>43665</v>
       </c>
       <c r="B65" t="n">
-        <v>13.40689659118652</v>
+        <v>13.40689754486084</v>
       </c>
       <c r="C65" t="n">
-        <v>13.76546316548612</v>
+        <v>13.7654641446664</v>
       </c>
       <c r="D65" t="n">
-        <v>13.3281866926254</v>
+        <v>13.32818764070084</v>
       </c>
       <c r="E65" t="n">
-        <v>13.66051691208419</v>
+        <v>13.66051788379931</v>
       </c>
       <c r="F65" t="n">
         <v>227100</v>
@@ -1812,16 +1812,16 @@
         <v>43672</v>
       </c>
       <c r="B70" t="n">
-        <v>14.26395988464355</v>
+        <v>14.26395893096924</v>
       </c>
       <c r="C70" t="n">
-        <v>14.29019707684683</v>
+        <v>14.29019612141832</v>
       </c>
       <c r="D70" t="n">
-        <v>13.96661254602217</v>
+        <v>13.9666116122282</v>
       </c>
       <c r="E70" t="n">
-        <v>13.99284890418666</v>
+        <v>13.99284796863856</v>
       </c>
       <c r="F70" t="n">
         <v>1397800</v>
@@ -1832,16 +1832,16 @@
         <v>43675</v>
       </c>
       <c r="B71" t="n">
-        <v>14.65750885009766</v>
+        <v>14.65750789642334</v>
       </c>
       <c r="C71" t="n">
-        <v>14.7624542786229</v>
+        <v>14.76245331812043</v>
       </c>
       <c r="D71" t="n">
-        <v>14.26395932293421</v>
+        <v>14.26395839486575</v>
       </c>
       <c r="E71" t="n">
-        <v>14.27270505332423</v>
+        <v>14.27270412468674</v>
       </c>
       <c r="F71" t="n">
         <v>1345200</v>
@@ -1872,16 +1872,16 @@
         <v>43677</v>
       </c>
       <c r="B73" t="n">
-        <v>14.94611072540283</v>
+        <v>14.94610977172852</v>
       </c>
       <c r="C73" t="n">
-        <v>15.03356635797652</v>
+        <v>15.03356539872188</v>
       </c>
       <c r="D73" t="n">
-        <v>14.37765161579001</v>
+        <v>14.37765069838766</v>
       </c>
       <c r="E73" t="n">
-        <v>14.8936380130896</v>
+        <v>14.89363706276344</v>
       </c>
       <c r="F73" t="n">
         <v>584400</v>
@@ -1932,16 +1932,16 @@
         <v>43682</v>
       </c>
       <c r="B76" t="n">
-        <v>14.3426685333252</v>
+        <v>14.34266948699951</v>
       </c>
       <c r="C76" t="n">
-        <v>14.51757979649447</v>
+        <v>14.517580761799</v>
       </c>
       <c r="D76" t="n">
-        <v>14.08030330664872</v>
+        <v>14.08030424287781</v>
       </c>
       <c r="E76" t="n">
-        <v>14.51757979649447</v>
+        <v>14.517580761799</v>
       </c>
       <c r="F76" t="n">
         <v>984200</v>
@@ -2052,16 +2052,16 @@
         <v>43690</v>
       </c>
       <c r="B82" t="n">
-        <v>15.56704425811768</v>
+        <v>15.56704235076904</v>
       </c>
       <c r="C82" t="n">
-        <v>15.91686682685728</v>
+        <v>15.91686487664672</v>
       </c>
       <c r="D82" t="n">
-        <v>15.34840598669424</v>
+        <v>15.34840410613421</v>
       </c>
       <c r="E82" t="n">
-        <v>15.91686682685728</v>
+        <v>15.91686487664672</v>
       </c>
       <c r="F82" t="n">
         <v>1028200</v>
@@ -2072,16 +2072,16 @@
         <v>43691</v>
       </c>
       <c r="B83" t="n">
-        <v>15.08603858947754</v>
+        <v>15.08604049682617</v>
       </c>
       <c r="C83" t="n">
-        <v>16.29292094268169</v>
+        <v>16.29292300261812</v>
       </c>
       <c r="D83" t="n">
-        <v>15.05105567033204</v>
+        <v>15.05105757325773</v>
       </c>
       <c r="E83" t="n">
-        <v>15.74195331075917</v>
+        <v>15.74195530103601</v>
       </c>
       <c r="F83" t="n">
         <v>474000</v>
@@ -2092,16 +2092,16 @@
         <v>43692</v>
       </c>
       <c r="B84" t="n">
-        <v>14.47385215759277</v>
+        <v>14.47385120391846</v>
       </c>
       <c r="C84" t="n">
-        <v>15.33966113586812</v>
+        <v>15.33966012514611</v>
       </c>
       <c r="D84" t="n">
-        <v>14.22023264316839</v>
+        <v>14.22023170620493</v>
       </c>
       <c r="E84" t="n">
-        <v>15.3046782135599</v>
+        <v>15.3046772051429</v>
       </c>
       <c r="F84" t="n">
         <v>1402800</v>
@@ -2112,16 +2112,16 @@
         <v>43693</v>
       </c>
       <c r="B85" t="n">
-        <v>15.56704425811768</v>
+        <v>15.56704235076904</v>
       </c>
       <c r="C85" t="n">
-        <v>15.56704425811768</v>
+        <v>15.56704235076904</v>
       </c>
       <c r="D85" t="n">
-        <v>14.29894328470832</v>
+        <v>14.29894153273348</v>
       </c>
       <c r="E85" t="n">
-        <v>14.61378126126528</v>
+        <v>14.61377947071498</v>
       </c>
       <c r="F85" t="n">
         <v>1108600</v>
@@ -2132,16 +2132,16 @@
         <v>43696</v>
       </c>
       <c r="B86" t="n">
-        <v>15.47959041595459</v>
+        <v>15.47958850860596</v>
       </c>
       <c r="C86" t="n">
-        <v>15.7157184833656</v>
+        <v>15.71571654692197</v>
       </c>
       <c r="D86" t="n">
-        <v>15.12976784423318</v>
+        <v>15.12976597998864</v>
       </c>
       <c r="E86" t="n">
-        <v>15.7157184833656</v>
+        <v>15.71571654692197</v>
       </c>
       <c r="F86" t="n">
         <v>399000</v>
@@ -2152,16 +2152,16 @@
         <v>43697</v>
       </c>
       <c r="B87" t="n">
-        <v>15.23471355438232</v>
+        <v>15.23471164703369</v>
       </c>
       <c r="C87" t="n">
-        <v>15.4795889985495</v>
+        <v>15.47958706054306</v>
       </c>
       <c r="D87" t="n">
-        <v>14.97234831769267</v>
+        <v>14.97234644319152</v>
       </c>
       <c r="E87" t="n">
-        <v>15.4795889985495</v>
+        <v>15.47958706054306</v>
       </c>
       <c r="F87" t="n">
         <v>1185200</v>
@@ -2232,16 +2232,16 @@
         <v>43703</v>
       </c>
       <c r="B91" t="n">
-        <v>16.35414123535156</v>
+        <v>16.35413932800293</v>
       </c>
       <c r="C91" t="n">
-        <v>16.45908665781508</v>
+        <v>16.45908473822689</v>
       </c>
       <c r="D91" t="n">
-        <v>15.75069921791538</v>
+        <v>15.75069738094491</v>
       </c>
       <c r="E91" t="n">
-        <v>16.36288529715901</v>
+        <v>16.36288338879057</v>
       </c>
       <c r="F91" t="n">
         <v>587300</v>
@@ -2272,16 +2272,16 @@
         <v>43705</v>
       </c>
       <c r="B93" t="n">
-        <v>17.01880073547363</v>
+        <v>17.018798828125</v>
       </c>
       <c r="C93" t="n">
-        <v>17.40360452606598</v>
+        <v>17.40360257559121</v>
       </c>
       <c r="D93" t="n">
-        <v>16.00431937961177</v>
+        <v>16.00431758595914</v>
       </c>
       <c r="E93" t="n">
-        <v>16.26668628286551</v>
+        <v>16.26668445980863</v>
       </c>
       <c r="F93" t="n">
         <v>1947300</v>
@@ -2452,16 +2452,16 @@
         <v>43718</v>
       </c>
       <c r="B102" t="n">
-        <v>17.56977272033691</v>
+        <v>17.56977081298828</v>
       </c>
       <c r="C102" t="n">
-        <v>17.69220962618194</v>
+        <v>17.69220770554174</v>
       </c>
       <c r="D102" t="n">
-        <v>17.10625895551573</v>
+        <v>17.10625709848547</v>
       </c>
       <c r="E102" t="n">
-        <v>17.69220962618194</v>
+        <v>17.69220770554174</v>
       </c>
       <c r="F102" t="n">
         <v>349000</v>
@@ -2532,16 +2532,16 @@
         <v>43724</v>
       </c>
       <c r="B106" t="n">
-        <v>16.61650657653809</v>
+        <v>16.61650848388672</v>
       </c>
       <c r="C106" t="n">
-        <v>17.25492984992965</v>
+        <v>17.25493183056058</v>
       </c>
       <c r="D106" t="n">
-        <v>16.45908677365744</v>
+        <v>16.45908866293642</v>
       </c>
       <c r="E106" t="n">
-        <v>17.05378306539435</v>
+        <v>17.05378502293637</v>
       </c>
       <c r="F106" t="n">
         <v>1080000</v>
@@ -2592,16 +2592,16 @@
         <v>43727</v>
       </c>
       <c r="B109" t="n">
-        <v>19.06525611877441</v>
+        <v>19.06525421142578</v>
       </c>
       <c r="C109" t="n">
-        <v>19.29264011547406</v>
+        <v>19.29263818537722</v>
       </c>
       <c r="D109" t="n">
-        <v>18.56676113942724</v>
+        <v>18.56675928194962</v>
       </c>
       <c r="E109" t="n">
-        <v>18.56676113942724</v>
+        <v>18.56675928194962</v>
       </c>
       <c r="F109" t="n">
         <v>586300</v>
@@ -2612,16 +2612,16 @@
         <v>43728</v>
       </c>
       <c r="B110" t="n">
-        <v>19.28389167785645</v>
+        <v>19.28388977050781</v>
       </c>
       <c r="C110" t="n">
-        <v>19.66869543887903</v>
+        <v>19.66869349346988</v>
       </c>
       <c r="D110" t="n">
-        <v>18.85536093702379</v>
+        <v>18.85535907206066</v>
       </c>
       <c r="E110" t="n">
-        <v>19.27514761635631</v>
+        <v>19.27514570987255</v>
       </c>
       <c r="F110" t="n">
         <v>1032800</v>
@@ -2652,16 +2652,16 @@
         <v>43732</v>
       </c>
       <c r="B112" t="n">
-        <v>19.67744255065918</v>
+        <v>19.67744445800781</v>
       </c>
       <c r="C112" t="n">
-        <v>20.73565088270633</v>
+        <v>20.73565289262785</v>
       </c>
       <c r="D112" t="n">
-        <v>19.67744255065918</v>
+        <v>19.67744445800781</v>
       </c>
       <c r="E112" t="n">
-        <v>20.38583001542122</v>
+        <v>20.38583199143435</v>
       </c>
       <c r="F112" t="n">
         <v>1691800</v>
@@ -2672,16 +2672,16 @@
         <v>43733</v>
       </c>
       <c r="B113" t="n">
-        <v>19.98353576660156</v>
+        <v>19.9835376739502</v>
       </c>
       <c r="C113" t="n">
-        <v>20.63945049634946</v>
+        <v>20.63945246630254</v>
       </c>
       <c r="D113" t="n">
-        <v>19.52876782030444</v>
+        <v>19.52876968424729</v>
       </c>
       <c r="E113" t="n">
-        <v>20.44704777472053</v>
+        <v>20.44704972630954</v>
       </c>
       <c r="F113" t="n">
         <v>1513200</v>
@@ -2792,16 +2792,16 @@
         <v>43741</v>
       </c>
       <c r="B119" t="n">
-        <v>18.89034461975098</v>
+        <v>18.89034271240234</v>
       </c>
       <c r="C119" t="n">
-        <v>19.23141974668809</v>
+        <v>19.23141780490128</v>
       </c>
       <c r="D119" t="n">
-        <v>18.76790606878893</v>
+        <v>18.76790417380286</v>
       </c>
       <c r="E119" t="n">
-        <v>18.81163471844589</v>
+        <v>18.81163281904455</v>
       </c>
       <c r="F119" t="n">
         <v>610400</v>
@@ -2812,16 +2812,16 @@
         <v>43742</v>
       </c>
       <c r="B120" t="n">
-        <v>19.41507530212402</v>
+        <v>19.41507720947266</v>
       </c>
       <c r="C120" t="n">
-        <v>19.98353436097165</v>
+        <v>19.98353632416604</v>
       </c>
       <c r="D120" t="n">
-        <v>18.82037905542412</v>
+        <v>18.82038090434943</v>
       </c>
       <c r="E120" t="n">
-        <v>18.89034322161956</v>
+        <v>18.8903450774182</v>
       </c>
       <c r="F120" t="n">
         <v>953700</v>
@@ -2872,16 +2872,16 @@
         <v>43747</v>
       </c>
       <c r="B123" t="n">
-        <v>18.3918514251709</v>
+        <v>18.39184951782227</v>
       </c>
       <c r="C123" t="n">
-        <v>19.31013146958495</v>
+        <v>19.310129467005</v>
       </c>
       <c r="D123" t="n">
-        <v>18.23443160771076</v>
+        <v>18.23442971668753</v>
       </c>
       <c r="E123" t="n">
-        <v>19.1439659213684</v>
+        <v>19.14396393602085</v>
       </c>
       <c r="F123" t="n">
         <v>1216800</v>
@@ -2892,16 +2892,16 @@
         <v>43748</v>
       </c>
       <c r="B124" t="n">
-        <v>18.33937644958496</v>
+        <v>18.33937454223633</v>
       </c>
       <c r="C124" t="n">
-        <v>18.69794305865369</v>
+        <v>18.69794111401308</v>
       </c>
       <c r="D124" t="n">
-        <v>18.33937644958496</v>
+        <v>18.33937454223633</v>
       </c>
       <c r="E124" t="n">
-        <v>18.4093406253038</v>
+        <v>18.40933871067869</v>
       </c>
       <c r="F124" t="n">
         <v>1209500</v>
@@ -3052,16 +3052,16 @@
         <v>43760</v>
       </c>
       <c r="B132" t="n">
-        <v>22.21364402770996</v>
+        <v>22.21364593505859</v>
       </c>
       <c r="C132" t="n">
-        <v>22.38855528046314</v>
+        <v>22.38855720283032</v>
       </c>
       <c r="D132" t="n">
-        <v>21.42654672647531</v>
+        <v>21.42654856624075</v>
       </c>
       <c r="E132" t="n">
-        <v>21.61894777004195</v>
+        <v>21.61894962632768</v>
       </c>
       <c r="F132" t="n">
         <v>754400</v>
@@ -3072,16 +3072,16 @@
         <v>43761</v>
       </c>
       <c r="B133" t="n">
-        <v>22.03873443603516</v>
+        <v>22.03873634338379</v>
       </c>
       <c r="C133" t="n">
-        <v>22.80834027813461</v>
+        <v>22.80834225208901</v>
       </c>
       <c r="D133" t="n">
-        <v>21.99500578882208</v>
+        <v>21.99500769238621</v>
       </c>
       <c r="E133" t="n">
-        <v>22.37106381446786</v>
+        <v>22.37106575057804</v>
       </c>
       <c r="F133" t="n">
         <v>2305600</v>
@@ -3112,16 +3112,16 @@
         <v>43763</v>
       </c>
       <c r="B135" t="n">
-        <v>22.70339393615723</v>
+        <v>22.70339584350586</v>
       </c>
       <c r="C135" t="n">
-        <v>23.0881977038432</v>
+        <v>23.08819964351982</v>
       </c>
       <c r="D135" t="n">
-        <v>22.13493484839588</v>
+        <v>22.13493670798735</v>
       </c>
       <c r="E135" t="n">
-        <v>22.73837685507294</v>
+        <v>22.73837876536055</v>
       </c>
       <c r="F135" t="n">
         <v>977400</v>
@@ -3192,16 +3192,16 @@
         <v>43769</v>
       </c>
       <c r="B139" t="n">
-        <v>23.60418701171875</v>
+        <v>23.60418510437012</v>
       </c>
       <c r="C139" t="n">
-        <v>23.93651811036675</v>
+        <v>23.93651617616393</v>
       </c>
       <c r="D139" t="n">
-        <v>23.350567490403</v>
+        <v>23.35056560354822</v>
       </c>
       <c r="E139" t="n">
-        <v>23.66540545934402</v>
+        <v>23.66540354704859</v>
       </c>
       <c r="F139" t="n">
         <v>983900</v>
@@ -3252,16 +3252,16 @@
         <v>43774</v>
       </c>
       <c r="B142" t="n">
-        <v>24.46124649047852</v>
+        <v>24.46124839782715</v>
       </c>
       <c r="C142" t="n">
-        <v>25.22210832450975</v>
+        <v>25.22211029118606</v>
       </c>
       <c r="D142" t="n">
-        <v>24.43501096839025</v>
+        <v>24.43501287369319</v>
       </c>
       <c r="E142" t="n">
-        <v>24.8897772547205</v>
+        <v>24.88977919548352</v>
       </c>
       <c r="F142" t="n">
         <v>572300</v>
@@ -3272,16 +3272,16 @@
         <v>43775</v>
       </c>
       <c r="B143" t="n">
-        <v>24.40002632141113</v>
+        <v>24.40002822875977</v>
       </c>
       <c r="C143" t="n">
-        <v>24.83730278476286</v>
+        <v>24.83730472629337</v>
       </c>
       <c r="D143" t="n">
-        <v>24.40002632141113</v>
+        <v>24.40002822875977</v>
       </c>
       <c r="E143" t="n">
-        <v>24.65364747083225</v>
+        <v>24.65364939800644</v>
       </c>
       <c r="F143" t="n">
         <v>511100</v>
@@ -3312,16 +3312,16 @@
         <v>43777</v>
       </c>
       <c r="B145" t="n">
-        <v>24.05020904541016</v>
+        <v>24.05020713806152</v>
       </c>
       <c r="C145" t="n">
-        <v>24.74110676048281</v>
+        <v>24.74110479834119</v>
       </c>
       <c r="D145" t="n">
-        <v>24.04146331467888</v>
+        <v>24.04146140802384</v>
       </c>
       <c r="E145" t="n">
-        <v>24.37379441015708</v>
+        <v>24.37379247714588</v>
       </c>
       <c r="F145" t="n">
         <v>636200</v>
@@ -3392,16 +3392,16 @@
         <v>43783</v>
       </c>
       <c r="B149" t="n">
-        <v>24.05020904541016</v>
+        <v>24.05020713806152</v>
       </c>
       <c r="C149" t="n">
-        <v>25.04719899568961</v>
+        <v>25.04719700927275</v>
       </c>
       <c r="D149" t="n">
-        <v>23.4817498924978</v>
+        <v>23.48174803023192</v>
       </c>
       <c r="E149" t="n">
-        <v>24.63615965978507</v>
+        <v>24.63615770596648</v>
       </c>
       <c r="F149" t="n">
         <v>1658400</v>
@@ -3412,16 +3412,16 @@
         <v>43787</v>
       </c>
       <c r="B150" t="n">
-        <v>24.05020904541016</v>
+        <v>24.05020713806152</v>
       </c>
       <c r="C150" t="n">
-        <v>24.60992246759124</v>
+        <v>24.60992051585345</v>
       </c>
       <c r="D150" t="n">
-        <v>23.91028068986488</v>
+        <v>23.91027879361354</v>
       </c>
       <c r="E150" t="n">
-        <v>24.43501285719844</v>
+        <v>24.43501091933219</v>
       </c>
       <c r="F150" t="n">
         <v>1045200</v>
@@ -3452,16 +3452,16 @@
         <v>43790</v>
       </c>
       <c r="B152" t="n">
-        <v>23.52547454833984</v>
+        <v>23.52547645568848</v>
       </c>
       <c r="C152" t="n">
-        <v>23.97149676299973</v>
+        <v>23.97149870651001</v>
       </c>
       <c r="D152" t="n">
-        <v>23.45551037749579</v>
+        <v>23.45551227917201</v>
       </c>
       <c r="E152" t="n">
-        <v>23.87529540256013</v>
+        <v>23.87529733827079</v>
       </c>
       <c r="F152" t="n">
         <v>699200</v>
@@ -3512,16 +3512,16 @@
         <v>43795</v>
       </c>
       <c r="B155" t="n">
-        <v>23.42053031921387</v>
+        <v>23.4205322265625</v>
       </c>
       <c r="C155" t="n">
-        <v>24.13766352391739</v>
+        <v>24.13766548966876</v>
       </c>
       <c r="D155" t="n">
-        <v>23.3155832235628</v>
+        <v>23.31558512236463</v>
       </c>
       <c r="E155" t="n">
-        <v>24.06769934950918</v>
+        <v>24.06770130956273</v>
       </c>
       <c r="F155" t="n">
         <v>1676700</v>
@@ -3572,16 +3572,16 @@
         <v>43798</v>
       </c>
       <c r="B158" t="n">
-        <v>23.63042259216309</v>
+        <v>23.63042068481445</v>
       </c>
       <c r="C158" t="n">
-        <v>24.01522471329396</v>
+        <v>24.01522277488572</v>
       </c>
       <c r="D158" t="n">
-        <v>23.48174851461059</v>
+        <v>23.48174661926231</v>
       </c>
       <c r="E158" t="n">
-        <v>23.56920414871397</v>
+        <v>23.56920224630663</v>
       </c>
       <c r="F158" t="n">
         <v>1630000</v>
@@ -3592,16 +3592,16 @@
         <v>43801</v>
       </c>
       <c r="B159" t="n">
-        <v>25.08218193054199</v>
+        <v>25.08218002319336</v>
       </c>
       <c r="C159" t="n">
-        <v>25.44074855030696</v>
+        <v>25.44074661569149</v>
       </c>
       <c r="D159" t="n">
-        <v>23.79658786975181</v>
+        <v>23.79658606016485</v>
       </c>
       <c r="E159" t="n">
-        <v>23.79658786975181</v>
+        <v>23.79658606016485</v>
       </c>
       <c r="F159" t="n">
         <v>1775700</v>
@@ -3672,16 +3672,16 @@
         <v>43805</v>
       </c>
       <c r="B163" t="n">
-        <v>26.8050479888916</v>
+        <v>26.80504989624023</v>
       </c>
       <c r="C163" t="n">
-        <v>27.46096271130205</v>
+        <v>27.46096466532317</v>
       </c>
       <c r="D163" t="n">
-        <v>26.64762818862071</v>
+        <v>26.64763008476793</v>
       </c>
       <c r="E163" t="n">
-        <v>26.76132100796186</v>
+        <v>26.76132291219905</v>
       </c>
       <c r="F163" t="n">
         <v>1348800</v>
@@ -3712,16 +3712,16 @@
         <v>43809</v>
       </c>
       <c r="B165" t="n">
-        <v>26.00920486450195</v>
+        <v>26.00920677185059</v>
       </c>
       <c r="C165" t="n">
-        <v>26.36777144512823</v>
+        <v>26.36777337877184</v>
       </c>
       <c r="D165" t="n">
-        <v>25.86053079438296</v>
+        <v>25.86053269082878</v>
       </c>
       <c r="E165" t="n">
-        <v>26.36777144512823</v>
+        <v>26.36777337877184</v>
       </c>
       <c r="F165" t="n">
         <v>763900</v>
@@ -3752,16 +3752,16 @@
         <v>43811</v>
       </c>
       <c r="B167" t="n">
-        <v>28.20433235168457</v>
+        <v>28.20433616638184</v>
       </c>
       <c r="C167" t="n">
-        <v>28.52791600578213</v>
+        <v>28.52791986424479</v>
       </c>
       <c r="D167" t="n">
-        <v>27.13737836400466</v>
+        <v>27.13738203439408</v>
       </c>
       <c r="E167" t="n">
-        <v>27.16361388466928</v>
+        <v>27.16361755860711</v>
       </c>
       <c r="F167" t="n">
         <v>1320800</v>
@@ -3772,16 +3772,16 @@
         <v>43812</v>
       </c>
       <c r="B168" t="n">
-        <v>28.86024856567383</v>
+        <v>28.86025047302246</v>
       </c>
       <c r="C168" t="n">
-        <v>29.55989028791373</v>
+        <v>29.55989224150107</v>
       </c>
       <c r="D168" t="n">
-        <v>28.51917343459155</v>
+        <v>28.51917531939883</v>
       </c>
       <c r="E168" t="n">
-        <v>28.81652158356287</v>
+        <v>28.81652348802163</v>
       </c>
       <c r="F168" t="n">
         <v>1941500</v>
@@ -3792,16 +3792,16 @@
         <v>43815</v>
       </c>
       <c r="B169" t="n">
-        <v>29.48118209838867</v>
+        <v>29.48118019104004</v>
       </c>
       <c r="C169" t="n">
-        <v>30.15458833771514</v>
+        <v>30.15458638679904</v>
       </c>
       <c r="D169" t="n">
-        <v>29.21881685432572</v>
+        <v>29.21881496395137</v>
       </c>
       <c r="E169" t="n">
-        <v>29.29752676116011</v>
+        <v>29.29752486569346</v>
       </c>
       <c r="F169" t="n">
         <v>1422400</v>
@@ -3832,16 +3832,16 @@
         <v>43817</v>
       </c>
       <c r="B171" t="n">
-        <v>29.01766967773438</v>
+        <v>29.01766777038574</v>
       </c>
       <c r="C171" t="n">
-        <v>29.19258095021458</v>
+        <v>29.19257903136893</v>
       </c>
       <c r="D171" t="n">
-        <v>28.56290170374785</v>
+        <v>28.56289982629139</v>
       </c>
       <c r="E171" t="n">
-        <v>28.5978846254749</v>
+        <v>28.59788274571899</v>
       </c>
       <c r="F171" t="n">
         <v>1262800</v>
@@ -3872,16 +3872,16 @@
         <v>43819</v>
       </c>
       <c r="B173" t="n">
-        <v>29.08763122558594</v>
+        <v>29.08763313293457</v>
       </c>
       <c r="C173" t="n">
-        <v>29.31501687315646</v>
+        <v>29.31501879541534</v>
       </c>
       <c r="D173" t="n">
-        <v>28.89523183474349</v>
+        <v>28.89523372947601</v>
       </c>
       <c r="E173" t="n">
-        <v>29.28003395258332</v>
+        <v>29.28003587254828</v>
       </c>
       <c r="F173" t="n">
         <v>2528100</v>
@@ -3932,16 +3932,16 @@
         <v>43826</v>
       </c>
       <c r="B176" t="n">
-        <v>30.60935211181641</v>
+        <v>30.60935592651367</v>
       </c>
       <c r="C176" t="n">
-        <v>31.13408252784284</v>
+        <v>31.13408640793475</v>
       </c>
       <c r="D176" t="n">
-        <v>30.43444086108939</v>
+        <v>30.4344446539883</v>
       </c>
       <c r="E176" t="n">
-        <v>30.91544429847272</v>
+        <v>30.9154481513168</v>
       </c>
       <c r="F176" t="n">
         <v>646400</v>
@@ -4012,16 +4012,16 @@
         <v>43836</v>
       </c>
       <c r="B180" t="n">
-        <v>33.23301315307617</v>
+        <v>33.23301696777344</v>
       </c>
       <c r="C180" t="n">
-        <v>33.67028964193243</v>
+        <v>33.67029350682309</v>
       </c>
       <c r="D180" t="n">
-        <v>32.49838851835145</v>
+        <v>32.49839224872381</v>
       </c>
       <c r="E180" t="n">
-        <v>33.20677763131435</v>
+        <v>33.20678144300013</v>
       </c>
       <c r="F180" t="n">
         <v>1231600</v>
@@ -4132,16 +4132,16 @@
         <v>43844</v>
       </c>
       <c r="B186" t="n">
-        <v>36.53007888793945</v>
+        <v>36.53008270263672</v>
       </c>
       <c r="C186" t="n">
-        <v>36.74871713600984</v>
+        <v>36.74872097353867</v>
       </c>
       <c r="D186" t="n">
-        <v>35.20950200134754</v>
+        <v>35.20950567814199</v>
       </c>
       <c r="E186" t="n">
-        <v>35.37566920502018</v>
+        <v>35.37567289916683</v>
       </c>
       <c r="F186" t="n">
         <v>1956900</v>
@@ -4232,16 +4232,16 @@
         <v>43851</v>
       </c>
       <c r="B191" t="n">
-        <v>35.6817626953125</v>
+        <v>35.68175888061523</v>
       </c>
       <c r="C191" t="n">
-        <v>36.29395047905773</v>
+        <v>36.29394659891216</v>
       </c>
       <c r="D191" t="n">
-        <v>35.28821316746521</v>
+        <v>35.28820939484188</v>
       </c>
       <c r="E191" t="n">
-        <v>35.62929164903621</v>
+        <v>35.62928783994857</v>
       </c>
       <c r="F191" t="n">
         <v>1445700</v>
@@ -4292,16 +4292,16 @@
         <v>43854</v>
       </c>
       <c r="B194" t="n">
-        <v>35.29695510864258</v>
+        <v>35.29695892333984</v>
       </c>
       <c r="C194" t="n">
-        <v>36.04032372930043</v>
+        <v>36.04032762433681</v>
       </c>
       <c r="D194" t="n">
-        <v>34.80720429013636</v>
+        <v>34.8072080519041</v>
       </c>
       <c r="E194" t="n">
-        <v>35.63803020132452</v>
+        <v>35.63803405288327</v>
       </c>
       <c r="F194" t="n">
         <v>1110500</v>
@@ -4312,16 +4312,16 @@
         <v>43857</v>
       </c>
       <c r="B195" t="n">
-        <v>34.71975708007812</v>
+        <v>34.71975326538086</v>
       </c>
       <c r="C195" t="n">
-        <v>35.29696196508228</v>
+        <v>35.29695808696688</v>
       </c>
       <c r="D195" t="n">
-        <v>33.44291041569851</v>
+        <v>33.44290674128978</v>
       </c>
       <c r="E195" t="n">
-        <v>34.47487995518034</v>
+        <v>34.47487616738799</v>
       </c>
       <c r="F195" t="n">
         <v>1317600</v>
@@ -4472,16 +4472,16 @@
         <v>43867</v>
       </c>
       <c r="B203" t="n">
-        <v>43.47403335571289</v>
+        <v>43.47402954101562</v>
       </c>
       <c r="C203" t="n">
-        <v>43.47403335571289</v>
+        <v>43.47402954101562</v>
       </c>
       <c r="D203" t="n">
-        <v>39.53854444596122</v>
+        <v>39.5385409765896</v>
       </c>
       <c r="E203" t="n">
-        <v>39.53854444596122</v>
+        <v>39.5385409765896</v>
       </c>
       <c r="F203" t="n">
         <v>6803000</v>
@@ -4492,16 +4492,16 @@
         <v>43868</v>
       </c>
       <c r="B204" t="n">
-        <v>40.86786270141602</v>
+        <v>40.86785888671875</v>
       </c>
       <c r="C204" t="n">
-        <v>47.30457353755293</v>
+        <v>47.30456912203875</v>
       </c>
       <c r="D204" t="n">
-        <v>40.84162717807931</v>
+        <v>40.84162336583092</v>
       </c>
       <c r="E204" t="n">
-        <v>44.61094860314898</v>
+        <v>44.61094443906375</v>
       </c>
       <c r="F204" t="n">
         <v>8429100</v>
@@ -4572,16 +4572,16 @@
         <v>43874</v>
       </c>
       <c r="B208" t="n">
-        <v>41.10399627685547</v>
+        <v>41.1039924621582</v>
       </c>
       <c r="C208" t="n">
-        <v>42.69568267430085</v>
+        <v>42.69567871188554</v>
       </c>
       <c r="D208" t="n">
-        <v>40.12449772523263</v>
+        <v>40.1244940014387</v>
       </c>
       <c r="E208" t="n">
-        <v>41.1389792020237</v>
+        <v>41.13897538407981</v>
       </c>
       <c r="F208" t="n">
         <v>1557300</v>
@@ -4632,16 +4632,16 @@
         <v>43879</v>
       </c>
       <c r="B211" t="n">
-        <v>42.86184310913086</v>
+        <v>42.86183929443359</v>
       </c>
       <c r="C211" t="n">
-        <v>43.37782953722005</v>
+        <v>43.37782567660008</v>
       </c>
       <c r="D211" t="n">
-        <v>42.06599997456838</v>
+        <v>42.06599623070103</v>
       </c>
       <c r="E211" t="n">
-        <v>42.59073380132211</v>
+        <v>42.59073001075353</v>
       </c>
       <c r="F211" t="n">
         <v>1138300</v>
@@ -4732,16 +4732,16 @@
         <v>43888</v>
       </c>
       <c r="B216" t="n">
-        <v>39.09252166748047</v>
+        <v>39.0925178527832</v>
       </c>
       <c r="C216" t="n">
-        <v>41.60248796536411</v>
+        <v>41.60248390574118</v>
       </c>
       <c r="D216" t="n">
-        <v>38.91761039174722</v>
+        <v>38.91760659411801</v>
       </c>
       <c r="E216" t="n">
-        <v>41.10399299802515</v>
+        <v>41.10398898704599</v>
       </c>
       <c r="F216" t="n">
         <v>1773000</v>
@@ -4752,16 +4752,16 @@
         <v>43889</v>
       </c>
       <c r="B217" t="n">
-        <v>38.12176895141602</v>
+        <v>38.12176513671875</v>
       </c>
       <c r="C217" t="n">
-        <v>38.90012066007195</v>
+        <v>38.90011676748805</v>
       </c>
       <c r="D217" t="n">
-        <v>35.4718741823615</v>
+        <v>35.47187063282891</v>
       </c>
       <c r="E217" t="n">
-        <v>38.05180310354997</v>
+        <v>38.05179929585391</v>
       </c>
       <c r="F217" t="n">
         <v>3154200</v>
@@ -4772,16 +4772,16 @@
         <v>43892</v>
       </c>
       <c r="B218" t="n">
-        <v>41.10399627685547</v>
+        <v>41.1039924621582</v>
       </c>
       <c r="C218" t="n">
-        <v>41.49754584460963</v>
+        <v>41.4975419933886</v>
       </c>
       <c r="D218" t="n">
-        <v>38.56779091680011</v>
+        <v>38.56778733747791</v>
       </c>
       <c r="E218" t="n">
-        <v>38.56779091680011</v>
+        <v>38.56778733747791</v>
       </c>
       <c r="F218" t="n">
         <v>1962800</v>
@@ -4792,16 +4792,16 @@
         <v>43893</v>
       </c>
       <c r="B219" t="n">
-        <v>42.31962203979492</v>
+        <v>42.31961822509766</v>
       </c>
       <c r="C219" t="n">
-        <v>43.5090147351848</v>
+        <v>43.50901081327549</v>
       </c>
       <c r="D219" t="n">
-        <v>40.49180601094095</v>
+        <v>40.4918023610033</v>
       </c>
       <c r="E219" t="n">
-        <v>41.8736014471013</v>
+        <v>41.8735976726084</v>
       </c>
       <c r="F219" t="n">
         <v>2101900</v>
@@ -4852,16 +4852,16 @@
         <v>43896</v>
       </c>
       <c r="B222" t="n">
-        <v>37.85065078735352</v>
+        <v>37.85065460205078</v>
       </c>
       <c r="C222" t="n">
-        <v>38.43660300142383</v>
+        <v>38.43660687517504</v>
       </c>
       <c r="D222" t="n">
-        <v>34.80720690730548</v>
+        <v>34.80721041527573</v>
       </c>
       <c r="E222" t="n">
-        <v>35.85667111949734</v>
+        <v>35.8566747332356</v>
       </c>
       <c r="F222" t="n">
         <v>1754400</v>
@@ -4872,16 +4872,16 @@
         <v>43899</v>
       </c>
       <c r="B223" t="n">
-        <v>30.74928092956543</v>
+        <v>30.7492847442627</v>
       </c>
       <c r="C223" t="n">
-        <v>34.72849609955585</v>
+        <v>34.72850040790698</v>
       </c>
       <c r="D223" t="n">
-        <v>30.74928092956543</v>
+        <v>30.7492847442627</v>
       </c>
       <c r="E223" t="n">
-        <v>33.23301138778275</v>
+        <v>33.23301551060689</v>
       </c>
       <c r="F223" t="n">
         <v>2155800</v>
@@ -4912,16 +4912,16 @@
         <v>43901</v>
       </c>
       <c r="B225" t="n">
-        <v>30.88920974731445</v>
+        <v>30.88921356201172</v>
       </c>
       <c r="C225" t="n">
-        <v>34.1950188115032</v>
+        <v>34.19502303445503</v>
       </c>
       <c r="D225" t="n">
-        <v>28.51917206728659</v>
+        <v>28.51917558929342</v>
       </c>
       <c r="E225" t="n">
-        <v>33.06684804804742</v>
+        <v>33.06685213167455</v>
       </c>
       <c r="F225" t="n">
         <v>2211100</v>
@@ -4932,16 +4932,16 @@
         <v>43902</v>
       </c>
       <c r="B226" t="n">
-        <v>27.34727478027344</v>
+        <v>27.3472728729248</v>
       </c>
       <c r="C226" t="n">
-        <v>28.76404981338677</v>
+        <v>28.76404780722449</v>
       </c>
       <c r="D226" t="n">
-        <v>20.5519970555954</v>
+        <v>20.55199562218663</v>
       </c>
       <c r="E226" t="n">
-        <v>25.26583754860458</v>
+        <v>25.26583578642677</v>
       </c>
       <c r="F226" t="n">
         <v>1655000</v>
@@ -4972,16 +4972,16 @@
         <v>43906</v>
       </c>
       <c r="B228" t="n">
-        <v>24.01522254943848</v>
+        <v>24.01522445678711</v>
       </c>
       <c r="C228" t="n">
-        <v>27.81078238206535</v>
+        <v>27.81078459086677</v>
       </c>
       <c r="D228" t="n">
-        <v>24.01522254943848</v>
+        <v>24.01522445678711</v>
       </c>
       <c r="E228" t="n">
-        <v>24.31257067775135</v>
+        <v>24.31257260871611</v>
       </c>
       <c r="F228" t="n">
         <v>1420100</v>
@@ -5032,16 +5032,16 @@
         <v>43909</v>
       </c>
       <c r="B231" t="n">
-        <v>17.8758659362793</v>
+        <v>17.87586402893066</v>
       </c>
       <c r="C231" t="n">
-        <v>19.41507960150845</v>
+        <v>19.41507752992625</v>
       </c>
       <c r="D231" t="n">
-        <v>12.88216683848594</v>
+        <v>12.88216546396326</v>
       </c>
       <c r="E231" t="n">
-        <v>13.96661332273852</v>
+        <v>13.96661183250577</v>
       </c>
       <c r="F231" t="n">
         <v>3933800</v>
@@ -5052,16 +5052,16 @@
         <v>43910</v>
       </c>
       <c r="B232" t="n">
-        <v>19.54626083374023</v>
+        <v>19.5462589263916</v>
       </c>
       <c r="C232" t="n">
-        <v>23.60418641720726</v>
+        <v>23.60418411388116</v>
       </c>
       <c r="D232" t="n">
-        <v>18.40934087762918</v>
+        <v>18.40933908122262</v>
       </c>
       <c r="E232" t="n">
-        <v>20.11471997775699</v>
+        <v>20.1147180149374</v>
       </c>
       <c r="F232" t="n">
         <v>4389300</v>
@@ -5092,16 +5092,16 @@
         <v>43914</v>
       </c>
       <c r="B234" t="n">
-        <v>20.82310676574707</v>
+        <v>20.82310485839844</v>
       </c>
       <c r="C234" t="n">
-        <v>21.68891404816831</v>
+        <v>21.68891206151372</v>
       </c>
       <c r="D234" t="n">
-        <v>18.97780104320539</v>
+        <v>18.97779930488251</v>
       </c>
       <c r="E234" t="n">
-        <v>20.7356511308598</v>
+        <v>20.7356492315219</v>
       </c>
       <c r="F234" t="n">
         <v>2869200</v>
@@ -5192,16 +5192,16 @@
         <v>43921</v>
       </c>
       <c r="B239" t="n">
-        <v>21.04174613952637</v>
+        <v>21.0417423248291</v>
       </c>
       <c r="C239" t="n">
-        <v>23.1406731482139</v>
+        <v>23.14066895299826</v>
       </c>
       <c r="D239" t="n">
-        <v>20.40332280658114</v>
+        <v>20.40331910762483</v>
       </c>
       <c r="E239" t="n">
-        <v>23.06196490750891</v>
+        <v>23.06196072656243</v>
       </c>
       <c r="F239" t="n">
         <v>1663000</v>
@@ -5252,16 +5252,16 @@
         <v>43924</v>
       </c>
       <c r="B242" t="n">
-        <v>17.05378341674805</v>
+        <v>17.05378532409668</v>
       </c>
       <c r="C242" t="n">
-        <v>18.55801396889691</v>
+        <v>18.55801604448341</v>
       </c>
       <c r="D242" t="n">
-        <v>16.61650691888271</v>
+        <v>16.61650877732497</v>
       </c>
       <c r="E242" t="n">
-        <v>18.55801396889691</v>
+        <v>18.55801604448341</v>
       </c>
       <c r="F242" t="n">
         <v>2202300</v>
@@ -5272,16 +5272,16 @@
         <v>43927</v>
       </c>
       <c r="B243" t="n">
-        <v>20.12346649169922</v>
+        <v>20.12346458435059</v>
       </c>
       <c r="C243" t="n">
-        <v>21.40031318279222</v>
+        <v>21.40031115442111</v>
       </c>
       <c r="D243" t="n">
-        <v>18.24317771072155</v>
+        <v>18.24317598159103</v>
       </c>
       <c r="E243" t="n">
-        <v>18.88160105626805</v>
+        <v>18.8815992666263</v>
       </c>
       <c r="F243" t="n">
         <v>4954700</v>
@@ -5292,16 +5292,16 @@
         <v>43928</v>
       </c>
       <c r="B244" t="n">
-        <v>22.03873443603516</v>
+        <v>22.03873634338379</v>
       </c>
       <c r="C244" t="n">
-        <v>23.07945121854635</v>
+        <v>23.07945321596411</v>
       </c>
       <c r="D244" t="n">
-        <v>21.86382318333752</v>
+        <v>21.86382507554841</v>
       </c>
       <c r="E244" t="n">
-        <v>22.30109964700427</v>
+        <v>22.30110157705938</v>
       </c>
       <c r="F244" t="n">
         <v>4003700</v>
@@ -5392,16 +5392,16 @@
         <v>43936</v>
       </c>
       <c r="B249" t="n">
-        <v>21.33909225463867</v>
+        <v>21.33909034729004</v>
       </c>
       <c r="C249" t="n">
-        <v>22.37106503194663</v>
+        <v>22.37106303235734</v>
       </c>
       <c r="D249" t="n">
-        <v>20.55199491081855</v>
+        <v>20.55199307382291</v>
       </c>
       <c r="E249" t="n">
-        <v>20.99801712820135</v>
+        <v>20.99801525133898</v>
       </c>
       <c r="F249" t="n">
         <v>1195900</v>
@@ -5412,16 +5412,16 @@
         <v>43937</v>
       </c>
       <c r="B250" t="n">
-        <v>20.77938079833984</v>
+        <v>20.77937889099121</v>
       </c>
       <c r="C250" t="n">
-        <v>22.36232136169431</v>
+        <v>22.36231930904686</v>
       </c>
       <c r="D250" t="n">
-        <v>20.77938079833984</v>
+        <v>20.77937889099121</v>
       </c>
       <c r="E250" t="n">
-        <v>22.11744757372997</v>
+        <v>22.11744554355958</v>
       </c>
       <c r="F250" t="n">
         <v>1150400</v>
@@ -5532,16 +5532,16 @@
         <v>43948</v>
       </c>
       <c r="B256" t="n">
-        <v>24.95974540710449</v>
+        <v>24.95974349975586</v>
       </c>
       <c r="C256" t="n">
-        <v>25.92175244920407</v>
+        <v>25.92175046834176</v>
       </c>
       <c r="D256" t="n">
-        <v>24.00648242779263</v>
+        <v>24.00648059328949</v>
       </c>
       <c r="E256" t="n">
-        <v>25.27458337786827</v>
+        <v>25.27458144646067</v>
       </c>
       <c r="F256" t="n">
         <v>2033000</v>
@@ -5552,16 +5552,16 @@
         <v>43949</v>
       </c>
       <c r="B257" t="n">
-        <v>28.33551788330078</v>
+        <v>28.33551979064941</v>
       </c>
       <c r="C257" t="n">
-        <v>28.93895823841771</v>
+        <v>28.93896018638572</v>
       </c>
       <c r="D257" t="n">
-        <v>25.58942039211449</v>
+        <v>25.58942211461507</v>
       </c>
       <c r="E257" t="n">
-        <v>25.81680436705841</v>
+        <v>25.81680610486489</v>
       </c>
       <c r="F257" t="n">
         <v>3349000</v>
@@ -5572,16 +5572,16 @@
         <v>43950</v>
       </c>
       <c r="B258" t="n">
-        <v>28.86024856567383</v>
+        <v>28.86025047302246</v>
       </c>
       <c r="C258" t="n">
-        <v>30.34698931053043</v>
+        <v>30.34699131613646</v>
       </c>
       <c r="D258" t="n">
-        <v>27.70583888993927</v>
+        <v>27.70584072099397</v>
       </c>
       <c r="E258" t="n">
-        <v>29.12261379449443</v>
+        <v>29.12261571918255</v>
       </c>
       <c r="F258" t="n">
         <v>3060300</v>
@@ -5632,16 +5632,16 @@
         <v>43956</v>
       </c>
       <c r="B261" t="n">
-        <v>26.46397590637207</v>
+        <v>26.46397399902344</v>
       </c>
       <c r="C261" t="n">
-        <v>28.89523402384113</v>
+        <v>28.89523194126346</v>
       </c>
       <c r="D261" t="n">
-        <v>26.25408337126416</v>
+        <v>26.2540814790432</v>
       </c>
       <c r="E261" t="n">
-        <v>28.42297456879014</v>
+        <v>28.42297252024982</v>
       </c>
       <c r="F261" t="n">
         <v>1862000</v>
@@ -5732,16 +5732,16 @@
         <v>43963</v>
       </c>
       <c r="B266" t="n">
-        <v>20.55199813842773</v>
+        <v>20.5519962310791</v>
       </c>
       <c r="C266" t="n">
-        <v>22.69465393072893</v>
+        <v>22.694651824529</v>
       </c>
       <c r="D266" t="n">
-        <v>20.40332404261813</v>
+        <v>20.40332214906734</v>
       </c>
       <c r="E266" t="n">
-        <v>22.126193073289</v>
+        <v>22.12619101984564</v>
       </c>
       <c r="F266" t="n">
         <v>3436100</v>
@@ -5752,16 +5752,16 @@
         <v>43964</v>
       </c>
       <c r="B267" t="n">
-        <v>20.28963088989258</v>
+        <v>20.28962898254395</v>
       </c>
       <c r="C267" t="n">
-        <v>21.12920099498067</v>
+        <v>21.12919900870735</v>
       </c>
       <c r="D267" t="n">
-        <v>19.54626048346404</v>
+        <v>19.54625864599675</v>
       </c>
       <c r="E267" t="n">
-        <v>20.81436137153388</v>
+        <v>20.81435941485739</v>
       </c>
       <c r="F267" t="n">
         <v>3188300</v>
@@ -5792,16 +5792,16 @@
         <v>43966</v>
       </c>
       <c r="B269" t="n">
-        <v>21.57522010803223</v>
+        <v>21.57522201538086</v>
       </c>
       <c r="C269" t="n">
-        <v>21.76762114550933</v>
+        <v>21.7676230698671</v>
       </c>
       <c r="D269" t="n">
-        <v>19.91356993177791</v>
+        <v>19.91357169222903</v>
       </c>
       <c r="E269" t="n">
-        <v>20.10597096925501</v>
+        <v>20.10597274671526</v>
       </c>
       <c r="F269" t="n">
         <v>3697100</v>
@@ -5812,16 +5812,16 @@
         <v>43969</v>
       </c>
       <c r="B270" t="n">
-        <v>22.58095550537109</v>
+        <v>22.58095741271973</v>
       </c>
       <c r="C270" t="n">
-        <v>22.82583091673227</v>
+        <v>22.82583284476483</v>
       </c>
       <c r="D270" t="n">
-        <v>20.99801523084493</v>
+        <v>20.99801700448714</v>
       </c>
       <c r="E270" t="n">
-        <v>22.47601009198578</v>
+        <v>22.47601199046998</v>
       </c>
       <c r="F270" t="n">
         <v>4127300</v>
@@ -5852,16 +5852,16 @@
         <v>43971</v>
       </c>
       <c r="B272" t="n">
-        <v>23.35056686401367</v>
+        <v>23.35056495666504</v>
       </c>
       <c r="C272" t="n">
-        <v>24.5574493267472</v>
+        <v>24.55744732081656</v>
       </c>
       <c r="D272" t="n">
-        <v>22.90454461289459</v>
+        <v>22.90454274197847</v>
       </c>
       <c r="E272" t="n">
-        <v>24.38253805130057</v>
+        <v>24.38253605965725</v>
       </c>
       <c r="F272" t="n">
         <v>1832900</v>
@@ -5932,16 +5932,16 @@
         <v>43977</v>
       </c>
       <c r="B276" t="n">
-        <v>24.7236156463623</v>
+        <v>24.72361183166504</v>
       </c>
       <c r="C276" t="n">
-        <v>25.80806125111232</v>
+        <v>25.80805726909197</v>
       </c>
       <c r="D276" t="n">
-        <v>24.59243301970533</v>
+        <v>24.59242922524871</v>
       </c>
       <c r="E276" t="n">
-        <v>24.88977952835826</v>
+        <v>24.88977568802297</v>
       </c>
       <c r="F276" t="n">
         <v>1928700</v>
@@ -5972,16 +5972,16 @@
         <v>43979</v>
       </c>
       <c r="B278" t="n">
-        <v>25.36203765869141</v>
+        <v>25.36203575134277</v>
       </c>
       <c r="C278" t="n">
-        <v>26.29780912610245</v>
+        <v>26.29780714837925</v>
       </c>
       <c r="D278" t="n">
-        <v>24.609921525373</v>
+        <v>24.60991967458716</v>
       </c>
       <c r="E278" t="n">
-        <v>25.1871263869177</v>
+        <v>25.18712449272325</v>
       </c>
       <c r="F278" t="n">
         <v>2478400</v>
@@ -6152,16 +6152,16 @@
         <v>43992</v>
       </c>
       <c r="B287" t="n">
-        <v>27.99444007873535</v>
+        <v>27.99443817138672</v>
       </c>
       <c r="C287" t="n">
-        <v>30.25078842143119</v>
+        <v>30.2507863603505</v>
       </c>
       <c r="D287" t="n">
-        <v>27.43472836026485</v>
+        <v>27.43472649105112</v>
       </c>
       <c r="E287" t="n">
-        <v>29.99716725060322</v>
+        <v>29.99716520680253</v>
       </c>
       <c r="F287" t="n">
         <v>3410700</v>
@@ -6172,16 +6172,16 @@
         <v>43994</v>
       </c>
       <c r="B288" t="n">
-        <v>29.31501770019531</v>
+        <v>29.31501579284668</v>
       </c>
       <c r="C288" t="n">
-        <v>29.31501770019531</v>
+        <v>29.31501579284668</v>
       </c>
       <c r="D288" t="n">
-        <v>26.24533639255295</v>
+        <v>26.24533468492967</v>
       </c>
       <c r="E288" t="n">
-        <v>26.24533639255295</v>
+        <v>26.24533468492967</v>
       </c>
       <c r="F288" t="n">
         <v>3674500</v>
@@ -6192,16 +6192,16 @@
         <v>43997</v>
       </c>
       <c r="B289" t="n">
-        <v>28.93021392822266</v>
+        <v>28.93021583557129</v>
       </c>
       <c r="C289" t="n">
-        <v>29.14885217132172</v>
+        <v>29.14885409308502</v>
       </c>
       <c r="D289" t="n">
-        <v>27.22483329674156</v>
+        <v>27.22483509165565</v>
       </c>
       <c r="E289" t="n">
-        <v>28.4229716028785</v>
+        <v>28.42297347678501</v>
       </c>
       <c r="F289" t="n">
         <v>3246400</v>
@@ -6312,16 +6312,16 @@
         <v>44005</v>
       </c>
       <c r="B295" t="n">
-        <v>29.64734649658203</v>
+        <v>29.64734840393066</v>
       </c>
       <c r="C295" t="n">
-        <v>30.83673571251537</v>
+        <v>30.83673769638282</v>
       </c>
       <c r="D295" t="n">
-        <v>29.48117930006237</v>
+        <v>29.48118119672071</v>
       </c>
       <c r="E295" t="n">
-        <v>30.62684487164969</v>
+        <v>30.6268468420139</v>
       </c>
       <c r="F295" t="n">
         <v>1337100</v>
@@ -6332,16 +6332,16 @@
         <v>44006</v>
       </c>
       <c r="B296" t="n">
-        <v>29.17508697509766</v>
+        <v>29.17508888244629</v>
       </c>
       <c r="C296" t="n">
-        <v>29.4724351118426</v>
+        <v>29.47243703863064</v>
       </c>
       <c r="D296" t="n">
-        <v>28.01192994907473</v>
+        <v>28.01193178038088</v>
       </c>
       <c r="E296" t="n">
-        <v>29.4724351118426</v>
+        <v>29.47243703863064</v>
       </c>
       <c r="F296" t="n">
         <v>2563900</v>
@@ -6352,16 +6352,16 @@
         <v>44007</v>
       </c>
       <c r="B297" t="n">
-        <v>29.05265235900879</v>
+        <v>29.05265426635742</v>
       </c>
       <c r="C297" t="n">
-        <v>29.3674919796364</v>
+        <v>29.36749390765471</v>
       </c>
       <c r="D297" t="n">
-        <v>28.36175467331542</v>
+        <v>28.36175653530562</v>
       </c>
       <c r="E297" t="n">
-        <v>29.03516089829003</v>
+        <v>29.03516280449032</v>
       </c>
       <c r="F297" t="n">
         <v>2662400</v>
@@ -6412,16 +6412,16 @@
         <v>44012</v>
       </c>
       <c r="B300" t="n">
-        <v>28.60662460327148</v>
+        <v>28.60662651062012</v>
       </c>
       <c r="C300" t="n">
-        <v>29.97967239153654</v>
+        <v>29.97967439043323</v>
       </c>
       <c r="D300" t="n">
-        <v>28.32676794172412</v>
+        <v>28.32676983041329</v>
       </c>
       <c r="E300" t="n">
-        <v>28.93895563991694</v>
+        <v>28.93895756942377</v>
       </c>
       <c r="F300" t="n">
         <v>2290400</v>
@@ -6452,16 +6452,16 @@
         <v>44014</v>
       </c>
       <c r="B302" t="n">
-        <v>28.21307945251465</v>
+        <v>28.21307754516602</v>
       </c>
       <c r="C302" t="n">
-        <v>28.99143445634729</v>
+        <v>28.99143249637787</v>
       </c>
       <c r="D302" t="n">
-        <v>27.90698722460383</v>
+        <v>27.9069853379486</v>
       </c>
       <c r="E302" t="n">
-        <v>28.50168355553491</v>
+        <v>28.50168162867516</v>
       </c>
       <c r="F302" t="n">
         <v>1693900</v>
@@ -6512,16 +6512,16 @@
         <v>44019</v>
       </c>
       <c r="B305" t="n">
-        <v>28.39673614501953</v>
+        <v>28.39673805236816</v>
       </c>
       <c r="C305" t="n">
-        <v>29.46368850515272</v>
+        <v>29.46369048416628</v>
       </c>
       <c r="D305" t="n">
-        <v>27.96820371967529</v>
+        <v>27.96820559824031</v>
       </c>
       <c r="E305" t="n">
-        <v>27.98569517950106</v>
+        <v>27.98569705924094</v>
       </c>
       <c r="F305" t="n">
         <v>2271100</v>
@@ -6552,16 +6552,16 @@
         <v>44021</v>
       </c>
       <c r="B307" t="n">
-        <v>29.66483688354492</v>
+        <v>29.66483497619629</v>
       </c>
       <c r="C307" t="n">
-        <v>30.27702466573552</v>
+        <v>30.27702271902529</v>
       </c>
       <c r="D307" t="n">
-        <v>28.95645107137374</v>
+        <v>28.95644920957192</v>
       </c>
       <c r="E307" t="n">
-        <v>29.21007224824849</v>
+        <v>29.21007037013969</v>
       </c>
       <c r="F307" t="n">
         <v>1551300</v>
@@ -6612,16 +6612,16 @@
         <v>44026</v>
       </c>
       <c r="B310" t="n">
-        <v>28.41422653198242</v>
+        <v>28.41422843933105</v>
       </c>
       <c r="C310" t="n">
-        <v>28.83401154348613</v>
+        <v>28.83401347901348</v>
       </c>
       <c r="D310" t="n">
-        <v>27.36476233514578</v>
+        <v>27.36476417204751</v>
       </c>
       <c r="E310" t="n">
-        <v>28.51042455315965</v>
+        <v>28.51042646696572</v>
       </c>
       <c r="F310" t="n">
         <v>1676500</v>
@@ -6632,16 +6632,16 @@
         <v>44027</v>
       </c>
       <c r="B311" t="n">
-        <v>27.86326026916504</v>
+        <v>27.86325836181641</v>
       </c>
       <c r="C311" t="n">
-        <v>29.09637991685148</v>
+        <v>29.09637792509101</v>
       </c>
       <c r="D311" t="n">
-        <v>27.68834899468117</v>
+        <v>27.68834709930589</v>
       </c>
       <c r="E311" t="n">
-        <v>28.96519562694981</v>
+        <v>28.96519364416941</v>
       </c>
       <c r="F311" t="n">
         <v>2158900</v>
@@ -6672,16 +6672,16 @@
         <v>44029</v>
       </c>
       <c r="B313" t="n">
-        <v>28.07315063476562</v>
+        <v>28.07314872741699</v>
       </c>
       <c r="C313" t="n">
-        <v>28.34426327224438</v>
+        <v>28.34426134647578</v>
       </c>
       <c r="D313" t="n">
-        <v>27.15487063010601</v>
+        <v>27.15486878514724</v>
       </c>
       <c r="E313" t="n">
-        <v>27.54842015671871</v>
+        <v>27.54841828502136</v>
       </c>
       <c r="F313" t="n">
         <v>1920600</v>
@@ -6732,16 +6732,16 @@
         <v>44034</v>
       </c>
       <c r="B316" t="n">
-        <v>28.11687850952148</v>
+        <v>28.11688041687012</v>
       </c>
       <c r="C316" t="n">
-        <v>28.69408331963795</v>
+        <v>28.6940852661421</v>
       </c>
       <c r="D316" t="n">
-        <v>27.92447579409775</v>
+        <v>27.92447768839448</v>
       </c>
       <c r="E316" t="n">
-        <v>28.58913456423152</v>
+        <v>28.58913650361632</v>
       </c>
       <c r="F316" t="n">
         <v>1990600</v>
@@ -6752,16 +6752,16 @@
         <v>44035</v>
       </c>
       <c r="B317" t="n">
-        <v>27.02368545532227</v>
+        <v>27.0236873626709</v>
       </c>
       <c r="C317" t="n">
-        <v>28.24805923512145</v>
+        <v>28.24806122888715</v>
       </c>
       <c r="D317" t="n">
-        <v>26.81379295033475</v>
+        <v>26.81379484286904</v>
       </c>
       <c r="E317" t="n">
-        <v>27.98569402090639</v>
+        <v>27.98569599615419</v>
       </c>
       <c r="F317" t="n">
         <v>1990400</v>
@@ -6772,16 +6772,16 @@
         <v>44036</v>
       </c>
       <c r="B318" t="n">
-        <v>26.15787887573242</v>
+        <v>26.15788078308105</v>
       </c>
       <c r="C318" t="n">
-        <v>26.66511952533576</v>
+        <v>26.66512146967075</v>
       </c>
       <c r="D318" t="n">
-        <v>25.44949144585545</v>
+        <v>25.44949330155075</v>
       </c>
       <c r="E318" t="n">
-        <v>26.66511952533576</v>
+        <v>26.66512146967075</v>
       </c>
       <c r="F318" t="n">
         <v>3685600</v>
@@ -6812,16 +6812,16 @@
         <v>44040</v>
       </c>
       <c r="B320" t="n">
-        <v>24.63615798950195</v>
+        <v>24.63615608215332</v>
       </c>
       <c r="C320" t="n">
-        <v>25.18712564359724</v>
+        <v>25.1871236935923</v>
       </c>
       <c r="D320" t="n">
-        <v>24.35630129738515</v>
+        <v>24.35629941170321</v>
       </c>
       <c r="E320" t="n">
-        <v>24.9247604117571</v>
+        <v>24.92475848206466</v>
       </c>
       <c r="F320" t="n">
         <v>2550000</v>
@@ -6932,16 +6932,16 @@
         <v>44048</v>
       </c>
       <c r="B326" t="n">
-        <v>25.96548080444336</v>
+        <v>25.96547889709473</v>
       </c>
       <c r="C326" t="n">
-        <v>26.21910032430609</v>
+        <v>26.21909839832731</v>
       </c>
       <c r="D326" t="n">
-        <v>25.60691418348315</v>
+        <v>25.60691230247378</v>
       </c>
       <c r="E326" t="n">
-        <v>25.71185961650304</v>
+        <v>25.71185772778469</v>
       </c>
       <c r="F326" t="n">
         <v>1719300</v>
@@ -7052,16 +7052,16 @@
         <v>44056</v>
       </c>
       <c r="B332" t="n">
-        <v>25.08218193054199</v>
+        <v>25.08218002319336</v>
       </c>
       <c r="C332" t="n">
-        <v>25.49322126664199</v>
+        <v>25.4932193280363</v>
       </c>
       <c r="D332" t="n">
-        <v>24.49623131588844</v>
+        <v>24.49622945309782</v>
       </c>
       <c r="E332" t="n">
-        <v>24.91601638272387</v>
+        <v>24.91601448801113</v>
       </c>
       <c r="F332" t="n">
         <v>2154700</v>
@@ -7112,16 +7112,16 @@
         <v>44061</v>
       </c>
       <c r="B335" t="n">
-        <v>24.90727043151855</v>
+        <v>24.90726852416992</v>
       </c>
       <c r="C335" t="n">
-        <v>25.03845305523375</v>
+        <v>25.03845113783942</v>
       </c>
       <c r="D335" t="n">
-        <v>23.93651768156406</v>
+        <v>23.93651584855371</v>
       </c>
       <c r="E335" t="n">
-        <v>23.96275320546056</v>
+        <v>23.96275137044115</v>
       </c>
       <c r="F335" t="n">
         <v>2792800</v>
@@ -7172,16 +7172,16 @@
         <v>44064</v>
       </c>
       <c r="B338" t="n">
-        <v>24.44375610351562</v>
+        <v>24.44375419616699</v>
       </c>
       <c r="C338" t="n">
-        <v>24.54870152546935</v>
+        <v>24.54869960993182</v>
       </c>
       <c r="D338" t="n">
-        <v>23.5254744869948</v>
+        <v>23.52547265129977</v>
       </c>
       <c r="E338" t="n">
-        <v>23.87529534030289</v>
+        <v>23.87529347731131</v>
       </c>
       <c r="F338" t="n">
         <v>2429700</v>
@@ -7312,16 +7312,16 @@
         <v>44075</v>
       </c>
       <c r="B345" t="n">
-        <v>28.09939002990723</v>
+        <v>28.09938812255859</v>
       </c>
       <c r="C345" t="n">
-        <v>28.14311701455262</v>
+        <v>28.14311510423586</v>
       </c>
       <c r="D345" t="n">
-        <v>26.36777374786229</v>
+        <v>26.36777195805344</v>
       </c>
       <c r="E345" t="n">
-        <v>26.70010483624646</v>
+        <v>26.70010302387942</v>
       </c>
       <c r="F345" t="n">
         <v>3041200</v>
@@ -7352,16 +7352,16 @@
         <v>44077</v>
       </c>
       <c r="B347" t="n">
-        <v>27.37351036071777</v>
+        <v>27.37350845336914</v>
       </c>
       <c r="C347" t="n">
-        <v>28.2655548904017</v>
+        <v>28.26555292089662</v>
       </c>
       <c r="D347" t="n">
-        <v>26.8487798543885</v>
+        <v>26.84877798360237</v>
       </c>
       <c r="E347" t="n">
-        <v>28.0731521478752</v>
+        <v>28.07315019177649</v>
       </c>
       <c r="F347" t="n">
         <v>2237800</v>
@@ -7412,16 +7412,16 @@
         <v>44083</v>
       </c>
       <c r="B350" t="n">
-        <v>26.47271919250488</v>
+        <v>26.47272109985352</v>
       </c>
       <c r="C350" t="n">
-        <v>27.46096332921972</v>
+        <v>27.46096530777094</v>
       </c>
       <c r="D350" t="n">
-        <v>25.88676862724358</v>
+        <v>25.88677049237472</v>
       </c>
       <c r="E350" t="n">
-        <v>26.88375849395664</v>
+        <v>26.88376043092049</v>
       </c>
       <c r="F350" t="n">
         <v>2119000</v>
@@ -7532,16 +7532,16 @@
         <v>44091</v>
       </c>
       <c r="B356" t="n">
-        <v>24.87228775024414</v>
+        <v>24.87228584289551</v>
       </c>
       <c r="C356" t="n">
-        <v>25.05594307929509</v>
+        <v>25.05594115786273</v>
       </c>
       <c r="D356" t="n">
-        <v>24.33880988724904</v>
+        <v>24.33880802081053</v>
       </c>
       <c r="E356" t="n">
-        <v>24.7498491961327</v>
+        <v>24.74984729817335</v>
       </c>
       <c r="F356" t="n">
         <v>1158600</v>
@@ -7632,16 +7632,16 @@
         <v>44098</v>
       </c>
       <c r="B361" t="n">
-        <v>22.83458137512207</v>
+        <v>22.83457946777344</v>
       </c>
       <c r="C361" t="n">
-        <v>23.17565654138019</v>
+        <v>23.1756546055419</v>
       </c>
       <c r="D361" t="n">
-        <v>22.40605056754511</v>
+        <v>22.4060486959912</v>
       </c>
       <c r="E361" t="n">
-        <v>23.0007452587425</v>
+        <v>23.00074333751437</v>
       </c>
       <c r="F361" t="n">
         <v>3887300</v>
@@ -7652,16 +7652,16 @@
         <v>44099</v>
       </c>
       <c r="B362" t="n">
-        <v>22.3885555267334</v>
+        <v>22.38855743408203</v>
       </c>
       <c r="C362" t="n">
-        <v>22.96576033185978</v>
+        <v>22.96576228838224</v>
       </c>
       <c r="D362" t="n">
-        <v>22.18740875150879</v>
+        <v>22.18741064172113</v>
       </c>
       <c r="E362" t="n">
-        <v>22.84332345443217</v>
+        <v>22.84332540052386</v>
       </c>
       <c r="F362" t="n">
         <v>3181400</v>
@@ -7692,16 +7692,16 @@
         <v>44103</v>
       </c>
       <c r="B364" t="n">
-        <v>21.82009696960449</v>
+        <v>21.82009506225586</v>
       </c>
       <c r="C364" t="n">
-        <v>22.29235469953017</v>
+        <v>22.29235275090032</v>
       </c>
       <c r="D364" t="n">
-        <v>21.55773008135477</v>
+        <v>21.55772819694027</v>
       </c>
       <c r="E364" t="n">
-        <v>22.29235469953017</v>
+        <v>22.29235275090032</v>
       </c>
       <c r="F364" t="n">
         <v>1168900</v>
@@ -7752,16 +7752,16 @@
         <v>44106</v>
       </c>
       <c r="B367" t="n">
-        <v>22.64217567443848</v>
+        <v>22.64217758178711</v>
       </c>
       <c r="C367" t="n">
-        <v>22.79084974484632</v>
+        <v>22.79085166471906</v>
       </c>
       <c r="D367" t="n">
-        <v>22.3360834719024</v>
+        <v>22.33608535346621</v>
       </c>
       <c r="E367" t="n">
-        <v>22.68590432342749</v>
+        <v>22.68590623445976</v>
       </c>
       <c r="F367" t="n">
         <v>1030500</v>
@@ -7792,16 +7792,16 @@
         <v>44110</v>
       </c>
       <c r="B369" t="n">
-        <v>21.54023933410645</v>
+        <v>21.54024124145508</v>
       </c>
       <c r="C369" t="n">
-        <v>22.51973941342096</v>
+        <v>22.51974140750253</v>
       </c>
       <c r="D369" t="n">
-        <v>21.28661983529732</v>
+        <v>21.28662172018841</v>
       </c>
       <c r="E369" t="n">
-        <v>22.27486397657297</v>
+        <v>22.27486594897127</v>
       </c>
       <c r="F369" t="n">
         <v>2126200</v>
@@ -7832,16 +7832,16 @@
         <v>44112</v>
       </c>
       <c r="B371" t="n">
-        <v>21.53149604797363</v>
+        <v>21.531494140625</v>
       </c>
       <c r="C371" t="n">
-        <v>21.67142439747801</v>
+        <v>21.67142247773394</v>
       </c>
       <c r="D371" t="n">
-        <v>21.09421953875309</v>
+        <v>21.09421767014021</v>
       </c>
       <c r="E371" t="n">
-        <v>21.48776739620508</v>
+        <v>21.48776549273011</v>
       </c>
       <c r="F371" t="n">
         <v>1373200</v>
@@ -7892,16 +7892,16 @@
         <v>44118</v>
       </c>
       <c r="B374" t="n">
-        <v>21.51400184631348</v>
+        <v>21.51400375366211</v>
       </c>
       <c r="C374" t="n">
-        <v>22.01249673642265</v>
+        <v>22.01249868796592</v>
       </c>
       <c r="D374" t="n">
-        <v>21.21665372448041</v>
+        <v>21.2166556054673</v>
       </c>
       <c r="E374" t="n">
-        <v>21.71514861458958</v>
+        <v>21.71515053977112</v>
       </c>
       <c r="F374" t="n">
         <v>2069800</v>
@@ -7912,16 +7912,16 @@
         <v>44119</v>
       </c>
       <c r="B375" t="n">
-        <v>22.11744689941406</v>
+        <v>22.1174488067627</v>
       </c>
       <c r="C375" t="n">
-        <v>22.61594185894634</v>
+        <v>22.61594380928382</v>
       </c>
       <c r="D375" t="n">
-        <v>21.01550988293759</v>
+        <v>21.01551169525816</v>
       </c>
       <c r="E375" t="n">
-        <v>21.19916521831157</v>
+        <v>21.19916704647008</v>
       </c>
       <c r="F375" t="n">
         <v>2238800</v>
@@ -7932,16 +7932,16 @@
         <v>44120</v>
       </c>
       <c r="B376" t="n">
-        <v>21.73264312744141</v>
+        <v>21.73264503479004</v>
       </c>
       <c r="C376" t="n">
-        <v>22.47601353649965</v>
+        <v>22.47601550908961</v>
       </c>
       <c r="D376" t="n">
-        <v>21.65393322130127</v>
+        <v>21.65393512174199</v>
       </c>
       <c r="E376" t="n">
-        <v>22.19615516573608</v>
+        <v>22.1961571137645</v>
       </c>
       <c r="F376" t="n">
         <v>1621500</v>
@@ -8012,16 +8012,16 @@
         <v>44126</v>
       </c>
       <c r="B380" t="n">
-        <v>22.0737190246582</v>
+        <v>22.07371711730957</v>
       </c>
       <c r="C380" t="n">
-        <v>22.17866612576683</v>
+        <v>22.17866420934991</v>
       </c>
       <c r="D380" t="n">
-        <v>21.47027694645817</v>
+        <v>21.47027509125183</v>
       </c>
       <c r="E380" t="n">
-        <v>21.91629920703405</v>
+        <v>21.91629731328777</v>
       </c>
       <c r="F380" t="n">
         <v>2196600</v>
@@ -8052,16 +8052,16 @@
         <v>44130</v>
       </c>
       <c r="B382" t="n">
-        <v>22.08246421813965</v>
+        <v>22.08246231079102</v>
       </c>
       <c r="C382" t="n">
-        <v>22.58095918310227</v>
+        <v>22.58095723269669</v>
       </c>
       <c r="D382" t="n">
-        <v>21.64518769896857</v>
+        <v>21.64518582938921</v>
       </c>
       <c r="E382" t="n">
-        <v>22.20490110972274</v>
+        <v>22.20489919179875</v>
       </c>
       <c r="F382" t="n">
         <v>1812600</v>
@@ -8092,16 +8092,16 @@
         <v>44132</v>
       </c>
       <c r="B384" t="n">
-        <v>21.03299713134766</v>
+        <v>21.03299903869629</v>
       </c>
       <c r="C384" t="n">
-        <v>21.32159952922045</v>
+        <v>21.32160146274059</v>
       </c>
       <c r="D384" t="n">
-        <v>20.70066775455491</v>
+        <v>20.7006696317667</v>
       </c>
       <c r="E384" t="n">
-        <v>21.22539984198106</v>
+        <v>21.22540176677747</v>
       </c>
       <c r="F384" t="n">
         <v>2892700</v>
@@ -8152,16 +8152,16 @@
         <v>44138</v>
       </c>
       <c r="B387" t="n">
-        <v>20.49077987670898</v>
+        <v>20.49077796936035</v>
       </c>
       <c r="C387" t="n">
-        <v>20.67443523130533</v>
+        <v>20.67443330686146</v>
       </c>
       <c r="D387" t="n">
-        <v>19.99228486500153</v>
+        <v>19.99228300405444</v>
       </c>
       <c r="E387" t="n">
-        <v>20.40332423105838</v>
+        <v>20.4033223318504</v>
       </c>
       <c r="F387" t="n">
         <v>1832100</v>
@@ -8192,16 +8192,16 @@
         <v>44140</v>
       </c>
       <c r="B389" t="n">
-        <v>22.30110168457031</v>
+        <v>22.30110359191895</v>
       </c>
       <c r="C389" t="n">
-        <v>22.32733887529535</v>
+        <v>22.32734078488797</v>
       </c>
       <c r="D389" t="n">
-        <v>21.4527858680573</v>
+        <v>21.45278770285194</v>
       </c>
       <c r="E389" t="n">
-        <v>22.05622624203577</v>
+        <v>22.05622812844091</v>
       </c>
       <c r="F389" t="n">
         <v>1467100</v>
@@ -8272,16 +8272,16 @@
         <v>44146</v>
       </c>
       <c r="B393" t="n">
-        <v>23.64791297912598</v>
+        <v>23.64791488647461</v>
       </c>
       <c r="C393" t="n">
-        <v>24.33880895421739</v>
+        <v>24.33881091729101</v>
       </c>
       <c r="D393" t="n">
-        <v>23.44676452939591</v>
+        <v>23.44676642052069</v>
       </c>
       <c r="E393" t="n">
-        <v>24.25135332408398</v>
+        <v>24.25135528010376</v>
       </c>
       <c r="F393" t="n">
         <v>1219800</v>
@@ -8312,16 +8312,16 @@
         <v>44148</v>
       </c>
       <c r="B395" t="n">
-        <v>25.18712615966797</v>
+        <v>25.18712425231934</v>
       </c>
       <c r="C395" t="n">
-        <v>25.34454596922849</v>
+        <v>25.3445440499589</v>
       </c>
       <c r="D395" t="n">
-        <v>23.17565489280634</v>
+        <v>23.17565313778064</v>
       </c>
       <c r="E395" t="n">
-        <v>23.61293140021778</v>
+        <v>23.61292961207839</v>
       </c>
       <c r="F395" t="n">
         <v>2680000</v>
@@ -8372,16 +8372,16 @@
         <v>44153</v>
       </c>
       <c r="B398" t="n">
-        <v>25.53694725036621</v>
+        <v>25.53694915771484</v>
       </c>
       <c r="C398" t="n">
-        <v>26.32404458540901</v>
+        <v>26.32404655154576</v>
       </c>
       <c r="D398" t="n">
-        <v>25.23085337893918</v>
+        <v>25.23085526342573</v>
       </c>
       <c r="E398" t="n">
-        <v>26.00920498416093</v>
+        <v>26.00920692678238</v>
       </c>
       <c r="F398" t="n">
         <v>2536100</v>
@@ -8412,16 +8412,16 @@
         <v>44158</v>
       </c>
       <c r="B400" t="n">
-        <v>24.7673397064209</v>
+        <v>24.76734161376953</v>
       </c>
       <c r="C400" t="n">
-        <v>26.05293363277471</v>
+        <v>26.05293563912775</v>
       </c>
       <c r="D400" t="n">
-        <v>24.7673397064209</v>
+        <v>24.76734161376953</v>
       </c>
       <c r="E400" t="n">
-        <v>25.92174935353888</v>
+        <v>25.92175134978934</v>
       </c>
       <c r="F400" t="n">
         <v>941500</v>
@@ -8452,16 +8452,16 @@
         <v>44160</v>
       </c>
       <c r="B402" t="n">
-        <v>24.89852523803711</v>
+        <v>24.89852333068848</v>
       </c>
       <c r="C402" t="n">
-        <v>25.07343651881606</v>
+        <v>25.07343459806837</v>
       </c>
       <c r="D402" t="n">
-        <v>24.05020936283768</v>
+        <v>24.05020752047418</v>
       </c>
       <c r="E402" t="n">
-        <v>24.46999443501404</v>
+        <v>24.46999256049296</v>
       </c>
       <c r="F402" t="n">
         <v>1261400</v>
@@ -8592,16 +8592,16 @@
         <v>44169</v>
       </c>
       <c r="B409" t="n">
-        <v>23.60418701171875</v>
+        <v>23.60418510437012</v>
       </c>
       <c r="C409" t="n">
-        <v>24.62741416395164</v>
+        <v>24.6274121739206</v>
       </c>
       <c r="D409" t="n">
-        <v>23.36805728395479</v>
+        <v>23.36805539568675</v>
       </c>
       <c r="E409" t="n">
-        <v>24.22512055494127</v>
+        <v>24.22511859741778</v>
       </c>
       <c r="F409" t="n">
         <v>2314400</v>
@@ -8612,16 +8612,16 @@
         <v>44172</v>
       </c>
       <c r="B410" t="n">
-        <v>23.35056686401367</v>
+        <v>23.35056495666504</v>
       </c>
       <c r="C410" t="n">
-        <v>23.94526153076157</v>
+        <v>23.94525957483639</v>
       </c>
       <c r="D410" t="n">
-        <v>23.19314704972723</v>
+        <v>23.19314515523714</v>
       </c>
       <c r="E410" t="n">
-        <v>23.70913347740945</v>
+        <v>23.70913154077196</v>
       </c>
       <c r="F410" t="n">
         <v>1296900</v>
@@ -8652,16 +8652,16 @@
         <v>44174</v>
       </c>
       <c r="B412" t="n">
-        <v>24.13766098022461</v>
+        <v>24.13766288757324</v>
       </c>
       <c r="C412" t="n">
-        <v>24.43500910714352</v>
+        <v>24.43501103798848</v>
       </c>
       <c r="D412" t="n">
-        <v>23.49049201812973</v>
+        <v>23.49049387433932</v>
       </c>
       <c r="E412" t="n">
-        <v>23.70913024862438</v>
+        <v>23.70913212211068</v>
       </c>
       <c r="F412" t="n">
         <v>2240700</v>
@@ -8672,16 +8672,16 @@
         <v>44175</v>
       </c>
       <c r="B413" t="n">
-        <v>24.63615798950195</v>
+        <v>24.63615608215332</v>
       </c>
       <c r="C413" t="n">
-        <v>24.83730477845123</v>
+        <v>24.83730285552967</v>
       </c>
       <c r="D413" t="n">
-        <v>23.39429266717552</v>
+        <v>23.39429085597297</v>
       </c>
       <c r="E413" t="n">
-        <v>24.18139003077341</v>
+        <v>24.18138815863323</v>
       </c>
       <c r="F413" t="n">
         <v>1331100</v>
@@ -8692,16 +8692,16 @@
         <v>44176</v>
       </c>
       <c r="B414" t="n">
-        <v>24.20762825012207</v>
+        <v>24.20762634277344</v>
       </c>
       <c r="C414" t="n">
-        <v>24.57494059115718</v>
+        <v>24.57493865486756</v>
       </c>
       <c r="D414" t="n">
-        <v>24.01522551505568</v>
+        <v>24.0152236228667</v>
       </c>
       <c r="E414" t="n">
-        <v>24.2950838871452</v>
+        <v>24.29508197290583</v>
       </c>
       <c r="F414" t="n">
         <v>938700</v>
@@ -8712,16 +8712,16 @@
         <v>44179</v>
       </c>
       <c r="B415" t="n">
-        <v>24.95099639892578</v>
+        <v>24.95099830627441</v>
       </c>
       <c r="C415" t="n">
-        <v>25.18712442896379</v>
+        <v>25.18712635436295</v>
       </c>
       <c r="D415" t="n">
-        <v>24.10267896526914</v>
+        <v>24.10268080776918</v>
       </c>
       <c r="E415" t="n">
-        <v>24.62741107172201</v>
+        <v>24.62741295433456</v>
       </c>
       <c r="F415" t="n">
         <v>2344600</v>
@@ -8752,16 +8752,16 @@
         <v>44181</v>
       </c>
       <c r="B417" t="n">
-        <v>26.31529998779297</v>
+        <v>26.31529808044434</v>
       </c>
       <c r="C417" t="n">
-        <v>26.60390241199491</v>
+        <v>26.6039004837282</v>
       </c>
       <c r="D417" t="n">
-        <v>24.7673407724928</v>
+        <v>24.76733897734118</v>
       </c>
       <c r="E417" t="n">
-        <v>25.39702000208065</v>
+        <v>25.3970181612895</v>
       </c>
       <c r="F417" t="n">
         <v>2062300</v>
@@ -8772,16 +8772,16 @@
         <v>44182</v>
       </c>
       <c r="B418" t="n">
-        <v>26.07917022705078</v>
+        <v>26.07917213439941</v>
       </c>
       <c r="C418" t="n">
-        <v>26.48146547497467</v>
+        <v>26.48146741174591</v>
       </c>
       <c r="D418" t="n">
-        <v>25.85178624658554</v>
+        <v>25.85178813730402</v>
       </c>
       <c r="E418" t="n">
-        <v>26.31529993769671</v>
+        <v>26.31530186231512</v>
       </c>
       <c r="F418" t="n">
         <v>1046800</v>
@@ -8952,16 +8952,16 @@
         <v>44201</v>
       </c>
       <c r="B427" t="n">
-        <v>23.95400428771973</v>
+        <v>23.95400619506836</v>
       </c>
       <c r="C427" t="n">
-        <v>24.95974149457043</v>
+        <v>24.95974348200135</v>
       </c>
       <c r="D427" t="n">
-        <v>23.90153157883066</v>
+        <v>23.90153348200113</v>
       </c>
       <c r="E427" t="n">
-        <v>24.88977565861522</v>
+        <v>24.88977764047509</v>
       </c>
       <c r="F427" t="n">
         <v>1214100</v>
@@ -9052,16 +9052,16 @@
         <v>44208</v>
       </c>
       <c r="B432" t="n">
-        <v>22.88705062866211</v>
+        <v>22.88705253601074</v>
       </c>
       <c r="C432" t="n">
-        <v>23.26310866176136</v>
+        <v>23.26311060044971</v>
       </c>
       <c r="D432" t="n">
-        <v>22.52848405479477</v>
+        <v>22.52848593226138</v>
       </c>
       <c r="E432" t="n">
-        <v>22.93077760866452</v>
+        <v>22.93077951965725</v>
       </c>
       <c r="F432" t="n">
         <v>1882900</v>
@@ -9072,16 +9072,16 @@
         <v>44209</v>
       </c>
       <c r="B433" t="n">
-        <v>22.85206985473633</v>
+        <v>22.8520679473877</v>
       </c>
       <c r="C433" t="n">
-        <v>23.15816374771049</v>
+        <v>23.15816181481372</v>
       </c>
       <c r="D433" t="n">
-        <v>22.57221315307225</v>
+        <v>22.57221126908186</v>
       </c>
       <c r="E433" t="n">
-        <v>22.85206985473633</v>
+        <v>22.8520679473877</v>
       </c>
       <c r="F433" t="n">
         <v>1251100</v>
@@ -9092,16 +9092,16 @@
         <v>44210</v>
       </c>
       <c r="B434" t="n">
-        <v>23.52547454833984</v>
+        <v>23.52547645568848</v>
       </c>
       <c r="C434" t="n">
-        <v>23.52547454833984</v>
+        <v>23.52547645568848</v>
       </c>
       <c r="D434" t="n">
-        <v>22.58095740790637</v>
+        <v>22.58095923867744</v>
       </c>
       <c r="E434" t="n">
-        <v>22.92203253226147</v>
+        <v>22.92203439068551</v>
       </c>
       <c r="F434" t="n">
         <v>1124400</v>
@@ -9252,16 +9252,16 @@
         <v>44223</v>
       </c>
       <c r="B442" t="n">
-        <v>21.48776626586914</v>
+        <v>21.48776817321777</v>
       </c>
       <c r="C442" t="n">
-        <v>22.17866391477103</v>
+        <v>22.17866588344678</v>
       </c>
       <c r="D442" t="n">
-        <v>21.33909219383186</v>
+        <v>21.33909408798353</v>
       </c>
       <c r="E442" t="n">
-        <v>21.94253421187463</v>
+        <v>21.94253615959047</v>
       </c>
       <c r="F442" t="n">
         <v>1472500</v>
@@ -9292,16 +9292,16 @@
         <v>44225</v>
       </c>
       <c r="B444" t="n">
-        <v>22.30110168457031</v>
+        <v>22.30110359191895</v>
       </c>
       <c r="C444" t="n">
-        <v>23.00074342312976</v>
+        <v>23.00074539031673</v>
       </c>
       <c r="D444" t="n">
-        <v>21.75013402396443</v>
+        <v>21.7501358841904</v>
       </c>
       <c r="E444" t="n">
-        <v>22.30984741481199</v>
+        <v>22.30984932290862</v>
       </c>
       <c r="F444" t="n">
         <v>1668700</v>
@@ -9312,16 +9312,16 @@
         <v>44228</v>
       </c>
       <c r="B445" t="n">
-        <v>21.85507774353027</v>
+        <v>21.85507965087891</v>
       </c>
       <c r="C445" t="n">
-        <v>22.68590370273859</v>
+        <v>22.68590568259553</v>
       </c>
       <c r="D445" t="n">
-        <v>21.34783710567771</v>
+        <v>21.34783896875815</v>
       </c>
       <c r="E445" t="n">
-        <v>22.65092078450452</v>
+        <v>22.65092276130841</v>
       </c>
       <c r="F445" t="n">
         <v>3093300</v>
@@ -9352,16 +9352,16 @@
         <v>44230</v>
       </c>
       <c r="B447" t="n">
-        <v>21.87257385253906</v>
+        <v>21.87257194519043</v>
       </c>
       <c r="C447" t="n">
-        <v>22.44977878149045</v>
+        <v>22.44977682380796</v>
       </c>
       <c r="D447" t="n">
-        <v>21.7326454860101</v>
+        <v>21.73264359086361</v>
       </c>
       <c r="E447" t="n">
-        <v>22.19615757460814</v>
+        <v>22.19615563904212</v>
       </c>
       <c r="F447" t="n">
         <v>3818200</v>
@@ -9372,16 +9372,16 @@
         <v>44231</v>
       </c>
       <c r="B448" t="n">
-        <v>21.98626136779785</v>
+        <v>21.98626327514648</v>
       </c>
       <c r="C448" t="n">
-        <v>22.21364534260563</v>
+        <v>22.21364726968024</v>
       </c>
       <c r="D448" t="n">
-        <v>21.80260604280547</v>
+        <v>21.80260793422167</v>
       </c>
       <c r="E448" t="n">
-        <v>21.87257021443268</v>
+        <v>21.87257211191839</v>
       </c>
       <c r="F448" t="n">
         <v>1611200</v>
@@ -9452,16 +9452,16 @@
         <v>44237</v>
       </c>
       <c r="B452" t="n">
-        <v>20.33335494995117</v>
+        <v>20.3333568572998</v>
       </c>
       <c r="C452" t="n">
-        <v>21.12919795648157</v>
+        <v>21.12919993848341</v>
       </c>
       <c r="D452" t="n">
-        <v>20.17593516086563</v>
+        <v>20.17593705344767</v>
       </c>
       <c r="E452" t="n">
-        <v>20.98926962575605</v>
+        <v>20.98927159463206</v>
       </c>
       <c r="F452" t="n">
         <v>1712500</v>
@@ -9532,16 +9532,16 @@
         <v>44245</v>
       </c>
       <c r="B456" t="n">
-        <v>20.33335494995117</v>
+        <v>20.3333568572998</v>
       </c>
       <c r="C456" t="n">
-        <v>20.41206484449394</v>
+        <v>20.41206675922587</v>
       </c>
       <c r="D456" t="n">
-        <v>20.00976964260009</v>
+        <v>20.00977151959516</v>
       </c>
       <c r="E456" t="n">
-        <v>20.34210067913117</v>
+        <v>20.34210258730019</v>
       </c>
       <c r="F456" t="n">
         <v>740300</v>
@@ -9572,16 +9572,16 @@
         <v>44249</v>
       </c>
       <c r="B458" t="n">
-        <v>20.33335494995117</v>
+        <v>20.3333568572998</v>
       </c>
       <c r="C458" t="n">
-        <v>20.69192150594499</v>
+        <v>20.69192344692857</v>
       </c>
       <c r="D458" t="n">
-        <v>19.93106141613461</v>
+        <v>19.93106328574653</v>
       </c>
       <c r="E458" t="n">
-        <v>20.42081057367394</v>
+        <v>20.42081248922626</v>
       </c>
       <c r="F458" t="n">
         <v>1855000</v>
@@ -9592,16 +9592,16 @@
         <v>44250</v>
       </c>
       <c r="B459" t="n">
-        <v>20.81435966491699</v>
+        <v>20.81436157226562</v>
       </c>
       <c r="C459" t="n">
-        <v>21.12045353282876</v>
+        <v>21.12045546822667</v>
       </c>
       <c r="D459" t="n">
-        <v>20.2459005776965</v>
+        <v>20.2459024329537</v>
       </c>
       <c r="E459" t="n">
-        <v>20.46453881647956</v>
+        <v>20.46454069177194</v>
       </c>
       <c r="F459" t="n">
         <v>988000</v>
@@ -9772,16 +9772,16 @@
         <v>44263</v>
       </c>
       <c r="B468" t="n">
-        <v>19.74740791320801</v>
+        <v>19.74740600585938</v>
       </c>
       <c r="C468" t="n">
-        <v>20.87558215472276</v>
+        <v>20.87558013840683</v>
       </c>
       <c r="D468" t="n">
-        <v>19.62497101930504</v>
+        <v>19.62496912378225</v>
       </c>
       <c r="E468" t="n">
-        <v>20.62196096812081</v>
+        <v>20.62195897630147</v>
       </c>
       <c r="F468" t="n">
         <v>1138000</v>
@@ -9792,16 +9792,16 @@
         <v>44264</v>
       </c>
       <c r="B469" t="n">
-        <v>18.12948417663574</v>
+        <v>18.12948226928711</v>
       </c>
       <c r="C469" t="n">
-        <v>19.8348632773014</v>
+        <v>19.83486119053495</v>
       </c>
       <c r="D469" t="n">
-        <v>17.92833737713335</v>
+        <v>17.92833549094676</v>
       </c>
       <c r="E469" t="n">
-        <v>19.74740763940719</v>
+        <v>19.74740556184168</v>
       </c>
       <c r="F469" t="n">
         <v>3517000</v>
@@ -9852,16 +9852,16 @@
         <v>44267</v>
       </c>
       <c r="B472" t="n">
-        <v>20.65694046020508</v>
+        <v>20.65694236755371</v>
       </c>
       <c r="C472" t="n">
-        <v>21.37407357923675</v>
+        <v>21.37407555280153</v>
       </c>
       <c r="D472" t="n">
-        <v>19.82611452879387</v>
+        <v>19.82611635942859</v>
       </c>
       <c r="E472" t="n">
-        <v>20.24589952509378</v>
+        <v>20.24590139448915</v>
       </c>
       <c r="F472" t="n">
         <v>2643100</v>
@@ -9872,16 +9872,16 @@
         <v>44270</v>
       </c>
       <c r="B473" t="n">
-        <v>20.98052787780762</v>
+        <v>20.98052597045898</v>
       </c>
       <c r="C473" t="n">
-        <v>21.27787605404299</v>
+        <v>21.27787411966231</v>
       </c>
       <c r="D473" t="n">
-        <v>20.31586734669781</v>
+        <v>20.31586549977375</v>
       </c>
       <c r="E473" t="n">
-        <v>20.4645414348155</v>
+        <v>20.46453957437541</v>
       </c>
       <c r="F473" t="n">
         <v>840900</v>
@@ -9892,16 +9892,16 @@
         <v>44271</v>
       </c>
       <c r="B474" t="n">
-        <v>20.81435966491699</v>
+        <v>20.81436157226562</v>
       </c>
       <c r="C474" t="n">
-        <v>21.17292624307503</v>
+        <v>21.17292818328134</v>
       </c>
       <c r="D474" t="n">
-        <v>20.53450298616705</v>
+        <v>20.53450486787068</v>
       </c>
       <c r="E474" t="n">
-        <v>20.90181529404569</v>
+        <v>20.90181720940843</v>
       </c>
       <c r="F474" t="n">
         <v>1100300</v>
@@ -9912,16 +9912,16 @@
         <v>44272</v>
       </c>
       <c r="B475" t="n">
-        <v>21.4615306854248</v>
+        <v>21.46153259277344</v>
       </c>
       <c r="C475" t="n">
-        <v>21.66267746819511</v>
+        <v>21.66267939342024</v>
       </c>
       <c r="D475" t="n">
-        <v>20.3770835346688</v>
+        <v>20.37708534563946</v>
       </c>
       <c r="E475" t="n">
-        <v>20.6831774077978</v>
+        <v>20.68317924597191</v>
       </c>
       <c r="F475" t="n">
         <v>1051400</v>
@@ -9932,16 +9932,16 @@
         <v>44273</v>
       </c>
       <c r="B476" t="n">
-        <v>20.42955780029297</v>
+        <v>20.4295597076416</v>
       </c>
       <c r="C476" t="n">
-        <v>21.25163638654255</v>
+        <v>21.25163837064226</v>
       </c>
       <c r="D476" t="n">
-        <v>20.19342809935691</v>
+        <v>20.19342998465995</v>
       </c>
       <c r="E476" t="n">
-        <v>21.25163638654255</v>
+        <v>21.25163837064226</v>
       </c>
       <c r="F476" t="n">
         <v>770600</v>
@@ -9972,16 +9972,16 @@
         <v>44277</v>
       </c>
       <c r="B478" t="n">
-        <v>22.30110168457031</v>
+        <v>22.30110359191895</v>
       </c>
       <c r="C478" t="n">
-        <v>22.58095837999409</v>
+        <v>22.58096031127806</v>
       </c>
       <c r="D478" t="n">
-        <v>21.31285752034541</v>
+        <v>21.31285934317238</v>
       </c>
       <c r="E478" t="n">
-        <v>21.42654867733226</v>
+        <v>21.42655050988291</v>
       </c>
       <c r="F478" t="n">
         <v>3225800</v>
@@ -9992,16 +9992,16 @@
         <v>44278</v>
       </c>
       <c r="B479" t="n">
-        <v>23.40303993225098</v>
+        <v>23.40303802490234</v>
       </c>
       <c r="C479" t="n">
-        <v>23.60418673439288</v>
+        <v>23.60418481065078</v>
       </c>
       <c r="D479" t="n">
-        <v>21.72389800134264</v>
+        <v>21.72389623084414</v>
       </c>
       <c r="E479" t="n">
-        <v>22.18741172061003</v>
+        <v>22.18740991233514</v>
       </c>
       <c r="F479" t="n">
         <v>2996700</v>
@@ -10032,16 +10032,16 @@
         <v>44280</v>
       </c>
       <c r="B481" t="n">
-        <v>23.69164085388184</v>
+        <v>23.6916389465332</v>
       </c>
       <c r="C481" t="n">
-        <v>24.0851903702895</v>
+        <v>24.08518843125728</v>
       </c>
       <c r="D481" t="n">
-        <v>22.70339503182592</v>
+        <v>22.70339320403824</v>
       </c>
       <c r="E481" t="n">
-        <v>23.35056571838018</v>
+        <v>23.35056383849056</v>
       </c>
       <c r="F481" t="n">
         <v>2016400</v>
@@ -10132,16 +10132,16 @@
         <v>44287</v>
       </c>
       <c r="B486" t="n">
-        <v>23.5167293548584</v>
+        <v>23.51673126220703</v>
       </c>
       <c r="C486" t="n">
-        <v>23.52547508492306</v>
+        <v>23.52547699298102</v>
       </c>
       <c r="D486" t="n">
-        <v>22.2223913306826</v>
+        <v>22.22239313305261</v>
       </c>
       <c r="E486" t="n">
-        <v>23.5167293548584</v>
+        <v>23.51673126220703</v>
       </c>
       <c r="F486" t="n">
         <v>1244600</v>
@@ -10232,16 +10232,16 @@
         <v>44295</v>
       </c>
       <c r="B491" t="n">
-        <v>23.8578052520752</v>
+        <v>23.85780715942383</v>
       </c>
       <c r="C491" t="n">
-        <v>24.00647932139237</v>
+        <v>24.00648124062698</v>
       </c>
       <c r="D491" t="n">
-        <v>23.01823354649663</v>
+        <v>23.01823538672442</v>
       </c>
       <c r="E491" t="n">
-        <v>23.45551002471451</v>
+        <v>23.45551189990104</v>
       </c>
       <c r="F491" t="n">
         <v>1479500</v>
@@ -10312,16 +10312,16 @@
         <v>44301</v>
       </c>
       <c r="B495" t="n">
-        <v>24.05020904541016</v>
+        <v>24.05020713806152</v>
       </c>
       <c r="C495" t="n">
-        <v>24.40002993427333</v>
+        <v>24.40002799918148</v>
       </c>
       <c r="D495" t="n">
-        <v>23.70038815654698</v>
+        <v>23.70038627694157</v>
       </c>
       <c r="E495" t="n">
-        <v>23.70038815654698</v>
+        <v>23.70038627694157</v>
       </c>
       <c r="F495" t="n">
         <v>383100</v>
@@ -10332,16 +10332,16 @@
         <v>44302</v>
       </c>
       <c r="B496" t="n">
-        <v>25.00346946716309</v>
+        <v>25.00346755981445</v>
       </c>
       <c r="C496" t="n">
-        <v>25.5806742921028</v>
+        <v>25.58067234072305</v>
       </c>
       <c r="D496" t="n">
-        <v>23.87529533873165</v>
+        <v>23.87529351744393</v>
       </c>
       <c r="E496" t="n">
-        <v>24.25135338154213</v>
+        <v>24.25135153156744</v>
       </c>
       <c r="F496" t="n">
         <v>1936400</v>
@@ -10392,16 +10392,16 @@
         <v>44308</v>
       </c>
       <c r="B499" t="n">
-        <v>23.47300338745117</v>
+        <v>23.47300148010254</v>
       </c>
       <c r="C499" t="n">
-        <v>24.6186673862146</v>
+        <v>24.61866538577261</v>
       </c>
       <c r="D499" t="n">
-        <v>23.34182076696456</v>
+        <v>23.34181887027545</v>
       </c>
       <c r="E499" t="n">
-        <v>24.05895398249705</v>
+        <v>24.05895202753576</v>
       </c>
       <c r="F499" t="n">
         <v>479300</v>
@@ -10412,16 +10412,16 @@
         <v>44309</v>
       </c>
       <c r="B500" t="n">
-        <v>24.01522254943848</v>
+        <v>24.01522445678711</v>
       </c>
       <c r="C500" t="n">
-        <v>24.0589511965888</v>
+        <v>24.05895310741047</v>
       </c>
       <c r="D500" t="n">
-        <v>23.29808941694648</v>
+        <v>23.29809126733862</v>
       </c>
       <c r="E500" t="n">
-        <v>23.53421910732623</v>
+        <v>23.53422097647238</v>
       </c>
       <c r="F500" t="n">
         <v>849000</v>
@@ -10512,16 +10512,16 @@
         <v>44316</v>
       </c>
       <c r="B505" t="n">
-        <v>22.76461410522461</v>
+        <v>22.76461601257324</v>
       </c>
       <c r="C505" t="n">
-        <v>23.52547424482788</v>
+        <v>23.52547621592569</v>
       </c>
       <c r="D505" t="n">
-        <v>22.56346565707531</v>
+        <v>22.56346754757059</v>
       </c>
       <c r="E505" t="n">
-        <v>23.23687183530985</v>
+        <v>23.23687378222692</v>
       </c>
       <c r="F505" t="n">
         <v>743400</v>
@@ -10532,16 +10532,16 @@
         <v>44319</v>
       </c>
       <c r="B506" t="n">
-        <v>23.08819961547852</v>
+        <v>23.08819770812988</v>
       </c>
       <c r="C506" t="n">
-        <v>23.75286011721265</v>
+        <v>23.75285815495547</v>
       </c>
       <c r="D506" t="n">
-        <v>22.76461592910326</v>
+        <v>22.76461404848633</v>
       </c>
       <c r="E506" t="n">
-        <v>22.76461592910326</v>
+        <v>22.76461404848633</v>
       </c>
       <c r="F506" t="n">
         <v>492900</v>
@@ -10552,16 +10552,16 @@
         <v>44320</v>
       </c>
       <c r="B507" t="n">
-        <v>23.5167293548584</v>
+        <v>23.51673126220703</v>
       </c>
       <c r="C507" t="n">
-        <v>23.90153313731625</v>
+        <v>23.90153507587479</v>
       </c>
       <c r="D507" t="n">
-        <v>22.790850440266</v>
+        <v>22.79085228874147</v>
       </c>
       <c r="E507" t="n">
-        <v>23.08819859015469</v>
+        <v>23.08820046274689</v>
       </c>
       <c r="F507" t="n">
         <v>826900</v>
@@ -10572,16 +10572,16 @@
         <v>44321</v>
       </c>
       <c r="B508" t="n">
-        <v>24.13766098022461</v>
+        <v>24.13766288757324</v>
       </c>
       <c r="C508" t="n">
-        <v>24.51371900356778</v>
+        <v>24.51372094063237</v>
       </c>
       <c r="D508" t="n">
-        <v>23.1756524324327</v>
+        <v>23.17565426376379</v>
       </c>
       <c r="E508" t="n">
-        <v>23.24561659946789</v>
+        <v>23.24561843632752</v>
       </c>
       <c r="F508" t="n">
         <v>512200</v>
@@ -10632,16 +10632,16 @@
         <v>44326</v>
       </c>
       <c r="B511" t="n">
-        <v>25.09967231750488</v>
+        <v>25.09967041015625</v>
       </c>
       <c r="C511" t="n">
-        <v>25.18712628496021</v>
+        <v>25.18712437096586</v>
       </c>
       <c r="D511" t="n">
-        <v>24.51372172793567</v>
+        <v>24.51371986511399</v>
       </c>
       <c r="E511" t="n">
-        <v>24.55744871166333</v>
+        <v>24.5574468455188</v>
       </c>
       <c r="F511" t="n">
         <v>963200</v>
@@ -10652,16 +10652,16 @@
         <v>44327</v>
       </c>
       <c r="B512" t="n">
-        <v>25.53694725036621</v>
+        <v>25.53694915771484</v>
       </c>
       <c r="C512" t="n">
-        <v>25.53694725036621</v>
+        <v>25.53694915771484</v>
       </c>
       <c r="D512" t="n">
-        <v>24.46999156528212</v>
+        <v>24.46999339294008</v>
       </c>
       <c r="E512" t="n">
-        <v>24.93350523733319</v>
+        <v>24.93350709961088</v>
       </c>
       <c r="F512" t="n">
         <v>476700</v>
@@ -10672,16 +10672,16 @@
         <v>44328</v>
       </c>
       <c r="B513" t="n">
-        <v>23.42053031921387</v>
+        <v>23.4205322265625</v>
       </c>
       <c r="C513" t="n">
-        <v>25.3532916797891</v>
+        <v>25.35329374454022</v>
       </c>
       <c r="D513" t="n">
-        <v>22.87830671649212</v>
+        <v>22.87830857968251</v>
       </c>
       <c r="E513" t="n">
-        <v>25.28332750538089</v>
+        <v>25.28332956443419</v>
       </c>
       <c r="F513" t="n">
         <v>1663700</v>
@@ -10712,16 +10712,16 @@
         <v>44330</v>
       </c>
       <c r="B515" t="n">
-        <v>24.15515518188477</v>
+        <v>24.15515327453613</v>
       </c>
       <c r="C515" t="n">
-        <v>24.45250167449084</v>
+        <v>24.45249974366302</v>
       </c>
       <c r="D515" t="n">
-        <v>23.04447244451242</v>
+        <v>23.04447062486594</v>
       </c>
       <c r="E515" t="n">
-        <v>23.04447244451242</v>
+        <v>23.04447062486594</v>
       </c>
       <c r="F515" t="n">
         <v>745100</v>
@@ -10732,16 +10732,16 @@
         <v>44333</v>
       </c>
       <c r="B516" t="n">
-        <v>24.81106948852539</v>
+        <v>24.81106758117676</v>
       </c>
       <c r="C516" t="n">
-        <v>25.01221627935886</v>
+        <v>25.01221435654708</v>
       </c>
       <c r="D516" t="n">
-        <v>23.48174852044099</v>
+        <v>23.48174671528379</v>
       </c>
       <c r="E516" t="n">
-        <v>23.83156938886387</v>
+        <v>23.83156755681421</v>
       </c>
       <c r="F516" t="n">
         <v>854000</v>
@@ -10752,16 +10752,16 @@
         <v>44334</v>
       </c>
       <c r="B517" t="n">
-        <v>25.1084156036377</v>
+        <v>25.10841751098633</v>
       </c>
       <c r="C517" t="n">
-        <v>25.72934909545677</v>
+        <v>25.72935104997431</v>
       </c>
       <c r="D517" t="n">
-        <v>24.5661936826348</v>
+        <v>24.5661955487938</v>
       </c>
       <c r="E517" t="n">
-        <v>24.67113910756812</v>
+        <v>24.67114098169926</v>
       </c>
       <c r="F517" t="n">
         <v>683300</v>
@@ -10772,16 +10772,16 @@
         <v>44335</v>
       </c>
       <c r="B518" t="n">
-        <v>24.46999168395996</v>
+        <v>24.46999359130859</v>
       </c>
       <c r="C518" t="n">
-        <v>25.63314706656199</v>
+        <v>25.63314906457444</v>
       </c>
       <c r="D518" t="n">
-        <v>24.32131761243591</v>
+        <v>24.32131950819593</v>
       </c>
       <c r="E518" t="n">
-        <v>25.0821794297831</v>
+        <v>25.08218138484958</v>
       </c>
       <c r="F518" t="n">
         <v>1238500</v>
@@ -10792,16 +10792,16 @@
         <v>44336</v>
       </c>
       <c r="B519" t="n">
-        <v>25.1084156036377</v>
+        <v>25.10841751098633</v>
       </c>
       <c r="C519" t="n">
-        <v>25.44949240486463</v>
+        <v>25.449494338123</v>
       </c>
       <c r="D519" t="n">
-        <v>24.36504689478139</v>
+        <v>24.36504874566037</v>
       </c>
       <c r="E519" t="n">
-        <v>24.49622950998677</v>
+        <v>24.49623137083098</v>
       </c>
       <c r="F519" t="n">
         <v>1217700</v>
@@ -10872,16 +10872,16 @@
         <v>44342</v>
       </c>
       <c r="B523" t="n">
-        <v>27.02368545532227</v>
+        <v>27.0236873626709</v>
       </c>
       <c r="C523" t="n">
-        <v>27.11114108275307</v>
+        <v>27.11114299627437</v>
       </c>
       <c r="D523" t="n">
-        <v>26.13164105806731</v>
+        <v>26.13164290245489</v>
       </c>
       <c r="E523" t="n">
-        <v>26.2978065833781</v>
+        <v>26.29780843949375</v>
       </c>
       <c r="F523" t="n">
         <v>688100</v>
@@ -10892,16 +10892,16 @@
         <v>44343</v>
       </c>
       <c r="B524" t="n">
-        <v>27.70584106445312</v>
+        <v>27.70583915710449</v>
       </c>
       <c r="C524" t="n">
-        <v>27.70584106445312</v>
+        <v>27.70583915710449</v>
       </c>
       <c r="D524" t="n">
-        <v>26.81379654752638</v>
+        <v>26.81379470158862</v>
       </c>
       <c r="E524" t="n">
-        <v>27.11114471983529</v>
+        <v>27.11114285342725</v>
       </c>
       <c r="F524" t="n">
         <v>998900</v>
@@ -10952,16 +10952,16 @@
         <v>44348</v>
       </c>
       <c r="B527" t="n">
-        <v>30.37322044372559</v>
+        <v>30.37322425842285</v>
       </c>
       <c r="C527" t="n">
-        <v>31.2127903890981</v>
+        <v>31.21279430924039</v>
       </c>
       <c r="D527" t="n">
-        <v>29.13135698321471</v>
+        <v>29.13136064194126</v>
       </c>
       <c r="E527" t="n">
-        <v>29.2975208256881</v>
+        <v>29.29752450528385</v>
       </c>
       <c r="F527" t="n">
         <v>3409000</v>
@@ -10992,16 +10992,16 @@
         <v>44351</v>
       </c>
       <c r="B529" t="n">
-        <v>30.52190399169922</v>
+        <v>30.52190017700195</v>
       </c>
       <c r="C529" t="n">
-        <v>30.85423176186658</v>
+        <v>30.85422790563423</v>
       </c>
       <c r="D529" t="n">
-        <v>30.18082548628231</v>
+        <v>30.18082171421382</v>
       </c>
       <c r="E529" t="n">
-        <v>30.60935796571057</v>
+        <v>30.60935414008311</v>
       </c>
       <c r="F529" t="n">
         <v>1113000</v>
@@ -11052,16 +11052,16 @@
         <v>44356</v>
       </c>
       <c r="B532" t="n">
-        <v>31.91244316101074</v>
+        <v>31.91243934631348</v>
       </c>
       <c r="C532" t="n">
-        <v>32.1048425688429</v>
+        <v>32.10483873114692</v>
       </c>
       <c r="D532" t="n">
-        <v>30.91544985356672</v>
+        <v>30.91544615804641</v>
       </c>
       <c r="E532" t="n">
-        <v>31.42269223820431</v>
+        <v>31.42268848205008</v>
       </c>
       <c r="F532" t="n">
         <v>930900</v>
@@ -11092,16 +11092,16 @@
         <v>44358</v>
       </c>
       <c r="B534" t="n">
-        <v>33.14556121826172</v>
+        <v>33.14556503295898</v>
       </c>
       <c r="C534" t="n">
-        <v>33.95889580420251</v>
+        <v>33.95889971250583</v>
       </c>
       <c r="D534" t="n">
-        <v>31.65882039793151</v>
+        <v>31.65882404152092</v>
       </c>
       <c r="E534" t="n">
-        <v>31.79874874948288</v>
+        <v>31.79875240917653</v>
       </c>
       <c r="F534" t="n">
         <v>1304000</v>
@@ -11112,16 +11112,16 @@
         <v>44361</v>
       </c>
       <c r="B535" t="n">
-        <v>33.54784774780273</v>
+        <v>33.54785537719727</v>
       </c>
       <c r="C535" t="n">
-        <v>34.28247227279675</v>
+        <v>34.28248006925834</v>
       </c>
       <c r="D535" t="n">
-        <v>32.97064300217561</v>
+        <v>32.97065050030321</v>
       </c>
       <c r="E535" t="n">
-        <v>33.31171807875241</v>
+        <v>33.31172565444673</v>
       </c>
       <c r="F535" t="n">
         <v>1573500</v>
@@ -11152,16 +11152,16 @@
         <v>44363</v>
       </c>
       <c r="B537" t="n">
-        <v>33.6965217590332</v>
+        <v>33.69652557373047</v>
       </c>
       <c r="C537" t="n">
-        <v>34.36992788417019</v>
+        <v>34.36993177510205</v>
       </c>
       <c r="D537" t="n">
-        <v>33.10182552738377</v>
+        <v>33.101829274757</v>
       </c>
       <c r="E537" t="n">
-        <v>34.05508831021996</v>
+        <v>34.05509216550963</v>
       </c>
       <c r="F537" t="n">
         <v>1453900</v>
@@ -11312,16 +11312,16 @@
         <v>44375</v>
       </c>
       <c r="B545" t="n">
-        <v>32.34096908569336</v>
+        <v>32.34096527099609</v>
       </c>
       <c r="C545" t="n">
-        <v>32.61208171290355</v>
+        <v>32.61207786622787</v>
       </c>
       <c r="D545" t="n">
-        <v>31.43143317778327</v>
+        <v>31.43142947036801</v>
       </c>
       <c r="E545" t="n">
-        <v>31.60634444255904</v>
+        <v>31.60634071451257</v>
       </c>
       <c r="F545" t="n">
         <v>891000</v>
@@ -11352,16 +11352,16 @@
         <v>44377</v>
       </c>
       <c r="B547" t="n">
-        <v>33.46039581298828</v>
+        <v>33.46039199829102</v>
       </c>
       <c r="C547" t="n">
-        <v>34.09007503116541</v>
+        <v>34.09007114468072</v>
       </c>
       <c r="D547" t="n">
-        <v>32.64706460438268</v>
+        <v>32.64706088241032</v>
       </c>
       <c r="E547" t="n">
-        <v>32.83071993096604</v>
+        <v>32.83071618805582</v>
       </c>
       <c r="F547" t="n">
         <v>1605100</v>
@@ -11372,16 +11372,16 @@
         <v>44378</v>
       </c>
       <c r="B548" t="n">
-        <v>33.53910446166992</v>
+        <v>33.53910827636719</v>
       </c>
       <c r="C548" t="n">
-        <v>33.78398155744986</v>
+        <v>33.78398539999915</v>
       </c>
       <c r="D548" t="n">
-        <v>32.76075286615723</v>
+        <v>32.76075659232573</v>
       </c>
       <c r="E548" t="n">
-        <v>33.23301226213844</v>
+        <v>33.23301604202116</v>
       </c>
       <c r="F548" t="n">
         <v>860200</v>
@@ -11512,16 +11512,16 @@
         <v>44390</v>
       </c>
       <c r="B555" t="n">
-        <v>34.04634857177734</v>
+        <v>34.04634475708008</v>
       </c>
       <c r="C555" t="n">
-        <v>34.57107903754478</v>
+        <v>34.57107516405448</v>
       </c>
       <c r="D555" t="n">
-        <v>33.39043382149058</v>
+        <v>33.39043008028479</v>
       </c>
       <c r="E555" t="n">
-        <v>34.57107903754478</v>
+        <v>34.57107516405448</v>
       </c>
       <c r="F555" t="n">
         <v>920800</v>
@@ -11572,16 +11572,16 @@
         <v>44393</v>
       </c>
       <c r="B558" t="n">
-        <v>33.4254150390625</v>
+        <v>33.42541885375977</v>
       </c>
       <c r="C558" t="n">
-        <v>34.50985883603434</v>
+        <v>34.50986277449446</v>
       </c>
       <c r="D558" t="n">
-        <v>32.72577000548159</v>
+        <v>32.72577374033141</v>
       </c>
       <c r="E558" t="n">
-        <v>34.28247653542888</v>
+        <v>34.28248044793884</v>
       </c>
       <c r="F558" t="n">
         <v>877400</v>
@@ -11612,16 +11612,16 @@
         <v>44397</v>
       </c>
       <c r="B560" t="n">
-        <v>32.88319396972656</v>
+        <v>32.8831901550293</v>
       </c>
       <c r="C560" t="n">
-        <v>33.2155250691583</v>
+        <v>33.21552121590814</v>
       </c>
       <c r="D560" t="n">
-        <v>31.9649139170268</v>
+        <v>31.96491020885691</v>
       </c>
       <c r="E560" t="n">
-        <v>32.82197552195692</v>
+        <v>32.82197171436146</v>
       </c>
       <c r="F560" t="n">
         <v>924500</v>
@@ -11632,16 +11632,16 @@
         <v>44398</v>
       </c>
       <c r="B561" t="n">
-        <v>32.34971618652344</v>
+        <v>32.34971237182617</v>
       </c>
       <c r="C561" t="n">
-        <v>33.07559342486297</v>
+        <v>33.07558952456984</v>
       </c>
       <c r="D561" t="n">
-        <v>32.19229638328742</v>
+        <v>32.19229258715319</v>
       </c>
       <c r="E561" t="n">
-        <v>33.07559342486297</v>
+        <v>33.07558952456984</v>
       </c>
       <c r="F561" t="n">
         <v>460900</v>
@@ -11672,16 +11672,16 @@
         <v>44400</v>
       </c>
       <c r="B563" t="n">
-        <v>32.7607536315918</v>
+        <v>32.76075744628906</v>
       </c>
       <c r="C563" t="n">
-        <v>33.33795846144773</v>
+        <v>33.33796234335534</v>
       </c>
       <c r="D563" t="n">
-        <v>32.36720412574574</v>
+        <v>32.36720789461769</v>
       </c>
       <c r="E563" t="n">
-        <v>33.11932021777268</v>
+        <v>33.11932407422182</v>
       </c>
       <c r="F563" t="n">
         <v>561000</v>
@@ -11692,16 +11692,16 @@
         <v>44403</v>
       </c>
       <c r="B564" t="n">
-        <v>32.97064590454102</v>
+        <v>32.97064971923828</v>
       </c>
       <c r="C564" t="n">
-        <v>33.41666642790693</v>
+        <v>33.41667029420868</v>
       </c>
       <c r="D564" t="n">
-        <v>32.37594964928337</v>
+        <v>32.3759533951744</v>
       </c>
       <c r="E564" t="n">
-        <v>33.08433871879298</v>
+        <v>33.08434254664448</v>
       </c>
       <c r="F564" t="n">
         <v>436800</v>
@@ -11732,16 +11732,16 @@
         <v>44405</v>
       </c>
       <c r="B566" t="n">
-        <v>32.62082290649414</v>
+        <v>32.62082672119141</v>
       </c>
       <c r="C566" t="n">
-        <v>32.69078874071425</v>
+        <v>32.69079256359336</v>
       </c>
       <c r="D566" t="n">
-        <v>31.6063416633848</v>
+        <v>31.60634535944806</v>
       </c>
       <c r="E566" t="n">
-        <v>32.09609249446174</v>
+        <v>32.09609624779674</v>
       </c>
       <c r="F566" t="n">
         <v>535400</v>
@@ -11812,16 +11812,16 @@
         <v>44411</v>
       </c>
       <c r="B570" t="n">
-        <v>31.45767402648926</v>
+        <v>31.45767593383789</v>
       </c>
       <c r="C570" t="n">
-        <v>31.80749324202077</v>
+        <v>31.80749517057972</v>
       </c>
       <c r="D570" t="n">
-        <v>30.52190253730594</v>
+        <v>30.52190438791667</v>
       </c>
       <c r="E570" t="n">
-        <v>30.83673883043777</v>
+        <v>30.83674070013772</v>
       </c>
       <c r="F570" t="n">
         <v>798700</v>
@@ -11972,16 +11972,16 @@
         <v>44421</v>
       </c>
       <c r="B578" t="n">
-        <v>29.66483688354492</v>
+        <v>29.66483497619629</v>
       </c>
       <c r="C578" t="n">
-        <v>30.72304857488147</v>
+        <v>30.7230465994934</v>
       </c>
       <c r="D578" t="n">
-        <v>29.22756037285949</v>
+        <v>29.22755849362626</v>
       </c>
       <c r="E578" t="n">
-        <v>30.39071749263714</v>
+        <v>30.39071553861684</v>
       </c>
       <c r="F578" t="n">
         <v>1030500</v>
@@ -12092,16 +12092,16 @@
         <v>44431</v>
       </c>
       <c r="B584" t="n">
-        <v>30.00591659545898</v>
+        <v>30.00591278076172</v>
       </c>
       <c r="C584" t="n">
-        <v>30.4257016626031</v>
+        <v>30.42569779453793</v>
       </c>
       <c r="D584" t="n">
-        <v>29.17509052383503</v>
+        <v>29.17508681476194</v>
       </c>
       <c r="E584" t="n">
-        <v>29.29752741806601</v>
+        <v>29.29752369342733</v>
       </c>
       <c r="F584" t="n">
         <v>803400</v>
@@ -12132,16 +12132,16 @@
         <v>44433</v>
       </c>
       <c r="B586" t="n">
-        <v>32.22727966308594</v>
+        <v>32.22727584838867</v>
       </c>
       <c r="C586" t="n">
-        <v>32.27975404890109</v>
+        <v>32.27975022799251</v>
       </c>
       <c r="D586" t="n">
-        <v>31.42269243085174</v>
+        <v>31.42268871139232</v>
       </c>
       <c r="E586" t="n">
-        <v>31.92118741955233</v>
+        <v>31.92118364108677</v>
       </c>
       <c r="F586" t="n">
         <v>461300</v>
@@ -12172,16 +12172,16 @@
         <v>44435</v>
       </c>
       <c r="B588" t="n">
-        <v>30.46942710876465</v>
+        <v>30.46942329406738</v>
       </c>
       <c r="C588" t="n">
-        <v>30.7317923454543</v>
+        <v>30.73178849790956</v>
       </c>
       <c r="D588" t="n">
-        <v>29.77852942776306</v>
+        <v>29.77852569956449</v>
       </c>
       <c r="E588" t="n">
-        <v>30.7317923454543</v>
+        <v>30.73178849790956</v>
       </c>
       <c r="F588" t="n">
         <v>654900</v>
@@ -12232,16 +12232,16 @@
         <v>44440</v>
       </c>
       <c r="B591" t="n">
-        <v>29.42870903015137</v>
+        <v>29.4287109375</v>
       </c>
       <c r="C591" t="n">
-        <v>30.52190025213092</v>
+        <v>30.52190223033202</v>
       </c>
       <c r="D591" t="n">
-        <v>29.42870903015137</v>
+        <v>29.4287109375</v>
       </c>
       <c r="E591" t="n">
-        <v>30.37322451114117</v>
+        <v>30.37322647970623</v>
       </c>
       <c r="F591" t="n">
         <v>539500</v>
@@ -12272,16 +12272,16 @@
         <v>44442</v>
       </c>
       <c r="B593" t="n">
-        <v>28.41422653198242</v>
+        <v>28.41422843933105</v>
       </c>
       <c r="C593" t="n">
-        <v>29.50741770865503</v>
+        <v>29.5074196893858</v>
       </c>
       <c r="D593" t="n">
-        <v>27.65336473906425</v>
+        <v>27.65336659533887</v>
       </c>
       <c r="E593" t="n">
-        <v>29.28877947332051</v>
+        <v>29.28878143937485</v>
       </c>
       <c r="F593" t="n">
         <v>1806900</v>
@@ -12312,16 +12312,16 @@
         <v>44447</v>
       </c>
       <c r="B595" t="n">
-        <v>26.70884895324707</v>
+        <v>26.7088508605957</v>
       </c>
       <c r="C595" t="n">
-        <v>27.96820405019139</v>
+        <v>27.96820604747386</v>
       </c>
       <c r="D595" t="n">
-        <v>26.70884895324707</v>
+        <v>26.7088508605957</v>
       </c>
       <c r="E595" t="n">
-        <v>27.89823987813893</v>
+        <v>27.89824187042507</v>
       </c>
       <c r="F595" t="n">
         <v>518300</v>
@@ -12372,16 +12372,16 @@
         <v>44452</v>
       </c>
       <c r="B598" t="n">
-        <v>28.86024856567383</v>
+        <v>28.86025047302246</v>
       </c>
       <c r="C598" t="n">
-        <v>29.41996194346575</v>
+        <v>29.41996388780535</v>
       </c>
       <c r="D598" t="n">
-        <v>28.06440548109689</v>
+        <v>28.06440733584895</v>
       </c>
       <c r="E598" t="n">
-        <v>28.21307788750511</v>
+        <v>28.2130797520828</v>
       </c>
       <c r="F598" t="n">
         <v>676500</v>
@@ -12492,16 +12492,16 @@
         <v>44460</v>
       </c>
       <c r="B604" t="n">
-        <v>27.69709396362305</v>
+        <v>27.69709205627441</v>
       </c>
       <c r="C604" t="n">
-        <v>28.16935172281972</v>
+        <v>28.16934978294925</v>
       </c>
       <c r="D604" t="n">
-        <v>26.90125085595213</v>
+        <v>26.9012490034089</v>
       </c>
       <c r="E604" t="n">
-        <v>27.25107172722328</v>
+        <v>27.25106985058978</v>
       </c>
       <c r="F604" t="n">
         <v>267700</v>
@@ -12532,16 +12532,16 @@
         <v>44462</v>
       </c>
       <c r="B606" t="n">
-        <v>29.44619941711426</v>
+        <v>29.44619750976562</v>
       </c>
       <c r="C606" t="n">
-        <v>29.58613110699141</v>
+        <v>29.58612919057884</v>
       </c>
       <c r="D606" t="n">
-        <v>28.46670094105993</v>
+        <v>28.46669909715735</v>
       </c>
       <c r="E606" t="n">
-        <v>28.86025047845166</v>
+        <v>28.86024860905729</v>
       </c>
       <c r="F606" t="n">
         <v>1113800</v>
@@ -12572,16 +12572,16 @@
         <v>44466</v>
       </c>
       <c r="B608" t="n">
-        <v>27.32978057861328</v>
+        <v>27.32978248596191</v>
       </c>
       <c r="C608" t="n">
-        <v>27.68834716635849</v>
+        <v>27.68834909873153</v>
       </c>
       <c r="D608" t="n">
-        <v>26.98870545077696</v>
+        <v>26.98870733432192</v>
       </c>
       <c r="E608" t="n">
-        <v>27.56591028315108</v>
+        <v>27.56591220697923</v>
       </c>
       <c r="F608" t="n">
         <v>409300</v>
@@ -12592,16 +12592,16 @@
         <v>44467</v>
       </c>
       <c r="B609" t="n">
-        <v>24.95099639892578</v>
+        <v>24.95099830627441</v>
       </c>
       <c r="C609" t="n">
-        <v>27.32103410556418</v>
+        <v>27.32103619408748</v>
       </c>
       <c r="D609" t="n">
-        <v>24.77608514074903</v>
+        <v>24.77608703472679</v>
       </c>
       <c r="E609" t="n">
-        <v>27.32103410556418</v>
+        <v>27.32103619408748</v>
       </c>
       <c r="F609" t="n">
         <v>1189200</v>
@@ -12632,16 +12632,16 @@
         <v>44469</v>
       </c>
       <c r="B611" t="n">
-        <v>24.44375610351562</v>
+        <v>24.44375419616699</v>
       </c>
       <c r="C611" t="n">
-        <v>25.51945585296703</v>
+        <v>25.51945386168145</v>
       </c>
       <c r="D611" t="n">
-        <v>23.74411272882204</v>
+        <v>23.74411087606664</v>
       </c>
       <c r="E611" t="n">
-        <v>25.20461625095105</v>
+        <v>25.20461428423243</v>
       </c>
       <c r="F611" t="n">
         <v>2108000</v>
@@ -12652,16 +12652,16 @@
         <v>44470</v>
       </c>
       <c r="B612" t="n">
-        <v>25.08218193054199</v>
+        <v>25.08218002319336</v>
       </c>
       <c r="C612" t="n">
-        <v>25.08218193054199</v>
+        <v>25.08218002319336</v>
       </c>
       <c r="D612" t="n">
-        <v>23.85780798489986</v>
+        <v>23.85780617065748</v>
       </c>
       <c r="E612" t="n">
-        <v>24.44375859955341</v>
+        <v>24.44375674075302</v>
       </c>
       <c r="F612" t="n">
         <v>1977000</v>
@@ -12672,16 +12672,16 @@
         <v>44473</v>
       </c>
       <c r="B613" t="n">
-        <v>24.40002632141113</v>
+        <v>24.40002822875977</v>
       </c>
       <c r="C613" t="n">
-        <v>25.08217820474767</v>
+        <v>25.08218016542008</v>
       </c>
       <c r="D613" t="n">
-        <v>24.06769694321784</v>
+        <v>24.06769882458831</v>
       </c>
       <c r="E613" t="n">
-        <v>25.08217820474767</v>
+        <v>25.08218016542008</v>
       </c>
       <c r="F613" t="n">
         <v>966400</v>
@@ -12692,16 +12692,16 @@
         <v>44474</v>
       </c>
       <c r="B614" t="n">
-        <v>24.1289176940918</v>
+        <v>24.12891578674316</v>
       </c>
       <c r="C614" t="n">
-        <v>24.95974372133053</v>
+        <v>24.95974174830655</v>
       </c>
       <c r="D614" t="n">
-        <v>23.93651663228211</v>
+        <v>23.93651474014245</v>
       </c>
       <c r="E614" t="n">
-        <v>24.95974372133053</v>
+        <v>24.95974174830655</v>
       </c>
       <c r="F614" t="n">
         <v>1123700</v>
@@ -12712,16 +12712,16 @@
         <v>44475</v>
       </c>
       <c r="B615" t="n">
-        <v>25.0384521484375</v>
+        <v>25.03845405578613</v>
       </c>
       <c r="C615" t="n">
-        <v>25.0384521484375</v>
+        <v>25.03845405578613</v>
       </c>
       <c r="D615" t="n">
-        <v>23.45551165437001</v>
+        <v>23.45551344113533</v>
       </c>
       <c r="E615" t="n">
-        <v>23.83156971865774</v>
+        <v>23.83157153406996</v>
       </c>
       <c r="F615" t="n">
         <v>1528000</v>
@@ -12732,16 +12732,16 @@
         <v>44476</v>
       </c>
       <c r="B616" t="n">
-        <v>25.20461654663086</v>
+        <v>25.20461845397949</v>
       </c>
       <c r="C616" t="n">
-        <v>25.74684012667738</v>
+        <v>25.74684207505855</v>
       </c>
       <c r="D616" t="n">
-        <v>25.01221549207367</v>
+        <v>25.01221738486243</v>
       </c>
       <c r="E616" t="n">
-        <v>25.28332644805822</v>
+        <v>25.28332836136319</v>
       </c>
       <c r="F616" t="n">
         <v>920700</v>
@@ -12752,16 +12752,16 @@
         <v>44477</v>
       </c>
       <c r="B617" t="n">
-        <v>25.84304237365723</v>
+        <v>25.84304046630859</v>
       </c>
       <c r="C617" t="n">
-        <v>26.37652027647562</v>
+        <v>26.37651832975359</v>
       </c>
       <c r="D617" t="n">
-        <v>25.2745832156796</v>
+        <v>25.27458135028616</v>
       </c>
       <c r="E617" t="n">
-        <v>25.44074876489932</v>
+        <v>25.44074688724201</v>
       </c>
       <c r="F617" t="n">
         <v>712200</v>
@@ -12792,16 +12792,16 @@
         <v>44482</v>
       </c>
       <c r="B619" t="n">
-        <v>24.99472427368164</v>
+        <v>24.99472236633301</v>
       </c>
       <c r="C619" t="n">
-        <v>25.16963553811629</v>
+        <v>25.16963361742017</v>
       </c>
       <c r="D619" t="n">
-        <v>24.24260817192107</v>
+        <v>24.24260632196645</v>
       </c>
       <c r="E619" t="n">
-        <v>24.48748360851409</v>
+        <v>24.48748173987302</v>
       </c>
       <c r="F619" t="n">
         <v>570100</v>
@@ -12832,16 +12832,16 @@
         <v>44484</v>
       </c>
       <c r="B621" t="n">
-        <v>24.93350791931152</v>
+        <v>24.93350601196289</v>
       </c>
       <c r="C621" t="n">
-        <v>25.40576570390476</v>
+        <v>25.40576376042963</v>
       </c>
       <c r="D621" t="n">
-        <v>24.53995837541918</v>
+        <v>24.53995649817606</v>
       </c>
       <c r="E621" t="n">
-        <v>25.37953017969699</v>
+        <v>25.37952823822881</v>
       </c>
       <c r="F621" t="n">
         <v>833600</v>
@@ -12912,16 +12912,16 @@
         <v>44490</v>
       </c>
       <c r="B625" t="n">
-        <v>21.36532974243164</v>
+        <v>21.36533164978027</v>
       </c>
       <c r="C625" t="n">
-        <v>22.56346640067376</v>
+        <v>22.56346841498373</v>
       </c>
       <c r="D625" t="n">
-        <v>21.08547305344304</v>
+        <v>21.08547493580801</v>
       </c>
       <c r="E625" t="n">
-        <v>22.41479232613888</v>
+        <v>22.41479432717626</v>
       </c>
       <c r="F625" t="n">
         <v>1161600</v>
@@ -12972,16 +12972,16 @@
         <v>44495</v>
       </c>
       <c r="B628" t="n">
-        <v>20.12346649169922</v>
+        <v>20.12346458435059</v>
       </c>
       <c r="C628" t="n">
-        <v>21.57522446533426</v>
+        <v>21.57522242038466</v>
       </c>
       <c r="D628" t="n">
-        <v>19.9223196844302</v>
+        <v>19.92231779614673</v>
       </c>
       <c r="E628" t="n">
-        <v>21.55773300346453</v>
+        <v>21.55773096017281</v>
       </c>
       <c r="F628" t="n">
         <v>1203400</v>
@@ -13012,16 +13012,16 @@
         <v>44497</v>
       </c>
       <c r="B630" t="n">
-        <v>19.12647438049316</v>
+        <v>19.1264762878418</v>
       </c>
       <c r="C630" t="n">
-        <v>20.34210248725202</v>
+        <v>20.34210451582669</v>
       </c>
       <c r="D630" t="n">
-        <v>19.00403582916734</v>
+        <v>19.00403772430604</v>
       </c>
       <c r="E630" t="n">
-        <v>19.50253076019573</v>
+        <v>19.50253270504581</v>
       </c>
       <c r="F630" t="n">
         <v>1714300</v>
@@ -13052,16 +13052,16 @@
         <v>44501</v>
       </c>
       <c r="B632" t="n">
-        <v>19.67744255065918</v>
+        <v>19.67744445800781</v>
       </c>
       <c r="C632" t="n">
-        <v>19.97479070487089</v>
+        <v>19.9747926410417</v>
       </c>
       <c r="D632" t="n">
-        <v>18.37435877747371</v>
+        <v>18.3743605585135</v>
       </c>
       <c r="E632" t="n">
-        <v>18.46181441131436</v>
+        <v>18.46181620083128</v>
       </c>
       <c r="F632" t="n">
         <v>2083000</v>
@@ -13072,16 +13072,16 @@
         <v>44503</v>
       </c>
       <c r="B633" t="n">
-        <v>20.70941352844238</v>
+        <v>20.70941543579102</v>
       </c>
       <c r="C633" t="n">
-        <v>20.93679748908476</v>
+        <v>20.93679941737559</v>
       </c>
       <c r="D633" t="n">
-        <v>19.25765580656032</v>
+        <v>19.25765758020125</v>
       </c>
       <c r="E633" t="n">
-        <v>19.44131112011147</v>
+        <v>19.44131291066716</v>
       </c>
       <c r="F633" t="n">
         <v>1146900</v>
@@ -13152,16 +13152,16 @@
         <v>44509</v>
       </c>
       <c r="B637" t="n">
-        <v>21.48776626586914</v>
+        <v>21.48776817321777</v>
       </c>
       <c r="C637" t="n">
-        <v>21.87257004080282</v>
+        <v>21.87257198230833</v>
       </c>
       <c r="D637" t="n">
-        <v>20.1934282670019</v>
+        <v>20.1934300594594</v>
       </c>
       <c r="E637" t="n">
-        <v>20.29837368957091</v>
+        <v>20.29837549134383</v>
       </c>
       <c r="F637" t="n">
         <v>1107100</v>
@@ -13212,16 +13212,16 @@
         <v>44512</v>
       </c>
       <c r="B640" t="n">
-        <v>23.82282066345215</v>
+        <v>23.82282257080078</v>
       </c>
       <c r="C640" t="n">
-        <v>24.15515169772873</v>
+        <v>24.15515363168509</v>
       </c>
       <c r="D640" t="n">
-        <v>22.77335819013016</v>
+        <v>22.77336001345471</v>
       </c>
       <c r="E640" t="n">
-        <v>23.6304196270291</v>
+        <v>23.63042151897335</v>
       </c>
       <c r="F640" t="n">
         <v>1535100</v>
@@ -13272,16 +13272,16 @@
         <v>44518</v>
       </c>
       <c r="B643" t="n">
-        <v>22.85206985473633</v>
+        <v>22.8520679473877</v>
       </c>
       <c r="C643" t="n">
-        <v>23.11443676360454</v>
+        <v>23.11443483435745</v>
       </c>
       <c r="D643" t="n">
-        <v>21.35658497968982</v>
+        <v>21.35658319716188</v>
       </c>
       <c r="E643" t="n">
-        <v>21.65393314222729</v>
+        <v>21.65393133488117</v>
       </c>
       <c r="F643" t="n">
         <v>1745300</v>
@@ -13312,16 +13312,16 @@
         <v>44522</v>
       </c>
       <c r="B645" t="n">
-        <v>23.60418701171875</v>
+        <v>23.60418510437012</v>
       </c>
       <c r="C645" t="n">
-        <v>24.76734252083155</v>
+        <v>24.76734051949353</v>
       </c>
       <c r="D645" t="n">
-        <v>23.018236391755</v>
+        <v>23.01823453175441</v>
       </c>
       <c r="E645" t="n">
-        <v>24.57494144714107</v>
+        <v>24.57493946135012</v>
       </c>
       <c r="F645" t="n">
         <v>1417300</v>
@@ -13352,16 +13352,16 @@
         <v>44524</v>
       </c>
       <c r="B647" t="n">
-        <v>23.07945251464844</v>
+        <v>23.07945442199707</v>
       </c>
       <c r="C647" t="n">
-        <v>23.54296619267316</v>
+        <v>23.54296813832782</v>
       </c>
       <c r="D647" t="n">
-        <v>22.23113672800283</v>
+        <v>22.23113856524435</v>
       </c>
       <c r="E647" t="n">
-        <v>22.8258330188791</v>
+        <v>22.82583490526793</v>
       </c>
       <c r="F647" t="n">
         <v>983600</v>
@@ -13372,16 +13372,16 @@
         <v>44525</v>
       </c>
       <c r="B648" t="n">
-        <v>23.77034759521484</v>
+        <v>23.77034950256348</v>
       </c>
       <c r="C648" t="n">
-        <v>23.95400289972348</v>
+        <v>23.95400482180874</v>
       </c>
       <c r="D648" t="n">
-        <v>23.11443293383729</v>
+        <v>23.11443478855489</v>
       </c>
       <c r="E648" t="n">
-        <v>23.12317866282493</v>
+        <v>23.12318051824429</v>
       </c>
       <c r="F648" t="n">
         <v>1061000</v>
@@ -13392,16 +13392,16 @@
         <v>44526</v>
       </c>
       <c r="B649" t="n">
-        <v>22.4672679901123</v>
+        <v>22.46726608276367</v>
       </c>
       <c r="C649" t="n">
-        <v>23.1144370373956</v>
+        <v>23.11443507510585</v>
       </c>
       <c r="D649" t="n">
-        <v>22.07371845618714</v>
+        <v>22.07371658224871</v>
       </c>
       <c r="E649" t="n">
-        <v>22.31859390708252</v>
+        <v>22.31859201235551</v>
       </c>
       <c r="F649" t="n">
         <v>728600</v>
@@ -13492,16 +13492,16 @@
         <v>44533</v>
       </c>
       <c r="B654" t="n">
-        <v>22.09995460510254</v>
+        <v>22.09995269775391</v>
       </c>
       <c r="C654" t="n">
-        <v>22.79085060441233</v>
+        <v>22.79084863743554</v>
       </c>
       <c r="D654" t="n">
-        <v>21.03299888261361</v>
+        <v>21.03299706734918</v>
       </c>
       <c r="E654" t="n">
-        <v>21.03299888261361</v>
+        <v>21.03299706734918</v>
       </c>
       <c r="F654" t="n">
         <v>1059100</v>
@@ -13672,16 +13672,16 @@
         <v>44546</v>
       </c>
       <c r="B663" t="n">
-        <v>19.94855308532715</v>
+        <v>19.94855117797852</v>
       </c>
       <c r="C663" t="n">
-        <v>21.22540130855765</v>
+        <v>21.22539927912524</v>
       </c>
       <c r="D663" t="n">
-        <v>19.73866056946956</v>
+        <v>19.73865868218945</v>
       </c>
       <c r="E663" t="n">
-        <v>20.20217425120348</v>
+        <v>20.20217231960526</v>
       </c>
       <c r="F663" t="n">
         <v>912000</v>
@@ -13692,16 +13692,16 @@
         <v>44547</v>
       </c>
       <c r="B664" t="n">
-        <v>19.57249450683594</v>
+        <v>19.57249641418457</v>
       </c>
       <c r="C664" t="n">
-        <v>19.89607983592369</v>
+        <v>19.89608177480587</v>
       </c>
       <c r="D664" t="n">
-        <v>19.15270948646052</v>
+        <v>19.1527113529009</v>
       </c>
       <c r="E664" t="n">
-        <v>19.71242451503847</v>
+        <v>19.71242643602335</v>
       </c>
       <c r="F664" t="n">
         <v>983600</v>
@@ -13712,16 +13712,16 @@
         <v>44550</v>
       </c>
       <c r="B665" t="n">
-        <v>19.06525611877441</v>
+        <v>19.06525421142578</v>
       </c>
       <c r="C665" t="n">
-        <v>19.3888414862525</v>
+        <v>19.38883954653136</v>
       </c>
       <c r="D665" t="n">
-        <v>18.64547104859549</v>
+        <v>18.64546918324348</v>
       </c>
       <c r="E665" t="n">
-        <v>19.25765886033128</v>
+        <v>19.25765693373407</v>
       </c>
       <c r="F665" t="n">
         <v>742400</v>
@@ -13792,16 +13792,16 @@
         <v>44557</v>
       </c>
       <c r="B669" t="n">
-        <v>19.26640129089355</v>
+        <v>19.26640319824219</v>
       </c>
       <c r="C669" t="n">
-        <v>19.66869483055133</v>
+        <v>19.6686967777265</v>
       </c>
       <c r="D669" t="n">
-        <v>18.68919650125056</v>
+        <v>18.68919835145667</v>
       </c>
       <c r="E669" t="n">
-        <v>19.24016410297258</v>
+        <v>19.24016600772377</v>
       </c>
       <c r="F669" t="n">
         <v>750800</v>
@@ -13812,16 +13812,16 @@
         <v>44558</v>
       </c>
       <c r="B670" t="n">
-        <v>19.3713493347168</v>
+        <v>19.37134742736816</v>
       </c>
       <c r="C670" t="n">
-        <v>19.59873332331799</v>
+        <v>19.5987313935806</v>
       </c>
       <c r="D670" t="n">
-        <v>18.95156427948884</v>
+        <v>18.95156241347323</v>
       </c>
       <c r="E670" t="n">
-        <v>19.26640390494857</v>
+        <v>19.26640200793311</v>
       </c>
       <c r="F670" t="n">
         <v>786500</v>
@@ -13872,16 +13872,16 @@
         <v>44564</v>
       </c>
       <c r="B673" t="n">
-        <v>18.4180850982666</v>
+        <v>18.41808319091797</v>
       </c>
       <c r="C673" t="n">
-        <v>19.69493330305429</v>
+        <v>19.69493126347721</v>
       </c>
       <c r="D673" t="n">
-        <v>18.4180850982666</v>
+        <v>18.41808319091797</v>
       </c>
       <c r="E673" t="n">
-        <v>19.43256641096385</v>
+        <v>19.43256439855708</v>
       </c>
       <c r="F673" t="n">
         <v>684800</v>
@@ -13892,16 +13892,16 @@
         <v>44565</v>
       </c>
       <c r="B674" t="n">
-        <v>17.84088134765625</v>
+        <v>17.84087944030762</v>
       </c>
       <c r="C674" t="n">
-        <v>18.62797873527332</v>
+        <v>18.62797674377699</v>
       </c>
       <c r="D674" t="n">
-        <v>17.70969872773299</v>
+        <v>17.70969683440894</v>
       </c>
       <c r="E674" t="n">
-        <v>18.50554184575528</v>
+        <v>18.50553986734854</v>
       </c>
       <c r="F674" t="n">
         <v>701900</v>
@@ -13972,16 +13972,16 @@
         <v>44571</v>
       </c>
       <c r="B678" t="n">
-        <v>17.31614685058594</v>
+        <v>17.31614875793457</v>
       </c>
       <c r="C678" t="n">
-        <v>17.79715194914944</v>
+        <v>17.79715390948009</v>
       </c>
       <c r="D678" t="n">
-        <v>16.94883456378794</v>
+        <v>16.94883643067766</v>
       </c>
       <c r="E678" t="n">
-        <v>17.79715194914944</v>
+        <v>17.79715390948009</v>
       </c>
       <c r="F678" t="n">
         <v>513900</v>
@@ -14052,16 +14052,16 @@
         <v>44575</v>
       </c>
       <c r="B682" t="n">
-        <v>18.34812164306641</v>
+        <v>18.34811973571777</v>
       </c>
       <c r="C682" t="n">
-        <v>18.42683154695619</v>
+        <v>18.4268296314254</v>
       </c>
       <c r="D682" t="n">
-        <v>17.51729728923059</v>
+        <v>17.51729546824893</v>
       </c>
       <c r="E682" t="n">
-        <v>18.2781574693952</v>
+        <v>18.27815556931958</v>
       </c>
       <c r="F682" t="n">
         <v>846900</v>
@@ -14132,16 +14132,16 @@
         <v>44581</v>
       </c>
       <c r="B686" t="n">
-        <v>19.00403785705566</v>
+        <v>19.00403594970703</v>
       </c>
       <c r="C686" t="n">
-        <v>19.85235540459185</v>
+        <v>19.85235341210145</v>
       </c>
       <c r="D686" t="n">
-        <v>17.64848126248454</v>
+        <v>17.64847949118694</v>
       </c>
       <c r="E686" t="n">
-        <v>17.92833797867386</v>
+        <v>17.92833617928832</v>
       </c>
       <c r="F686" t="n">
         <v>1099700</v>
@@ -14192,16 +14192,16 @@
         <v>44586</v>
       </c>
       <c r="B689" t="n">
-        <v>19.97479248046875</v>
+        <v>19.97479057312012</v>
       </c>
       <c r="C689" t="n">
-        <v>20.10597510885206</v>
+        <v>20.10597318897709</v>
       </c>
       <c r="D689" t="n">
-        <v>18.89909259241693</v>
+        <v>18.8990907877845</v>
       </c>
       <c r="E689" t="n">
-        <v>19.10898513144576</v>
+        <v>19.10898330677115</v>
       </c>
       <c r="F689" t="n">
         <v>1099300</v>
@@ -14232,16 +14232,16 @@
         <v>44588</v>
       </c>
       <c r="B691" t="n">
-        <v>22.16117477416992</v>
+        <v>22.16117286682129</v>
       </c>
       <c r="C691" t="n">
-        <v>23.01823637651123</v>
+        <v>23.01823439539776</v>
       </c>
       <c r="D691" t="n">
-        <v>21.26913024859302</v>
+        <v>21.26912841802009</v>
       </c>
       <c r="E691" t="n">
-        <v>21.41780433618917</v>
+        <v>21.41780249282029</v>
       </c>
       <c r="F691" t="n">
         <v>1415400</v>
@@ -14252,16 +14252,16 @@
         <v>44589</v>
       </c>
       <c r="B692" t="n">
-        <v>22.21364402770996</v>
+        <v>22.21364593505859</v>
       </c>
       <c r="C692" t="n">
-        <v>22.38855528046314</v>
+        <v>22.38855720283032</v>
       </c>
       <c r="D692" t="n">
-        <v>21.40905526758453</v>
+        <v>21.40905710584809</v>
       </c>
       <c r="E692" t="n">
-        <v>21.85507746083554</v>
+        <v>21.85507933739627</v>
       </c>
       <c r="F692" t="n">
         <v>1167000</v>
@@ -14292,16 +14292,16 @@
         <v>44593</v>
       </c>
       <c r="B694" t="n">
-        <v>21.71515083312988</v>
+        <v>21.71514892578125</v>
       </c>
       <c r="C694" t="n">
-        <v>22.66841373261876</v>
+        <v>22.66841174154035</v>
       </c>
       <c r="D694" t="n">
-        <v>21.47902112377155</v>
+        <v>21.47901923716335</v>
       </c>
       <c r="E694" t="n">
-        <v>22.51973965651286</v>
+        <v>22.51973767849323</v>
       </c>
       <c r="F694" t="n">
         <v>1542100</v>
@@ -14372,16 +14372,16 @@
         <v>44599</v>
       </c>
       <c r="B698" t="n">
-        <v>19.82611656188965</v>
+        <v>19.82611465454102</v>
       </c>
       <c r="C698" t="n">
-        <v>20.61321392768527</v>
+        <v>20.61321194461484</v>
       </c>
       <c r="D698" t="n">
-        <v>19.52002267850317</v>
+        <v>19.52002080060194</v>
       </c>
       <c r="E698" t="n">
-        <v>20.00102782898977</v>
+        <v>20.001025904814</v>
       </c>
       <c r="F698" t="n">
         <v>648500</v>
@@ -14452,16 +14452,16 @@
         <v>44603</v>
       </c>
       <c r="B702" t="n">
-        <v>19.06525611877441</v>
+        <v>19.06525421142578</v>
       </c>
       <c r="C702" t="n">
-        <v>20.08848326988405</v>
+        <v>20.08848126016853</v>
       </c>
       <c r="D702" t="n">
-        <v>18.7591638809841</v>
+        <v>18.75916200425791</v>
       </c>
       <c r="E702" t="n">
-        <v>20.0097733607158</v>
+        <v>20.00977135887467</v>
       </c>
       <c r="F702" t="n">
         <v>2202700</v>
@@ -14532,16 +14532,16 @@
         <v>44609</v>
       </c>
       <c r="B706" t="n">
-        <v>19.78238868713379</v>
+        <v>19.78239059448242</v>
       </c>
       <c r="C706" t="n">
-        <v>20.91930686778672</v>
+        <v>20.91930888475303</v>
       </c>
       <c r="D706" t="n">
-        <v>19.78238868713379</v>
+        <v>19.78239059448242</v>
       </c>
       <c r="E706" t="n">
-        <v>20.38582902845644</v>
+        <v>20.38583099398668</v>
       </c>
       <c r="F706" t="n">
         <v>844900</v>
@@ -14552,16 +14552,16 @@
         <v>44610</v>
       </c>
       <c r="B707" t="n">
-        <v>19.70367813110352</v>
+        <v>19.70368003845215</v>
       </c>
       <c r="C707" t="n">
-        <v>20.11471740806482</v>
+        <v>20.11471935520274</v>
       </c>
       <c r="D707" t="n">
-        <v>19.42381979206722</v>
+        <v>19.4238216723251</v>
       </c>
       <c r="E707" t="n">
-        <v>20.00102626101675</v>
+        <v>20.00102819714917</v>
       </c>
       <c r="F707" t="n">
         <v>986100</v>
@@ -14572,16 +14572,16 @@
         <v>44613</v>
       </c>
       <c r="B708" t="n">
-        <v>18.92532539367676</v>
+        <v>18.92532730102539</v>
       </c>
       <c r="C708" t="n">
-        <v>19.6686957383062</v>
+        <v>19.66869772057383</v>
       </c>
       <c r="D708" t="n">
-        <v>18.71543288485386</v>
+        <v>18.71543477104893</v>
       </c>
       <c r="E708" t="n">
-        <v>19.31887489026805</v>
+        <v>19.31887683727973</v>
       </c>
       <c r="F708" t="n">
         <v>1006600</v>
@@ -14592,16 +14592,16 @@
         <v>44614</v>
       </c>
       <c r="B709" t="n">
-        <v>19.47629356384277</v>
+        <v>19.47629547119141</v>
       </c>
       <c r="C709" t="n">
-        <v>19.83486012087871</v>
+        <v>19.83486206334241</v>
       </c>
       <c r="D709" t="n">
-        <v>19.04776284124074</v>
+        <v>19.04776470662258</v>
       </c>
       <c r="E709" t="n">
-        <v>19.15270825555125</v>
+        <v>19.15271013121059</v>
       </c>
       <c r="F709" t="n">
         <v>681200</v>
@@ -14612,16 +14612,16 @@
         <v>44615</v>
       </c>
       <c r="B710" t="n">
-        <v>20.35959434509277</v>
+        <v>20.35959625244141</v>
       </c>
       <c r="C710" t="n">
-        <v>20.94554491906982</v>
+        <v>20.94554688131208</v>
       </c>
       <c r="D710" t="n">
-        <v>19.48504134919136</v>
+        <v>19.48504317460921</v>
       </c>
       <c r="E710" t="n">
-        <v>19.53751406188375</v>
+        <v>19.53751589221741</v>
       </c>
       <c r="F710" t="n">
         <v>2509600</v>
@@ -14632,16 +14632,16 @@
         <v>44616</v>
       </c>
       <c r="B711" t="n">
-        <v>20.42081260681152</v>
+        <v>20.42081451416016</v>
       </c>
       <c r="C711" t="n">
-        <v>20.61321366369564</v>
+        <v>20.61321558901495</v>
       </c>
       <c r="D711" t="n">
-        <v>19.02152749216333</v>
+        <v>19.02152926881567</v>
       </c>
       <c r="E711" t="n">
-        <v>19.85235349813248</v>
+        <v>19.85235535238579</v>
       </c>
       <c r="F711" t="n">
         <v>1354200</v>
@@ -14652,16 +14652,16 @@
         <v>44617</v>
       </c>
       <c r="B712" t="n">
-        <v>20.03600883483887</v>
+        <v>20.03600692749023</v>
       </c>
       <c r="C712" t="n">
-        <v>20.64819659407332</v>
+        <v>20.64819462844683</v>
       </c>
       <c r="D712" t="n">
-        <v>19.67744224296874</v>
+        <v>19.67744036975423</v>
       </c>
       <c r="E712" t="n">
-        <v>20.36833990462127</v>
+        <v>20.36833796563603</v>
       </c>
       <c r="F712" t="n">
         <v>1087600</v>
@@ -14752,16 +14752,16 @@
         <v>44628</v>
       </c>
       <c r="B717" t="n">
-        <v>17.54353332519531</v>
+        <v>17.54353141784668</v>
       </c>
       <c r="C717" t="n">
-        <v>18.19070236761176</v>
+        <v>18.19070038990233</v>
       </c>
       <c r="D717" t="n">
-        <v>16.87887282182983</v>
+        <v>16.87887098674368</v>
       </c>
       <c r="E717" t="n">
-        <v>17.66597188376101</v>
+        <v>17.66596996310075</v>
       </c>
       <c r="F717" t="n">
         <v>1340300</v>
@@ -14812,16 +14812,16 @@
         <v>44631</v>
       </c>
       <c r="B720" t="n">
-        <v>16.49407005310059</v>
+        <v>16.49407196044922</v>
       </c>
       <c r="C720" t="n">
-        <v>17.9983006070584</v>
+        <v>17.99830268835392</v>
       </c>
       <c r="D720" t="n">
-        <v>16.2054676308855</v>
+        <v>16.2054695048606</v>
       </c>
       <c r="E720" t="n">
-        <v>17.9983006070584</v>
+        <v>17.99830268835392</v>
       </c>
       <c r="F720" t="n">
         <v>1712100</v>
@@ -14872,16 +14872,16 @@
         <v>44636</v>
       </c>
       <c r="B723" t="n">
-        <v>16.80891036987305</v>
+        <v>16.80890846252441</v>
       </c>
       <c r="C723" t="n">
-        <v>17.17622274708315</v>
+        <v>17.17622079805467</v>
       </c>
       <c r="D723" t="n">
-        <v>16.25794263809674</v>
+        <v>16.25794079326778</v>
       </c>
       <c r="E723" t="n">
-        <v>16.68647346682891</v>
+        <v>16.6864715733735</v>
       </c>
       <c r="F723" t="n">
         <v>1316100</v>
@@ -14952,16 +14952,16 @@
         <v>44642</v>
       </c>
       <c r="B727" t="n">
-        <v>18.58424949645996</v>
+        <v>18.58425140380859</v>
       </c>
       <c r="C727" t="n">
-        <v>18.84661470447318</v>
+        <v>18.84661663874902</v>
       </c>
       <c r="D727" t="n">
-        <v>18.15571876706381</v>
+        <v>18.15572063043125</v>
       </c>
       <c r="E727" t="n">
-        <v>18.33062834971351</v>
+        <v>18.33063023103237</v>
       </c>
       <c r="F727" t="n">
         <v>1779700</v>
@@ -15052,16 +15052,16 @@
         <v>44649</v>
       </c>
       <c r="B732" t="n">
-        <v>22.21364402770996</v>
+        <v>22.21364593505859</v>
       </c>
       <c r="C732" t="n">
-        <v>22.25737267493692</v>
+        <v>22.25737458604026</v>
       </c>
       <c r="D732" t="n">
-        <v>20.70941359272647</v>
+        <v>20.70941537091611</v>
       </c>
       <c r="E732" t="n">
-        <v>20.8318504688073</v>
+        <v>20.83185225750984</v>
       </c>
       <c r="F732" t="n">
         <v>2430600</v>
@@ -15092,16 +15092,16 @@
         <v>44651</v>
       </c>
       <c r="B734" t="n">
-        <v>22.12618827819824</v>
+        <v>22.12619018554688</v>
       </c>
       <c r="C734" t="n">
-        <v>22.26611661239113</v>
+        <v>22.26611853180204</v>
       </c>
       <c r="D734" t="n">
-        <v>21.50525650372695</v>
+        <v>21.50525835754926</v>
       </c>
       <c r="E734" t="n">
-        <v>21.93378723570235</v>
+        <v>21.93378912646539</v>
       </c>
       <c r="F734" t="n">
         <v>1166300</v>
@@ -15112,16 +15112,16 @@
         <v>44652</v>
       </c>
       <c r="B735" t="n">
-        <v>23.50798416137695</v>
+        <v>23.50798225402832</v>
       </c>
       <c r="C735" t="n">
-        <v>23.62167698673521</v>
+        <v>23.62167507016197</v>
       </c>
       <c r="D735" t="n">
-        <v>22.02124504607528</v>
+        <v>22.02124325935501</v>
       </c>
       <c r="E735" t="n">
-        <v>22.35357445573077</v>
+        <v>22.35357264204656</v>
       </c>
       <c r="F735" t="n">
         <v>2217800</v>
@@ -15212,16 +15212,16 @@
         <v>44659</v>
       </c>
       <c r="B740" t="n">
-        <v>22.88705062866211</v>
+        <v>22.88705253601074</v>
       </c>
       <c r="C740" t="n">
-        <v>23.28934418253186</v>
+        <v>23.28934612340661</v>
       </c>
       <c r="D740" t="n">
-        <v>22.3535727986304</v>
+        <v>22.35357466152034</v>
       </c>
       <c r="E740" t="n">
-        <v>23.08819740559698</v>
+        <v>23.08819932970868</v>
       </c>
       <c r="F740" t="n">
         <v>1404400</v>
@@ -15292,16 +15292,16 @@
         <v>44665</v>
       </c>
       <c r="B744" t="n">
-        <v>22.88705062866211</v>
+        <v>22.88705253601074</v>
       </c>
       <c r="C744" t="n">
-        <v>23.29808991214781</v>
+        <v>23.29809185375142</v>
       </c>
       <c r="D744" t="n">
-        <v>22.51973832517882</v>
+        <v>22.51974020191658</v>
       </c>
       <c r="E744" t="n">
-        <v>22.78210354134801</v>
+        <v>22.78210543995062</v>
       </c>
       <c r="F744" t="n">
         <v>1181000</v>
@@ -15312,16 +15312,16 @@
         <v>44669</v>
       </c>
       <c r="B745" t="n">
-        <v>22.99199867248535</v>
+        <v>22.99200057983398</v>
       </c>
       <c r="C745" t="n">
-        <v>23.26310962954921</v>
+        <v>23.26311155938841</v>
       </c>
       <c r="D745" t="n">
-        <v>22.70339458738447</v>
+        <v>22.70339647079135</v>
       </c>
       <c r="E745" t="n">
-        <v>22.78210448912518</v>
+        <v>22.78210637906161</v>
       </c>
       <c r="F745" t="n">
         <v>878700</v>
@@ -15332,16 +15332,16 @@
         <v>44670</v>
       </c>
       <c r="B746" t="n">
-        <v>22.83458137512207</v>
+        <v>22.83457946777344</v>
       </c>
       <c r="C746" t="n">
-        <v>23.07070943818205</v>
+        <v>23.07070751110989</v>
       </c>
       <c r="D746" t="n">
-        <v>22.48475880984669</v>
+        <v>22.48475693171837</v>
       </c>
       <c r="E746" t="n">
-        <v>22.95701827212188</v>
+        <v>22.95701635454622</v>
       </c>
       <c r="F746" t="n">
         <v>1086700</v>
@@ -15372,16 +15372,16 @@
         <v>44673</v>
       </c>
       <c r="B748" t="n">
-        <v>21.4615306854248</v>
+        <v>21.46153259277344</v>
       </c>
       <c r="C748" t="n">
-        <v>22.49350178888535</v>
+        <v>22.49350378794825</v>
       </c>
       <c r="D748" t="n">
-        <v>21.44403922568545</v>
+        <v>21.44404113147957</v>
       </c>
       <c r="E748" t="n">
-        <v>22.09120822334474</v>
+        <v>22.09121018665465</v>
       </c>
       <c r="F748" t="n">
         <v>866400</v>
@@ -15412,16 +15412,16 @@
         <v>44677</v>
       </c>
       <c r="B750" t="n">
-        <v>21.29536437988281</v>
+        <v>21.29536628723145</v>
       </c>
       <c r="C750" t="n">
-        <v>22.39730128224088</v>
+        <v>22.397303288286</v>
       </c>
       <c r="D750" t="n">
-        <v>21.03299749756288</v>
+        <v>21.03299938141226</v>
       </c>
       <c r="E750" t="n">
-        <v>21.93378762446315</v>
+        <v>21.93378958899304</v>
       </c>
       <c r="F750" t="n">
         <v>740500</v>
@@ -15452,16 +15452,16 @@
         <v>44679</v>
       </c>
       <c r="B752" t="n">
-        <v>21.50525856018066</v>
+        <v>21.50525665283203</v>
       </c>
       <c r="C752" t="n">
-        <v>21.66267836822037</v>
+        <v>21.66267644690982</v>
       </c>
       <c r="D752" t="n">
-        <v>20.95428923204171</v>
+        <v>20.95428737355976</v>
       </c>
       <c r="E752" t="n">
-        <v>21.56647700373444</v>
+        <v>21.56647509095621</v>
       </c>
       <c r="F752" t="n">
         <v>769100</v>
@@ -15532,16 +15532,16 @@
         <v>44685</v>
       </c>
       <c r="B756" t="n">
-        <v>21.71626281738281</v>
+        <v>21.71626472473145</v>
       </c>
       <c r="C756" t="n">
-        <v>21.71626281738281</v>
+        <v>21.71626472473145</v>
       </c>
       <c r="D756" t="n">
-        <v>19.7388612330252</v>
+        <v>19.73886296669781</v>
       </c>
       <c r="E756" t="n">
-        <v>20.20464976524007</v>
+        <v>20.20465153982308</v>
       </c>
       <c r="F756" t="n">
         <v>1110100</v>
@@ -15612,16 +15612,16 @@
         <v>44691</v>
       </c>
       <c r="B760" t="n">
-        <v>20.08161163330078</v>
+        <v>20.08161354064941</v>
       </c>
       <c r="C760" t="n">
-        <v>20.38920776524142</v>
+        <v>20.38920970180549</v>
       </c>
       <c r="D760" t="n">
-        <v>19.202766499907</v>
+        <v>19.20276832378304</v>
       </c>
       <c r="E760" t="n">
-        <v>19.29943832472075</v>
+        <v>19.29944015777867</v>
       </c>
       <c r="F760" t="n">
         <v>949400</v>
@@ -15752,16 +15752,16 @@
         <v>44700</v>
       </c>
       <c r="B767" t="n">
-        <v>20.48588180541992</v>
+        <v>20.48587989807129</v>
       </c>
       <c r="C767" t="n">
-        <v>21.47897785225722</v>
+        <v>21.47897585244587</v>
       </c>
       <c r="D767" t="n">
-        <v>20.20465160052363</v>
+        <v>20.20464971935908</v>
       </c>
       <c r="E767" t="n">
-        <v>20.63528556130411</v>
+        <v>20.63528364004516</v>
       </c>
       <c r="F767" t="n">
         <v>1617100</v>
@@ -15792,16 +15792,16 @@
         <v>44704</v>
       </c>
       <c r="B769" t="n">
-        <v>21.10986328125</v>
+        <v>21.10986137390137</v>
       </c>
       <c r="C769" t="n">
-        <v>21.64595774322865</v>
+        <v>21.64595578744204</v>
       </c>
       <c r="D769" t="n">
-        <v>20.91651625367948</v>
+        <v>20.91651436380042</v>
       </c>
       <c r="E769" t="n">
-        <v>21.09228597396826</v>
+        <v>21.0922840682078</v>
       </c>
       <c r="F769" t="n">
         <v>807400</v>
@@ -15832,16 +15832,16 @@
         <v>44706</v>
       </c>
       <c r="B771" t="n">
-        <v>20.43314933776855</v>
+        <v>20.43315124511719</v>
       </c>
       <c r="C771" t="n">
-        <v>20.53861149126161</v>
+        <v>20.53861340845469</v>
       </c>
       <c r="D771" t="n">
-        <v>19.56309285744106</v>
+        <v>19.56309468357358</v>
       </c>
       <c r="E771" t="n">
-        <v>20.41557203280903</v>
+        <v>20.4155739385169</v>
       </c>
       <c r="F771" t="n">
         <v>1204100</v>
@@ -15912,16 +15912,16 @@
         <v>44712</v>
       </c>
       <c r="B775" t="n">
-        <v>21.1362247467041</v>
+        <v>21.13622665405273</v>
       </c>
       <c r="C775" t="n">
-        <v>21.68110946590977</v>
+        <v>21.6811114224292</v>
       </c>
       <c r="D775" t="n">
-        <v>20.90772648757637</v>
+        <v>20.90772837430515</v>
       </c>
       <c r="E775" t="n">
-        <v>21.2328982475948</v>
+        <v>21.23290016366732</v>
       </c>
       <c r="F775" t="n">
         <v>717400</v>
@@ -15992,16 +15992,16 @@
         <v>44718</v>
       </c>
       <c r="B779" t="n">
-        <v>21.1450138092041</v>
+        <v>21.14501190185547</v>
       </c>
       <c r="C779" t="n">
-        <v>22.16447404763528</v>
+        <v>22.16447204832804</v>
       </c>
       <c r="D779" t="n">
-        <v>20.91651386938138</v>
+        <v>20.91651198264418</v>
       </c>
       <c r="E779" t="n">
-        <v>22.16447404763528</v>
+        <v>22.16447204832804</v>
       </c>
       <c r="F779" t="n">
         <v>518800</v>
@@ -16112,16 +16112,16 @@
         <v>44726</v>
       </c>
       <c r="B785" t="n">
-        <v>18.07784271240234</v>
+        <v>18.07784461975098</v>
       </c>
       <c r="C785" t="n">
-        <v>18.83365000443733</v>
+        <v>18.83365199152933</v>
       </c>
       <c r="D785" t="n">
-        <v>17.831767167099</v>
+        <v>17.83176904848481</v>
       </c>
       <c r="E785" t="n">
-        <v>18.55241985193983</v>
+        <v>18.55242180935992</v>
       </c>
       <c r="F785" t="n">
         <v>1231100</v>
@@ -16172,16 +16172,16 @@
         <v>44732</v>
       </c>
       <c r="B788" t="n">
-        <v>17.84055709838867</v>
+        <v>17.84055519104004</v>
       </c>
       <c r="C788" t="n">
-        <v>18.47332672260683</v>
+        <v>18.47332474760827</v>
       </c>
       <c r="D788" t="n">
-        <v>17.47144204301615</v>
+        <v>17.47144017512991</v>
       </c>
       <c r="E788" t="n">
-        <v>18.10421166723431</v>
+        <v>18.10420973169815</v>
       </c>
       <c r="F788" t="n">
         <v>715300</v>
@@ -16192,16 +16192,16 @@
         <v>44733</v>
       </c>
       <c r="B789" t="n">
-        <v>17.67357635498047</v>
+        <v>17.6735782623291</v>
       </c>
       <c r="C789" t="n">
-        <v>18.16572916550731</v>
+        <v>18.16573112596953</v>
       </c>
       <c r="D789" t="n">
-        <v>17.39234617753656</v>
+        <v>17.39234805453457</v>
       </c>
       <c r="E789" t="n">
-        <v>17.90207629321966</v>
+        <v>17.90207822522822</v>
       </c>
       <c r="F789" t="n">
         <v>1258800</v>
@@ -16232,16 +16232,16 @@
         <v>44735</v>
       </c>
       <c r="B791" t="n">
-        <v>17.84055709838867</v>
+        <v>17.84055519104004</v>
       </c>
       <c r="C791" t="n">
-        <v>18.20088350050658</v>
+        <v>18.20088155463516</v>
       </c>
       <c r="D791" t="n">
-        <v>17.43628910626192</v>
+        <v>17.43628724213392</v>
       </c>
       <c r="E791" t="n">
-        <v>17.84055709838867</v>
+        <v>17.84055519104004</v>
       </c>
       <c r="F791" t="n">
         <v>3238200</v>
@@ -16252,16 +16252,16 @@
         <v>44736</v>
       </c>
       <c r="B792" t="n">
-        <v>17.4099235534668</v>
+        <v>17.40992164611816</v>
       </c>
       <c r="C792" t="n">
-        <v>18.17451964184861</v>
+        <v>18.17451765073446</v>
       </c>
       <c r="D792" t="n">
-        <v>17.21657820613845</v>
+        <v>17.21657631997182</v>
       </c>
       <c r="E792" t="n">
-        <v>17.98996127171607</v>
+        <v>17.98995930082126</v>
       </c>
       <c r="F792" t="n">
         <v>1906300</v>
@@ -16312,16 +16312,16 @@
         <v>44741</v>
       </c>
       <c r="B795" t="n">
-        <v>16.80352210998535</v>
+        <v>16.80352020263672</v>
       </c>
       <c r="C795" t="n">
-        <v>17.08475232500363</v>
+        <v>17.08475038573288</v>
       </c>
       <c r="D795" t="n">
-        <v>16.44319401119584</v>
+        <v>16.44319214474763</v>
       </c>
       <c r="E795" t="n">
-        <v>16.84746370248284</v>
+        <v>16.84746179014645</v>
       </c>
       <c r="F795" t="n">
         <v>1315700</v>
@@ -16332,16 +16332,16 @@
         <v>44742</v>
       </c>
       <c r="B796" t="n">
-        <v>16.63653945922852</v>
+        <v>16.63654136657715</v>
       </c>
       <c r="C796" t="n">
-        <v>17.06717339455875</v>
+        <v>17.06717535127876</v>
       </c>
       <c r="D796" t="n">
-        <v>16.39925085927182</v>
+        <v>16.39925273941575</v>
       </c>
       <c r="E796" t="n">
-        <v>16.56623191215958</v>
+        <v>16.56623381144759</v>
       </c>
       <c r="F796" t="n">
         <v>1355100</v>
@@ -16372,16 +16372,16 @@
         <v>44746</v>
       </c>
       <c r="B798" t="n">
-        <v>16.20590400695801</v>
+        <v>16.20590591430664</v>
       </c>
       <c r="C798" t="n">
-        <v>16.78594163504879</v>
+        <v>16.78594361066477</v>
       </c>
       <c r="D798" t="n">
-        <v>16.1180191622822</v>
+        <v>16.11802105928725</v>
       </c>
       <c r="E798" t="n">
-        <v>16.4519795605335</v>
+        <v>16.45198149684391</v>
       </c>
       <c r="F798" t="n">
         <v>455600</v>
@@ -16392,16 +16392,16 @@
         <v>44747</v>
       </c>
       <c r="B799" t="n">
-        <v>16.43440628051758</v>
+        <v>16.43440437316895</v>
       </c>
       <c r="C799" t="n">
-        <v>16.4871365243508</v>
+        <v>16.48713461088238</v>
       </c>
       <c r="D799" t="n">
-        <v>15.51161779398297</v>
+        <v>15.51161599373157</v>
       </c>
       <c r="E799" t="n">
-        <v>15.99498367062421</v>
+        <v>15.9949818142742</v>
       </c>
       <c r="F799" t="n">
         <v>1135600</v>
@@ -16532,16 +16532,16 @@
         <v>44756</v>
       </c>
       <c r="B806" t="n">
-        <v>16.81230735778809</v>
+        <v>16.81230545043945</v>
       </c>
       <c r="C806" t="n">
-        <v>17.31325051254866</v>
+        <v>17.31324854836826</v>
       </c>
       <c r="D806" t="n">
-        <v>16.81230735778809</v>
+        <v>16.81230545043945</v>
       </c>
       <c r="E806" t="n">
-        <v>17.13748080811364</v>
+        <v>17.13747886387423</v>
       </c>
       <c r="F806" t="n">
         <v>1103500</v>
@@ -16552,16 +16552,16 @@
         <v>44757</v>
       </c>
       <c r="B807" t="n">
-        <v>16.52228927612305</v>
+        <v>16.52228736877441</v>
       </c>
       <c r="C807" t="n">
-        <v>17.09354000358701</v>
+        <v>17.09353803029265</v>
       </c>
       <c r="D807" t="n">
-        <v>16.28500234340354</v>
+        <v>16.28500046344753</v>
       </c>
       <c r="E807" t="n">
-        <v>17.07596269708505</v>
+        <v>17.07596072581984</v>
       </c>
       <c r="F807" t="n">
         <v>1251500</v>
@@ -16712,16 +16712,16 @@
         <v>44769</v>
       </c>
       <c r="B815" t="n">
-        <v>18.13057518005371</v>
+        <v>18.13057327270508</v>
       </c>
       <c r="C815" t="n">
-        <v>18.13057518005371</v>
+        <v>18.13057327270508</v>
       </c>
       <c r="D815" t="n">
-        <v>17.27809596576369</v>
+        <v>17.27809414809644</v>
       </c>
       <c r="E815" t="n">
-        <v>17.33082620678572</v>
+        <v>17.33082438357121</v>
       </c>
       <c r="F815" t="n">
         <v>961700</v>
@@ -16792,16 +16792,16 @@
         <v>44775</v>
       </c>
       <c r="B819" t="n">
-        <v>18.06026840209961</v>
+        <v>18.06026649475098</v>
       </c>
       <c r="C819" t="n">
-        <v>19.1148833250202</v>
+        <v>19.11488130629347</v>
       </c>
       <c r="D819" t="n">
-        <v>17.77024954973608</v>
+        <v>17.7702476730164</v>
       </c>
       <c r="E819" t="n">
-        <v>19.06215308175343</v>
+        <v>19.06215106859556</v>
       </c>
       <c r="F819" t="n">
         <v>3204200</v>
@@ -16832,16 +16832,16 @@
         <v>44777</v>
       </c>
       <c r="B821" t="n">
-        <v>20.17828559875488</v>
+        <v>20.17828750610352</v>
       </c>
       <c r="C821" t="n">
-        <v>21.10107409247204</v>
+        <v>21.10107608704708</v>
       </c>
       <c r="D821" t="n">
-        <v>18.82486482140632</v>
+        <v>18.82486660082311</v>
       </c>
       <c r="E821" t="n">
-        <v>18.8336534748243</v>
+        <v>18.83365525507184</v>
       </c>
       <c r="F821" t="n">
         <v>3708400</v>
@@ -16952,16 +16952,16 @@
         <v>44785</v>
       </c>
       <c r="B827" t="n">
-        <v>19.87947845458984</v>
+        <v>19.87948036193848</v>
       </c>
       <c r="C827" t="n">
-        <v>19.98493893613145</v>
+        <v>19.98494085359855</v>
       </c>
       <c r="D827" t="n">
-        <v>19.39611260602109</v>
+        <v>19.39611446699289</v>
       </c>
       <c r="E827" t="n">
-        <v>19.39611260602109</v>
+        <v>19.39611446699289</v>
       </c>
       <c r="F827" t="n">
         <v>1366700</v>
@@ -17012,16 +17012,16 @@
         <v>44790</v>
       </c>
       <c r="B830" t="n">
-        <v>20.35405540466309</v>
+        <v>20.35405349731445</v>
       </c>
       <c r="C830" t="n">
-        <v>20.60013267266286</v>
+        <v>20.60013074225469</v>
       </c>
       <c r="D830" t="n">
-        <v>19.94978740323229</v>
+        <v>19.94978553376702</v>
       </c>
       <c r="E830" t="n">
-        <v>20.2573818929017</v>
+        <v>20.2573799946122</v>
       </c>
       <c r="F830" t="n">
         <v>979500</v>
@@ -17032,16 +17032,16 @@
         <v>44791</v>
       </c>
       <c r="B831" t="n">
-        <v>19.92341995239258</v>
+        <v>19.92341804504395</v>
       </c>
       <c r="C831" t="n">
-        <v>20.51224627983922</v>
+        <v>20.51224431611989</v>
       </c>
       <c r="D831" t="n">
-        <v>19.67734270280182</v>
+        <v>19.67734081901114</v>
       </c>
       <c r="E831" t="n">
-        <v>20.51224627983922</v>
+        <v>20.51224431611989</v>
       </c>
       <c r="F831" t="n">
         <v>1397000</v>
@@ -17092,16 +17092,16 @@
         <v>44796</v>
       </c>
       <c r="B834" t="n">
-        <v>18.06026840209961</v>
+        <v>18.06026649475098</v>
       </c>
       <c r="C834" t="n">
-        <v>18.23603811467444</v>
+        <v>18.23603618876274</v>
       </c>
       <c r="D834" t="n">
-        <v>17.52417396364836</v>
+        <v>17.52417211291677</v>
       </c>
       <c r="E834" t="n">
-        <v>17.65600040994738</v>
+        <v>17.65599854529357</v>
       </c>
       <c r="F834" t="n">
         <v>3245100</v>
@@ -17112,16 +17112,16 @@
         <v>44797</v>
       </c>
       <c r="B835" t="n">
-        <v>18.54363441467285</v>
+        <v>18.54363250732422</v>
       </c>
       <c r="C835" t="n">
-        <v>18.91274947287775</v>
+        <v>18.91274752756293</v>
       </c>
       <c r="D835" t="n">
-        <v>17.85813454193111</v>
+        <v>17.85813270509117</v>
       </c>
       <c r="E835" t="n">
-        <v>18.08663449951169</v>
+        <v>18.08663263916885</v>
       </c>
       <c r="F835" t="n">
         <v>3184700</v>
@@ -17152,16 +17152,16 @@
         <v>44799</v>
       </c>
       <c r="B837" t="n">
-        <v>19.11488151550293</v>
+        <v>19.11488342285156</v>
       </c>
       <c r="C837" t="n">
-        <v>19.23791929689937</v>
+        <v>19.23792121652514</v>
       </c>
       <c r="D837" t="n">
-        <v>18.54363251810853</v>
+        <v>18.54363436845597</v>
       </c>
       <c r="E837" t="n">
-        <v>18.80728538574777</v>
+        <v>18.80728726240341</v>
       </c>
       <c r="F837" t="n">
         <v>1224800</v>
@@ -17172,16 +17172,16 @@
         <v>44802</v>
       </c>
       <c r="B838" t="n">
-        <v>19.64219093322754</v>
+        <v>19.64218902587891</v>
       </c>
       <c r="C838" t="n">
-        <v>20.02009464470181</v>
+        <v>20.02009270065696</v>
       </c>
       <c r="D838" t="n">
-        <v>18.72819110303263</v>
+        <v>18.72818928443765</v>
       </c>
       <c r="E838" t="n">
-        <v>18.974268367223</v>
+        <v>18.97426652473278</v>
       </c>
       <c r="F838" t="n">
         <v>1940700</v>
@@ -17312,16 +17312,16 @@
         <v>44812</v>
       </c>
       <c r="B845" t="n">
-        <v>20.39799499511719</v>
+        <v>20.39799690246582</v>
       </c>
       <c r="C845" t="n">
-        <v>20.43314960549685</v>
+        <v>20.43315151613267</v>
       </c>
       <c r="D845" t="n">
-        <v>19.79159305244484</v>
+        <v>19.79159490309085</v>
       </c>
       <c r="E845" t="n">
-        <v>19.91463083624548</v>
+        <v>19.91463269839634</v>
       </c>
       <c r="F845" t="n">
         <v>1389900</v>
@@ -17512,16 +17512,16 @@
         <v>44826</v>
       </c>
       <c r="B855" t="n">
-        <v>20.91651344299316</v>
+        <v>20.9165153503418</v>
       </c>
       <c r="C855" t="n">
-        <v>21.07470583474289</v>
+        <v>21.07470775651687</v>
       </c>
       <c r="D855" t="n">
-        <v>19.79159274835349</v>
+        <v>19.79159455312212</v>
       </c>
       <c r="E855" t="n">
-        <v>20.31890016209787</v>
+        <v>20.31890201495095</v>
       </c>
       <c r="F855" t="n">
         <v>1592700</v>
@@ -17532,16 +17532,16 @@
         <v>44827</v>
       </c>
       <c r="B856" t="n">
-        <v>20.15191841125488</v>
+        <v>20.15192031860352</v>
       </c>
       <c r="C856" t="n">
-        <v>20.61770524144714</v>
+        <v>20.61770719288179</v>
       </c>
       <c r="D856" t="n">
-        <v>19.95857141644542</v>
+        <v>19.95857330549405</v>
       </c>
       <c r="E856" t="n">
-        <v>20.4858788116996</v>
+        <v>20.48588075065707</v>
       </c>
       <c r="F856" t="n">
         <v>1009700</v>
@@ -17632,16 +17632,16 @@
         <v>44834</v>
       </c>
       <c r="B861" t="n">
-        <v>17.67357635498047</v>
+        <v>17.6735782623291</v>
       </c>
       <c r="C861" t="n">
-        <v>17.98117081389469</v>
+        <v>17.9811727544392</v>
       </c>
       <c r="D861" t="n">
-        <v>17.00565384541915</v>
+        <v>17.00565568068497</v>
       </c>
       <c r="E861" t="n">
-        <v>17.12869162898484</v>
+        <v>17.12869347752901</v>
       </c>
       <c r="F861" t="n">
         <v>2723400</v>
@@ -17672,16 +17672,16 @@
         <v>44838</v>
       </c>
       <c r="B863" t="n">
-        <v>18.77213287353516</v>
+        <v>18.77213478088379</v>
       </c>
       <c r="C863" t="n">
-        <v>19.56309317046481</v>
+        <v>19.56309515817922</v>
       </c>
       <c r="D863" t="n">
-        <v>18.6227291315168</v>
+        <v>18.62273102368521</v>
       </c>
       <c r="E863" t="n">
-        <v>19.07972733392818</v>
+        <v>19.07972927253005</v>
       </c>
       <c r="F863" t="n">
         <v>1360700</v>
@@ -17732,16 +17732,16 @@
         <v>44841</v>
       </c>
       <c r="B866" t="n">
-        <v>17.47144317626953</v>
+        <v>17.4714412689209</v>
       </c>
       <c r="C866" t="n">
-        <v>18.50848085988</v>
+        <v>18.50847883931848</v>
       </c>
       <c r="D866" t="n">
-        <v>17.41871292958584</v>
+        <v>17.41871102799374</v>
       </c>
       <c r="E866" t="n">
-        <v>18.44696195937163</v>
+        <v>18.44695994552611</v>
       </c>
       <c r="F866" t="n">
         <v>1871900</v>
@@ -17812,16 +17812,16 @@
         <v>44848</v>
       </c>
       <c r="B870" t="n">
-        <v>16.63653945922852</v>
+        <v>16.63654136657715</v>
       </c>
       <c r="C870" t="n">
-        <v>17.56811487695791</v>
+        <v>17.56811689110994</v>
       </c>
       <c r="D870" t="n">
-        <v>16.52228864757641</v>
+        <v>16.5222905418264</v>
       </c>
       <c r="E870" t="n">
-        <v>17.40992247698677</v>
+        <v>17.40992447300235</v>
       </c>
       <c r="F870" t="n">
         <v>1935700</v>
@@ -17972,16 +17972,16 @@
         <v>44860</v>
       </c>
       <c r="B878" t="n">
-        <v>15.21281051635742</v>
+        <v>15.21280956268311</v>
       </c>
       <c r="C878" t="n">
-        <v>16.0652914653156</v>
+        <v>16.06529045820019</v>
       </c>
       <c r="D878" t="n">
-        <v>15.11613868057135</v>
+        <v>15.11613773295728</v>
       </c>
       <c r="E878" t="n">
-        <v>15.96861795326526</v>
+        <v>15.96861695221021</v>
       </c>
       <c r="F878" t="n">
         <v>1638200</v>
@@ -18012,16 +18012,16 @@
         <v>44862</v>
       </c>
       <c r="B880" t="n">
-        <v>15.94225215911865</v>
+        <v>15.94225025177002</v>
       </c>
       <c r="C880" t="n">
-        <v>16.22348236845592</v>
+        <v>16.22348042746059</v>
       </c>
       <c r="D880" t="n">
-        <v>15.5379841522624</v>
+        <v>15.53798229328084</v>
       </c>
       <c r="E880" t="n">
-        <v>15.65223329620656</v>
+        <v>15.65223142355611</v>
       </c>
       <c r="F880" t="n">
         <v>1750700</v>
@@ -18212,16 +18212,16 @@
         <v>44879</v>
       </c>
       <c r="B890" t="n">
-        <v>14.56246471405029</v>
+        <v>14.56246376037598</v>
       </c>
       <c r="C890" t="n">
-        <v>14.94036841872623</v>
+        <v>14.94036744030356</v>
       </c>
       <c r="D890" t="n">
-        <v>14.12304211349952</v>
+        <v>14.12304118860234</v>
       </c>
       <c r="E890" t="n">
-        <v>14.32517610744947</v>
+        <v>14.32517516931483</v>
       </c>
       <c r="F890" t="n">
         <v>1798400</v>
@@ -18232,16 +18232,16 @@
         <v>44881</v>
       </c>
       <c r="B891" t="n">
-        <v>13.55179214477539</v>
+        <v>13.55179119110107</v>
       </c>
       <c r="C891" t="n">
-        <v>14.57125237449792</v>
+        <v>14.57125134908158</v>
       </c>
       <c r="D891" t="n">
-        <v>13.40238840371619</v>
+        <v>13.4023874605558</v>
       </c>
       <c r="E891" t="n">
-        <v>14.56246372193396</v>
+        <v>14.5624626971361</v>
       </c>
       <c r="F891" t="n">
         <v>2598100</v>
@@ -18292,16 +18292,16 @@
         <v>44886</v>
       </c>
       <c r="B894" t="n">
-        <v>13.67483234405518</v>
+        <v>13.67483139038086</v>
       </c>
       <c r="C894" t="n">
-        <v>13.85060122495416</v>
+        <v>13.85060025902183</v>
       </c>
       <c r="D894" t="n">
-        <v>13.12994755607012</v>
+        <v>13.12994664039573</v>
       </c>
       <c r="E894" t="n">
-        <v>13.25298619176548</v>
+        <v>13.25298526751045</v>
       </c>
       <c r="F894" t="n">
         <v>1078200</v>
@@ -18392,16 +18392,16 @@
         <v>44893</v>
       </c>
       <c r="B899" t="n">
-        <v>12.83113956451416</v>
+        <v>12.83114051818848</v>
       </c>
       <c r="C899" t="n">
-        <v>13.45511965644873</v>
+        <v>13.45512065650036</v>
       </c>
       <c r="D899" t="n">
-        <v>12.78719713925329</v>
+        <v>12.78719808966159</v>
       </c>
       <c r="E899" t="n">
-        <v>13.24419618282298</v>
+        <v>13.24419716719772</v>
       </c>
       <c r="F899" t="n">
         <v>874000</v>
@@ -18552,16 +18552,16 @@
         <v>44903</v>
       </c>
       <c r="B907" t="n">
-        <v>11.08223628997803</v>
+        <v>11.08223724365234</v>
       </c>
       <c r="C907" t="n">
-        <v>11.36346728888048</v>
+        <v>11.36346826675594</v>
       </c>
       <c r="D907" t="n">
-        <v>10.91525609155356</v>
+        <v>10.91525703085851</v>
       </c>
       <c r="E907" t="n">
-        <v>11.28437109663079</v>
+        <v>11.28437206769968</v>
       </c>
       <c r="F907" t="n">
         <v>2262600</v>
@@ -18572,16 +18572,16 @@
         <v>44904</v>
       </c>
       <c r="B908" t="n">
-        <v>10.65160369873047</v>
+        <v>10.65160274505615</v>
       </c>
       <c r="C908" t="n">
-        <v>11.18769896776008</v>
+        <v>11.18769796608733</v>
       </c>
       <c r="D908" t="n">
-        <v>10.55493102868214</v>
+        <v>10.55493008366326</v>
       </c>
       <c r="E908" t="n">
-        <v>11.0470838701872</v>
+        <v>11.0470828811042</v>
       </c>
       <c r="F908" t="n">
         <v>1248000</v>
@@ -18692,16 +18692,16 @@
         <v>44914</v>
       </c>
       <c r="B914" t="n">
-        <v>10.22975730895996</v>
+        <v>10.22975826263428</v>
       </c>
       <c r="C914" t="n">
-        <v>10.33521862082982</v>
+        <v>10.33521958433582</v>
       </c>
       <c r="D914" t="n">
-        <v>9.421219746492405</v>
+        <v>9.421220624790395</v>
       </c>
       <c r="E914" t="n">
-        <v>9.421219746492405</v>
+        <v>9.421220624790395</v>
       </c>
       <c r="F914" t="n">
         <v>2225500</v>
@@ -18732,16 +18732,16 @@
         <v>44916</v>
       </c>
       <c r="B916" t="n">
-        <v>10.95040988922119</v>
+        <v>10.95041084289551</v>
       </c>
       <c r="C916" t="n">
-        <v>11.58317859067994</v>
+        <v>11.58317959946226</v>
       </c>
       <c r="D916" t="n">
-        <v>10.7834296903763</v>
+        <v>10.78343062950826</v>
       </c>
       <c r="E916" t="n">
-        <v>11.42498620578225</v>
+        <v>11.42498720078756</v>
       </c>
       <c r="F916" t="n">
         <v>3646500</v>
@@ -18752,16 +18752,16 @@
         <v>44917</v>
       </c>
       <c r="B917" t="n">
-        <v>11.32831478118896</v>
+        <v>11.32831573486328</v>
       </c>
       <c r="C917" t="n">
-        <v>11.39862232921651</v>
+        <v>11.39862328880967</v>
       </c>
       <c r="D917" t="n">
-        <v>10.80979598588673</v>
+        <v>10.80979689590953</v>
       </c>
       <c r="E917" t="n">
-        <v>10.95919973497829</v>
+        <v>10.95920065757865</v>
       </c>
       <c r="F917" t="n">
         <v>1785900</v>
@@ -18832,16 +18832,16 @@
         <v>44923</v>
       </c>
       <c r="B921" t="n">
-        <v>11.22285270690918</v>
+        <v>11.2228536605835</v>
       </c>
       <c r="C921" t="n">
-        <v>11.53044799937938</v>
+        <v>11.53044897919194</v>
       </c>
       <c r="D921" t="n">
-        <v>10.97677546717459</v>
+        <v>10.97677639993822</v>
       </c>
       <c r="E921" t="n">
-        <v>11.12617920625201</v>
+        <v>11.12618015171139</v>
       </c>
       <c r="F921" t="n">
         <v>1106200</v>
@@ -18912,16 +18912,16 @@
         <v>44930</v>
       </c>
       <c r="B925" t="n">
-        <v>10.18581485748291</v>
+        <v>10.18581581115723</v>
       </c>
       <c r="C925" t="n">
-        <v>10.3527950579406</v>
+        <v>10.35279602724888</v>
       </c>
       <c r="D925" t="n">
-        <v>9.89579604112398</v>
+        <v>9.895796967644506</v>
       </c>
       <c r="E925" t="n">
-        <v>10.00125735269705</v>
+        <v>10.00125828909167</v>
       </c>
       <c r="F925" t="n">
         <v>928500</v>
@@ -18972,16 +18972,16 @@
         <v>44935</v>
       </c>
       <c r="B928" t="n">
-        <v>10.28248977661133</v>
+        <v>10.28248882293701</v>
       </c>
       <c r="C928" t="n">
-        <v>10.73948973199201</v>
+        <v>10.73948873593213</v>
       </c>
       <c r="D928" t="n">
-        <v>10.08914357717087</v>
+        <v>10.08914264142891</v>
       </c>
       <c r="E928" t="n">
-        <v>10.53735487845604</v>
+        <v>10.53735390114364</v>
       </c>
       <c r="F928" t="n">
         <v>2217200</v>
@@ -19032,16 +19032,16 @@
         <v>44938</v>
       </c>
       <c r="B931" t="n">
-        <v>9.667296409606934</v>
+        <v>9.66729736328125</v>
       </c>
       <c r="C931" t="n">
-        <v>10.12429627854627</v>
+        <v>10.12429727730341</v>
       </c>
       <c r="D931" t="n">
-        <v>9.412431355969849</v>
+        <v>9.412432284501847</v>
       </c>
       <c r="E931" t="n">
-        <v>10.06277654964627</v>
+        <v>10.06277754233452</v>
       </c>
       <c r="F931" t="n">
         <v>3972100</v>
@@ -19092,16 +19092,16 @@
         <v>44943</v>
       </c>
       <c r="B934" t="n">
-        <v>9.526680946350098</v>
+        <v>9.526681900024414</v>
       </c>
       <c r="C934" t="n">
-        <v>9.640930909065455</v>
+        <v>9.640931874176834</v>
       </c>
       <c r="D934" t="n">
-        <v>9.271815902794916</v>
+        <v>9.271816830955808</v>
       </c>
       <c r="E934" t="n">
-        <v>9.421219635720229</v>
+        <v>9.421220578837275</v>
       </c>
       <c r="F934" t="n">
         <v>2424500</v>
@@ -19172,16 +19172,16 @@
         <v>44949</v>
       </c>
       <c r="B938" t="n">
-        <v>9.421219825744629</v>
+        <v>9.421220779418945</v>
       </c>
       <c r="C938" t="n">
-        <v>9.614565146733135</v>
+        <v>9.614566119979063</v>
       </c>
       <c r="D938" t="n">
-        <v>9.30696986072487</v>
+        <v>9.306970802834096</v>
       </c>
       <c r="E938" t="n">
-        <v>9.412431173481876</v>
+        <v>9.41243212626655</v>
       </c>
       <c r="F938" t="n">
         <v>1364300</v>
@@ -19252,16 +19252,16 @@
         <v>44953</v>
       </c>
       <c r="B942" t="n">
-        <v>9.79912281036377</v>
+        <v>9.799123764038086</v>
       </c>
       <c r="C942" t="n">
-        <v>9.94852654869279</v>
+        <v>9.94852751690744</v>
       </c>
       <c r="D942" t="n">
-        <v>9.535469943319168</v>
+        <v>9.53547087133415</v>
       </c>
       <c r="E942" t="n">
-        <v>9.82548876757385</v>
+        <v>9.825489723814165</v>
       </c>
       <c r="F942" t="n">
         <v>1116000</v>
@@ -19272,16 +19272,16 @@
         <v>44956</v>
       </c>
       <c r="B943" t="n">
-        <v>9.526680946350098</v>
+        <v>9.526681900024414</v>
       </c>
       <c r="C943" t="n">
-        <v>10.07156480367042</v>
+        <v>10.07156581189067</v>
       </c>
       <c r="D943" t="n">
-        <v>9.438796101759211</v>
+        <v>9.438797046635759</v>
       </c>
       <c r="E943" t="n">
-        <v>9.746392219695323</v>
+        <v>9.746393195363973</v>
       </c>
       <c r="F943" t="n">
         <v>1135100</v>
@@ -19332,16 +19332,16 @@
         <v>44959</v>
       </c>
       <c r="B946" t="n">
-        <v>9.605777740478516</v>
+        <v>9.605778694152832</v>
       </c>
       <c r="C946" t="n">
-        <v>9.851854147360314</v>
+        <v>9.85185512546542</v>
       </c>
       <c r="D946" t="n">
-        <v>9.465162650831775</v>
+        <v>9.465163590545639</v>
       </c>
       <c r="E946" t="n">
-        <v>9.482739117971594</v>
+        <v>9.482740059430473</v>
       </c>
       <c r="F946" t="n">
         <v>2651600</v>
@@ -19392,16 +19392,16 @@
         <v>44964</v>
       </c>
       <c r="B949" t="n">
-        <v>7.971126079559326</v>
+        <v>7.97112512588501</v>
       </c>
       <c r="C949" t="n">
-        <v>8.709356217201787</v>
+        <v>8.7093551752048</v>
       </c>
       <c r="D949" t="n">
-        <v>7.971126079559327</v>
+        <v>7.97112512588501</v>
       </c>
       <c r="E949" t="n">
-        <v>8.63904866486747</v>
+        <v>8.639047631282157</v>
       </c>
       <c r="F949" t="n">
         <v>4130600</v>
@@ -19432,16 +19432,16 @@
         <v>44966</v>
       </c>
       <c r="B951" t="n">
-        <v>7.575645923614502</v>
+        <v>7.575644969940186</v>
       </c>
       <c r="C951" t="n">
-        <v>8.076587445874921</v>
+        <v>8.076586429138645</v>
       </c>
       <c r="D951" t="n">
-        <v>7.531703493666784</v>
+        <v>7.531702545524242</v>
       </c>
       <c r="E951" t="n">
-        <v>7.988703424111625</v>
+        <v>7.988702418438795</v>
       </c>
       <c r="F951" t="n">
         <v>2053700</v>
@@ -19472,16 +19472,16 @@
         <v>44970</v>
       </c>
       <c r="B953" t="n">
-        <v>7.522914886474609</v>
+        <v>7.522915363311768</v>
       </c>
       <c r="C953" t="n">
-        <v>7.645952671621207</v>
+        <v>7.64595315625707</v>
       </c>
       <c r="D953" t="n">
-        <v>7.232895214594074</v>
+        <v>7.232895673048444</v>
       </c>
       <c r="E953" t="n">
-        <v>7.566856473665793</v>
+        <v>7.566856953288173</v>
       </c>
       <c r="F953" t="n">
         <v>2712600</v>
@@ -19652,16 +19652,16 @@
         <v>44985</v>
       </c>
       <c r="B962" t="n">
-        <v>7.206530094146729</v>
+        <v>7.206530570983887</v>
       </c>
       <c r="C962" t="n">
-        <v>7.689895096404264</v>
+        <v>7.689895605224415</v>
       </c>
       <c r="D962" t="n">
-        <v>7.18016497420746</v>
+        <v>7.180165449300108</v>
       </c>
       <c r="E962" t="n">
-        <v>7.628376203835287</v>
+        <v>7.628376708584893</v>
       </c>
       <c r="F962" t="n">
         <v>2084200</v>
@@ -19712,16 +19712,16 @@
         <v>44988</v>
       </c>
       <c r="B965" t="n">
-        <v>6.767107963562012</v>
+        <v>6.767107486724854</v>
       </c>
       <c r="C965" t="n">
-        <v>7.215319222753471</v>
+        <v>7.215318714333577</v>
       </c>
       <c r="D965" t="n">
-        <v>6.591339088819902</v>
+        <v>6.591338624368113</v>
       </c>
       <c r="E965" t="n">
-        <v>7.215319222753471</v>
+        <v>7.215318714333577</v>
       </c>
       <c r="F965" t="n">
         <v>7336400</v>
@@ -19752,16 +19752,16 @@
         <v>44992</v>
       </c>
       <c r="B967" t="n">
-        <v>7.4877610206604</v>
+        <v>7.487761497497559</v>
       </c>
       <c r="C967" t="n">
-        <v>7.64595257647055</v>
+        <v>7.645953063381696</v>
       </c>
       <c r="D967" t="n">
-        <v>7.276837549360133</v>
+        <v>7.27683801276522</v>
       </c>
       <c r="E967" t="n">
-        <v>7.329568626718211</v>
+        <v>7.329569093481328</v>
       </c>
       <c r="F967" t="n">
         <v>1239000</v>
@@ -19832,16 +19832,16 @@
         <v>44998</v>
       </c>
       <c r="B971" t="n">
-        <v>7.71626091003418</v>
+        <v>7.716259956359863</v>
       </c>
       <c r="C971" t="n">
-        <v>7.839299544365341</v>
+        <v>7.839298575484334</v>
       </c>
       <c r="D971" t="n">
-        <v>7.478973132984524</v>
+        <v>7.478972208637269</v>
       </c>
       <c r="E971" t="n">
-        <v>7.71626091003418</v>
+        <v>7.716259956359863</v>
       </c>
       <c r="F971" t="n">
         <v>789800</v>
@@ -19852,16 +19852,16 @@
         <v>44999</v>
       </c>
       <c r="B972" t="n">
-        <v>7.584433078765869</v>
+        <v>7.584434032440186</v>
       </c>
       <c r="C972" t="n">
-        <v>7.900817003243273</v>
+        <v>7.900817996700026</v>
       </c>
       <c r="D972" t="n">
-        <v>7.417452045581592</v>
+        <v>7.417452978259544</v>
       </c>
       <c r="E972" t="n">
-        <v>7.76020192569776</v>
+        <v>7.760202901473431</v>
       </c>
       <c r="F972" t="n">
         <v>959500</v>
@@ -19872,16 +19872,16 @@
         <v>45000</v>
       </c>
       <c r="B973" t="n">
-        <v>7.63716459274292</v>
+        <v>7.637163639068604</v>
       </c>
       <c r="C973" t="n">
-        <v>7.865664551086281</v>
+        <v>7.86566356887853</v>
       </c>
       <c r="D973" t="n">
-        <v>7.153800392266266</v>
+        <v>7.153799498951003</v>
       </c>
       <c r="E973" t="n">
-        <v>7.50533814500058</v>
+        <v>7.505337207787805</v>
       </c>
       <c r="F973" t="n">
         <v>1097200</v>
@@ -19892,16 +19892,16 @@
         <v>45001</v>
       </c>
       <c r="B974" t="n">
-        <v>8.067798614501953</v>
+        <v>8.06779956817627</v>
       </c>
       <c r="C974" t="n">
-        <v>8.190836397104201</v>
+        <v>8.190837365322505</v>
       </c>
       <c r="D974" t="n">
-        <v>7.575644969696861</v>
+        <v>7.575645865194924</v>
       </c>
       <c r="E974" t="n">
-        <v>7.584433622206174</v>
+        <v>7.584434518743122</v>
       </c>
       <c r="F974" t="n">
         <v>1773100</v>
@@ -19912,16 +19912,16 @@
         <v>45002</v>
       </c>
       <c r="B975" t="n">
-        <v>7.71626091003418</v>
+        <v>7.716259956359863</v>
       </c>
       <c r="C975" t="n">
-        <v>8.050222199105507</v>
+        <v>8.05022120415598</v>
       </c>
       <c r="D975" t="n">
-        <v>7.575645806874069</v>
+        <v>7.575644870578767</v>
       </c>
       <c r="E975" t="n">
-        <v>8.050222199105507</v>
+        <v>8.05022120415598</v>
       </c>
       <c r="F975" t="n">
         <v>1382600</v>
@@ -19932,16 +19932,16 @@
         <v>45005</v>
       </c>
       <c r="B976" t="n">
-        <v>7.37351131439209</v>
+        <v>7.373510837554932</v>
       </c>
       <c r="C976" t="n">
-        <v>7.760202822321058</v>
+        <v>7.76020232047697</v>
       </c>
       <c r="D976" t="n">
-        <v>7.241684035362706</v>
+        <v>7.241683567050679</v>
       </c>
       <c r="E976" t="n">
-        <v>7.689895275424882</v>
+        <v>7.689894778127509</v>
       </c>
       <c r="F976" t="n">
         <v>1329600</v>
@@ -19972,16 +19972,16 @@
         <v>45007</v>
       </c>
       <c r="B978" t="n">
-        <v>7.285626411437988</v>
+        <v>7.285626888275146</v>
       </c>
       <c r="C978" t="n">
-        <v>7.54049147671118</v>
+        <v>7.540491970229008</v>
       </c>
       <c r="D978" t="n">
-        <v>7.171376438986963</v>
+        <v>7.171376908346571</v>
       </c>
       <c r="E978" t="n">
-        <v>7.34714530501467</v>
+        <v>7.347145785878179</v>
       </c>
       <c r="F978" t="n">
         <v>921100</v>
@@ -20012,16 +20012,16 @@
         <v>45009</v>
       </c>
       <c r="B980" t="n">
-        <v>7.013185024261475</v>
+        <v>7.013184547424316</v>
       </c>
       <c r="C980" t="n">
-        <v>7.109858117893817</v>
+        <v>7.109857634483707</v>
       </c>
       <c r="D980" t="n">
-        <v>6.767108172942622</v>
+        <v>6.767107712836605</v>
       </c>
       <c r="E980" t="n">
-        <v>6.890146808135082</v>
+        <v>6.890146339663479</v>
       </c>
       <c r="F980" t="n">
         <v>2102500</v>
@@ -20032,16 +20032,16 @@
         <v>45012</v>
       </c>
       <c r="B981" t="n">
-        <v>7.188953876495361</v>
+        <v>7.18895435333252</v>
       </c>
       <c r="C981" t="n">
-        <v>7.268050077191407</v>
+        <v>7.268050559274948</v>
       </c>
       <c r="D981" t="n">
-        <v>6.995607701253039</v>
+        <v>6.995608165265711</v>
       </c>
       <c r="E981" t="n">
-        <v>7.039550128098851</v>
+        <v>7.039550595026186</v>
       </c>
       <c r="F981" t="n">
         <v>840700</v>
@@ -20052,16 +20052,16 @@
         <v>45013</v>
       </c>
       <c r="B982" t="n">
-        <v>7.37351131439209</v>
+        <v>7.373510837554932</v>
       </c>
       <c r="C982" t="n">
-        <v>7.54049152873749</v>
+        <v>7.540491041101899</v>
       </c>
       <c r="D982" t="n">
-        <v>6.98681896833105</v>
+        <v>6.986818516500876</v>
       </c>
       <c r="E982" t="n">
-        <v>7.17137648846653</v>
+        <v>7.171376024701217</v>
       </c>
       <c r="F982" t="n">
         <v>1275200</v>
@@ -20212,16 +20212,16 @@
         <v>45026</v>
       </c>
       <c r="B990" t="n">
-        <v>6.459511756896973</v>
+        <v>6.459512233734131</v>
       </c>
       <c r="C990" t="n">
-        <v>6.846203672479111</v>
+        <v>6.846204177861626</v>
       </c>
       <c r="D990" t="n">
-        <v>6.450723523327346</v>
+        <v>6.450723999515762</v>
       </c>
       <c r="E990" t="n">
-        <v>6.731953702611793</v>
+        <v>6.731954199560445</v>
       </c>
       <c r="F990" t="n">
         <v>934600</v>
@@ -20232,16 +20232,16 @@
         <v>45027</v>
       </c>
       <c r="B991" t="n">
-        <v>7.224107265472412</v>
+        <v>7.22410774230957</v>
       </c>
       <c r="C991" t="n">
-        <v>7.347145048327199</v>
+        <v>7.347145533285635</v>
       </c>
       <c r="D991" t="n">
-        <v>6.485877215815548</v>
+        <v>6.485877643924814</v>
       </c>
       <c r="E991" t="n">
-        <v>6.494665449276882</v>
+        <v>6.494665877966228</v>
       </c>
       <c r="F991" t="n">
         <v>3985600</v>
@@ -20272,16 +20272,16 @@
         <v>45029</v>
       </c>
       <c r="B993" t="n">
-        <v>7.347145080566406</v>
+        <v>7.347145557403564</v>
       </c>
       <c r="C993" t="n">
-        <v>7.593222323619837</v>
+        <v>7.593222816427657</v>
       </c>
       <c r="D993" t="n">
-        <v>7.206529992039898</v>
+        <v>7.206530459750994</v>
       </c>
       <c r="E993" t="n">
-        <v>7.478972354659038</v>
+        <v>7.47897284005192</v>
       </c>
       <c r="F993" t="n">
         <v>1224500</v>
@@ -20312,16 +20312,16 @@
         <v>45033</v>
       </c>
       <c r="B995" t="n">
-        <v>6.934088230133057</v>
+        <v>6.934088706970215</v>
       </c>
       <c r="C995" t="n">
-        <v>7.048338621152793</v>
+        <v>7.048339105846619</v>
       </c>
       <c r="D995" t="n">
-        <v>6.793473137922977</v>
+        <v>6.793473605090441</v>
       </c>
       <c r="E995" t="n">
-        <v>7.048338621152793</v>
+        <v>7.048339105846619</v>
       </c>
       <c r="F995" t="n">
         <v>961500</v>
@@ -20352,16 +20352,16 @@
         <v>45035</v>
       </c>
       <c r="B997" t="n">
-        <v>6.459511756896973</v>
+        <v>6.459512233734131</v>
       </c>
       <c r="C997" t="n">
-        <v>6.714376816406515</v>
+        <v>6.714377312057653</v>
       </c>
       <c r="D997" t="n">
-        <v>6.424357984486417</v>
+        <v>6.424358458728545</v>
       </c>
       <c r="E997" t="n">
-        <v>6.635281038015775</v>
+        <v>6.635281527828113</v>
       </c>
       <c r="F997" t="n">
         <v>2440300</v>
@@ -20372,16 +20372,16 @@
         <v>45036</v>
       </c>
       <c r="B998" t="n">
-        <v>6.485877513885498</v>
+        <v>6.48587703704834</v>
       </c>
       <c r="C998" t="n">
-        <v>6.600127487595527</v>
+        <v>6.600127002358792</v>
       </c>
       <c r="D998" t="n">
-        <v>6.292531340058365</v>
+        <v>6.292530877435881</v>
       </c>
       <c r="E998" t="n">
-        <v>6.424358200564858</v>
+        <v>6.424357728250556</v>
       </c>
       <c r="F998" t="n">
         <v>2265600</v>
@@ -20432,16 +20432,16 @@
         <v>45042</v>
       </c>
       <c r="B1001" t="n">
-        <v>6.345261573791504</v>
+        <v>6.345262050628662</v>
       </c>
       <c r="C1001" t="n">
-        <v>6.600127043802088</v>
+        <v>6.600127539792014</v>
       </c>
       <c r="D1001" t="n">
-        <v>6.099185175187229</v>
+        <v>6.099185633532104</v>
       </c>
       <c r="E1001" t="n">
-        <v>6.213435141215075</v>
+        <v>6.213435608145669</v>
       </c>
       <c r="F1001" t="n">
         <v>2004400</v>
@@ -20452,16 +20452,16 @@
         <v>45043</v>
       </c>
       <c r="B1002" t="n">
-        <v>6.389204502105713</v>
+        <v>6.389204025268555</v>
       </c>
       <c r="C1002" t="n">
-        <v>6.450723816149789</v>
+        <v>6.45072333472134</v>
       </c>
       <c r="D1002" t="n">
-        <v>6.187070092036369</v>
+        <v>6.187069630284845</v>
       </c>
       <c r="E1002" t="n">
-        <v>6.29253141405532</v>
+        <v>6.292530944433039</v>
       </c>
       <c r="F1002" t="n">
         <v>1042500</v>
